--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -480,11 +480,15 @@
       <c r="D2" t="n">
         <v>-19295293</v>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>-19295293</v>
+      </c>
       <c r="F2" t="n">
         <v>179987736</v>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>179987736</v>
+      </c>
       <c r="H2" t="n">
         <v>-152171550</v>
       </c>
@@ -511,11 +515,15 @@
       <c r="D3" t="n">
         <v>794806</v>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>794806</v>
+      </c>
       <c r="F3" t="n">
         <v>-8457319</v>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>-8457319</v>
+      </c>
       <c r="H3" t="n">
         <v>23455312</v>
       </c>
@@ -542,11 +550,15 @@
       <c r="D4" t="n">
         <v>-21969977</v>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>-21969977</v>
+      </c>
       <c r="F4" t="n">
         <v>23897674</v>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>23897674</v>
+      </c>
       <c r="H4" t="n">
         <v>24937333</v>
       </c>
@@ -573,11 +585,15 @@
       <c r="D5" t="n">
         <v>2060861</v>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>2060861</v>
+      </c>
       <c r="F5" t="n">
         <v>-55349731</v>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>-55349731</v>
+      </c>
       <c r="H5" t="n">
         <v>-74920379</v>
       </c>
@@ -604,11 +620,15 @@
       <c r="D6" t="n">
         <v>-33777436</v>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>-33777436</v>
+      </c>
       <c r="F6" t="n">
         <v>-44624115</v>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>-44624115</v>
+      </c>
       <c r="H6" t="n">
         <v>134240155</v>
       </c>
@@ -635,11 +655,15 @@
       <c r="D7" t="n">
         <v>-56911898</v>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>-56911898</v>
+      </c>
       <c r="F7" t="n">
         <v>-237629422</v>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>-237629422</v>
+      </c>
       <c r="H7" t="n">
         <v>14027832</v>
       </c>
@@ -666,11 +690,15 @@
       <c r="D8" t="n">
         <v>-16676813</v>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>-16676813</v>
+      </c>
       <c r="F8" t="n">
         <v>-13474533</v>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>-13474533</v>
+      </c>
       <c r="H8" t="n">
         <v>6415609</v>
       </c>
@@ -697,11 +725,15 @@
       <c r="D9" t="n">
         <v>-12799990</v>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>-12799990</v>
+      </c>
       <c r="F9" t="n">
         <v>-11948556</v>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>-11948556</v>
+      </c>
       <c r="H9" t="n">
         <v>143202260</v>
       </c>
@@ -728,11 +760,15 @@
       <c r="D10" t="n">
         <v>-76458409</v>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>-76458409</v>
+      </c>
       <c r="F10" t="n">
         <v>-221747342</v>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>-221747342</v>
+      </c>
       <c r="H10" t="n">
         <v>523101554</v>
       </c>
@@ -759,11 +795,15 @@
       <c r="D11" t="n">
         <v>-100573740</v>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>-100573740</v>
+      </c>
       <c r="F11" t="n">
         <v>-250196137</v>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>-250196137</v>
+      </c>
       <c r="H11" t="n">
         <v>75319114</v>
       </c>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,26 +471,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 10,412 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-19295293</v>
+        <v>-40076614</v>
       </c>
       <c r="E2" t="n">
         <v>-19295293</v>
       </c>
       <c r="F2" t="n">
-        <v>179987736</v>
+        <v>190400051</v>
       </c>
       <c r="G2" t="n">
         <v>179987736</v>
       </c>
       <c r="H2" t="n">
-        <v>-152171550</v>
+        <v>-159305098</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -513,19 +513,19 @@
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>794806</v>
+        <v>330900</v>
       </c>
       <c r="E3" t="n">
         <v>794806</v>
       </c>
       <c r="F3" t="n">
-        <v>-8457319</v>
+        <v>-7773557</v>
       </c>
       <c r="G3" t="n">
         <v>-8457319</v>
       </c>
       <c r="H3" t="n">
-        <v>23455312</v>
+        <v>26716125</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -541,26 +541,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -13,777 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>-21969977</v>
+        <v>-36628981</v>
       </c>
       <c r="E4" t="n">
         <v>-21969977</v>
       </c>
       <c r="F4" t="n">
-        <v>23897674</v>
+        <v>10120854</v>
       </c>
       <c r="G4" t="n">
         <v>23897674</v>
       </c>
       <c r="H4" t="n">
-        <v>24937333</v>
+        <v>4526865</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -571,147 +571,147 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 18,117 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>2060861</v>
+        <v>-17322902</v>
       </c>
       <c r="E5" t="n">
-        <v>2060861</v>
+        <v>-33777436</v>
       </c>
       <c r="F5" t="n">
-        <v>-55349731</v>
+        <v>-26507588</v>
       </c>
       <c r="G5" t="n">
-        <v>-55349731</v>
+        <v>-44624115</v>
       </c>
       <c r="H5" t="n">
-        <v>-74920379</v>
+        <v>142208820</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 50,942 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>-33777436</v>
+        <v>-42264080</v>
       </c>
       <c r="E6" t="n">
-        <v>-33777436</v>
+        <v>-100573740</v>
       </c>
       <c r="F6" t="n">
-        <v>-44624115</v>
+        <v>-199253908</v>
       </c>
       <c r="G6" t="n">
-        <v>-44624115</v>
+        <v>-250196137</v>
       </c>
       <c r="H6" t="n">
-        <v>134240155</v>
+        <v>107516694</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-56911898</v>
+        <v>-2594232</v>
       </c>
       <c r="E7" t="n">
-        <v>-56911898</v>
+        <v>-1185638</v>
       </c>
       <c r="F7" t="n">
-        <v>-237629422</v>
+        <v>1933566</v>
       </c>
       <c r="G7" t="n">
-        <v>-237629422</v>
+        <v>3593460</v>
       </c>
       <c r="H7" t="n">
-        <v>14027832</v>
+        <v>-10036304</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>卜蜂</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-16676813</v>
+        <v>1187789</v>
       </c>
       <c r="E8" t="n">
-        <v>-16676813</v>
+        <v>2060861</v>
       </c>
       <c r="F8" t="n">
-        <v>-13474533</v>
+        <v>-52374080</v>
       </c>
       <c r="G8" t="n">
-        <v>-13474533</v>
+        <v>-55349731</v>
       </c>
       <c r="H8" t="n">
-        <v>6415609</v>
+        <v>-74862642</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,30 +723,30 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-12799990</v>
+        <v>-12828305</v>
       </c>
       <c r="E9" t="n">
-        <v>-12799990</v>
+        <v>-16676813</v>
       </c>
       <c r="F9" t="n">
-        <v>-11948556</v>
+        <v>-17393261</v>
       </c>
       <c r="G9" t="n">
-        <v>-11948556</v>
+        <v>-13474533</v>
       </c>
       <c r="H9" t="n">
-        <v>143202260</v>
+        <v>3961347</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,30 +758,30 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-76458409</v>
+        <v>-19001106</v>
       </c>
       <c r="E10" t="n">
-        <v>-76458409</v>
+        <v>-12799990</v>
       </c>
       <c r="F10" t="n">
-        <v>-221747342</v>
+        <v>-12948152</v>
       </c>
       <c r="G10" t="n">
-        <v>-221747342</v>
+        <v>-11948556</v>
       </c>
       <c r="H10" t="n">
-        <v>523101554</v>
+        <v>124967642</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,23 +793,198 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-100573740</v>
+        <v>-99074232</v>
       </c>
       <c r="E11" t="n">
-        <v>-100573740</v>
+        <v>-76458409</v>
       </c>
       <c r="F11" t="n">
-        <v>-250196137</v>
+        <v>-218817336</v>
       </c>
       <c r="G11" t="n">
-        <v>-250196137</v>
+        <v>-221747342</v>
       </c>
       <c r="H11" t="n">
-        <v>75319114</v>
+        <v>500478625</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>鴻海</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>🔴 5d 翻紅</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-800201</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2221404</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-928939</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2237966</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-2082946</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>亞翔</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>76291</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-913675</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-6097204</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-5596978</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-2639153</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>建準</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 31,353 千)</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-1319042</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-5549289</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-89742469</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-121095499</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-259716164</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>廣達</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 34,732 千)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-51598125</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-56911898</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-202897294</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-237629422</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-5345392</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2412</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -9,343 千)</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-46281468</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-35824111</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-54977869</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-45634511</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-116120404</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>中華電</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,210 +466,210 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 10,412 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -17,487 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-40076614</v>
+        <v>-10587111</v>
       </c>
       <c r="E2" t="n">
-        <v>-19295293</v>
+        <v>14233120</v>
       </c>
       <c r="F2" t="n">
-        <v>190400051</v>
+        <v>41673068</v>
       </c>
       <c r="G2" t="n">
-        <v>179987736</v>
+        <v>59160199</v>
       </c>
       <c r="H2" t="n">
-        <v>-159305098</v>
+        <v>2312903</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 22,641 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>330900</v>
+        <v>1126790</v>
       </c>
       <c r="E3" t="n">
-        <v>794806</v>
+        <v>-1319042</v>
       </c>
       <c r="F3" t="n">
-        <v>-7773557</v>
+        <v>-67101183</v>
       </c>
       <c r="G3" t="n">
-        <v>-8457319</v>
+        <v>-89742469</v>
       </c>
       <c r="H3" t="n">
-        <v>26716125</v>
+        <v>-258486321</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -13,777 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>-36628981</v>
+        <v>-52104977</v>
       </c>
       <c r="E4" t="n">
-        <v>-21969977</v>
+        <v>-40076614</v>
       </c>
       <c r="F4" t="n">
-        <v>10120854</v>
+        <v>197618224</v>
       </c>
       <c r="G4" t="n">
-        <v>23897674</v>
+        <v>190400051</v>
       </c>
       <c r="H4" t="n">
-        <v>4526865</v>
+        <v>-164210652</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 18,117 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>-17322902</v>
+        <v>782768</v>
       </c>
       <c r="E5" t="n">
-        <v>-33777436</v>
+        <v>-1607048</v>
       </c>
       <c r="F5" t="n">
-        <v>-26507588</v>
+        <v>-13492329</v>
       </c>
       <c r="G5" t="n">
-        <v>-44624115</v>
+        <v>-16184928</v>
       </c>
       <c r="H5" t="n">
-        <v>142208820</v>
+        <v>-66642949</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 50,942 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -10,709 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>-42264080</v>
+        <v>-15093238</v>
       </c>
       <c r="E6" t="n">
-        <v>-100573740</v>
+        <v>-19001106</v>
       </c>
       <c r="F6" t="n">
-        <v>-199253908</v>
+        <v>-23657473</v>
       </c>
       <c r="G6" t="n">
-        <v>-250196137</v>
+        <v>-12948152</v>
       </c>
       <c r="H6" t="n">
-        <v>107516694</v>
+        <v>123936234</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 23,405 千)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>-2594232</v>
+        <v>-34134732</v>
       </c>
       <c r="E7" t="n">
-        <v>-1185638</v>
+        <v>-42264080</v>
       </c>
       <c r="F7" t="n">
-        <v>1933566</v>
+        <v>-175849216</v>
       </c>
       <c r="G7" t="n">
-        <v>3593460</v>
+        <v>-199253908</v>
       </c>
       <c r="H7" t="n">
-        <v>-10036304</v>
+        <v>97200352</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
+        <v>8223413</v>
+      </c>
+      <c r="E8" t="n">
         <v>1187789</v>
       </c>
-      <c r="E8" t="n">
-        <v>2060861</v>
-      </c>
       <c r="F8" t="n">
+        <v>-50737807</v>
+      </c>
+      <c r="G8" t="n">
         <v>-52374080</v>
       </c>
-      <c r="G8" t="n">
-        <v>-55349731</v>
-      </c>
       <c r="H8" t="n">
-        <v>-74862642</v>
+        <v>-75044868</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,30 +723,30 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-12828305</v>
+        <v>-24206159</v>
       </c>
       <c r="E9" t="n">
-        <v>-16676813</v>
+        <v>-17322902</v>
       </c>
       <c r="F9" t="n">
-        <v>-17393261</v>
+        <v>-22579037</v>
       </c>
       <c r="G9" t="n">
-        <v>-13474533</v>
+        <v>-26507588</v>
       </c>
       <c r="H9" t="n">
-        <v>3961347</v>
+        <v>134806062</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,30 +758,30 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-19001106</v>
+        <v>-9774310</v>
       </c>
       <c r="E10" t="n">
-        <v>-12799990</v>
+        <v>-12828305</v>
       </c>
       <c r="F10" t="n">
-        <v>-12948152</v>
+        <v>-16113473</v>
       </c>
       <c r="G10" t="n">
-        <v>-11948556</v>
+        <v>-17393261</v>
       </c>
       <c r="H10" t="n">
-        <v>124967642</v>
+        <v>4141347</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,198 +793,233 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-99074232</v>
+        <v>-886416</v>
       </c>
       <c r="E11" t="n">
-        <v>-76458409</v>
+        <v>330900</v>
       </c>
       <c r="F11" t="n">
-        <v>-218817336</v>
+        <v>-8668666</v>
       </c>
       <c r="G11" t="n">
-        <v>-221747342</v>
+        <v>-7773557</v>
       </c>
       <c r="H11" t="n">
-        <v>500478625</v>
+        <v>26339490</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-800201</v>
+        <v>-68160196</v>
       </c>
       <c r="E12" t="n">
-        <v>2221404</v>
+        <v>-99074232</v>
       </c>
       <c r="F12" t="n">
-        <v>-928939</v>
+        <v>-214912448</v>
       </c>
       <c r="G12" t="n">
-        <v>2237966</v>
+        <v>-218817336</v>
       </c>
       <c r="H12" t="n">
-        <v>-2082946</v>
+        <v>501064900</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>76291</v>
+        <v>177128</v>
       </c>
       <c r="E13" t="n">
-        <v>-913675</v>
+        <v>-706287</v>
       </c>
       <c r="F13" t="n">
-        <v>-6097204</v>
+        <v>-4446644</v>
       </c>
       <c r="G13" t="n">
-        <v>-5596978</v>
+        <v>-3879336</v>
       </c>
       <c r="H13" t="n">
-        <v>-2639153</v>
+        <v>-19141301</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 31,353 千)</t>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-1319042</v>
+        <v>1694120</v>
       </c>
       <c r="E14" t="n">
-        <v>-5549289</v>
+        <v>76291</v>
       </c>
       <c r="F14" t="n">
-        <v>-89742469</v>
+        <v>-5367585</v>
       </c>
       <c r="G14" t="n">
-        <v>-121095499</v>
+        <v>-6097204</v>
       </c>
       <c r="H14" t="n">
-        <v>-259716164</v>
+        <v>-2400512</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 34,732 千)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>-51598125</v>
+        <v>-214109</v>
       </c>
       <c r="E15" t="n">
-        <v>-56911898</v>
+        <v>1893080</v>
       </c>
       <c r="F15" t="n">
-        <v>-202897294</v>
+        <v>1777038</v>
       </c>
       <c r="G15" t="n">
-        <v>-237629422</v>
+        <v>3309115</v>
       </c>
       <c r="H15" t="n">
-        <v>-5345392</v>
+        <v>-4148900</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>華星光</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -9,343 千)</t>
+          <t>📉 20d 巨變(減碼 -11,402 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-46281468</v>
+        <v>-43778879</v>
       </c>
       <c r="E16" t="n">
-        <v>-35824111</v>
+        <v>-36628981</v>
       </c>
       <c r="F16" t="n">
-        <v>-54977869</v>
+        <v>-1280701</v>
       </c>
       <c r="G16" t="n">
-        <v>-45634511</v>
+        <v>10120854</v>
       </c>
       <c r="H16" t="n">
-        <v>-116120404</v>
+        <v>-5657825</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>台灣大</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -10,344 千)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-35494025</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-51598125</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-213240835</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-202897294</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-11609146</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>緯創</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,77 +466,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -17,487 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>-10587111</v>
+        <v>492096</v>
       </c>
       <c r="E2" t="n">
-        <v>14233120</v>
+        <v>-2544773</v>
       </c>
       <c r="F2" t="n">
-        <v>41673068</v>
+        <v>-16682304</v>
       </c>
       <c r="G2" t="n">
-        <v>59160199</v>
+        <v>-17024626</v>
       </c>
       <c r="H2" t="n">
-        <v>2312903</v>
+        <v>-43196502</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 22,641 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>1126790</v>
+        <v>-48937896</v>
       </c>
       <c r="E3" t="n">
-        <v>-1319042</v>
+        <v>-52104977</v>
       </c>
       <c r="F3" t="n">
-        <v>-67101183</v>
+        <v>197174163</v>
       </c>
       <c r="G3" t="n">
-        <v>-89742469</v>
+        <v>197618224</v>
       </c>
       <c r="H3" t="n">
-        <v>-258486321</v>
+        <v>-155574594</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,128 +548,128 @@
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>-52104977</v>
+        <v>-13473886</v>
       </c>
       <c r="E4" t="n">
-        <v>-40076614</v>
+        <v>-10587111</v>
       </c>
       <c r="F4" t="n">
-        <v>197618224</v>
+        <v>42426973</v>
       </c>
       <c r="G4" t="n">
-        <v>190400051</v>
+        <v>41673068</v>
       </c>
       <c r="H4" t="n">
-        <v>-164210652</v>
+        <v>-3439929</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -56,073 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>782768</v>
+        <v>-39178294</v>
       </c>
       <c r="E5" t="n">
-        <v>-1607048</v>
+        <v>-34134732</v>
       </c>
       <c r="F5" t="n">
-        <v>-13492329</v>
+        <v>-231922106</v>
       </c>
       <c r="G5" t="n">
-        <v>-16184928</v>
+        <v>-175849216</v>
       </c>
       <c r="H5" t="n">
-        <v>-66642949</v>
+        <v>7701146</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -10,709 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>-15093238</v>
+        <v>2784253</v>
       </c>
       <c r="E6" t="n">
-        <v>-19001106</v>
+        <v>782768</v>
       </c>
       <c r="F6" t="n">
-        <v>-23657473</v>
+        <v>-11110546</v>
       </c>
       <c r="G6" t="n">
-        <v>-12948152</v>
+        <v>-13492329</v>
       </c>
       <c r="H6" t="n">
-        <v>123936234</v>
+        <v>-65881134</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 23,405 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-34134732</v>
+        <v>-16887087</v>
       </c>
       <c r="E7" t="n">
-        <v>-42264080</v>
+        <v>-24206159</v>
       </c>
       <c r="F7" t="n">
-        <v>-175849216</v>
+        <v>-19831169</v>
       </c>
       <c r="G7" t="n">
-        <v>-199253908</v>
+        <v>-22579037</v>
       </c>
       <c r="H7" t="n">
-        <v>97200352</v>
+        <v>123706032</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
+        <v>6331225</v>
+      </c>
+      <c r="E8" t="n">
         <v>8223413</v>
       </c>
-      <c r="E8" t="n">
-        <v>1187789</v>
-      </c>
       <c r="F8" t="n">
+        <v>-42873722</v>
+      </c>
+      <c r="G8" t="n">
         <v>-50737807</v>
       </c>
-      <c r="G8" t="n">
-        <v>-52374080</v>
-      </c>
       <c r="H8" t="n">
-        <v>-75044868</v>
+        <v>-83764514</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,30 +723,30 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-24206159</v>
+        <v>-7327434</v>
       </c>
       <c r="E9" t="n">
-        <v>-17322902</v>
+        <v>-9774310</v>
       </c>
       <c r="F9" t="n">
-        <v>-22579037</v>
+        <v>-13862410</v>
       </c>
       <c r="G9" t="n">
-        <v>-26507588</v>
+        <v>-16113473</v>
       </c>
       <c r="H9" t="n">
-        <v>134806062</v>
+        <v>3920347</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,30 +758,30 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-9774310</v>
+        <v>-1389207</v>
       </c>
       <c r="E10" t="n">
-        <v>-12828305</v>
+        <v>-886416</v>
       </c>
       <c r="F10" t="n">
-        <v>-16113473</v>
+        <v>-9702782</v>
       </c>
       <c r="G10" t="n">
-        <v>-17393261</v>
+        <v>-8668666</v>
       </c>
       <c r="H10" t="n">
-        <v>4141347</v>
+        <v>29035783</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,23 +793,23 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-886416</v>
+        <v>-20164935</v>
       </c>
       <c r="E11" t="n">
-        <v>330900</v>
+        <v>-15093238</v>
       </c>
       <c r="F11" t="n">
-        <v>-8668666</v>
+        <v>-27141151</v>
       </c>
       <c r="G11" t="n">
-        <v>-7773557</v>
+        <v>-23657473</v>
       </c>
       <c r="H11" t="n">
-        <v>26339490</v>
+        <v>94718997</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
@@ -828,19 +828,19 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
+        <v>-56285501</v>
+      </c>
+      <c r="E12" t="n">
         <v>-68160196</v>
       </c>
-      <c r="E12" t="n">
-        <v>-99074232</v>
-      </c>
       <c r="F12" t="n">
+        <v>-218199656</v>
+      </c>
+      <c r="G12" t="n">
         <v>-214912448</v>
       </c>
-      <c r="G12" t="n">
-        <v>-218817336</v>
-      </c>
       <c r="H12" t="n">
-        <v>501064900</v>
+        <v>467355952</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -851,175 +851,385 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🔴 5d 翻紅 / 📈 20d 巨變(加碼 11,125 千)</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>177128</v>
+        <v>-3317835</v>
       </c>
       <c r="E13" t="n">
-        <v>-706287</v>
+        <v>1126790</v>
       </c>
       <c r="F13" t="n">
-        <v>-4446644</v>
+        <v>-55975763</v>
       </c>
       <c r="G13" t="n">
-        <v>-3879336</v>
+        <v>-67101183</v>
       </c>
       <c r="H13" t="n">
-        <v>-19141301</v>
+        <v>-277016444</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>1694120</v>
+        <v>70693</v>
       </c>
       <c r="E14" t="n">
-        <v>76291</v>
+        <v>177128</v>
       </c>
       <c r="F14" t="n">
-        <v>-5367585</v>
+        <v>-4588539</v>
       </c>
       <c r="G14" t="n">
-        <v>-6097204</v>
+        <v>-4446644</v>
       </c>
       <c r="H14" t="n">
-        <v>-2400512</v>
+        <v>-18934710</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>-214109</v>
+        <v>-5432097</v>
       </c>
       <c r="E15" t="n">
-        <v>1893080</v>
+        <v>-3720877</v>
       </c>
       <c r="F15" t="n">
-        <v>1777038</v>
+        <v>385624</v>
       </c>
       <c r="G15" t="n">
-        <v>3309115</v>
+        <v>-698890</v>
       </c>
       <c r="H15" t="n">
-        <v>-4148900</v>
+        <v>-4451767</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>亞翔</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -11,402 千)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>-43778879</v>
+        <v>-149213</v>
       </c>
       <c r="E16" t="n">
-        <v>-36628981</v>
+        <v>20061</v>
       </c>
       <c r="F16" t="n">
-        <v>-1280701</v>
+        <v>5689071</v>
       </c>
       <c r="G16" t="n">
-        <v>10120854</v>
+        <v>5745220</v>
       </c>
       <c r="H16" t="n">
-        <v>-5657825</v>
+        <v>9880002</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>致茂</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1725471</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1694120</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-5544849</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-5367585</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-2077695</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>建準</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>🔴 5d 翻紅</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-3507738</v>
+      </c>
+      <c r="E18" t="n">
+        <v>254005</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-2501552</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-524714</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-3560361</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1514</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>🟢 5d 翻綠</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3560636</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-1078303</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-1231035</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-5613622</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-5449146</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>亞力</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>🔴 5d 翻紅</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-1571108</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1050787</v>
+      </c>
+      <c r="F20" t="n">
+        <v>421817</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1755468</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5179047</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 20,224 千)</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-19057291</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-20728692</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-94797468</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-115021028</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-279295682</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>3231</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -10,344 千)</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -11,788 千)</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
         <v>1</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D22" t="n">
+        <v>-42300050</v>
+      </c>
+      <c r="E22" t="n">
         <v>-35494025</v>
       </c>
-      <c r="E17" t="n">
-        <v>-51598125</v>
-      </c>
-      <c r="F17" t="n">
+      <c r="F22" t="n">
+        <v>-225029096</v>
+      </c>
+      <c r="G22" t="n">
         <v>-213240835</v>
       </c>
-      <c r="G17" t="n">
-        <v>-202897294</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-11609146</v>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="H22" t="n">
+        <v>-84254403</v>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>緯創</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>4904</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -9,549 千)</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-39329925</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-39125116</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-142963374</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-133414697</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-172722318</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>遠傳</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,42 +466,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 9,826 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>492096</v>
+        <v>-23887216</v>
       </c>
       <c r="E2" t="n">
-        <v>-2544773</v>
+        <v>-48937896</v>
       </c>
       <c r="F2" t="n">
-        <v>-16682304</v>
+        <v>207000535</v>
       </c>
       <c r="G2" t="n">
-        <v>-17024626</v>
+        <v>197174163</v>
       </c>
       <c r="H2" t="n">
-        <v>-43196502</v>
+        <v>-132579480</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -513,205 +513,205 @@
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>-48937896</v>
+        <v>-22577470</v>
       </c>
       <c r="E3" t="n">
-        <v>-52104977</v>
+        <v>-13473886</v>
       </c>
       <c r="F3" t="n">
-        <v>197174163</v>
+        <v>44851996</v>
       </c>
       <c r="G3" t="n">
-        <v>197618224</v>
+        <v>42426973</v>
       </c>
       <c r="H3" t="n">
-        <v>-155574594</v>
+        <v>-5443072</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 12,337 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>-13473886</v>
+        <v>-1847173</v>
       </c>
       <c r="E4" t="n">
-        <v>-10587111</v>
+        <v>-16887087</v>
       </c>
       <c r="F4" t="n">
-        <v>42426973</v>
+        <v>-7493987</v>
       </c>
       <c r="G4" t="n">
-        <v>41673068</v>
+        <v>-19831169</v>
       </c>
       <c r="H4" t="n">
-        <v>-3439929</v>
+        <v>118402559</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -56,073 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 19,881 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>-39178294</v>
+        <v>18088967</v>
       </c>
       <c r="E5" t="n">
-        <v>-34134732</v>
+        <v>6331225</v>
       </c>
       <c r="F5" t="n">
-        <v>-231922106</v>
+        <v>-22992379</v>
       </c>
       <c r="G5" t="n">
-        <v>-175849216</v>
+        <v>-42873722</v>
       </c>
       <c r="H5" t="n">
-        <v>7701146</v>
+        <v>-72522904</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 54,746 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>2784253</v>
+        <v>-10606966</v>
       </c>
       <c r="E6" t="n">
-        <v>782768</v>
+        <v>-39178294</v>
       </c>
       <c r="F6" t="n">
-        <v>-11110546</v>
+        <v>-177176220</v>
       </c>
       <c r="G6" t="n">
-        <v>-13492329</v>
+        <v>-231922106</v>
       </c>
       <c r="H6" t="n">
-        <v>-65881134</v>
+        <v>17664661</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-16887087</v>
+        <v>3514589</v>
       </c>
       <c r="E7" t="n">
-        <v>-24206159</v>
+        <v>2784253</v>
       </c>
       <c r="F7" t="n">
-        <v>-19831169</v>
+        <v>-8178400</v>
       </c>
       <c r="G7" t="n">
-        <v>-22579037</v>
+        <v>-11110546</v>
       </c>
       <c r="H7" t="n">
-        <v>123706032</v>
+        <v>-65904315</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>6331225</v>
+        <v>-2746133</v>
       </c>
       <c r="E8" t="n">
-        <v>8223413</v>
+        <v>-7327434</v>
       </c>
       <c r="F8" t="n">
-        <v>-42873722</v>
+        <v>-18662602</v>
       </c>
       <c r="G8" t="n">
-        <v>-50737807</v>
+        <v>-13862410</v>
       </c>
       <c r="H8" t="n">
-        <v>-83764514</v>
+        <v>4770189</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,30 +723,30 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-7327434</v>
+        <v>-5444650</v>
       </c>
       <c r="E9" t="n">
-        <v>-9774310</v>
+        <v>-1389207</v>
       </c>
       <c r="F9" t="n">
-        <v>-13862410</v>
+        <v>-7521457</v>
       </c>
       <c r="G9" t="n">
-        <v>-16113473</v>
+        <v>-9702782</v>
       </c>
       <c r="H9" t="n">
-        <v>3920347</v>
+        <v>28371289</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,30 +758,30 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-1389207</v>
+        <v>-27474758</v>
       </c>
       <c r="E10" t="n">
-        <v>-886416</v>
+        <v>-20164935</v>
       </c>
       <c r="F10" t="n">
-        <v>-9702782</v>
+        <v>-21036834</v>
       </c>
       <c r="G10" t="n">
-        <v>-8668666</v>
+        <v>-27141151</v>
       </c>
       <c r="H10" t="n">
-        <v>29035783</v>
+        <v>77606995</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,441 +793,196 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-20164935</v>
+        <v>-73455454</v>
       </c>
       <c r="E11" t="n">
-        <v>-15093238</v>
+        <v>-56285501</v>
       </c>
       <c r="F11" t="n">
-        <v>-27141151</v>
+        <v>-225398231</v>
       </c>
       <c r="G11" t="n">
-        <v>-23657473</v>
+        <v>-218199656</v>
       </c>
       <c r="H11" t="n">
-        <v>94718997</v>
+        <v>409358376</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-56285501</v>
+        <v>-182549</v>
       </c>
       <c r="E12" t="n">
-        <v>-68160196</v>
+        <v>-149213</v>
       </c>
       <c r="F12" t="n">
-        <v>-218199656</v>
+        <v>5164022</v>
       </c>
       <c r="G12" t="n">
-        <v>-214912448</v>
+        <v>5689071</v>
       </c>
       <c r="H12" t="n">
-        <v>467355952</v>
+        <v>9418041</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>致茂</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅 / 📈 20d 巨變(加碼 11,125 千)</t>
+          <t>📈 20d 巨變(加碼 15,092 千)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3317835</v>
+        <v>-17548375</v>
       </c>
       <c r="E13" t="n">
-        <v>1126790</v>
+        <v>-19057291</v>
       </c>
       <c r="F13" t="n">
-        <v>-55975763</v>
+        <v>-79705934</v>
       </c>
       <c r="G13" t="n">
-        <v>-67101183</v>
+        <v>-94797468</v>
       </c>
       <c r="H13" t="n">
-        <v>-277016444</v>
+        <v>-277080327</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>📉 20d 巨變(減碼 -18,552 千)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>70693</v>
+        <v>-41279255</v>
       </c>
       <c r="E14" t="n">
-        <v>177128</v>
+        <v>-41421559</v>
       </c>
       <c r="F14" t="n">
-        <v>-4588539</v>
+        <v>-24758000</v>
       </c>
       <c r="G14" t="n">
-        <v>-4446644</v>
+        <v>-6205883</v>
       </c>
       <c r="H14" t="n">
-        <v>-18934710</v>
+        <v>-15884449</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>📉 20d 巨變(減碼 -13,268 千)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-5432097</v>
+        <v>-44628836</v>
       </c>
       <c r="E15" t="n">
-        <v>-3720877</v>
+        <v>-44288983</v>
       </c>
       <c r="F15" t="n">
-        <v>385624</v>
+        <v>-71516742</v>
       </c>
       <c r="G15" t="n">
-        <v>-698890</v>
+        <v>-58248860</v>
       </c>
       <c r="H15" t="n">
-        <v>-4451767</v>
+        <v>-146450529</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>📉 20d 巨變(減碼 -8,824 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-149213</v>
+        <v>-35826517</v>
       </c>
       <c r="E16" t="n">
-        <v>20061</v>
+        <v>-39329925</v>
       </c>
       <c r="F16" t="n">
-        <v>5689071</v>
+        <v>-151787473</v>
       </c>
       <c r="G16" t="n">
-        <v>5745220</v>
+        <v>-142963374</v>
       </c>
       <c r="H16" t="n">
-        <v>9880002</v>
+        <v>-177712512</v>
       </c>
       <c r="I16" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2421</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1725471</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1694120</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-5544849</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-5367585</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-2077695</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>建準</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>🔴 5d 翻紅</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" t="n">
-        <v>-3507738</v>
-      </c>
-      <c r="E18" t="n">
-        <v>254005</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-2501552</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-524714</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-3560361</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>台燿</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>1514</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>🟢 5d 翻綠</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" t="n">
-        <v>3560636</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-1078303</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-1231035</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-5613622</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-5449146</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>亞力</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>🔴 5d 翻紅</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" t="n">
-        <v>-1571108</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1050787</v>
-      </c>
-      <c r="F20" t="n">
-        <v>421817</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1755468</v>
-      </c>
-      <c r="H20" t="n">
-        <v>5179047</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>金像電</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 20,224 千)</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>-19057291</v>
-      </c>
-      <c r="E21" t="n">
-        <v>-20728692</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-94797468</v>
-      </c>
-      <c r="G21" t="n">
-        <v>-115021028</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-279295682</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -11,788 千)</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="n">
-        <v>-42300050</v>
-      </c>
-      <c r="E22" t="n">
-        <v>-35494025</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-225029096</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-213240835</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-84254403</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>4904</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -9,549 千)</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="n">
-        <v>-39329925</v>
-      </c>
-      <c r="E23" t="n">
-        <v>-39125116</v>
-      </c>
-      <c r="F23" t="n">
-        <v>-142963374</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-133414697</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-172722318</v>
-      </c>
-      <c r="I23" t="inlineStr">
         <is>
           <t>遠傳</t>
         </is>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,322 +466,322 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 9,826 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 🟢 5d 翻綠 / 📉 20d 巨變(減碼 -19,361 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>-23887216</v>
+        <v>20454693</v>
       </c>
       <c r="E2" t="n">
-        <v>-48937896</v>
+        <v>-10606966</v>
       </c>
       <c r="F2" t="n">
-        <v>207000535</v>
+        <v>-196537443</v>
       </c>
       <c r="G2" t="n">
-        <v>197174163</v>
+        <v>-177176220</v>
       </c>
       <c r="H2" t="n">
-        <v>-132579480</v>
+        <v>22235464</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 58,869 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>-22577470</v>
+        <v>61628361</v>
       </c>
       <c r="E3" t="n">
-        <v>-13473886</v>
+        <v>-23887216</v>
       </c>
       <c r="F3" t="n">
-        <v>44851996</v>
+        <v>265869773</v>
       </c>
       <c r="G3" t="n">
-        <v>42426973</v>
+        <v>207000535</v>
       </c>
       <c r="H3" t="n">
-        <v>-5443072</v>
+        <v>-33071088</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 12,337 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>-1847173</v>
+        <v>-247558</v>
       </c>
       <c r="E4" t="n">
-        <v>-16887087</v>
+        <v>2659207</v>
       </c>
       <c r="F4" t="n">
-        <v>-7493987</v>
+        <v>8005023</v>
       </c>
       <c r="G4" t="n">
-        <v>-19831169</v>
+        <v>8409142</v>
       </c>
       <c r="H4" t="n">
-        <v>118402559</v>
+        <v>11391505</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>健鼎</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 19,881 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>18088967</v>
+        <v>877367</v>
       </c>
       <c r="E5" t="n">
-        <v>6331225</v>
+        <v>-2210124</v>
       </c>
       <c r="F5" t="n">
-        <v>-22992379</v>
+        <v>-5977137</v>
       </c>
       <c r="G5" t="n">
-        <v>-42873722</v>
+        <v>-8004998</v>
       </c>
       <c r="H5" t="n">
-        <v>-72522904</v>
+        <v>-20016604</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 54,746 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>-10606966</v>
+        <v>-29116185</v>
       </c>
       <c r="E6" t="n">
-        <v>-39178294</v>
+        <v>-22577470</v>
       </c>
       <c r="F6" t="n">
-        <v>-177176220</v>
+        <v>45493085</v>
       </c>
       <c r="G6" t="n">
-        <v>-231922106</v>
+        <v>44851996</v>
       </c>
       <c r="H6" t="n">
-        <v>17664661</v>
+        <v>-8106561</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 9,683 千)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>3514589</v>
+        <v>8258290</v>
       </c>
       <c r="E7" t="n">
-        <v>2784253</v>
+        <v>18088967</v>
       </c>
       <c r="F7" t="n">
-        <v>-8178400</v>
+        <v>-13309850</v>
       </c>
       <c r="G7" t="n">
-        <v>-11110546</v>
+        <v>-22992379</v>
       </c>
       <c r="H7" t="n">
-        <v>-65904315</v>
+        <v>-67865586</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 14,960 千)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>-2746133</v>
+        <v>-51756901</v>
       </c>
       <c r="E8" t="n">
-        <v>-7327434</v>
+        <v>-73455454</v>
       </c>
       <c r="F8" t="n">
-        <v>-18662602</v>
+        <v>-210437915</v>
       </c>
       <c r="G8" t="n">
-        <v>-13862410</v>
+        <v>-225398231</v>
       </c>
       <c r="H8" t="n">
-        <v>4770189</v>
+        <v>380870460</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -16,322 千)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>-5444650</v>
+        <v>-24400677</v>
       </c>
       <c r="E9" t="n">
-        <v>-1389207</v>
+        <v>-27474758</v>
       </c>
       <c r="F9" t="n">
-        <v>-7521457</v>
+        <v>-37358945</v>
       </c>
       <c r="G9" t="n">
-        <v>-9702782</v>
+        <v>-21036834</v>
       </c>
       <c r="H9" t="n">
-        <v>28371289</v>
+        <v>72196807</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-27474758</v>
+        <v>4393326</v>
       </c>
       <c r="E10" t="n">
-        <v>-20164935</v>
+        <v>3514589</v>
       </c>
       <c r="F10" t="n">
-        <v>-21036834</v>
+        <v>-6844060</v>
       </c>
       <c r="G10" t="n">
-        <v>-27141151</v>
+        <v>-8178400</v>
       </c>
       <c r="H10" t="n">
-        <v>77606995</v>
+        <v>-65414520</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,198 +793,299 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-73455454</v>
+        <v>-2623666</v>
       </c>
       <c r="E11" t="n">
-        <v>-56285501</v>
+        <v>-1847173</v>
       </c>
       <c r="F11" t="n">
-        <v>-225398231</v>
+        <v>-9081513</v>
       </c>
       <c r="G11" t="n">
-        <v>-218199656</v>
+        <v>-7493987</v>
       </c>
       <c r="H11" t="n">
-        <v>409358376</v>
+        <v>133084065</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-182549</v>
+        <v>-313847</v>
       </c>
       <c r="E12" t="n">
-        <v>-149213</v>
+        <v>-2746133</v>
       </c>
       <c r="F12" t="n">
-        <v>5164022</v>
+        <v>-19126353</v>
       </c>
       <c r="G12" t="n">
-        <v>5689071</v>
+        <v>-18662602</v>
       </c>
       <c r="H12" t="n">
-        <v>9418041</v>
+        <v>4341500</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 15,092 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>-17548375</v>
+        <v>-1012931</v>
       </c>
       <c r="E13" t="n">
-        <v>-19057291</v>
+        <v>-5444650</v>
       </c>
       <c r="F13" t="n">
-        <v>-79705934</v>
+        <v>-6473840</v>
       </c>
       <c r="G13" t="n">
-        <v>-94797468</v>
+        <v>-7521457</v>
       </c>
       <c r="H13" t="n">
-        <v>-277080327</v>
+        <v>25818501</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -18,552 千)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-41279255</v>
+        <v>-1274972</v>
       </c>
       <c r="E14" t="n">
-        <v>-41421559</v>
+        <v>1271979</v>
       </c>
       <c r="F14" t="n">
-        <v>-24758000</v>
+        <v>5790425</v>
       </c>
       <c r="G14" t="n">
-        <v>-6205883</v>
+        <v>6962047</v>
       </c>
       <c r="H14" t="n">
-        <v>-15884449</v>
+        <v>8634226</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>原相</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -13,268 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>-44628836</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-44288983</v>
-      </c>
+        <v>-790450</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>-71516742</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-58248860</v>
-      </c>
+        <v>3593644</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>-146450529</v>
+        <v>15974693</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>藥華藥</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -8,824 千)</t>
+          <t>📈 20d 巨變(加碼 11,388 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-35826517</v>
+        <v>-29103170</v>
       </c>
       <c r="E16" t="n">
-        <v>-39329925</v>
+        <v>-17548375</v>
       </c>
       <c r="F16" t="n">
-        <v>-151787473</v>
+        <v>-68318244</v>
       </c>
       <c r="G16" t="n">
-        <v>-142963374</v>
+        <v>-79705934</v>
       </c>
       <c r="H16" t="n">
-        <v>-177712512</v>
+        <v>-288428827</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>台積電</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3045</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -14,681 千)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-40876850</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-41279255</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-39439324</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-24758000</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-22767208</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>台灣大</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 9,669 千)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-36612809</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-50014891</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-208604968</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-218274214</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-94295658</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2412</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -18,589 千)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-50794188</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-44628836</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-90105685</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-71516742</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-159489570</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>中華電</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,26 +471,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 🟢 5d 翻綠 / 📉 20d 巨變(減碼 -19,361 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -13,399 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
+        <v>-27735143</v>
+      </c>
+      <c r="E2" t="n">
         <v>20454693</v>
       </c>
-      <c r="E2" t="n">
-        <v>-10606966</v>
-      </c>
       <c r="F2" t="n">
+        <v>-209936265</v>
+      </c>
+      <c r="G2" t="n">
         <v>-196537443</v>
       </c>
-      <c r="G2" t="n">
-        <v>-177176220</v>
-      </c>
       <c r="H2" t="n">
-        <v>22235464</v>
+        <v>16139982</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -501,245 +501,245 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 58,869 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>61628361</v>
+        <v>-30100117</v>
       </c>
       <c r="E3" t="n">
-        <v>-23887216</v>
+        <v>-29116185</v>
       </c>
       <c r="F3" t="n">
-        <v>265869773</v>
+        <v>46804087</v>
       </c>
       <c r="G3" t="n">
-        <v>207000535</v>
+        <v>45493085</v>
       </c>
       <c r="H3" t="n">
-        <v>-33071088</v>
+        <v>-8845219</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>-247558</v>
+        <v>1264568</v>
       </c>
       <c r="E4" t="n">
-        <v>2659207</v>
+        <v>-1012931</v>
       </c>
       <c r="F4" t="n">
-        <v>8005023</v>
+        <v>-2288735</v>
       </c>
       <c r="G4" t="n">
-        <v>8409142</v>
+        <v>-6473840</v>
       </c>
       <c r="H4" t="n">
-        <v>11391505</v>
+        <v>23413971</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 13,367 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>877367</v>
+        <v>-5075202</v>
       </c>
       <c r="E5" t="n">
-        <v>-2210124</v>
+        <v>-40876850</v>
       </c>
       <c r="F5" t="n">
-        <v>-5977137</v>
+        <v>-26072637</v>
       </c>
       <c r="G5" t="n">
-        <v>-8004998</v>
+        <v>-39439324</v>
       </c>
       <c r="H5" t="n">
-        <v>-20016604</v>
+        <v>8330512</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 10,176 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>-29116185</v>
+        <v>7350345</v>
       </c>
       <c r="E6" t="n">
-        <v>-22577470</v>
+        <v>8258290</v>
       </c>
       <c r="F6" t="n">
-        <v>45493085</v>
+        <v>-3133976</v>
       </c>
       <c r="G6" t="n">
-        <v>44851996</v>
+        <v>-13309850</v>
       </c>
       <c r="H6" t="n">
-        <v>-8106561</v>
+        <v>-73605154</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 9,683 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 14,327 千)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>8258290</v>
+        <v>-20766181</v>
       </c>
       <c r="E7" t="n">
-        <v>18088967</v>
+        <v>-51756901</v>
       </c>
       <c r="F7" t="n">
-        <v>-13309850</v>
+        <v>-196111151</v>
       </c>
       <c r="G7" t="n">
-        <v>-22992379</v>
+        <v>-210437915</v>
       </c>
       <c r="H7" t="n">
-        <v>-67865586</v>
+        <v>390890338</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 14,960 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-51756901</v>
+        <v>-3061802</v>
       </c>
       <c r="E8" t="n">
-        <v>-73455454</v>
+        <v>-247558</v>
       </c>
       <c r="F8" t="n">
-        <v>-210437915</v>
+        <v>7937798</v>
       </c>
       <c r="G8" t="n">
-        <v>-225398231</v>
+        <v>8005023</v>
       </c>
       <c r="H8" t="n">
-        <v>380870460</v>
+        <v>11739191</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>健鼎</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -16,322 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-24400677</v>
+        <v>805811</v>
       </c>
       <c r="E9" t="n">
-        <v>-27474758</v>
+        <v>-237050</v>
       </c>
       <c r="F9" t="n">
-        <v>-37358945</v>
+        <v>-16007257</v>
       </c>
       <c r="G9" t="n">
-        <v>-21036834</v>
+        <v>-17115987</v>
       </c>
       <c r="H9" t="n">
-        <v>72196807</v>
+        <v>-39185523</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
@@ -758,19 +758,19 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
+        <v>3632738</v>
+      </c>
+      <c r="E10" t="n">
         <v>4393326</v>
       </c>
-      <c r="E10" t="n">
-        <v>3514589</v>
-      </c>
       <c r="F10" t="n">
+        <v>-5523286</v>
+      </c>
+      <c r="G10" t="n">
         <v>-6844060</v>
       </c>
-      <c r="G10" t="n">
-        <v>-8178400</v>
-      </c>
       <c r="H10" t="n">
-        <v>-65414520</v>
+        <v>-62600389</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,30 +793,30 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-2623666</v>
+        <v>-1936244</v>
       </c>
       <c r="E11" t="n">
-        <v>-1847173</v>
+        <v>-313847</v>
       </c>
       <c r="F11" t="n">
-        <v>-9081513</v>
+        <v>-22033033</v>
       </c>
       <c r="G11" t="n">
-        <v>-7493987</v>
+        <v>-19126353</v>
       </c>
       <c r="H11" t="n">
-        <v>133084065</v>
+        <v>976692</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,93 +828,93 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-313847</v>
+        <v>-17187609</v>
       </c>
       <c r="E12" t="n">
-        <v>-2746133</v>
+        <v>-24400677</v>
       </c>
       <c r="F12" t="n">
-        <v>-19126353</v>
+        <v>-40811097</v>
       </c>
       <c r="G12" t="n">
-        <v>-18662602</v>
+        <v>-37358945</v>
       </c>
       <c r="H12" t="n">
-        <v>4341500</v>
+        <v>60008254</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-1012931</v>
+        <v>801858</v>
       </c>
       <c r="E13" t="n">
-        <v>-5444650</v>
+        <v>877367</v>
       </c>
       <c r="F13" t="n">
-        <v>-6473840</v>
+        <v>-3975426</v>
       </c>
       <c r="G13" t="n">
-        <v>-7521457</v>
+        <v>-5977137</v>
       </c>
       <c r="H13" t="n">
-        <v>25818501</v>
+        <v>-14795938</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
+          <t>🟢 5d 翻綠 / 📈 20d 巨變(加碼 17,931 千)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-1274972</v>
+        <v>6597485</v>
       </c>
       <c r="E14" t="n">
-        <v>1271979</v>
+        <v>-2623666</v>
       </c>
       <c r="F14" t="n">
-        <v>5790425</v>
+        <v>8849613</v>
       </c>
       <c r="G14" t="n">
-        <v>6962047</v>
+        <v>-9081513</v>
       </c>
       <c r="H14" t="n">
-        <v>8634226</v>
+        <v>161874868</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
@@ -933,15 +933,19 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
+        <v>-2013643</v>
+      </c>
+      <c r="E15" t="n">
         <v>-790450</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
+        <v>3469071</v>
+      </c>
+      <c r="G15" t="n">
         <v>3593644</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>15974693</v>
+        <v>14828007</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -952,140 +956,175 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 11,388 千)</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>-29103170</v>
+        <v>1747876</v>
       </c>
       <c r="E16" t="n">
-        <v>-17548375</v>
+        <v>-283718</v>
       </c>
       <c r="F16" t="n">
-        <v>-68318244</v>
+        <v>-2564024</v>
       </c>
       <c r="G16" t="n">
-        <v>-79705934</v>
+        <v>-1663100</v>
       </c>
       <c r="H16" t="n">
-        <v>-288428827</v>
+        <v>-5899354</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>卜蜂</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -14,681 千)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>-40876850</v>
+        <v>-1954648</v>
       </c>
       <c r="E17" t="n">
-        <v>-41279255</v>
+        <v>-1274972</v>
       </c>
       <c r="F17" t="n">
-        <v>-39439324</v>
+        <v>5077736</v>
       </c>
       <c r="G17" t="n">
-        <v>-24758000</v>
+        <v>5790425</v>
       </c>
       <c r="H17" t="n">
-        <v>-22767208</v>
+        <v>8094666</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>原相</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 9,669 千)</t>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>-36612809</v>
+        <v>316313</v>
       </c>
       <c r="E18" t="n">
-        <v>-50014891</v>
+        <v>-33420</v>
       </c>
       <c r="F18" t="n">
-        <v>-208604968</v>
+        <v>-6116747</v>
       </c>
       <c r="G18" t="n">
-        <v>-218274214</v>
+        <v>-6121929</v>
       </c>
       <c r="H18" t="n">
-        <v>-94295658</v>
+        <v>-5319303</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>中保科</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -18,589 千)</t>
+          <t>📈 20d 巨變(加碼 28,303 千)</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-50794188</v>
+        <v>102976642</v>
       </c>
       <c r="E19" t="n">
-        <v>-44628836</v>
+        <v>61628361</v>
       </c>
       <c r="F19" t="n">
-        <v>-90105685</v>
+        <v>294172415</v>
       </c>
       <c r="G19" t="n">
-        <v>-71516742</v>
+        <v>265869773</v>
       </c>
       <c r="H19" t="n">
-        <v>-159489570</v>
+        <v>7950927</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>長榮航</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 8,368 千)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-16776571</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-13631280</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-34504936</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-42872546</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-291563796</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>廣達</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,105 +466,105 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -13,399 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>-27735143</v>
+        <v>-30100117</v>
       </c>
       <c r="E2" t="n">
-        <v>20454693</v>
+        <v>-30100117</v>
       </c>
       <c r="F2" t="n">
-        <v>-209936265</v>
+        <v>46804087</v>
       </c>
       <c r="G2" t="n">
-        <v>-196537443</v>
+        <v>46804087</v>
       </c>
       <c r="H2" t="n">
-        <v>16139982</v>
+        <v>-8845219</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>-30100117</v>
+        <v>-3061802</v>
       </c>
       <c r="E3" t="n">
-        <v>-29116185</v>
+        <v>-3061802</v>
       </c>
       <c r="F3" t="n">
-        <v>46804087</v>
+        <v>7937798</v>
       </c>
       <c r="G3" t="n">
-        <v>45493085</v>
+        <v>7937798</v>
       </c>
       <c r="H3" t="n">
-        <v>-8845219</v>
+        <v>11739191</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>健鼎</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1264568</v>
+        <v>805811</v>
       </c>
       <c r="E4" t="n">
-        <v>-1012931</v>
+        <v>805811</v>
       </c>
       <c r="F4" t="n">
-        <v>-2288735</v>
+        <v>-16007257</v>
       </c>
       <c r="G4" t="n">
-        <v>-6473840</v>
+        <v>-16007257</v>
       </c>
       <c r="H4" t="n">
-        <v>23413971</v>
+        <v>-39185523</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
@@ -576,23 +576,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 13,367 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
         <v>-5075202</v>
       </c>
       <c r="E5" t="n">
-        <v>-40876850</v>
+        <v>-5075202</v>
       </c>
       <c r="F5" t="n">
         <v>-26072637</v>
       </c>
       <c r="G5" t="n">
-        <v>-39439324</v>
+        <v>-26072637</v>
       </c>
       <c r="H5" t="n">
         <v>8330512</v>
@@ -606,182 +606,182 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 10,176 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>7350345</v>
+        <v>3632738</v>
       </c>
       <c r="E6" t="n">
-        <v>8258290</v>
+        <v>3632738</v>
       </c>
       <c r="F6" t="n">
-        <v>-3133976</v>
+        <v>-5523286</v>
       </c>
       <c r="G6" t="n">
-        <v>-13309850</v>
+        <v>-5523286</v>
       </c>
       <c r="H6" t="n">
-        <v>-73605154</v>
+        <v>-62600389</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 14,327 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-20766181</v>
+        <v>7350345</v>
       </c>
       <c r="E7" t="n">
-        <v>-51756901</v>
+        <v>7350345</v>
       </c>
       <c r="F7" t="n">
-        <v>-196111151</v>
+        <v>-3133976</v>
       </c>
       <c r="G7" t="n">
-        <v>-210437915</v>
+        <v>-3133976</v>
       </c>
       <c r="H7" t="n">
-        <v>390890338</v>
+        <v>-73605154</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-3061802</v>
+        <v>-1936244</v>
       </c>
       <c r="E8" t="n">
-        <v>-247558</v>
+        <v>-1936244</v>
       </c>
       <c r="F8" t="n">
-        <v>7937798</v>
+        <v>-22033033</v>
       </c>
       <c r="G8" t="n">
-        <v>8005023</v>
+        <v>-22033033</v>
       </c>
       <c r="H8" t="n">
-        <v>11739191</v>
+        <v>976692</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>805811</v>
+        <v>-20766181</v>
       </c>
       <c r="E9" t="n">
-        <v>-237050</v>
+        <v>-20766181</v>
       </c>
       <c r="F9" t="n">
-        <v>-16007257</v>
+        <v>-196111151</v>
       </c>
       <c r="G9" t="n">
-        <v>-17115987</v>
+        <v>-196111151</v>
       </c>
       <c r="H9" t="n">
-        <v>-39185523</v>
+        <v>390890338</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>3632738</v>
+        <v>1264568</v>
       </c>
       <c r="E10" t="n">
-        <v>4393326</v>
+        <v>1264568</v>
       </c>
       <c r="F10" t="n">
-        <v>-5523286</v>
+        <v>-2288735</v>
       </c>
       <c r="G10" t="n">
-        <v>-6844060</v>
+        <v>-2288735</v>
       </c>
       <c r="H10" t="n">
-        <v>-62600389</v>
+        <v>23413971</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,30 +793,30 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-1936244</v>
+        <v>-17187609</v>
       </c>
       <c r="E11" t="n">
-        <v>-313847</v>
+        <v>-17187609</v>
       </c>
       <c r="F11" t="n">
-        <v>-22033033</v>
+        <v>-40811097</v>
       </c>
       <c r="G11" t="n">
-        <v>-19126353</v>
+        <v>-40811097</v>
       </c>
       <c r="H11" t="n">
-        <v>976692</v>
+        <v>60008254</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,23 +828,23 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-17187609</v>
+        <v>-27735143</v>
       </c>
       <c r="E12" t="n">
-        <v>-24400677</v>
+        <v>-27735143</v>
       </c>
       <c r="F12" t="n">
-        <v>-40811097</v>
+        <v>-209936265</v>
       </c>
       <c r="G12" t="n">
-        <v>-37358945</v>
+        <v>-209936265</v>
       </c>
       <c r="H12" t="n">
-        <v>60008254</v>
+        <v>16139982</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
@@ -866,13 +866,13 @@
         <v>801858</v>
       </c>
       <c r="E13" t="n">
-        <v>877367</v>
+        <v>801858</v>
       </c>
       <c r="F13" t="n">
         <v>-3975426</v>
       </c>
       <c r="G13" t="n">
-        <v>-5977137</v>
+        <v>-3975426</v>
       </c>
       <c r="H13" t="n">
         <v>-14795938</v>
@@ -886,245 +886,105 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠 / 📈 20d 巨變(加碼 17,931 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>6597485</v>
+        <v>-2013643</v>
       </c>
       <c r="E14" t="n">
-        <v>-2623666</v>
+        <v>-2013643</v>
       </c>
       <c r="F14" t="n">
-        <v>8849613</v>
+        <v>3469071</v>
       </c>
       <c r="G14" t="n">
-        <v>-9081513</v>
+        <v>3469071</v>
       </c>
       <c r="H14" t="n">
-        <v>161874868</v>
+        <v>14828007</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>藥華藥</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>-2013643</v>
+        <v>-1954648</v>
       </c>
       <c r="E15" t="n">
-        <v>-790450</v>
+        <v>-1954648</v>
       </c>
       <c r="F15" t="n">
-        <v>3469071</v>
+        <v>5077736</v>
       </c>
       <c r="G15" t="n">
-        <v>3593644</v>
+        <v>5077736</v>
       </c>
       <c r="H15" t="n">
-        <v>14828007</v>
+        <v>8094666</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>原相</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>1747876</v>
+        <v>316313</v>
       </c>
       <c r="E16" t="n">
-        <v>-283718</v>
+        <v>316313</v>
       </c>
       <c r="F16" t="n">
-        <v>-2564024</v>
+        <v>-6116747</v>
       </c>
       <c r="G16" t="n">
-        <v>-1663100</v>
+        <v>-6116747</v>
       </c>
       <c r="H16" t="n">
-        <v>-5899354</v>
+        <v>-5319303</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>卜蜂</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>3227</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" t="n">
-        <v>-1954648</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-1274972</v>
-      </c>
-      <c r="F17" t="n">
-        <v>5077736</v>
-      </c>
-      <c r="G17" t="n">
-        <v>5790425</v>
-      </c>
-      <c r="H17" t="n">
-        <v>8094666</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>原相</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>9917</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" t="n">
-        <v>316313</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-33420</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-6116747</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-6121929</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-5319303</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
           <t>中保科</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 28,303 千)</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>102976642</v>
-      </c>
-      <c r="E19" t="n">
-        <v>61628361</v>
-      </c>
-      <c r="F19" t="n">
-        <v>294172415</v>
-      </c>
-      <c r="G19" t="n">
-        <v>265869773</v>
-      </c>
-      <c r="H19" t="n">
-        <v>7950927</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>長榮航</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2382</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 8,368 千)</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>-16776571</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-13631280</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-34504936</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-42872546</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-291563796</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>廣達</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -466,322 +466,322 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>-30100117</v>
+        <v>14833221</v>
       </c>
       <c r="E2" t="n">
-        <v>-30100117</v>
+        <v>-5075202</v>
       </c>
       <c r="F2" t="n">
-        <v>46804087</v>
+        <v>-19024441</v>
       </c>
       <c r="G2" t="n">
-        <v>46804087</v>
+        <v>-26072637</v>
       </c>
       <c r="H2" t="n">
-        <v>-8845219</v>
+        <v>21871953</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -54,242 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>-3061802</v>
+        <v>-15028303</v>
       </c>
       <c r="E3" t="n">
-        <v>-3061802</v>
+        <v>6597485</v>
       </c>
       <c r="F3" t="n">
-        <v>7937798</v>
+        <v>-45392226</v>
       </c>
       <c r="G3" t="n">
-        <v>7937798</v>
+        <v>8849613</v>
       </c>
       <c r="H3" t="n">
-        <v>11739191</v>
+        <v>86814764</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>805811</v>
+        <v>-14884397</v>
       </c>
       <c r="E4" t="n">
-        <v>805811</v>
+        <v>-30100117</v>
       </c>
       <c r="F4" t="n">
-        <v>-16007257</v>
+        <v>42017787</v>
       </c>
       <c r="G4" t="n">
-        <v>-16007257</v>
+        <v>46804087</v>
       </c>
       <c r="H4" t="n">
-        <v>-39185523</v>
+        <v>-8369437</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>-5075202</v>
+        <v>-1002456</v>
       </c>
       <c r="E5" t="n">
-        <v>-5075202</v>
+        <v>1346923</v>
       </c>
       <c r="F5" t="n">
-        <v>-26072637</v>
+        <v>6407559</v>
       </c>
       <c r="G5" t="n">
-        <v>-26072637</v>
+        <v>8655988</v>
       </c>
       <c r="H5" t="n">
-        <v>8330512</v>
+        <v>10200573</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -17,563 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>3632738</v>
+        <v>-42758358</v>
       </c>
       <c r="E6" t="n">
-        <v>3632738</v>
+        <v>-17187609</v>
       </c>
       <c r="F6" t="n">
-        <v>-5523286</v>
+        <v>-58373805</v>
       </c>
       <c r="G6" t="n">
-        <v>-5523286</v>
+        <v>-40811097</v>
       </c>
       <c r="H6" t="n">
-        <v>-62600389</v>
+        <v>45543093</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>7350345</v>
+        <v>-3183994</v>
       </c>
       <c r="E7" t="n">
-        <v>7350345</v>
+        <v>-3061802</v>
       </c>
       <c r="F7" t="n">
-        <v>-3133976</v>
+        <v>7045383</v>
       </c>
       <c r="G7" t="n">
-        <v>-3133976</v>
+        <v>7937798</v>
       </c>
       <c r="H7" t="n">
-        <v>-73605154</v>
+        <v>12383143</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>健鼎</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-1936244</v>
+        <v>1056115</v>
       </c>
       <c r="E8" t="n">
-        <v>-1936244</v>
+        <v>805811</v>
       </c>
       <c r="F8" t="n">
-        <v>-22033033</v>
+        <v>-17408642</v>
       </c>
       <c r="G8" t="n">
-        <v>-22033033</v>
+        <v>-16007257</v>
       </c>
       <c r="H8" t="n">
-        <v>976692</v>
+        <v>-35614588</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-20766181</v>
+        <v>1157738</v>
       </c>
       <c r="E9" t="n">
-        <v>-20766181</v>
+        <v>-364777</v>
       </c>
       <c r="F9" t="n">
-        <v>-196111151</v>
+        <v>-8868544</v>
       </c>
       <c r="G9" t="n">
-        <v>-196111151</v>
+        <v>-8713956</v>
       </c>
       <c r="H9" t="n">
-        <v>390890338</v>
+        <v>-14009927</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>立隆電</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1264568</v>
+        <v>10346533</v>
       </c>
       <c r="E10" t="n">
-        <v>1264568</v>
+        <v>7350345</v>
       </c>
       <c r="F10" t="n">
-        <v>-2288735</v>
+        <v>496568</v>
       </c>
       <c r="G10" t="n">
-        <v>-2288735</v>
+        <v>-3133976</v>
       </c>
       <c r="H10" t="n">
-        <v>23413971</v>
+        <v>-77571068</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,58 +793,58 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-17187609</v>
+        <v>-22531859</v>
       </c>
       <c r="E11" t="n">
-        <v>-17187609</v>
+        <v>-20766181</v>
       </c>
       <c r="F11" t="n">
-        <v>-40811097</v>
+        <v>-199242648</v>
       </c>
       <c r="G11" t="n">
-        <v>-40811097</v>
+        <v>-196111151</v>
       </c>
       <c r="H11" t="n">
-        <v>60008254</v>
+        <v>359501728</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-27735143</v>
+        <v>3697648</v>
       </c>
       <c r="E12" t="n">
-        <v>-27735143</v>
+        <v>3632738</v>
       </c>
       <c r="F12" t="n">
-        <v>-209936265</v>
+        <v>-4532913</v>
       </c>
       <c r="G12" t="n">
-        <v>-209936265</v>
+        <v>-5523286</v>
       </c>
       <c r="H12" t="n">
-        <v>16139982</v>
+        <v>-60658902</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
@@ -863,19 +863,19 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>801858</v>
+        <v>1261328</v>
       </c>
       <c r="E13" t="n">
         <v>801858</v>
       </c>
       <c r="F13" t="n">
-        <v>-3975426</v>
+        <v>-3096187</v>
       </c>
       <c r="G13" t="n">
         <v>-3975426</v>
       </c>
       <c r="H13" t="n">
-        <v>-14795938</v>
+        <v>-14991293</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -898,19 +898,19 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-2013643</v>
+        <v>-2412807</v>
       </c>
       <c r="E14" t="n">
         <v>-2013643</v>
       </c>
       <c r="F14" t="n">
-        <v>3469071</v>
+        <v>2991490</v>
       </c>
       <c r="G14" t="n">
         <v>3469071</v>
       </c>
       <c r="H14" t="n">
-        <v>14828007</v>
+        <v>14445610</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -921,70 +921,70 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>📈 20d 巨變(加碼 20,270 千)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1954648</v>
+        <v>165901765</v>
       </c>
       <c r="E15" t="n">
-        <v>-1954648</v>
+        <v>102976642</v>
       </c>
       <c r="F15" t="n">
-        <v>5077736</v>
+        <v>314442831</v>
       </c>
       <c r="G15" t="n">
-        <v>5077736</v>
+        <v>294172415</v>
       </c>
       <c r="H15" t="n">
-        <v>8094666</v>
+        <v>81027367</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>📉 20d 巨變(減碼 -47,235 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>316313</v>
+        <v>-31079291</v>
       </c>
       <c r="E16" t="n">
-        <v>316313</v>
+        <v>-27735143</v>
       </c>
       <c r="F16" t="n">
-        <v>-6116747</v>
+        <v>-257171105</v>
       </c>
       <c r="G16" t="n">
-        <v>-6116747</v>
+        <v>-209936265</v>
       </c>
       <c r="H16" t="n">
-        <v>-5319303</v>
+        <v>-25098099</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,70 +466,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📈 20d 巨變(加碼 13,106 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>14833221</v>
+        <v>-3967492</v>
       </c>
       <c r="E2" t="n">
-        <v>-5075202</v>
+        <v>10098371</v>
       </c>
       <c r="F2" t="n">
-        <v>-19024441</v>
+        <v>34935536</v>
       </c>
       <c r="G2" t="n">
-        <v>-26072637</v>
+        <v>21829304</v>
       </c>
       <c r="H2" t="n">
-        <v>21871953</v>
+        <v>118987599</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -54,242 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>-15028303</v>
+        <v>25203233</v>
       </c>
       <c r="E3" t="n">
-        <v>6597485</v>
+        <v>14833221</v>
       </c>
       <c r="F3" t="n">
-        <v>-45392226</v>
+        <v>-12221307</v>
       </c>
       <c r="G3" t="n">
-        <v>8849613</v>
+        <v>-19024441</v>
       </c>
       <c r="H3" t="n">
-        <v>86814764</v>
+        <v>25379936</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
@@ -548,19 +548,19 @@
         <v>7</v>
       </c>
       <c r="D4" t="n">
+        <v>-14744880</v>
+      </c>
+      <c r="E4" t="n">
         <v>-14884397</v>
       </c>
-      <c r="E4" t="n">
-        <v>-30100117</v>
-      </c>
       <c r="F4" t="n">
+        <v>36753211</v>
+      </c>
+      <c r="G4" t="n">
         <v>42017787</v>
       </c>
-      <c r="G4" t="n">
-        <v>46804087</v>
-      </c>
       <c r="H4" t="n">
-        <v>-8369437</v>
+        <v>-6422989</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -571,252 +571,252 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -15,672 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>-1002456</v>
+        <v>-21099789</v>
       </c>
       <c r="E5" t="n">
-        <v>1346923</v>
+        <v>-22531859</v>
       </c>
       <c r="F5" t="n">
-        <v>6407559</v>
+        <v>-214914718</v>
       </c>
       <c r="G5" t="n">
-        <v>8655988</v>
+        <v>-199242648</v>
       </c>
       <c r="H5" t="n">
-        <v>10200573</v>
+        <v>349738481</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -17,563 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>-42758358</v>
+        <v>-2528250</v>
       </c>
       <c r="E6" t="n">
-        <v>-17187609</v>
+        <v>-3183994</v>
       </c>
       <c r="F6" t="n">
-        <v>-58373805</v>
+        <v>5025936</v>
       </c>
       <c r="G6" t="n">
-        <v>-40811097</v>
+        <v>7045383</v>
       </c>
       <c r="H6" t="n">
-        <v>45543093</v>
+        <v>11570800</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>健鼎</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-3183994</v>
+        <v>13691296</v>
       </c>
       <c r="E7" t="n">
-        <v>-3061802</v>
+        <v>10346533</v>
       </c>
       <c r="F7" t="n">
-        <v>7045383</v>
+        <v>-7136115</v>
       </c>
       <c r="G7" t="n">
-        <v>7937798</v>
+        <v>496568</v>
       </c>
       <c r="H7" t="n">
-        <v>12383143</v>
+        <v>-76024725</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1056115</v>
+        <v>-19666599</v>
       </c>
       <c r="E8" t="n">
-        <v>805811</v>
+        <v>-15028303</v>
       </c>
       <c r="F8" t="n">
-        <v>-17408642</v>
+        <v>-38905078</v>
       </c>
       <c r="G8" t="n">
-        <v>-16007257</v>
+        <v>-45392226</v>
       </c>
       <c r="H8" t="n">
-        <v>-35614588</v>
+        <v>84616249</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1157738</v>
+        <v>-39841055</v>
       </c>
       <c r="E9" t="n">
-        <v>-364777</v>
+        <v>-42758358</v>
       </c>
       <c r="F9" t="n">
-        <v>-8868544</v>
+        <v>-59452449</v>
       </c>
       <c r="G9" t="n">
-        <v>-8713956</v>
+        <v>-58373805</v>
       </c>
       <c r="H9" t="n">
-        <v>-14009927</v>
+        <v>39595409</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>10346533</v>
+        <v>-288839</v>
       </c>
       <c r="E10" t="n">
-        <v>7350345</v>
+        <v>-1002456</v>
       </c>
       <c r="F10" t="n">
-        <v>496568</v>
+        <v>5934767</v>
       </c>
       <c r="G10" t="n">
-        <v>-3133976</v>
+        <v>6407559</v>
       </c>
       <c r="H10" t="n">
-        <v>-77571068</v>
+        <v>10283625</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-22531859</v>
+        <v>2786256</v>
       </c>
       <c r="E11" t="n">
-        <v>-20766181</v>
+        <v>3697648</v>
       </c>
       <c r="F11" t="n">
-        <v>-199242648</v>
+        <v>-2377147</v>
       </c>
       <c r="G11" t="n">
-        <v>-196111151</v>
+        <v>-4532913</v>
       </c>
       <c r="H11" t="n">
-        <v>359501728</v>
+        <v>-59367015</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,161 +828,301 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>3697648</v>
+        <v>-1556382</v>
       </c>
       <c r="E12" t="n">
-        <v>3632738</v>
+        <v>-2412807</v>
       </c>
       <c r="F12" t="n">
-        <v>-4532913</v>
+        <v>3190619</v>
       </c>
       <c r="G12" t="n">
-        <v>-5523286</v>
+        <v>2991490</v>
       </c>
       <c r="H12" t="n">
-        <v>-60658902</v>
+        <v>14684332</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>藥華藥</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>1261328</v>
+        <v>-1165454</v>
       </c>
       <c r="E13" t="n">
-        <v>801858</v>
+        <v>1056115</v>
       </c>
       <c r="F13" t="n">
-        <v>-3096187</v>
+        <v>-19539272</v>
       </c>
       <c r="G13" t="n">
-        <v>-3975426</v>
+        <v>-17408642</v>
       </c>
       <c r="H13" t="n">
-        <v>-14991293</v>
+        <v>-34917529</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-2412807</v>
+        <v>-5309213</v>
       </c>
       <c r="E14" t="n">
-        <v>-2013643</v>
+        <v>1932952</v>
       </c>
       <c r="F14" t="n">
-        <v>2991490</v>
+        <v>-2219578</v>
       </c>
       <c r="G14" t="n">
-        <v>3469071</v>
+        <v>590996</v>
       </c>
       <c r="H14" t="n">
-        <v>14445610</v>
+        <v>-12156512</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>亞力</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 20,270 千)</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>165901765</v>
+        <v>2002335</v>
       </c>
       <c r="E15" t="n">
-        <v>102976642</v>
+        <v>-752022</v>
       </c>
       <c r="F15" t="n">
-        <v>314442831</v>
+        <v>1223778</v>
       </c>
       <c r="G15" t="n">
-        <v>294172415</v>
+        <v>-895485</v>
       </c>
       <c r="H15" t="n">
-        <v>81027367</v>
+        <v>-4196555</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>台燿</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>2472</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6474065</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1157738</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-1039677</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-8868544</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-9196062</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>立隆電</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -22,063 千)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-31281582</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-19106462</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-104197922</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-82134727</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-267107581</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 14,816 千)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>213984721</v>
+      </c>
+      <c r="E18" t="n">
+        <v>165901765</v>
+      </c>
+      <c r="F18" t="n">
+        <v>329259102</v>
+      </c>
+      <c r="G18" t="n">
+        <v>314442831</v>
+      </c>
+      <c r="H18" t="n">
+        <v>124460822</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>長榮航</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 10,728 千)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-13780172</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-30017275</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-196512336</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-207240513</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-115579822</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>2344</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -47,235 千)</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -20,197 千)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
         <v>1</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D20" t="n">
+        <v>-9393707</v>
+      </c>
+      <c r="E20" t="n">
         <v>-31079291</v>
       </c>
-      <c r="E16" t="n">
-        <v>-27735143</v>
-      </c>
-      <c r="F16" t="n">
+      <c r="F20" t="n">
+        <v>-277368453</v>
+      </c>
+      <c r="G20" t="n">
         <v>-257171105</v>
       </c>
-      <c r="G16" t="n">
-        <v>-209936265</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-25098099</v>
-      </c>
-      <c r="I16" t="inlineStr">
+      <c r="H20" t="n">
+        <v>-22418278</v>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>華邦電</t>
         </is>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,217 +466,217 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📈 20d 巨變(加碼 13,106 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>-3967492</v>
+        <v>3714243</v>
       </c>
       <c r="E2" t="n">
-        <v>10098371</v>
+        <v>-21099789</v>
       </c>
       <c r="F2" t="n">
-        <v>34935536</v>
+        <v>-217677992</v>
       </c>
       <c r="G2" t="n">
-        <v>21829304</v>
+        <v>-214914718</v>
       </c>
       <c r="H2" t="n">
-        <v>118987599</v>
+        <v>353831980</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>25203233</v>
+        <v>1036680</v>
       </c>
       <c r="E3" t="n">
-        <v>14833221</v>
+        <v>-1165454</v>
       </c>
       <c r="F3" t="n">
-        <v>-12221307</v>
+        <v>-18807809</v>
       </c>
       <c r="G3" t="n">
-        <v>-19024441</v>
+        <v>-19539272</v>
       </c>
       <c r="H3" t="n">
-        <v>25379936</v>
+        <v>-34163263</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>-14744880</v>
+        <v>36045928</v>
       </c>
       <c r="E4" t="n">
-        <v>-14884397</v>
+        <v>25203233</v>
       </c>
       <c r="F4" t="n">
-        <v>36753211</v>
+        <v>-13875769</v>
       </c>
       <c r="G4" t="n">
-        <v>42017787</v>
+        <v>-12221307</v>
       </c>
       <c r="H4" t="n">
-        <v>-6422989</v>
+        <v>28024976</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -15,672 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>-21099789</v>
+        <v>6681300</v>
       </c>
       <c r="E5" t="n">
-        <v>-22531859</v>
+        <v>-1831280</v>
       </c>
       <c r="F5" t="n">
-        <v>-214914718</v>
+        <v>-157923879</v>
       </c>
       <c r="G5" t="n">
-        <v>-199242648</v>
+        <v>-153463886</v>
       </c>
       <c r="H5" t="n">
-        <v>349738481</v>
+        <v>-170815560</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -42,086 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>-2528250</v>
+        <v>-11511118</v>
       </c>
       <c r="E6" t="n">
-        <v>-3183994</v>
+        <v>-19666599</v>
       </c>
       <c r="F6" t="n">
-        <v>5025936</v>
+        <v>-80991566</v>
       </c>
       <c r="G6" t="n">
-        <v>7045383</v>
+        <v>-38905078</v>
       </c>
       <c r="H6" t="n">
-        <v>11570800</v>
+        <v>130747495</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>13691296</v>
+        <v>-7339887</v>
       </c>
       <c r="E7" t="n">
-        <v>10346533</v>
+        <v>-14744880</v>
       </c>
       <c r="F7" t="n">
-        <v>-7136115</v>
+        <v>37007447</v>
       </c>
       <c r="G7" t="n">
-        <v>496568</v>
+        <v>36753211</v>
       </c>
       <c r="H7" t="n">
-        <v>-76024725</v>
+        <v>3243976</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,93 +688,93 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-19666599</v>
+        <v>-34707479</v>
       </c>
       <c r="E8" t="n">
-        <v>-15028303</v>
+        <v>-39841055</v>
       </c>
       <c r="F8" t="n">
-        <v>-38905078</v>
+        <v>-58910368</v>
       </c>
       <c r="G8" t="n">
-        <v>-45392226</v>
+        <v>-59452449</v>
       </c>
       <c r="H8" t="n">
-        <v>84616249</v>
+        <v>36348475</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-39841055</v>
+        <v>-1555687</v>
       </c>
       <c r="E9" t="n">
-        <v>-42758358</v>
+        <v>-288839</v>
       </c>
       <c r="F9" t="n">
-        <v>-59452449</v>
+        <v>6371162</v>
       </c>
       <c r="G9" t="n">
-        <v>-58373805</v>
+        <v>5934767</v>
       </c>
       <c r="H9" t="n">
-        <v>39595409</v>
+        <v>10527681</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-288839</v>
+        <v>-1417578</v>
       </c>
       <c r="E10" t="n">
-        <v>-1002456</v>
+        <v>-2528250</v>
       </c>
       <c r="F10" t="n">
-        <v>5934767</v>
+        <v>2460649</v>
       </c>
       <c r="G10" t="n">
-        <v>6407559</v>
+        <v>5025936</v>
       </c>
       <c r="H10" t="n">
-        <v>10283625</v>
+        <v>11510884</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>健鼎</t>
         </is>
       </c>
     </row>
@@ -793,19 +793,19 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
+        <v>3552749</v>
+      </c>
+      <c r="E11" t="n">
         <v>2786256</v>
       </c>
-      <c r="E11" t="n">
-        <v>3697648</v>
-      </c>
       <c r="F11" t="n">
+        <v>-591043</v>
+      </c>
+      <c r="G11" t="n">
         <v>-2377147</v>
       </c>
-      <c r="G11" t="n">
-        <v>-4532913</v>
-      </c>
       <c r="H11" t="n">
-        <v>-59367015</v>
+        <v>-57842754</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -828,19 +828,19 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
+        <v>-1560612</v>
+      </c>
+      <c r="E12" t="n">
         <v>-1556382</v>
       </c>
-      <c r="E12" t="n">
-        <v>-2412807</v>
-      </c>
       <c r="F12" t="n">
+        <v>2358053</v>
+      </c>
+      <c r="G12" t="n">
         <v>3190619</v>
       </c>
-      <c r="G12" t="n">
-        <v>2991490</v>
-      </c>
       <c r="H12" t="n">
-        <v>14684332</v>
+        <v>13842187</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -851,278 +851,243 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-1165454</v>
+        <v>623883</v>
       </c>
       <c r="E13" t="n">
-        <v>1056115</v>
+        <v>-246893</v>
       </c>
       <c r="F13" t="n">
-        <v>-19539272</v>
+        <v>-4464883</v>
       </c>
       <c r="G13" t="n">
-        <v>-17408642</v>
+        <v>-4684004</v>
       </c>
       <c r="H13" t="n">
-        <v>-34917529</v>
+        <v>-11639034</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-5309213</v>
+        <v>1175412</v>
       </c>
       <c r="E14" t="n">
-        <v>1932952</v>
+        <v>710474</v>
       </c>
       <c r="F14" t="n">
-        <v>-2219578</v>
+        <v>-6012208</v>
       </c>
       <c r="G14" t="n">
-        <v>590996</v>
+        <v>-2133121</v>
       </c>
       <c r="H14" t="n">
-        <v>-12156512</v>
+        <v>-6482129</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>2002335</v>
+        <v>-1581333</v>
       </c>
       <c r="E15" t="n">
-        <v>-752022</v>
+        <v>13691296</v>
       </c>
       <c r="F15" t="n">
-        <v>1223778</v>
+        <v>-11734354</v>
       </c>
       <c r="G15" t="n">
-        <v>-895485</v>
+        <v>-7136115</v>
       </c>
       <c r="H15" t="n">
-        <v>-4196555</v>
+        <v>-84241889</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>6474065</v>
+        <v>1170830</v>
       </c>
       <c r="E16" t="n">
-        <v>1157738</v>
+        <v>-3967492</v>
       </c>
       <c r="F16" t="n">
-        <v>-1039677</v>
+        <v>36294471</v>
       </c>
       <c r="G16" t="n">
-        <v>-8868544</v>
+        <v>34935536</v>
       </c>
       <c r="H16" t="n">
-        <v>-9196062</v>
+        <v>121949695</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -22,063 千)</t>
+          <t>📈 20d 巨變(加碼 18,239 千)</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-31281582</v>
+        <v>223295717</v>
       </c>
       <c r="E17" t="n">
-        <v>-19106462</v>
+        <v>213984721</v>
       </c>
       <c r="F17" t="n">
-        <v>-104197922</v>
+        <v>347497749</v>
       </c>
       <c r="G17" t="n">
-        <v>-82134727</v>
+        <v>329259102</v>
       </c>
       <c r="H17" t="n">
-        <v>-267107581</v>
+        <v>154302172</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 14,816 千)</t>
+          <t>📈 20d 巨變(加碼 10,904 千)</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>213984721</v>
+        <v>-3140336</v>
       </c>
       <c r="E18" t="n">
-        <v>165901765</v>
+        <v>-13780172</v>
       </c>
       <c r="F18" t="n">
-        <v>329259102</v>
+        <v>-185608049</v>
       </c>
       <c r="G18" t="n">
-        <v>314442831</v>
+        <v>-196512336</v>
       </c>
       <c r="H18" t="n">
-        <v>124460822</v>
+        <v>-105994781</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 10,728 千)</t>
+          <t>📉 20d 巨變(減碼 -20,159 千)</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-13780172</v>
+        <v>-1099054</v>
       </c>
       <c r="E19" t="n">
-        <v>-30017275</v>
+        <v>-9393707</v>
       </c>
       <c r="F19" t="n">
-        <v>-196512336</v>
+        <v>-297527376</v>
       </c>
       <c r="G19" t="n">
-        <v>-207240513</v>
+        <v>-277368453</v>
       </c>
       <c r="H19" t="n">
-        <v>-115579822</v>
+        <v>-1731224</v>
       </c>
       <c r="I19" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -20,197 千)</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>-9393707</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-31079291</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-277368453</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-257171105</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-22418278</v>
-      </c>
-      <c r="I20" t="inlineStr">
         <is>
           <t>華邦電</t>
         </is>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,140 +466,140 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 12,998 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>3714243</v>
+        <v>56952446</v>
       </c>
       <c r="E2" t="n">
-        <v>-21099789</v>
+        <v>36045928</v>
       </c>
       <c r="F2" t="n">
-        <v>-217677992</v>
+        <v>-877656</v>
       </c>
       <c r="G2" t="n">
-        <v>-214914718</v>
+        <v>-13875769</v>
       </c>
       <c r="H2" t="n">
-        <v>353831980</v>
+        <v>40388059</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 20,421 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>1036680</v>
+        <v>6972004</v>
       </c>
       <c r="E3" t="n">
-        <v>-1165454</v>
+        <v>-3140336</v>
       </c>
       <c r="F3" t="n">
-        <v>-18807809</v>
+        <v>-165187385</v>
       </c>
       <c r="G3" t="n">
-        <v>-19539272</v>
+        <v>-185608049</v>
       </c>
       <c r="H3" t="n">
-        <v>-34163263</v>
+        <v>-95341849</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 13,928 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>36045928</v>
+        <v>11104509</v>
       </c>
       <c r="E4" t="n">
-        <v>25203233</v>
+        <v>3714243</v>
       </c>
       <c r="F4" t="n">
-        <v>-13875769</v>
+        <v>-203749757</v>
       </c>
       <c r="G4" t="n">
-        <v>-12221307</v>
+        <v>-217677992</v>
       </c>
       <c r="H4" t="n">
-        <v>28024976</v>
+        <v>360530518</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 16,312 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>6681300</v>
+        <v>17714941</v>
       </c>
       <c r="E5" t="n">
-        <v>-1831280</v>
+        <v>-9386617</v>
       </c>
       <c r="F5" t="n">
-        <v>-157923879</v>
+        <v>-76878717</v>
       </c>
       <c r="G5" t="n">
-        <v>-153463886</v>
+        <v>-93190530</v>
       </c>
       <c r="H5" t="n">
-        <v>-170815560</v>
+        <v>-124907452</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
@@ -611,26 +611,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -42,086 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -26,078 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>6</v>
       </c>
       <c r="D6" t="n">
+        <v>-30700231</v>
+      </c>
+      <c r="E6" t="n">
         <v>-11511118</v>
       </c>
-      <c r="E6" t="n">
-        <v>-19666599</v>
-      </c>
       <c r="F6" t="n">
+        <v>-107069506</v>
+      </c>
+      <c r="G6" t="n">
         <v>-80991566</v>
       </c>
-      <c r="G6" t="n">
-        <v>-38905078</v>
-      </c>
       <c r="H6" t="n">
-        <v>130747495</v>
+        <v>108815533</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -641,77 +641,77 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-7339887</v>
+        <v>1189163</v>
       </c>
       <c r="E7" t="n">
-        <v>-14744880</v>
+        <v>1036680</v>
       </c>
       <c r="F7" t="n">
-        <v>37007447</v>
+        <v>-17119142</v>
       </c>
       <c r="G7" t="n">
-        <v>36753211</v>
+        <v>-18807809</v>
       </c>
       <c r="H7" t="n">
-        <v>3243976</v>
+        <v>-34234943</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-34707479</v>
+        <v>3420434</v>
       </c>
       <c r="E8" t="n">
-        <v>-39841055</v>
+        <v>3552749</v>
       </c>
       <c r="F8" t="n">
-        <v>-58910368</v>
+        <v>188850</v>
       </c>
       <c r="G8" t="n">
-        <v>-59452449</v>
+        <v>-591043</v>
       </c>
       <c r="H8" t="n">
-        <v>36348475</v>
+        <v>-57935298</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,268 +723,268 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-1555687</v>
+        <v>-3754653</v>
       </c>
       <c r="E9" t="n">
-        <v>-288839</v>
+        <v>-7339887</v>
       </c>
       <c r="F9" t="n">
-        <v>6371162</v>
+        <v>36837450</v>
       </c>
       <c r="G9" t="n">
-        <v>5934767</v>
+        <v>37007447</v>
       </c>
       <c r="H9" t="n">
-        <v>10527681</v>
+        <v>2227464</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-1417578</v>
+        <v>1867075</v>
       </c>
       <c r="E10" t="n">
-        <v>-2528250</v>
+        <v>4001237</v>
       </c>
       <c r="F10" t="n">
-        <v>2460649</v>
+        <v>-818035</v>
       </c>
       <c r="G10" t="n">
-        <v>5025936</v>
+        <v>5928015</v>
       </c>
       <c r="H10" t="n">
-        <v>11510884</v>
+        <v>26523115</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>3552749</v>
+        <v>-17332511</v>
       </c>
       <c r="E11" t="n">
-        <v>2786256</v>
+        <v>-34707479</v>
       </c>
       <c r="F11" t="n">
-        <v>-591043</v>
+        <v>-51842609</v>
       </c>
       <c r="G11" t="n">
-        <v>-2377147</v>
+        <v>-58910368</v>
       </c>
       <c r="H11" t="n">
-        <v>-57842754</v>
+        <v>46169402</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-1560612</v>
+        <v>-358251</v>
       </c>
       <c r="E12" t="n">
-        <v>-1556382</v>
+        <v>-1555687</v>
       </c>
       <c r="F12" t="n">
-        <v>2358053</v>
+        <v>6419854</v>
       </c>
       <c r="G12" t="n">
-        <v>3190619</v>
+        <v>6371162</v>
       </c>
       <c r="H12" t="n">
-        <v>13842187</v>
+        <v>10788043</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>623883</v>
+        <v>17327640</v>
       </c>
       <c r="E13" t="n">
-        <v>-246893</v>
+        <v>6681300</v>
       </c>
       <c r="F13" t="n">
-        <v>-4464883</v>
+        <v>-153926493</v>
       </c>
       <c r="G13" t="n">
-        <v>-4684004</v>
+        <v>-157923879</v>
       </c>
       <c r="H13" t="n">
-        <v>-11639034</v>
+        <v>-162329830</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>1175412</v>
+        <v>-2265526</v>
       </c>
       <c r="E14" t="n">
-        <v>710474</v>
+        <v>-1560612</v>
       </c>
       <c r="F14" t="n">
-        <v>-6012208</v>
+        <v>592978</v>
       </c>
       <c r="G14" t="n">
-        <v>-2133121</v>
+        <v>2358053</v>
       </c>
       <c r="H14" t="n">
-        <v>-6482129</v>
+        <v>12884251</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>藥華藥</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>-1581333</v>
+        <v>658671</v>
       </c>
       <c r="E15" t="n">
-        <v>13691296</v>
+        <v>623883</v>
       </c>
       <c r="F15" t="n">
-        <v>-11734354</v>
+        <v>-3961623</v>
       </c>
       <c r="G15" t="n">
-        <v>-7136115</v>
+        <v>-4464883</v>
       </c>
       <c r="H15" t="n">
-        <v>-84241889</v>
+        <v>-11613056</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>1170830</v>
+        <v>703187</v>
       </c>
       <c r="E16" t="n">
-        <v>-3967492</v>
+        <v>1175412</v>
       </c>
       <c r="F16" t="n">
-        <v>36294471</v>
+        <v>-5012967</v>
       </c>
       <c r="G16" t="n">
-        <v>34935536</v>
+        <v>-6012208</v>
       </c>
       <c r="H16" t="n">
-        <v>121949695</v>
+        <v>-6957237</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
@@ -996,100 +996,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 18,239 千)</t>
+          <t>📉 20d 巨變(減碼 -94,180 千)</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
+        <v>169390686</v>
+      </c>
+      <c r="E17" t="n">
         <v>223295717</v>
       </c>
-      <c r="E17" t="n">
-        <v>213984721</v>
-      </c>
       <c r="F17" t="n">
+        <v>253317450</v>
+      </c>
+      <c r="G17" t="n">
         <v>347497749</v>
       </c>
-      <c r="G17" t="n">
-        <v>329259102</v>
-      </c>
       <c r="H17" t="n">
-        <v>154302172</v>
+        <v>162255566</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>長榮航</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 10,904 千)</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>-3140336</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-13780172</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-185608049</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-196512336</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-105994781</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -20,159 千)</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>-1099054</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-9393707</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-297527376</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-277368453</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-1731224</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>華邦電</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,70 +466,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 12,998 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -25,106 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>56952446</v>
+        <v>-14797420</v>
       </c>
       <c r="E2" t="n">
-        <v>36045928</v>
+        <v>-3754653</v>
       </c>
       <c r="F2" t="n">
-        <v>-877656</v>
+        <v>11731050</v>
       </c>
       <c r="G2" t="n">
-        <v>-13875769</v>
+        <v>36837450</v>
       </c>
       <c r="H2" t="n">
-        <v>40388059</v>
+        <v>-9515111</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 20,421 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -13,372 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>6972004</v>
+        <v>-5172611</v>
       </c>
       <c r="E3" t="n">
-        <v>-3140336</v>
+        <v>2422313</v>
       </c>
       <c r="F3" t="n">
-        <v>-165187385</v>
+        <v>23855972</v>
       </c>
       <c r="G3" t="n">
-        <v>-185608049</v>
+        <v>37228026</v>
       </c>
       <c r="H3" t="n">
-        <v>-95341849</v>
+        <v>114745899</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
@@ -541,26 +541,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 13,928 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 21,206 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>8</v>
       </c>
       <c r="D4" t="n">
+        <v>1093149</v>
+      </c>
+      <c r="E4" t="n">
         <v>11104509</v>
       </c>
-      <c r="E4" t="n">
-        <v>3714243</v>
-      </c>
       <c r="F4" t="n">
+        <v>-182543797</v>
+      </c>
+      <c r="G4" t="n">
         <v>-203749757</v>
       </c>
-      <c r="G4" t="n">
-        <v>-217677992</v>
-      </c>
       <c r="H4" t="n">
-        <v>360530518</v>
+        <v>356262283</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -571,315 +571,315 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 16,312 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>17714941</v>
+        <v>-1724118</v>
       </c>
       <c r="E5" t="n">
-        <v>-9386617</v>
+        <v>1867075</v>
       </c>
       <c r="F5" t="n">
-        <v>-76878717</v>
+        <v>-3631393</v>
       </c>
       <c r="G5" t="n">
-        <v>-93190530</v>
+        <v>-818035</v>
       </c>
       <c r="H5" t="n">
-        <v>-124907452</v>
+        <v>25626345</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -26,078 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 24,764 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>-30700231</v>
+        <v>12106283</v>
       </c>
       <c r="E6" t="n">
-        <v>-11511118</v>
+        <v>6972004</v>
       </c>
       <c r="F6" t="n">
-        <v>-107069506</v>
+        <v>-140423204</v>
       </c>
       <c r="G6" t="n">
-        <v>-80991566</v>
+        <v>-165187385</v>
       </c>
       <c r="H6" t="n">
-        <v>108815533</v>
+        <v>-95621161</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 12,182 千)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1189163</v>
+        <v>-12948078</v>
       </c>
       <c r="E7" t="n">
-        <v>1036680</v>
+        <v>-17332511</v>
       </c>
       <c r="F7" t="n">
-        <v>-17119142</v>
+        <v>-39660563</v>
       </c>
       <c r="G7" t="n">
-        <v>-18807809</v>
+        <v>-51842609</v>
       </c>
       <c r="H7" t="n">
-        <v>-34234943</v>
+        <v>54301398</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 18,839 千)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>3420434</v>
+        <v>27777846</v>
       </c>
       <c r="E8" t="n">
-        <v>3552749</v>
+        <v>17714941</v>
       </c>
       <c r="F8" t="n">
-        <v>188850</v>
+        <v>-58039375</v>
       </c>
       <c r="G8" t="n">
-        <v>-591043</v>
+        <v>-76878717</v>
       </c>
       <c r="H8" t="n">
-        <v>-57935298</v>
+        <v>-107868576</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 27,414 千)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>-3754653</v>
+        <v>14483986</v>
       </c>
       <c r="E9" t="n">
-        <v>-7339887</v>
+        <v>17327640</v>
       </c>
       <c r="F9" t="n">
-        <v>36837450</v>
+        <v>-126512956</v>
       </c>
       <c r="G9" t="n">
-        <v>37007447</v>
+        <v>-153926493</v>
       </c>
       <c r="H9" t="n">
-        <v>2227464</v>
+        <v>-159593249</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1867075</v>
+        <v>1321493</v>
       </c>
       <c r="E10" t="n">
-        <v>4001237</v>
+        <v>1189163</v>
       </c>
       <c r="F10" t="n">
-        <v>-818035</v>
+        <v>-14673803</v>
       </c>
       <c r="G10" t="n">
-        <v>5928015</v>
+        <v>-17119142</v>
       </c>
       <c r="H10" t="n">
-        <v>26523115</v>
+        <v>-33623598</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-17332511</v>
+        <v>2350282</v>
       </c>
       <c r="E11" t="n">
-        <v>-34707479</v>
+        <v>3420434</v>
       </c>
       <c r="F11" t="n">
-        <v>-51842609</v>
+        <v>3945241</v>
       </c>
       <c r="G11" t="n">
-        <v>-58910368</v>
+        <v>188850</v>
       </c>
       <c r="H11" t="n">
-        <v>46169402</v>
+        <v>-57920276</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-358251</v>
+        <v>-54791511</v>
       </c>
       <c r="E12" t="n">
-        <v>-1555687</v>
+        <v>-30700231</v>
       </c>
       <c r="F12" t="n">
-        <v>6419854</v>
+        <v>-110433360</v>
       </c>
       <c r="G12" t="n">
-        <v>6371162</v>
+        <v>-107069506</v>
       </c>
       <c r="H12" t="n">
-        <v>10788043</v>
+        <v>100154253</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>17327640</v>
+        <v>493607</v>
       </c>
       <c r="E13" t="n">
-        <v>6681300</v>
+        <v>-143519</v>
       </c>
       <c r="F13" t="n">
-        <v>-153926493</v>
+        <v>-3842228</v>
       </c>
       <c r="G13" t="n">
-        <v>-157923879</v>
+        <v>-3658741</v>
       </c>
       <c r="H13" t="n">
-        <v>-162329830</v>
+        <v>-12789811</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>華城</t>
         </is>
       </c>
     </row>
@@ -898,19 +898,19 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
+        <v>-462401</v>
+      </c>
+      <c r="E14" t="n">
         <v>-2265526</v>
       </c>
-      <c r="E14" t="n">
-        <v>-1560612</v>
-      </c>
       <c r="F14" t="n">
+        <v>212288</v>
+      </c>
+      <c r="G14" t="n">
         <v>592978</v>
       </c>
-      <c r="G14" t="n">
-        <v>2358053</v>
-      </c>
       <c r="H14" t="n">
-        <v>12884251</v>
+        <v>13390118</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -933,19 +933,19 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
+        <v>906365</v>
+      </c>
+      <c r="E15" t="n">
         <v>658671</v>
       </c>
-      <c r="E15" t="n">
-        <v>623883</v>
-      </c>
       <c r="F15" t="n">
+        <v>-3443596</v>
+      </c>
+      <c r="G15" t="n">
         <v>-3961623</v>
       </c>
-      <c r="G15" t="n">
-        <v>-4464883</v>
-      </c>
       <c r="H15" t="n">
-        <v>-11613056</v>
+        <v>-11584777</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -956,70 +956,140 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>703187</v>
+        <v>-829896</v>
       </c>
       <c r="E16" t="n">
-        <v>1175412</v>
+        <v>520676</v>
       </c>
       <c r="F16" t="n">
-        <v>-5012967</v>
+        <v>3416730</v>
       </c>
       <c r="G16" t="n">
-        <v>-6012208</v>
+        <v>3581160</v>
       </c>
       <c r="H16" t="n">
-        <v>-6957237</v>
+        <v>14646120</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>研華</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -94,180 千)</t>
+          <t>📉 20d 巨變(減碼 -51,700 千)</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>169390686</v>
+        <v>-66286992</v>
       </c>
       <c r="E17" t="n">
-        <v>223295717</v>
+        <v>-34851569</v>
       </c>
       <c r="F17" t="n">
-        <v>253317450</v>
+        <v>-156280847</v>
       </c>
       <c r="G17" t="n">
-        <v>347497749</v>
+        <v>-104580988</v>
       </c>
       <c r="H17" t="n">
-        <v>162255566</v>
+        <v>-297750913</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>台積電</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3045</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 13,328 千)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>46767815</v>
+      </c>
+      <c r="E18" t="n">
+        <v>56952446</v>
+      </c>
+      <c r="F18" t="n">
+        <v>12450611</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-877656</v>
+      </c>
+      <c r="H18" t="n">
+        <v>55119611</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>台灣大</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -8,539 千)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-38545330</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-16968839</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-304557560</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-296018253</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-37593644</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>華邦電</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,140 +466,140 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -25,106 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>-14797420</v>
+        <v>20996028</v>
       </c>
       <c r="E2" t="n">
-        <v>-3754653</v>
+        <v>-12948078</v>
       </c>
       <c r="F2" t="n">
-        <v>11731050</v>
+        <v>-42784614</v>
       </c>
       <c r="G2" t="n">
-        <v>36837450</v>
+        <v>-39660563</v>
       </c>
       <c r="H2" t="n">
-        <v>-9515111</v>
+        <v>53656940</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -13,372 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>-5172611</v>
+        <v>1138791</v>
       </c>
       <c r="E3" t="n">
-        <v>2422313</v>
+        <v>-3677368</v>
       </c>
       <c r="F3" t="n">
-        <v>23855972</v>
+        <v>-27874721</v>
       </c>
       <c r="G3" t="n">
-        <v>37228026</v>
+        <v>-33736302</v>
       </c>
       <c r="H3" t="n">
-        <v>114745899</v>
+        <v>-281094100</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 21,206 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>1093149</v>
+        <v>1295541</v>
       </c>
       <c r="E4" t="n">
-        <v>11104509</v>
+        <v>-1247477</v>
       </c>
       <c r="F4" t="n">
-        <v>-182543797</v>
+        <v>-14639579</v>
       </c>
       <c r="G4" t="n">
-        <v>-203749757</v>
+        <v>-14100767</v>
       </c>
       <c r="H4" t="n">
-        <v>356262283</v>
+        <v>-24260885</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>瑞昱</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>-1724118</v>
+        <v>2333417</v>
       </c>
       <c r="E5" t="n">
-        <v>1867075</v>
+        <v>1093149</v>
       </c>
       <c r="F5" t="n">
-        <v>-3631393</v>
+        <v>-180568140</v>
       </c>
       <c r="G5" t="n">
-        <v>-818035</v>
+        <v>-182543797</v>
       </c>
       <c r="H5" t="n">
-        <v>25626345</v>
+        <v>246344438</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
@@ -611,26 +611,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 24,764 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 12,539 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>6</v>
       </c>
       <c r="D6" t="n">
+        <v>25869313</v>
+      </c>
+      <c r="E6" t="n">
         <v>12106283</v>
       </c>
-      <c r="E6" t="n">
-        <v>6972004</v>
-      </c>
       <c r="F6" t="n">
+        <v>-127884666</v>
+      </c>
+      <c r="G6" t="n">
         <v>-140423204</v>
       </c>
-      <c r="G6" t="n">
-        <v>-165187385</v>
-      </c>
       <c r="H6" t="n">
-        <v>-95621161</v>
+        <v>-103166190</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -641,322 +641,322 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 12,182 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-12948078</v>
+        <v>1572597</v>
       </c>
       <c r="E7" t="n">
-        <v>-17332511</v>
+        <v>1321493</v>
       </c>
       <c r="F7" t="n">
-        <v>-39660563</v>
+        <v>-14257695</v>
       </c>
       <c r="G7" t="n">
-        <v>-51842609</v>
+        <v>-14673803</v>
       </c>
       <c r="H7" t="n">
-        <v>54301398</v>
+        <v>-32103756</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 18,839 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>27777846</v>
+        <v>1301298</v>
       </c>
       <c r="E8" t="n">
-        <v>17714941</v>
+        <v>2350282</v>
       </c>
       <c r="F8" t="n">
-        <v>-58039375</v>
+        <v>3513835</v>
       </c>
       <c r="G8" t="n">
-        <v>-76878717</v>
+        <v>3945241</v>
       </c>
       <c r="H8" t="n">
-        <v>-107868576</v>
+        <v>-58004499</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 27,414 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>14483986</v>
+        <v>-3416056</v>
       </c>
       <c r="E9" t="n">
-        <v>17327640</v>
+        <v>-5454087</v>
       </c>
       <c r="F9" t="n">
-        <v>-126512956</v>
+        <v>666124</v>
       </c>
       <c r="G9" t="n">
-        <v>-153926493</v>
+        <v>-3809801</v>
       </c>
       <c r="H9" t="n">
-        <v>-159593249</v>
+        <v>-95075926</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1321493</v>
+        <v>-32679559</v>
       </c>
       <c r="E10" t="n">
-        <v>1189163</v>
+        <v>-54791511</v>
       </c>
       <c r="F10" t="n">
-        <v>-14673803</v>
+        <v>-116850954</v>
       </c>
       <c r="G10" t="n">
-        <v>-17119142</v>
+        <v>-110433360</v>
       </c>
       <c r="H10" t="n">
-        <v>-33623598</v>
+        <v>39979900</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>2350282</v>
+        <v>-425062</v>
       </c>
       <c r="E11" t="n">
-        <v>3420434</v>
+        <v>-462401</v>
       </c>
       <c r="F11" t="n">
-        <v>3945241</v>
+        <v>-1026893</v>
       </c>
       <c r="G11" t="n">
-        <v>188850</v>
+        <v>212288</v>
       </c>
       <c r="H11" t="n">
-        <v>-57920276</v>
+        <v>13144149</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>藥華藥</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-54791511</v>
+        <v>-11144922</v>
       </c>
       <c r="E12" t="n">
-        <v>-30700231</v>
+        <v>-5172611</v>
       </c>
       <c r="F12" t="n">
-        <v>-110433360</v>
+        <v>20523941</v>
       </c>
       <c r="G12" t="n">
-        <v>-107069506</v>
+        <v>23855972</v>
       </c>
       <c r="H12" t="n">
-        <v>100154253</v>
+        <v>103750293</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>493607</v>
+        <v>-1555774</v>
       </c>
       <c r="E13" t="n">
-        <v>-143519</v>
+        <v>-1724118</v>
       </c>
       <c r="F13" t="n">
-        <v>-3842228</v>
+        <v>-3052042</v>
       </c>
       <c r="G13" t="n">
-        <v>-3658741</v>
+        <v>-3631393</v>
       </c>
       <c r="H13" t="n">
-        <v>-12789811</v>
+        <v>28867234</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>-462401</v>
+        <v>36406729</v>
       </c>
       <c r="E14" t="n">
-        <v>-2265526</v>
+        <v>27777846</v>
       </c>
       <c r="F14" t="n">
-        <v>212288</v>
+        <v>-51919871</v>
       </c>
       <c r="G14" t="n">
-        <v>592978</v>
+        <v>-58039375</v>
       </c>
       <c r="H14" t="n">
-        <v>13390118</v>
+        <v>-97366316</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>906365</v>
+        <v>16165122</v>
       </c>
       <c r="E15" t="n">
-        <v>658671</v>
+        <v>14483986</v>
       </c>
       <c r="F15" t="n">
-        <v>-3443596</v>
+        <v>-124552977</v>
       </c>
       <c r="G15" t="n">
-        <v>-3961623</v>
+        <v>-126512956</v>
       </c>
       <c r="H15" t="n">
-        <v>-11584777</v>
+        <v>-157559267</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,128 +968,163 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>-829896</v>
+        <v>780052</v>
       </c>
       <c r="E16" t="n">
-        <v>520676</v>
+        <v>493607</v>
       </c>
       <c r="F16" t="n">
-        <v>3416730</v>
+        <v>-3530328</v>
       </c>
       <c r="G16" t="n">
-        <v>3581160</v>
+        <v>-3842228</v>
       </c>
       <c r="H16" t="n">
-        <v>14646120</v>
+        <v>-12465909</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>華城</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -51,700 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>-66286992</v>
+        <v>-1229356</v>
       </c>
       <c r="E17" t="n">
-        <v>-34851569</v>
+        <v>-829896</v>
       </c>
       <c r="F17" t="n">
-        <v>-156280847</v>
+        <v>2451942</v>
       </c>
       <c r="G17" t="n">
-        <v>-104580988</v>
+        <v>3416730</v>
       </c>
       <c r="H17" t="n">
-        <v>-297750913</v>
+        <v>10113527</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>研華</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 13,328 千)</t>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>46767815</v>
+        <v>392326</v>
       </c>
       <c r="E18" t="n">
-        <v>56952446</v>
+        <v>-82653</v>
       </c>
       <c r="F18" t="n">
-        <v>12450611</v>
+        <v>-6447334</v>
       </c>
       <c r="G18" t="n">
-        <v>-877656</v>
+        <v>-5970577</v>
       </c>
       <c r="H18" t="n">
-        <v>55119611</v>
+        <v>-9426157</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -8,539 千)</t>
+          <t>📈 20d 巨變(加碼 11,205 千)</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-38545330</v>
+        <v>107258943</v>
       </c>
       <c r="E19" t="n">
-        <v>-16968839</v>
+        <v>152008990</v>
       </c>
       <c r="F19" t="n">
-        <v>-304557560</v>
+        <v>270623489</v>
       </c>
       <c r="G19" t="n">
-        <v>-296018253</v>
+        <v>259418967</v>
       </c>
       <c r="H19" t="n">
-        <v>-37593644</v>
+        <v>189654441</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>長榮航</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -17,365 千)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-15676808</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-14797420</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-5634084</v>
+      </c>
+      <c r="G20" t="n">
+        <v>11731050</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-13891033</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,26 +471,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 23,247 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
+        <v>36847565</v>
+      </c>
+      <c r="E2" t="n">
         <v>20996028</v>
       </c>
-      <c r="E2" t="n">
-        <v>-12948078</v>
-      </c>
       <c r="F2" t="n">
+        <v>-19537827</v>
+      </c>
+      <c r="G2" t="n">
         <v>-42784614</v>
       </c>
-      <c r="G2" t="n">
-        <v>-39660563</v>
-      </c>
       <c r="H2" t="n">
-        <v>53656940</v>
+        <v>50650717</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -501,280 +501,280 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 37,482 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>1138791</v>
+        <v>32006890</v>
       </c>
       <c r="E3" t="n">
-        <v>-3677368</v>
+        <v>2333417</v>
       </c>
       <c r="F3" t="n">
-        <v>-27874721</v>
+        <v>-143085688</v>
       </c>
       <c r="G3" t="n">
-        <v>-33736302</v>
+        <v>-180568140</v>
       </c>
       <c r="H3" t="n">
-        <v>-281094100</v>
+        <v>168089197</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -12,612 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1295541</v>
+        <v>-35645812</v>
       </c>
       <c r="E4" t="n">
-        <v>-1247477</v>
+        <v>-32679559</v>
       </c>
       <c r="F4" t="n">
-        <v>-14639579</v>
+        <v>-129462721</v>
       </c>
       <c r="G4" t="n">
-        <v>-14100767</v>
+        <v>-116850954</v>
       </c>
       <c r="H4" t="n">
-        <v>-24260885</v>
+        <v>26696567</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 24,705 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>2333417</v>
+        <v>31549663</v>
       </c>
       <c r="E5" t="n">
-        <v>1093149</v>
+        <v>25869313</v>
       </c>
       <c r="F5" t="n">
-        <v>-180568140</v>
+        <v>-103179516</v>
       </c>
       <c r="G5" t="n">
-        <v>-182543797</v>
+        <v>-127884666</v>
       </c>
       <c r="H5" t="n">
-        <v>246344438</v>
+        <v>-120861067</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 12,539 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -13,853 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>25869313</v>
+        <v>-4019279</v>
       </c>
       <c r="E6" t="n">
-        <v>12106283</v>
+        <v>-11144922</v>
       </c>
       <c r="F6" t="n">
-        <v>-127884666</v>
+        <v>6671386</v>
       </c>
       <c r="G6" t="n">
-        <v>-140423204</v>
+        <v>20523941</v>
       </c>
       <c r="H6" t="n">
-        <v>-103166190</v>
+        <v>73296312</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 9,381 千)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1572597</v>
+        <v>47075336</v>
       </c>
       <c r="E7" t="n">
-        <v>1321493</v>
+        <v>36406729</v>
       </c>
       <c r="F7" t="n">
-        <v>-14257695</v>
+        <v>-42538794</v>
       </c>
       <c r="G7" t="n">
-        <v>-14673803</v>
+        <v>-51919871</v>
       </c>
       <c r="H7" t="n">
-        <v>-32103756</v>
+        <v>-87047695</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 32,474 千)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>1301298</v>
+        <v>19982706</v>
       </c>
       <c r="E8" t="n">
-        <v>2350282</v>
+        <v>16165122</v>
       </c>
       <c r="F8" t="n">
-        <v>3513835</v>
+        <v>-92079320</v>
       </c>
       <c r="G8" t="n">
-        <v>3945241</v>
+        <v>-124552977</v>
       </c>
       <c r="H8" t="n">
-        <v>-58004499</v>
+        <v>-152317412</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-3416056</v>
+        <v>3038951</v>
       </c>
       <c r="E9" t="n">
-        <v>-5454087</v>
+        <v>1572597</v>
       </c>
       <c r="F9" t="n">
-        <v>666124</v>
+        <v>-9248178</v>
       </c>
       <c r="G9" t="n">
-        <v>-3809801</v>
+        <v>-14257695</v>
       </c>
       <c r="H9" t="n">
-        <v>-95075926</v>
+        <v>-28232437</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-32679559</v>
+        <v>742987</v>
       </c>
       <c r="E10" t="n">
-        <v>-54791511</v>
+        <v>1301298</v>
       </c>
       <c r="F10" t="n">
-        <v>-116850954</v>
+        <v>5144436</v>
       </c>
       <c r="G10" t="n">
-        <v>-110433360</v>
+        <v>3513835</v>
       </c>
       <c r="H10" t="n">
-        <v>39979900</v>
+        <v>-58227808</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
@@ -793,19 +793,19 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
+        <v>-1573369</v>
+      </c>
+      <c r="E11" t="n">
         <v>-425062</v>
       </c>
-      <c r="E11" t="n">
-        <v>-462401</v>
-      </c>
       <c r="F11" t="n">
+        <v>-1544274</v>
+      </c>
+      <c r="G11" t="n">
         <v>-1026893</v>
       </c>
-      <c r="G11" t="n">
-        <v>212288</v>
-      </c>
       <c r="H11" t="n">
-        <v>13144149</v>
+        <v>12452179</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -816,245 +816,245 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-11144922</v>
+        <v>13306078</v>
       </c>
       <c r="E12" t="n">
-        <v>-5172611</v>
+        <v>1138791</v>
       </c>
       <c r="F12" t="n">
-        <v>20523941</v>
+        <v>-23208296</v>
       </c>
       <c r="G12" t="n">
-        <v>23855972</v>
+        <v>-27874721</v>
       </c>
       <c r="H12" t="n">
-        <v>103750293</v>
+        <v>-292614102</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>-1555774</v>
+        <v>1281709</v>
       </c>
       <c r="E13" t="n">
-        <v>-1724118</v>
+        <v>1295541</v>
       </c>
       <c r="F13" t="n">
-        <v>-3052042</v>
+        <v>-15602475</v>
       </c>
       <c r="G13" t="n">
-        <v>-3631393</v>
+        <v>-14639579</v>
       </c>
       <c r="H13" t="n">
-        <v>28867234</v>
+        <v>-24708996</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>瑞昱</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>36406729</v>
+        <v>846615</v>
       </c>
       <c r="E14" t="n">
-        <v>27777846</v>
+        <v>780052</v>
       </c>
       <c r="F14" t="n">
-        <v>-51919871</v>
+        <v>-3117566</v>
       </c>
       <c r="G14" t="n">
-        <v>-58039375</v>
+        <v>-3530328</v>
       </c>
       <c r="H14" t="n">
-        <v>-97366316</v>
+        <v>-11837562</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>華城</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>16165122</v>
+        <v>-1330495</v>
       </c>
       <c r="E15" t="n">
-        <v>14483986</v>
+        <v>-1555774</v>
       </c>
       <c r="F15" t="n">
-        <v>-124552977</v>
+        <v>1683157</v>
       </c>
       <c r="G15" t="n">
-        <v>-126512956</v>
+        <v>-3052042</v>
       </c>
       <c r="H15" t="n">
-        <v>-157559267</v>
+        <v>28163475</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>780052</v>
+        <v>248997</v>
       </c>
       <c r="E16" t="n">
-        <v>493607</v>
+        <v>75468</v>
       </c>
       <c r="F16" t="n">
-        <v>-3530328</v>
+        <v>-5282371</v>
       </c>
       <c r="G16" t="n">
-        <v>-3842228</v>
+        <v>-4505132</v>
       </c>
       <c r="H16" t="n">
-        <v>-12465909</v>
+        <v>-3305633</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>崇越</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>-1229356</v>
+        <v>399177</v>
       </c>
       <c r="E17" t="n">
-        <v>-829896</v>
+        <v>392326</v>
       </c>
       <c r="F17" t="n">
-        <v>2451942</v>
+        <v>-5946447</v>
       </c>
       <c r="G17" t="n">
-        <v>3416730</v>
+        <v>-6447334</v>
       </c>
       <c r="H17" t="n">
-        <v>10113527</v>
+        <v>-7620895</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>📉 20d 巨變(減碼 -9,385 千)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>392326</v>
+        <v>-48522380</v>
       </c>
       <c r="E18" t="n">
-        <v>-82653</v>
+        <v>-65914318</v>
       </c>
       <c r="F18" t="n">
-        <v>-6447334</v>
+        <v>-162335042</v>
       </c>
       <c r="G18" t="n">
-        <v>-5970577</v>
+        <v>-152949673</v>
       </c>
       <c r="H18" t="n">
-        <v>-9426157</v>
+        <v>-290657832</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
@@ -1066,26 +1066,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 11,205 千)</t>
+          <t>📈 20d 巨變(加碼 22,902 千)</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
+        <v>81792214</v>
+      </c>
+      <c r="E19" t="n">
         <v>107258943</v>
       </c>
-      <c r="E19" t="n">
-        <v>152008990</v>
-      </c>
       <c r="F19" t="n">
+        <v>293525645</v>
+      </c>
+      <c r="G19" t="n">
         <v>270623489</v>
       </c>
-      <c r="G19" t="n">
-        <v>259418967</v>
-      </c>
       <c r="H19" t="n">
-        <v>189654441</v>
+        <v>223577243</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1096,35 +1096,105 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -17,365 千)</t>
+          <t>📈 20d 巨變(加碼 11,737 千)</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
+        <v>45125514</v>
+      </c>
+      <c r="E20" t="n">
+        <v>41842315</v>
+      </c>
+      <c r="F20" t="n">
+        <v>29987370</v>
+      </c>
+      <c r="G20" t="n">
+        <v>18250844</v>
+      </c>
+      <c r="H20" t="n">
+        <v>67587494</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>台灣大</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -16,596 千)</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-13421367</v>
+      </c>
+      <c r="E21" t="n">
         <v>-15676808</v>
       </c>
-      <c r="E20" t="n">
-        <v>-14797420</v>
-      </c>
-      <c r="F20" t="n">
+      <c r="F21" t="n">
+        <v>-22230493</v>
+      </c>
+      <c r="G21" t="n">
         <v>-5634084</v>
       </c>
-      <c r="G20" t="n">
-        <v>11731050</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-13891033</v>
-      </c>
-      <c r="I20" t="inlineStr">
+      <c r="H21" t="n">
+        <v>-13888884</v>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>日月光投控</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 97,058 千)</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-24323552</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-22263347</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-205760762</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-302819068</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-113255896</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>華邦電</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -466,252 +466,252 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 23,247 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 50,092 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>36847565</v>
+        <v>42806316</v>
       </c>
       <c r="E2" t="n">
-        <v>20996028</v>
+        <v>32006890</v>
       </c>
       <c r="F2" t="n">
-        <v>-19537827</v>
+        <v>-92994028</v>
       </c>
       <c r="G2" t="n">
-        <v>-42784614</v>
+        <v>-143085688</v>
       </c>
       <c r="H2" t="n">
-        <v>50650717</v>
+        <v>163815846</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 37,482 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>32006890</v>
+        <v>-2727596</v>
       </c>
       <c r="E3" t="n">
-        <v>2333417</v>
+        <v>742987</v>
       </c>
       <c r="F3" t="n">
-        <v>-143085688</v>
+        <v>2277538</v>
       </c>
       <c r="G3" t="n">
-        <v>-180568140</v>
+        <v>5144436</v>
       </c>
       <c r="H3" t="n">
-        <v>168089197</v>
+        <v>-61649287</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -12,612 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>-35645812</v>
+        <v>48876152</v>
       </c>
       <c r="E4" t="n">
-        <v>-32679559</v>
+        <v>36847565</v>
       </c>
       <c r="F4" t="n">
-        <v>-129462721</v>
+        <v>-12016572</v>
       </c>
       <c r="G4" t="n">
-        <v>-116850954</v>
+        <v>-19537827</v>
       </c>
       <c r="H4" t="n">
-        <v>26696567</v>
+        <v>47451706</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 24,705 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 31,346 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>31549663</v>
+        <v>-32704482</v>
       </c>
       <c r="E5" t="n">
-        <v>25869313</v>
+        <v>-35645812</v>
       </c>
       <c r="F5" t="n">
-        <v>-103179516</v>
+        <v>-98116422</v>
       </c>
       <c r="G5" t="n">
-        <v>-127884666</v>
+        <v>-129462721</v>
       </c>
       <c r="H5" t="n">
-        <v>-120861067</v>
+        <v>24132806</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -13,853 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 44,518 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>-4019279</v>
+        <v>53870330</v>
       </c>
       <c r="E6" t="n">
-        <v>-11144922</v>
+        <v>31549663</v>
       </c>
       <c r="F6" t="n">
-        <v>6671386</v>
+        <v>-58661993</v>
       </c>
       <c r="G6" t="n">
-        <v>20523941</v>
+        <v>-103179516</v>
       </c>
       <c r="H6" t="n">
-        <v>73296312</v>
+        <v>-97469419</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 9,381 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 31,251 千)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>47075336</v>
+        <v>24413902</v>
       </c>
       <c r="E7" t="n">
-        <v>36406729</v>
+        <v>19982706</v>
       </c>
       <c r="F7" t="n">
-        <v>-42538794</v>
+        <v>-60828045</v>
       </c>
       <c r="G7" t="n">
-        <v>-51919871</v>
+        <v>-92079320</v>
       </c>
       <c r="H7" t="n">
-        <v>-87047695</v>
+        <v>-146180089</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 32,474 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>19982706</v>
+        <v>2601765</v>
       </c>
       <c r="E8" t="n">
-        <v>16165122</v>
+        <v>3038951</v>
       </c>
       <c r="F8" t="n">
-        <v>-92079320</v>
+        <v>-5236890</v>
       </c>
       <c r="G8" t="n">
-        <v>-124552977</v>
+        <v>-9248178</v>
       </c>
       <c r="H8" t="n">
-        <v>-152317412</v>
+        <v>-27765380</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,100 +723,100 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>3038951</v>
+        <v>367602</v>
       </c>
       <c r="E9" t="n">
-        <v>1572597</v>
+        <v>-223751</v>
       </c>
       <c r="F9" t="n">
-        <v>-9248178</v>
+        <v>-6690947</v>
       </c>
       <c r="G9" t="n">
-        <v>-14257695</v>
+        <v>-5710295</v>
       </c>
       <c r="H9" t="n">
-        <v>-28232437</v>
+        <v>-10991116</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>亞力</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>742987</v>
+        <v>-1492119</v>
       </c>
       <c r="E10" t="n">
-        <v>1301298</v>
+        <v>-1573369</v>
       </c>
       <c r="F10" t="n">
-        <v>5144436</v>
+        <v>-1715881</v>
       </c>
       <c r="G10" t="n">
-        <v>3513835</v>
+        <v>-1544274</v>
       </c>
       <c r="H10" t="n">
-        <v>-58227808</v>
+        <v>11641457</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>藥華藥</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-1573369</v>
+        <v>15839161</v>
       </c>
       <c r="E11" t="n">
-        <v>-425062</v>
+        <v>13306078</v>
       </c>
       <c r="F11" t="n">
-        <v>-1544274</v>
+        <v>-20885087</v>
       </c>
       <c r="G11" t="n">
-        <v>-1026893</v>
+        <v>-23208296</v>
       </c>
       <c r="H11" t="n">
-        <v>12452179</v>
+        <v>-292874568</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,30 +828,30 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>13306078</v>
+        <v>755240</v>
       </c>
       <c r="E12" t="n">
-        <v>1138791</v>
+        <v>1281709</v>
       </c>
       <c r="F12" t="n">
-        <v>-23208296</v>
+        <v>-14695085</v>
       </c>
       <c r="G12" t="n">
-        <v>-27874721</v>
+        <v>-15602475</v>
       </c>
       <c r="H12" t="n">
-        <v>-292614102</v>
+        <v>-24962375</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>瑞昱</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,23 +863,23 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1281709</v>
+        <v>50239449</v>
       </c>
       <c r="E13" t="n">
-        <v>1295541</v>
+        <v>47075336</v>
       </c>
       <c r="F13" t="n">
-        <v>-15602475</v>
+        <v>-36385118</v>
       </c>
       <c r="G13" t="n">
-        <v>-14639579</v>
+        <v>-42538794</v>
       </c>
       <c r="H13" t="n">
-        <v>-24708996</v>
+        <v>-80843416</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
@@ -898,19 +898,19 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
+        <v>700258</v>
+      </c>
+      <c r="E14" t="n">
         <v>846615</v>
       </c>
-      <c r="E14" t="n">
-        <v>780052</v>
-      </c>
       <c r="F14" t="n">
+        <v>-2764171</v>
+      </c>
+      <c r="G14" t="n">
         <v>-3117566</v>
       </c>
-      <c r="G14" t="n">
-        <v>-3530328</v>
-      </c>
       <c r="H14" t="n">
-        <v>-11837562</v>
+        <v>-11659132</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,198 +933,198 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>-1330495</v>
+        <v>287047</v>
       </c>
       <c r="E15" t="n">
-        <v>-1555774</v>
+        <v>-445420</v>
       </c>
       <c r="F15" t="n">
-        <v>1683157</v>
+        <v>-2615442</v>
       </c>
       <c r="G15" t="n">
-        <v>-3052042</v>
+        <v>-3225851</v>
       </c>
       <c r="H15" t="n">
-        <v>28163475</v>
+        <v>-12176757</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>鈊象</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>248997</v>
+        <v>-1492797</v>
       </c>
       <c r="E16" t="n">
-        <v>75468</v>
+        <v>-1330495</v>
       </c>
       <c r="F16" t="n">
-        <v>-5282371</v>
+        <v>2838692</v>
       </c>
       <c r="G16" t="n">
-        <v>-4505132</v>
+        <v>1683157</v>
       </c>
       <c r="H16" t="n">
-        <v>-3305633</v>
+        <v>16751233</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>399177</v>
+        <v>498165</v>
       </c>
       <c r="E17" t="n">
-        <v>392326</v>
+        <v>510583</v>
       </c>
       <c r="F17" t="n">
-        <v>-5946447</v>
+        <v>-931870</v>
       </c>
       <c r="G17" t="n">
-        <v>-6447334</v>
+        <v>-1729337</v>
       </c>
       <c r="H17" t="n">
-        <v>-7620895</v>
+        <v>-10055941</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -9,385 千)</t>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>-48522380</v>
+        <v>398620</v>
       </c>
       <c r="E18" t="n">
-        <v>-65914318</v>
+        <v>248997</v>
       </c>
       <c r="F18" t="n">
-        <v>-162335042</v>
+        <v>-5249750</v>
       </c>
       <c r="G18" t="n">
-        <v>-152949673</v>
+        <v>-5282371</v>
       </c>
       <c r="H18" t="n">
-        <v>-290657832</v>
+        <v>-2991939</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>崇越</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 22,902 千)</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>81792214</v>
+        <v>9149</v>
       </c>
       <c r="E19" t="n">
-        <v>107258943</v>
+        <v>-4019279</v>
       </c>
       <c r="F19" t="n">
-        <v>293525645</v>
+        <v>11722240</v>
       </c>
       <c r="G19" t="n">
-        <v>270623489</v>
+        <v>6671386</v>
       </c>
       <c r="H19" t="n">
-        <v>223577243</v>
+        <v>62994024</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 11,737 千)</t>
+          <t>📉 20d 巨變(減碼 -8,006 千)</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>45125514</v>
+        <v>-10396971</v>
       </c>
       <c r="E20" t="n">
-        <v>41842315</v>
+        <v>-14754581</v>
       </c>
       <c r="F20" t="n">
-        <v>29987370</v>
+        <v>-8415536</v>
       </c>
       <c r="G20" t="n">
-        <v>18250844</v>
+        <v>-409667</v>
       </c>
       <c r="H20" t="n">
-        <v>67587494</v>
+        <v>-109566727</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
@@ -1136,26 +1136,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -16,596 千)</t>
+          <t>📉 20d 巨變(減碼 -9,692 千)</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
+        <v>-16574880</v>
+      </c>
+      <c r="E21" t="n">
         <v>-13421367</v>
       </c>
-      <c r="E21" t="n">
-        <v>-15676808</v>
-      </c>
       <c r="F21" t="n">
+        <v>-31922263</v>
+      </c>
+      <c r="G21" t="n">
         <v>-22230493</v>
       </c>
-      <c r="G21" t="n">
-        <v>-5634084</v>
-      </c>
       <c r="H21" t="n">
-        <v>-13888884</v>
+        <v>-11557093</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1171,26 +1171,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 97,058 千)</t>
+          <t>📈 20d 巨變(加碼 17,341 千)</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
+        <v>-47027717</v>
+      </c>
+      <c r="E22" t="n">
         <v>-24323552</v>
       </c>
-      <c r="E22" t="n">
-        <v>-22263347</v>
-      </c>
       <c r="F22" t="n">
+        <v>-188419534</v>
+      </c>
+      <c r="G22" t="n">
         <v>-205760762</v>
       </c>
-      <c r="G22" t="n">
-        <v>-302819068</v>
-      </c>
       <c r="H22" t="n">
-        <v>-113255896</v>
+        <v>-155592726</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,26 +471,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 50,092 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 35,746 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
+        <v>59862429</v>
+      </c>
+      <c r="E2" t="n">
         <v>42806316</v>
       </c>
-      <c r="E2" t="n">
-        <v>32006890</v>
-      </c>
       <c r="F2" t="n">
+        <v>-57248372</v>
+      </c>
+      <c r="G2" t="n">
         <v>-92994028</v>
       </c>
-      <c r="G2" t="n">
-        <v>-143085688</v>
-      </c>
       <c r="H2" t="n">
-        <v>163815846</v>
+        <v>157481018</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -506,26 +506,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="n">
+        <v>-5373755</v>
+      </c>
+      <c r="E3" t="n">
         <v>-2727596</v>
       </c>
-      <c r="E3" t="n">
-        <v>742987</v>
-      </c>
       <c r="F3" t="n">
+        <v>241515</v>
+      </c>
+      <c r="G3" t="n">
         <v>2277538</v>
       </c>
-      <c r="G3" t="n">
-        <v>5144436</v>
-      </c>
       <c r="H3" t="n">
-        <v>-61649287</v>
+        <v>-65074175</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -548,19 +548,19 @@
         <v>7</v>
       </c>
       <c r="D4" t="n">
+        <v>47008167</v>
+      </c>
+      <c r="E4" t="n">
         <v>48876152</v>
       </c>
-      <c r="E4" t="n">
-        <v>36847565</v>
-      </c>
       <c r="F4" t="n">
+        <v>-7525011</v>
+      </c>
+      <c r="G4" t="n">
         <v>-12016572</v>
       </c>
-      <c r="G4" t="n">
-        <v>-19537827</v>
-      </c>
       <c r="H4" t="n">
-        <v>47451706</v>
+        <v>45691150</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -576,26 +576,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 31,346 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 20,821 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
+        <v>-10194554</v>
+      </c>
+      <c r="E5" t="n">
         <v>-32704482</v>
       </c>
-      <c r="E5" t="n">
-        <v>-35645812</v>
-      </c>
       <c r="F5" t="n">
+        <v>-77295887</v>
+      </c>
+      <c r="G5" t="n">
         <v>-98116422</v>
       </c>
-      <c r="G5" t="n">
-        <v>-129462721</v>
-      </c>
       <c r="H5" t="n">
-        <v>24132806</v>
+        <v>29008487</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -611,26 +611,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 44,518 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 94,343 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>6</v>
       </c>
       <c r="D6" t="n">
+        <v>122234059</v>
+      </c>
+      <c r="E6" t="n">
         <v>53870330</v>
       </c>
-      <c r="E6" t="n">
-        <v>31549663</v>
-      </c>
       <c r="F6" t="n">
+        <v>35681356</v>
+      </c>
+      <c r="G6" t="n">
         <v>-58661993</v>
       </c>
-      <c r="G6" t="n">
-        <v>-103179516</v>
-      </c>
       <c r="H6" t="n">
-        <v>-97469419</v>
+        <v>-25896856</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -646,26 +646,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 31,251 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 24,428 千)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
+        <v>20372409</v>
+      </c>
+      <c r="E7" t="n">
         <v>24413902</v>
       </c>
-      <c r="E7" t="n">
-        <v>19982706</v>
-      </c>
       <c r="F7" t="n">
+        <v>-36399947</v>
+      </c>
+      <c r="G7" t="n">
         <v>-60828045</v>
       </c>
-      <c r="G7" t="n">
-        <v>-92079320</v>
-      </c>
       <c r="H7" t="n">
-        <v>-146180089</v>
+        <v>-142649098</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -676,42 +676,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>2601765</v>
+        <v>-134062</v>
       </c>
       <c r="E8" t="n">
-        <v>3038951</v>
+        <v>-1492119</v>
       </c>
       <c r="F8" t="n">
-        <v>-5236890</v>
+        <v>-1584903</v>
       </c>
       <c r="G8" t="n">
-        <v>-9248178</v>
+        <v>-1715881</v>
       </c>
       <c r="H8" t="n">
-        <v>-27765380</v>
+        <v>10532278</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>藥華藥</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,30 +723,30 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>367602</v>
+        <v>12102538</v>
       </c>
       <c r="E9" t="n">
-        <v>-223751</v>
+        <v>15839161</v>
       </c>
       <c r="F9" t="n">
-        <v>-6690947</v>
+        <v>-19716462</v>
       </c>
       <c r="G9" t="n">
-        <v>-5710295</v>
+        <v>-20885087</v>
       </c>
       <c r="H9" t="n">
-        <v>-10991116</v>
+        <v>-295758390</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,30 +758,30 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-1492119</v>
+        <v>800344</v>
       </c>
       <c r="E10" t="n">
-        <v>-1573369</v>
+        <v>675429</v>
       </c>
       <c r="F10" t="n">
-        <v>-1715881</v>
+        <v>-162344</v>
       </c>
       <c r="G10" t="n">
-        <v>-1544274</v>
+        <v>651875</v>
       </c>
       <c r="H10" t="n">
-        <v>11641457</v>
+        <v>11514219</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>智易</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,30 +793,30 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>15839161</v>
+        <v>40278577</v>
       </c>
       <c r="E11" t="n">
-        <v>13306078</v>
+        <v>50239449</v>
       </c>
       <c r="F11" t="n">
-        <v>-20885087</v>
+        <v>-28624781</v>
       </c>
       <c r="G11" t="n">
-        <v>-23208296</v>
+        <v>-36385118</v>
       </c>
       <c r="H11" t="n">
-        <v>-292874568</v>
+        <v>-76160741</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,58 +828,58 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>755240</v>
+        <v>958753</v>
       </c>
       <c r="E12" t="n">
-        <v>1281709</v>
+        <v>-231311</v>
       </c>
       <c r="F12" t="n">
-        <v>-14695085</v>
+        <v>-7984644</v>
       </c>
       <c r="G12" t="n">
-        <v>-15602475</v>
+        <v>-11189609</v>
       </c>
       <c r="H12" t="n">
-        <v>-24962375</v>
+        <v>-13258346</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>50239449</v>
+        <v>2488067</v>
       </c>
       <c r="E13" t="n">
-        <v>47075336</v>
+        <v>2601765</v>
       </c>
       <c r="F13" t="n">
-        <v>-36385118</v>
+        <v>-2414846</v>
       </c>
       <c r="G13" t="n">
-        <v>-42538794</v>
+        <v>-5236890</v>
       </c>
       <c r="H13" t="n">
-        <v>-80843416</v>
+        <v>-26551035</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
@@ -898,19 +898,19 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
+        <v>1060236</v>
+      </c>
+      <c r="E14" t="n">
         <v>700258</v>
       </c>
-      <c r="E14" t="n">
-        <v>846615</v>
-      </c>
       <c r="F14" t="n">
+        <v>-1904778</v>
+      </c>
+      <c r="G14" t="n">
         <v>-2764171</v>
       </c>
-      <c r="G14" t="n">
-        <v>-3117566</v>
-      </c>
       <c r="H14" t="n">
-        <v>-11659132</v>
+        <v>-11471417</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,30 +933,30 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>287047</v>
+        <v>825214</v>
       </c>
       <c r="E15" t="n">
-        <v>-445420</v>
+        <v>367602</v>
       </c>
       <c r="F15" t="n">
-        <v>-2615442</v>
+        <v>-4811427</v>
       </c>
       <c r="G15" t="n">
-        <v>-3225851</v>
+        <v>-6690947</v>
       </c>
       <c r="H15" t="n">
-        <v>-12176757</v>
+        <v>-10171862</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>亞力</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,231 +968,161 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>-1492797</v>
+        <v>493484</v>
       </c>
       <c r="E16" t="n">
-        <v>-1330495</v>
+        <v>287047</v>
       </c>
       <c r="F16" t="n">
-        <v>2838692</v>
+        <v>-2401851</v>
       </c>
       <c r="G16" t="n">
-        <v>1683157</v>
+        <v>-2615442</v>
       </c>
       <c r="H16" t="n">
-        <v>16751233</v>
+        <v>-12361899</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>鈊象</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>498165</v>
+        <v>643796</v>
       </c>
       <c r="E17" t="n">
-        <v>510583</v>
+        <v>-1492797</v>
       </c>
       <c r="F17" t="n">
-        <v>-931870</v>
+        <v>2292746</v>
       </c>
       <c r="G17" t="n">
-        <v>-1729337</v>
+        <v>2838692</v>
       </c>
       <c r="H17" t="n">
-        <v>-10055941</v>
+        <v>15608943</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>📈 20d 巨變(加碼 33,836 千)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>398620</v>
+        <v>-49033372</v>
       </c>
       <c r="E18" t="n">
-        <v>248997</v>
+        <v>-48633678</v>
       </c>
       <c r="F18" t="n">
-        <v>-5249750</v>
+        <v>-129311579</v>
       </c>
       <c r="G18" t="n">
-        <v>-5282371</v>
+        <v>-163147323</v>
       </c>
       <c r="H18" t="n">
-        <v>-2991939</v>
+        <v>-301838210</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>📉 20d 巨變(減碼 -20,267 千)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>9149</v>
+        <v>66794202</v>
       </c>
       <c r="E19" t="n">
-        <v>-4019279</v>
+        <v>69613636</v>
       </c>
       <c r="F19" t="n">
-        <v>11722240</v>
+        <v>278517956</v>
       </c>
       <c r="G19" t="n">
-        <v>6671386</v>
+        <v>298784549</v>
       </c>
       <c r="H19" t="n">
-        <v>62994024</v>
+        <v>235666312</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -8,006 千)</t>
+          <t>📈 20d 巨變(加碼 67,344 千)</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-10396971</v>
+        <v>-23988142</v>
       </c>
       <c r="E20" t="n">
-        <v>-14754581</v>
+        <v>-47027717</v>
       </c>
       <c r="F20" t="n">
-        <v>-8415536</v>
+        <v>-121076028</v>
       </c>
       <c r="G20" t="n">
-        <v>-409667</v>
+        <v>-188419534</v>
       </c>
       <c r="H20" t="n">
-        <v>-109566727</v>
+        <v>-124426633</v>
       </c>
       <c r="I20" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -9,692 千)</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>-16574880</v>
-      </c>
-      <c r="E21" t="n">
-        <v>-13421367</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-31922263</v>
-      </c>
-      <c r="G21" t="n">
-        <v>-22230493</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-11557093</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 17,341 千)</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="n">
-        <v>-47027717</v>
-      </c>
-      <c r="E22" t="n">
-        <v>-24323552</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-188419534</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-205760762</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-155592726</v>
-      </c>
-      <c r="I22" t="inlineStr">
         <is>
           <t>華邦電</t>
         </is>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,77 +466,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 35,746 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 19,250 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>59862429</v>
+        <v>6718299</v>
       </c>
       <c r="E2" t="n">
-        <v>42806316</v>
+        <v>-23988142</v>
       </c>
       <c r="F2" t="n">
-        <v>-57248372</v>
+        <v>-101826254</v>
       </c>
       <c r="G2" t="n">
-        <v>-92994028</v>
+        <v>-121076028</v>
       </c>
       <c r="H2" t="n">
-        <v>157481018</v>
+        <v>-122096310</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>-5373755</v>
+        <v>42641906</v>
       </c>
       <c r="E3" t="n">
-        <v>-2727596</v>
+        <v>47008167</v>
       </c>
       <c r="F3" t="n">
-        <v>241515</v>
+        <v>-6494887</v>
       </c>
       <c r="G3" t="n">
-        <v>2277538</v>
+        <v>-7525011</v>
       </c>
       <c r="H3" t="n">
-        <v>-65074175</v>
+        <v>49456885</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,240 +548,240 @@
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>47008167</v>
+        <v>58615732</v>
       </c>
       <c r="E4" t="n">
-        <v>48876152</v>
+        <v>59862429</v>
       </c>
       <c r="F4" t="n">
-        <v>-7525011</v>
+        <v>-60131532</v>
       </c>
       <c r="G4" t="n">
-        <v>-12016572</v>
+        <v>-57248372</v>
       </c>
       <c r="H4" t="n">
-        <v>45691150</v>
+        <v>151966086</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 20,821 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 20,441 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>-10194554</v>
+        <v>25017882</v>
       </c>
       <c r="E5" t="n">
-        <v>-32704482</v>
+        <v>20372409</v>
       </c>
       <c r="F5" t="n">
-        <v>-77295887</v>
+        <v>-15959076</v>
       </c>
       <c r="G5" t="n">
-        <v>-98116422</v>
+        <v>-36399947</v>
       </c>
       <c r="H5" t="n">
-        <v>29008487</v>
+        <v>-135267044</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 94,343 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>122234059</v>
+        <v>-14879417</v>
       </c>
       <c r="E6" t="n">
-        <v>53870330</v>
+        <v>-10194554</v>
       </c>
       <c r="F6" t="n">
-        <v>35681356</v>
+        <v>-80396345</v>
       </c>
       <c r="G6" t="n">
-        <v>-58661993</v>
+        <v>-77295887</v>
       </c>
       <c r="H6" t="n">
-        <v>-25896856</v>
+        <v>15662344</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 24,428 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>20372409</v>
+        <v>-832489</v>
       </c>
       <c r="E7" t="n">
-        <v>24413902</v>
+        <v>-134062</v>
       </c>
       <c r="F7" t="n">
-        <v>-36399947</v>
+        <v>-2121654</v>
       </c>
       <c r="G7" t="n">
-        <v>-60828045</v>
+        <v>-1584903</v>
       </c>
       <c r="H7" t="n">
-        <v>-142649098</v>
+        <v>10339718</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>藥華藥</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-134062</v>
+        <v>6258334</v>
       </c>
       <c r="E8" t="n">
-        <v>-1492119</v>
+        <v>12102538</v>
       </c>
       <c r="F8" t="n">
-        <v>-1584903</v>
+        <v>-15514647</v>
       </c>
       <c r="G8" t="n">
-        <v>-1715881</v>
+        <v>-19716462</v>
       </c>
       <c r="H8" t="n">
-        <v>10532278</v>
+        <v>-297147170</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>12102538</v>
+        <v>843334</v>
       </c>
       <c r="E9" t="n">
-        <v>15839161</v>
+        <v>800344</v>
       </c>
       <c r="F9" t="n">
-        <v>-19716462</v>
+        <v>-854073</v>
       </c>
       <c r="G9" t="n">
-        <v>-20885087</v>
+        <v>-162344</v>
       </c>
       <c r="H9" t="n">
-        <v>-295758390</v>
+        <v>11526519</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>智易</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>800344</v>
+        <v>30004029</v>
       </c>
       <c r="E10" t="n">
-        <v>675429</v>
+        <v>40278577</v>
       </c>
       <c r="F10" t="n">
-        <v>-162344</v>
+        <v>-21956841</v>
       </c>
       <c r="G10" t="n">
-        <v>651875</v>
+        <v>-28624781</v>
       </c>
       <c r="H10" t="n">
-        <v>11514219</v>
+        <v>-69396413</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,65 +793,65 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>40278577</v>
+        <v>505195</v>
       </c>
       <c r="E11" t="n">
-        <v>50239449</v>
+        <v>958753</v>
       </c>
       <c r="F11" t="n">
-        <v>-28624781</v>
+        <v>-10095214</v>
       </c>
       <c r="G11" t="n">
-        <v>-36385118</v>
+        <v>-7984644</v>
       </c>
       <c r="H11" t="n">
-        <v>-76160741</v>
+        <v>-14006368</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>958753</v>
+        <v>1269474</v>
       </c>
       <c r="E12" t="n">
-        <v>-231311</v>
+        <v>2488067</v>
       </c>
       <c r="F12" t="n">
-        <v>-7984644</v>
+        <v>-1930817</v>
       </c>
       <c r="G12" t="n">
-        <v>-11189609</v>
+        <v>-2414846</v>
       </c>
       <c r="H12" t="n">
-        <v>-13258346</v>
+        <v>-27158283</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,30 +863,30 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>2488067</v>
+        <v>757937</v>
       </c>
       <c r="E13" t="n">
-        <v>2601765</v>
+        <v>1060236</v>
       </c>
       <c r="F13" t="n">
-        <v>-2414846</v>
+        <v>-1639666</v>
       </c>
       <c r="G13" t="n">
-        <v>-5236890</v>
+        <v>-1904778</v>
       </c>
       <c r="H13" t="n">
-        <v>-26551035</v>
+        <v>-11571450</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>華城</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,233 +898,93 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>1060236</v>
+        <v>699086</v>
       </c>
       <c r="E14" t="n">
-        <v>700258</v>
+        <v>493484</v>
       </c>
       <c r="F14" t="n">
-        <v>-1904778</v>
+        <v>-2166092</v>
       </c>
       <c r="G14" t="n">
-        <v>-2764171</v>
+        <v>-2401851</v>
       </c>
       <c r="H14" t="n">
-        <v>-11471417</v>
+        <v>-12312829</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>鈊象</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>825214</v>
+        <v>-2503286</v>
       </c>
       <c r="E15" t="n">
-        <v>367602</v>
+        <v>441995</v>
       </c>
       <c r="F15" t="n">
-        <v>-4811427</v>
+        <v>-1634620</v>
       </c>
       <c r="G15" t="n">
-        <v>-6690947</v>
+        <v>1117958</v>
       </c>
       <c r="H15" t="n">
-        <v>-10171862</v>
+        <v>-19272</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>聯亞</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>📈 20d 巨變(加碼 46,115 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>493484</v>
+        <v>154948461</v>
       </c>
       <c r="E16" t="n">
-        <v>287047</v>
+        <v>122234059</v>
       </c>
       <c r="F16" t="n">
-        <v>-2401851</v>
+        <v>81796427</v>
       </c>
       <c r="G16" t="n">
-        <v>-2615442</v>
+        <v>35681356</v>
       </c>
       <c r="H16" t="n">
-        <v>-12361899</v>
+        <v>6538234</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>鈊象</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>6285</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>🟢 5d 翻綠</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" t="n">
-        <v>643796</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-1492797</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2292746</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2838692</v>
-      </c>
-      <c r="H17" t="n">
-        <v>15608943</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>啟碁</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 33,836 千)</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>-49033372</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-48633678</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-129311579</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-163147323</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-301838210</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -20,267 千)</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>66794202</v>
-      </c>
-      <c r="E19" t="n">
-        <v>69613636</v>
-      </c>
-      <c r="F19" t="n">
-        <v>278517956</v>
-      </c>
-      <c r="G19" t="n">
-        <v>298784549</v>
-      </c>
-      <c r="H19" t="n">
-        <v>235666312</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>長榮航</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 67,344 千)</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>-23988142</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-47027717</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-121076028</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-188419534</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-124426633</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>華邦電</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,77 +466,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 19,250 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 11,889 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>6718299</v>
+        <v>-4478938</v>
       </c>
       <c r="E2" t="n">
-        <v>-23988142</v>
+        <v>-4298328</v>
       </c>
       <c r="F2" t="n">
-        <v>-101826254</v>
+        <v>10674952</v>
       </c>
       <c r="G2" t="n">
-        <v>-121076028</v>
+        <v>-1214281</v>
       </c>
       <c r="H2" t="n">
-        <v>-122096310</v>
+        <v>-93981358</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 30,850 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>42641906</v>
+        <v>59077327</v>
       </c>
       <c r="E3" t="n">
-        <v>47008167</v>
+        <v>58615732</v>
       </c>
       <c r="F3" t="n">
-        <v>-6494887</v>
+        <v>-29281311</v>
       </c>
       <c r="G3" t="n">
-        <v>-7525011</v>
+        <v>-60131532</v>
       </c>
       <c r="H3" t="n">
-        <v>49456885</v>
+        <v>111398643</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,275 +548,275 @@
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>58615732</v>
+        <v>33827124</v>
       </c>
       <c r="E4" t="n">
-        <v>59862429</v>
+        <v>42641906</v>
       </c>
       <c r="F4" t="n">
-        <v>-60131532</v>
+        <v>-3028444</v>
       </c>
       <c r="G4" t="n">
-        <v>-57248372</v>
+        <v>-6494887</v>
       </c>
       <c r="H4" t="n">
-        <v>151966086</v>
+        <v>53166943</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 20,441 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 21,667 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>25017882</v>
+        <v>35147578</v>
       </c>
       <c r="E5" t="n">
-        <v>20372409</v>
+        <v>30004029</v>
       </c>
       <c r="F5" t="n">
-        <v>-15959076</v>
+        <v>-289435</v>
       </c>
       <c r="G5" t="n">
-        <v>-36399947</v>
+        <v>-21956841</v>
       </c>
       <c r="H5" t="n">
-        <v>-135267044</v>
+        <v>-51440077</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 10,318 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>-14879417</v>
+        <v>28847498</v>
       </c>
       <c r="E6" t="n">
-        <v>-10194554</v>
+        <v>25017882</v>
       </c>
       <c r="F6" t="n">
-        <v>-80396345</v>
+        <v>-5640615</v>
       </c>
       <c r="G6" t="n">
-        <v>-77295887</v>
+        <v>-15959076</v>
       </c>
       <c r="H6" t="n">
-        <v>15662344</v>
+        <v>-129409389</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-832489</v>
+        <v>222371</v>
       </c>
       <c r="E7" t="n">
-        <v>-134062</v>
+        <v>1269474</v>
       </c>
       <c r="F7" t="n">
-        <v>-2121654</v>
+        <v>306310</v>
       </c>
       <c r="G7" t="n">
-        <v>-1584903</v>
+        <v>-1930817</v>
       </c>
       <c r="H7" t="n">
-        <v>10339718</v>
+        <v>-27220224</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>6258334</v>
+        <v>-936915</v>
       </c>
       <c r="E8" t="n">
-        <v>12102538</v>
+        <v>-832489</v>
       </c>
       <c r="F8" t="n">
-        <v>-15514647</v>
+        <v>-2652351</v>
       </c>
       <c r="G8" t="n">
-        <v>-19716462</v>
+        <v>-2121654</v>
       </c>
       <c r="H8" t="n">
-        <v>-297147170</v>
+        <v>10236894</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>藥華藥</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>843334</v>
+        <v>-1207595</v>
       </c>
       <c r="E9" t="n">
-        <v>800344</v>
+        <v>1507006</v>
       </c>
       <c r="F9" t="n">
-        <v>-854073</v>
+        <v>5371007</v>
       </c>
       <c r="G9" t="n">
-        <v>-162344</v>
+        <v>6921755</v>
       </c>
       <c r="H9" t="n">
-        <v>11526519</v>
+        <v>4853901</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>台燿</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>30004029</v>
+        <v>872208</v>
       </c>
       <c r="E10" t="n">
-        <v>40278577</v>
+        <v>757937</v>
       </c>
       <c r="F10" t="n">
-        <v>-21956841</v>
+        <v>-1165385</v>
       </c>
       <c r="G10" t="n">
-        <v>-28624781</v>
+        <v>-1639666</v>
       </c>
       <c r="H10" t="n">
-        <v>-69396413</v>
+        <v>-11130558</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>華城</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>505195</v>
+        <v>53848</v>
       </c>
       <c r="E11" t="n">
-        <v>958753</v>
+        <v>-107633</v>
       </c>
       <c r="F11" t="n">
-        <v>-10095214</v>
+        <v>-2995301</v>
       </c>
       <c r="G11" t="n">
-        <v>-7984644</v>
+        <v>-3309949</v>
       </c>
       <c r="H11" t="n">
-        <v>-14006368</v>
+        <v>-10128724</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>亞力</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,100 +828,100 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>1269474</v>
+        <v>808634</v>
       </c>
       <c r="E12" t="n">
-        <v>2488067</v>
+        <v>699086</v>
       </c>
       <c r="F12" t="n">
-        <v>-1930817</v>
+        <v>-1601382</v>
       </c>
       <c r="G12" t="n">
-        <v>-2414846</v>
+        <v>-2166092</v>
       </c>
       <c r="H12" t="n">
-        <v>-27158283</v>
+        <v>-12254296</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>鈊象</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>757937</v>
+        <v>-890763</v>
       </c>
       <c r="E13" t="n">
-        <v>1060236</v>
+        <v>1697839</v>
       </c>
       <c r="F13" t="n">
-        <v>-1639666</v>
+        <v>1365199</v>
       </c>
       <c r="G13" t="n">
-        <v>-1904778</v>
+        <v>2227745</v>
       </c>
       <c r="H13" t="n">
-        <v>-11571450</v>
+        <v>-3447384</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>立隆電</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>699086</v>
+        <v>-2307716</v>
       </c>
       <c r="E14" t="n">
-        <v>493484</v>
+        <v>6258334</v>
       </c>
       <c r="F14" t="n">
-        <v>-2166092</v>
+        <v>-17569127</v>
       </c>
       <c r="G14" t="n">
-        <v>-2401851</v>
+        <v>-15514647</v>
       </c>
       <c r="H14" t="n">
-        <v>-12312829</v>
+        <v>-304326354</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,56 +933,161 @@
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>-2503286</v>
+        <v>-6523550</v>
       </c>
       <c r="E15" t="n">
-        <v>441995</v>
+        <v>6718299</v>
       </c>
       <c r="F15" t="n">
-        <v>-1634620</v>
+        <v>-94000920</v>
       </c>
       <c r="G15" t="n">
-        <v>1117958</v>
+        <v>-101826254</v>
       </c>
       <c r="H15" t="n">
-        <v>-19272</v>
+        <v>-177632874</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 46,115 千)</t>
+          <t>📈 20d 巨變(加碼 11,619 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
+        <v>-15475640</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-14486014</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-121225112</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-132844513</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-287145600</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 11,926 千)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>72178224</v>
+      </c>
+      <c r="E17" t="n">
+        <v>66398587</v>
+      </c>
+      <c r="F17" t="n">
+        <v>293233955</v>
+      </c>
+      <c r="G17" t="n">
+        <v>281307605</v>
+      </c>
+      <c r="H17" t="n">
+        <v>280824107</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>長榮航</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3045</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 9,881 千)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>35309253</v>
+      </c>
+      <c r="E18" t="n">
+        <v>33261649</v>
+      </c>
+      <c r="F18" t="n">
+        <v>48205910</v>
+      </c>
+      <c r="G18" t="n">
+        <v>38325281</v>
+      </c>
+      <c r="H18" t="n">
+        <v>87328162</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>台灣大</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 26,001 千)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>147439824</v>
+      </c>
+      <c r="E19" t="n">
         <v>154948461</v>
       </c>
-      <c r="E16" t="n">
-        <v>122234059</v>
-      </c>
-      <c r="F16" t="n">
+      <c r="F19" t="n">
+        <v>107797837</v>
+      </c>
+      <c r="G19" t="n">
         <v>81796427</v>
       </c>
-      <c r="G16" t="n">
-        <v>35681356</v>
-      </c>
-      <c r="H16" t="n">
-        <v>6538234</v>
-      </c>
-      <c r="I16" t="inlineStr">
+      <c r="H19" t="n">
+        <v>43406979</v>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>緯創</t>
         </is>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,287 +466,287 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 11,889 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -11,434 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-4478938</v>
+        <v>-2305632</v>
       </c>
       <c r="E2" t="n">
-        <v>-4298328</v>
+        <v>7913964</v>
       </c>
       <c r="F2" t="n">
-        <v>10674952</v>
+        <v>12808418</v>
       </c>
       <c r="G2" t="n">
-        <v>-1214281</v>
+        <v>24242107</v>
       </c>
       <c r="H2" t="n">
-        <v>-93981358</v>
+        <v>20237286</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 30,850 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>59077327</v>
+        <v>-2044719</v>
       </c>
       <c r="E3" t="n">
-        <v>58615732</v>
+        <v>222371</v>
       </c>
       <c r="F3" t="n">
-        <v>-29281311</v>
+        <v>320874</v>
       </c>
       <c r="G3" t="n">
-        <v>-60131532</v>
+        <v>306310</v>
       </c>
       <c r="H3" t="n">
-        <v>111398643</v>
+        <v>-28248549</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>33827124</v>
+        <v>1300977</v>
       </c>
       <c r="E4" t="n">
-        <v>42641906</v>
+        <v>-4478938</v>
       </c>
       <c r="F4" t="n">
-        <v>-3028444</v>
+        <v>6568917</v>
       </c>
       <c r="G4" t="n">
-        <v>-6494887</v>
+        <v>10674952</v>
       </c>
       <c r="H4" t="n">
-        <v>53166943</v>
+        <v>-89941901</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 21,667 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>35147578</v>
+        <v>16355614</v>
       </c>
       <c r="E5" t="n">
-        <v>30004029</v>
+        <v>59077327</v>
       </c>
       <c r="F5" t="n">
-        <v>-289435</v>
+        <v>-29022786</v>
       </c>
       <c r="G5" t="n">
-        <v>-21956841</v>
+        <v>-29281311</v>
       </c>
       <c r="H5" t="n">
-        <v>-51440077</v>
+        <v>69743792</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 10,318 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 19,200 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>28847498</v>
+        <v>36489566</v>
       </c>
       <c r="E6" t="n">
-        <v>25017882</v>
+        <v>35147578</v>
       </c>
       <c r="F6" t="n">
-        <v>-5640615</v>
+        <v>18910606</v>
       </c>
       <c r="G6" t="n">
-        <v>-15959076</v>
+        <v>-289435</v>
       </c>
       <c r="H6" t="n">
-        <v>-129409389</v>
+        <v>-47659482</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 12,271 千)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>222371</v>
+        <v>27808773</v>
       </c>
       <c r="E7" t="n">
-        <v>1269474</v>
+        <v>28847498</v>
       </c>
       <c r="F7" t="n">
-        <v>306310</v>
+        <v>6630274</v>
       </c>
       <c r="G7" t="n">
-        <v>-1930817</v>
+        <v>-5640615</v>
       </c>
       <c r="H7" t="n">
-        <v>-27220224</v>
+        <v>-126191628</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>-936915</v>
+        <v>441148</v>
       </c>
       <c r="E8" t="n">
-        <v>-832489</v>
+        <v>872208</v>
       </c>
       <c r="F8" t="n">
-        <v>-2652351</v>
+        <v>-1242823</v>
       </c>
       <c r="G8" t="n">
-        <v>-2121654</v>
+        <v>-1165385</v>
       </c>
       <c r="H8" t="n">
-        <v>10236894</v>
+        <v>-10293425</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>華城</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>-1207595</v>
+        <v>1044568</v>
       </c>
       <c r="E9" t="n">
-        <v>1507006</v>
+        <v>808634</v>
       </c>
       <c r="F9" t="n">
-        <v>5371007</v>
+        <v>-1273037</v>
       </c>
       <c r="G9" t="n">
-        <v>6921755</v>
+        <v>-1601382</v>
       </c>
       <c r="H9" t="n">
-        <v>4853901</v>
+        <v>-11247890</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>鈊象</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,336 +758,161 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>872208</v>
+        <v>24860472</v>
       </c>
       <c r="E10" t="n">
-        <v>757937</v>
+        <v>33827124</v>
       </c>
       <c r="F10" t="n">
-        <v>-1165385</v>
+        <v>1702047</v>
       </c>
       <c r="G10" t="n">
-        <v>-1639666</v>
+        <v>-3028444</v>
       </c>
       <c r="H10" t="n">
-        <v>-11130558</v>
+        <v>-5014951</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>📉 20d 巨變(減碼 -12,747 千)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>53848</v>
+        <v>-35110701</v>
       </c>
       <c r="E11" t="n">
-        <v>-107633</v>
+        <v>-15475640</v>
       </c>
       <c r="F11" t="n">
-        <v>-2995301</v>
+        <v>-133971954</v>
       </c>
       <c r="G11" t="n">
-        <v>-3309949</v>
+        <v>-121225112</v>
       </c>
       <c r="H11" t="n">
-        <v>-10128724</v>
+        <v>-289833960</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>📈 20d 巨變(加碼 40,301 千)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>808634</v>
+        <v>86695556</v>
       </c>
       <c r="E12" t="n">
-        <v>699086</v>
+        <v>72178224</v>
       </c>
       <c r="F12" t="n">
-        <v>-1601382</v>
+        <v>333534595</v>
       </c>
       <c r="G12" t="n">
-        <v>-2166092</v>
+        <v>293233955</v>
       </c>
       <c r="H12" t="n">
-        <v>-12254296</v>
+        <v>320923496</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>📈 20d 巨變(加碼 11,005 千)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-890763</v>
+        <v>30303520</v>
       </c>
       <c r="E13" t="n">
-        <v>1697839</v>
+        <v>35309253</v>
       </c>
       <c r="F13" t="n">
-        <v>1365199</v>
+        <v>59210708</v>
       </c>
       <c r="G13" t="n">
-        <v>2227745</v>
+        <v>48205910</v>
       </c>
       <c r="H13" t="n">
-        <v>-3447384</v>
+        <v>89770857</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>📈 20d 巨變(加碼 8,806 千)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2307716</v>
+        <v>141134859</v>
       </c>
       <c r="E14" t="n">
-        <v>6258334</v>
+        <v>147439824</v>
       </c>
       <c r="F14" t="n">
-        <v>-17569127</v>
+        <v>116604300</v>
       </c>
       <c r="G14" t="n">
-        <v>-15514647</v>
+        <v>107797837</v>
       </c>
       <c r="H14" t="n">
-        <v>-304326354</v>
+        <v>46891354</v>
       </c>
       <c r="I14" t="inlineStr">
-        <is>
-          <t>廣達</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>🔴 5d 翻紅</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-6523550</v>
-      </c>
-      <c r="E15" t="n">
-        <v>6718299</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-94000920</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-101826254</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-177632874</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 11,619 千)</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="n">
-        <v>-15475640</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-14486014</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-121225112</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-132844513</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-287145600</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 11,926 千)</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="n">
-        <v>72178224</v>
-      </c>
-      <c r="E17" t="n">
-        <v>66398587</v>
-      </c>
-      <c r="F17" t="n">
-        <v>293233955</v>
-      </c>
-      <c r="G17" t="n">
-        <v>281307605</v>
-      </c>
-      <c r="H17" t="n">
-        <v>280824107</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>長榮航</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>3045</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 9,881 千)</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>35309253</v>
-      </c>
-      <c r="E18" t="n">
-        <v>33261649</v>
-      </c>
-      <c r="F18" t="n">
-        <v>48205910</v>
-      </c>
-      <c r="G18" t="n">
-        <v>38325281</v>
-      </c>
-      <c r="H18" t="n">
-        <v>87328162</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>台灣大</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 26,001 千)</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>147439824</v>
-      </c>
-      <c r="E19" t="n">
-        <v>154948461</v>
-      </c>
-      <c r="F19" t="n">
-        <v>107797837</v>
-      </c>
-      <c r="G19" t="n">
-        <v>81796427</v>
-      </c>
-      <c r="H19" t="n">
-        <v>43406979</v>
-      </c>
-      <c r="I19" t="inlineStr">
         <is>
           <t>緯創</t>
         </is>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,455 +466,525 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -11,434 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>-2305632</v>
+        <v>-2639783</v>
       </c>
       <c r="E2" t="n">
-        <v>7913964</v>
+        <v>16355614</v>
       </c>
       <c r="F2" t="n">
-        <v>12808418</v>
+        <v>-29574678</v>
       </c>
       <c r="G2" t="n">
-        <v>24242107</v>
+        <v>-29022786</v>
       </c>
       <c r="H2" t="n">
-        <v>20237286</v>
+        <v>89965269</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -8,702 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>-2044719</v>
+        <v>-11060516</v>
       </c>
       <c r="E3" t="n">
-        <v>222371</v>
+        <v>-2305632</v>
       </c>
       <c r="F3" t="n">
-        <v>320874</v>
+        <v>4106453</v>
       </c>
       <c r="G3" t="n">
-        <v>306310</v>
+        <v>12808418</v>
       </c>
       <c r="H3" t="n">
-        <v>-28248549</v>
+        <v>13486262</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 23,955 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1300977</v>
+        <v>46641870</v>
       </c>
       <c r="E4" t="n">
-        <v>-4478938</v>
+        <v>36489566</v>
       </c>
       <c r="F4" t="n">
-        <v>6568917</v>
+        <v>42865866</v>
       </c>
       <c r="G4" t="n">
-        <v>10674952</v>
+        <v>18910606</v>
       </c>
       <c r="H4" t="n">
-        <v>-89941901</v>
+        <v>-37634596</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 20,034 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>16355614</v>
+        <v>31395127</v>
       </c>
       <c r="E5" t="n">
-        <v>59077327</v>
+        <v>27808773</v>
       </c>
       <c r="F5" t="n">
-        <v>-29022786</v>
+        <v>26663812</v>
       </c>
       <c r="G5" t="n">
-        <v>-29281311</v>
+        <v>6630274</v>
       </c>
       <c r="H5" t="n">
-        <v>69743792</v>
+        <v>-118734925</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 19,200 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>36489566</v>
+        <v>-3225420</v>
       </c>
       <c r="E6" t="n">
-        <v>35147578</v>
+        <v>-2044719</v>
       </c>
       <c r="F6" t="n">
-        <v>18910606</v>
+        <v>396806</v>
       </c>
       <c r="G6" t="n">
-        <v>-289435</v>
+        <v>320874</v>
       </c>
       <c r="H6" t="n">
-        <v>-47659482</v>
+        <v>-27620927</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 12,271 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>27808773</v>
+        <v>4291633</v>
       </c>
       <c r="E7" t="n">
-        <v>28847498</v>
+        <v>1300977</v>
       </c>
       <c r="F7" t="n">
-        <v>6630274</v>
+        <v>10402296</v>
       </c>
       <c r="G7" t="n">
-        <v>-5640615</v>
+        <v>6568917</v>
       </c>
       <c r="H7" t="n">
-        <v>-126191628</v>
+        <v>-86995880</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>441148</v>
+        <v>2043599</v>
       </c>
       <c r="E8" t="n">
-        <v>872208</v>
+        <v>1044568</v>
       </c>
       <c r="F8" t="n">
-        <v>-1242823</v>
+        <v>42585</v>
       </c>
       <c r="G8" t="n">
-        <v>-1165385</v>
+        <v>-1273037</v>
       </c>
       <c r="H8" t="n">
-        <v>-10293425</v>
+        <v>-10167105</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>鈊象</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1044568</v>
+        <v>20209361</v>
       </c>
       <c r="E9" t="n">
-        <v>808634</v>
+        <v>24860472</v>
       </c>
       <c r="F9" t="n">
-        <v>-1273037</v>
+        <v>6903276</v>
       </c>
       <c r="G9" t="n">
-        <v>-1601382</v>
+        <v>1702047</v>
       </c>
       <c r="H9" t="n">
-        <v>-11247890</v>
+        <v>-11439629</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>24860472</v>
+        <v>-262038</v>
       </c>
       <c r="E10" t="n">
-        <v>33827124</v>
+        <v>452433</v>
       </c>
       <c r="F10" t="n">
-        <v>1702047</v>
+        <v>-114636</v>
       </c>
       <c r="G10" t="n">
-        <v>-3028444</v>
+        <v>742731</v>
       </c>
       <c r="H10" t="n">
-        <v>-5014951</v>
+        <v>12015781</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>智易</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -12,747 千)</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-35110701</v>
+        <v>1674088</v>
       </c>
       <c r="E11" t="n">
-        <v>-15475640</v>
+        <v>-515228</v>
       </c>
       <c r="F11" t="n">
-        <v>-133971954</v>
+        <v>-1262122</v>
       </c>
       <c r="G11" t="n">
-        <v>-121225112</v>
+        <v>-670341</v>
       </c>
       <c r="H11" t="n">
-        <v>-289833960</v>
+        <v>6503466</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 40,301 千)</t>
+          <t>📉 20d 巨變(減碼 -9,785 千)</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>86695556</v>
+        <v>-42783017</v>
       </c>
       <c r="E12" t="n">
-        <v>72178224</v>
+        <v>-35110701</v>
       </c>
       <c r="F12" t="n">
-        <v>333534595</v>
+        <v>-143757075</v>
       </c>
       <c r="G12" t="n">
-        <v>293233955</v>
+        <v>-133971954</v>
       </c>
       <c r="H12" t="n">
-        <v>320923496</v>
+        <v>-301645339</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 11,005 千)</t>
+          <t>📈 20d 巨變(加碼 22,983 千)</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>30303520</v>
+        <v>87495305</v>
       </c>
       <c r="E13" t="n">
-        <v>35309253</v>
+        <v>86695556</v>
       </c>
       <c r="F13" t="n">
-        <v>59210708</v>
+        <v>356517442</v>
       </c>
       <c r="G13" t="n">
-        <v>48205910</v>
+        <v>333534595</v>
       </c>
       <c r="H13" t="n">
-        <v>89770857</v>
+        <v>329756656</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 8,806 千)</t>
+          <t>📈 20d 巨變(加碼 12,220 千)</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>141134859</v>
+        <v>29851847</v>
       </c>
       <c r="E14" t="n">
-        <v>147439824</v>
+        <v>30303520</v>
       </c>
       <c r="F14" t="n">
-        <v>116604300</v>
+        <v>71430388</v>
       </c>
       <c r="G14" t="n">
-        <v>107797837</v>
+        <v>59210708</v>
       </c>
       <c r="H14" t="n">
-        <v>46891354</v>
+        <v>80504303</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>台灣大</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 13,919 千)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-22693774</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-10475751</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-68756547</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-82675249</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-31598851</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -10,606 千)</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-10931142</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-5176967</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-57423379</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-46817100</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-8946192</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,147 +466,147 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>-2639783</v>
+        <v>1488980</v>
       </c>
       <c r="E2" t="n">
-        <v>16355614</v>
+        <v>-5059249</v>
       </c>
       <c r="F2" t="n">
-        <v>-29574678</v>
+        <v>3928985</v>
       </c>
       <c r="G2" t="n">
-        <v>-29022786</v>
+        <v>-719507</v>
       </c>
       <c r="H2" t="n">
-        <v>89965269</v>
+        <v>-63614824</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -8,702 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 14,757 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>-11060516</v>
+        <v>50423677</v>
       </c>
       <c r="E3" t="n">
-        <v>-2305632</v>
+        <v>46641870</v>
       </c>
       <c r="F3" t="n">
-        <v>4106453</v>
+        <v>57623007</v>
       </c>
       <c r="G3" t="n">
-        <v>12808418</v>
+        <v>42865866</v>
       </c>
       <c r="H3" t="n">
-        <v>13486262</v>
+        <v>-32527849</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 23,955 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 13,995 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>46641870</v>
+        <v>33414902</v>
       </c>
       <c r="E4" t="n">
-        <v>36489566</v>
+        <v>31395127</v>
       </c>
       <c r="F4" t="n">
-        <v>42865866</v>
+        <v>40658860</v>
       </c>
       <c r="G4" t="n">
-        <v>18910606</v>
+        <v>26663812</v>
       </c>
       <c r="H4" t="n">
-        <v>-37634596</v>
+        <v>-114490397</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 20,034 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>31395127</v>
+        <v>-3003076</v>
       </c>
       <c r="E5" t="n">
-        <v>27808773</v>
+        <v>-3225420</v>
       </c>
       <c r="F5" t="n">
-        <v>26663812</v>
+        <v>437104</v>
       </c>
       <c r="G5" t="n">
-        <v>6630274</v>
+        <v>396806</v>
       </c>
       <c r="H5" t="n">
-        <v>-118734925</v>
+        <v>-25354771</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,93 +618,93 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>-3225420</v>
+        <v>10905516</v>
       </c>
       <c r="E6" t="n">
-        <v>-2044719</v>
+        <v>4291633</v>
       </c>
       <c r="F6" t="n">
-        <v>396806</v>
+        <v>3442141</v>
       </c>
       <c r="G6" t="n">
-        <v>320874</v>
+        <v>10402296</v>
       </c>
       <c r="H6" t="n">
-        <v>-27620927</v>
+        <v>-85831007</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>4291633</v>
+        <v>150838</v>
       </c>
       <c r="E7" t="n">
-        <v>1300977</v>
+        <v>-352123</v>
       </c>
       <c r="F7" t="n">
-        <v>10402296</v>
+        <v>-7706197</v>
       </c>
       <c r="G7" t="n">
-        <v>6568917</v>
+        <v>-9847705</v>
       </c>
       <c r="H7" t="n">
-        <v>-86995880</v>
+        <v>-30307123</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>瑞昱</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>2043599</v>
+        <v>-17295226</v>
       </c>
       <c r="E8" t="n">
-        <v>1044568</v>
+        <v>-11060516</v>
       </c>
       <c r="F8" t="n">
-        <v>42585</v>
+        <v>-1446054</v>
       </c>
       <c r="G8" t="n">
-        <v>-1273037</v>
+        <v>4106453</v>
       </c>
       <c r="H8" t="n">
-        <v>-10167105</v>
+        <v>12794153</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
@@ -723,19 +723,19 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
+        <v>8801197</v>
+      </c>
+      <c r="E9" t="n">
         <v>20209361</v>
       </c>
-      <c r="E9" t="n">
-        <v>24860472</v>
-      </c>
       <c r="F9" t="n">
+        <v>14076176</v>
+      </c>
+      <c r="G9" t="n">
         <v>6903276</v>
       </c>
-      <c r="G9" t="n">
-        <v>1702047</v>
-      </c>
       <c r="H9" t="n">
-        <v>-11439629</v>
+        <v>-28471738</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -751,26 +751,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
+        <v>-198063</v>
+      </c>
+      <c r="E10" t="n">
         <v>-262038</v>
       </c>
-      <c r="E10" t="n">
-        <v>452433</v>
-      </c>
       <c r="F10" t="n">
+        <v>564291</v>
+      </c>
+      <c r="G10" t="n">
         <v>-114636</v>
       </c>
-      <c r="G10" t="n">
-        <v>742731</v>
-      </c>
       <c r="H10" t="n">
-        <v>12015781</v>
+        <v>11543748</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -781,210 +781,245 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>📉 20d 巨變(減碼 -11,357 千)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1674088</v>
+        <v>-42126042</v>
       </c>
       <c r="E11" t="n">
-        <v>-515228</v>
+        <v>-42783017</v>
       </c>
       <c r="F11" t="n">
-        <v>-1262122</v>
+        <v>-155114153</v>
       </c>
       <c r="G11" t="n">
-        <v>-670341</v>
+        <v>-143757075</v>
       </c>
       <c r="H11" t="n">
-        <v>6503466</v>
+        <v>-302204269</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -9,785 千)</t>
+          <t>📈 20d 巨變(加碼 54,446 千)</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-42783017</v>
+        <v>113149863</v>
       </c>
       <c r="E12" t="n">
-        <v>-35110701</v>
+        <v>87495305</v>
       </c>
       <c r="F12" t="n">
-        <v>-143757075</v>
+        <v>410963112</v>
       </c>
       <c r="G12" t="n">
-        <v>-133971954</v>
+        <v>356517442</v>
       </c>
       <c r="H12" t="n">
-        <v>-301645339</v>
+        <v>364807699</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 22,983 千)</t>
+          <t>📈 20d 巨變(加碼 14,405 千)</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>87495305</v>
+        <v>30724905</v>
       </c>
       <c r="E13" t="n">
-        <v>86695556</v>
+        <v>29851847</v>
       </c>
       <c r="F13" t="n">
-        <v>356517442</v>
+        <v>85835178</v>
       </c>
       <c r="G13" t="n">
-        <v>333534595</v>
+        <v>71430388</v>
       </c>
       <c r="H13" t="n">
-        <v>329756656</v>
+        <v>82377469</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 12,220 千)</t>
+          <t>📉 20d 巨變(減碼 -29,423 千)</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>29851847</v>
+        <v>-28962854</v>
       </c>
       <c r="E14" t="n">
-        <v>30303520</v>
+        <v>-3151387</v>
       </c>
       <c r="F14" t="n">
-        <v>71430388</v>
+        <v>-43130027</v>
       </c>
       <c r="G14" t="n">
-        <v>59210708</v>
+        <v>-13707361</v>
       </c>
       <c r="H14" t="n">
-        <v>80504303</v>
+        <v>-299258948</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 13,919 千)</t>
+          <t>📈 20d 巨變(加碼 12,843 千)</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-22693774</v>
+        <v>41911273</v>
       </c>
       <c r="E15" t="n">
-        <v>-10475751</v>
+        <v>120946904</v>
       </c>
       <c r="F15" t="n">
-        <v>-68756547</v>
+        <v>134504527</v>
       </c>
       <c r="G15" t="n">
-        <v>-82675249</v>
+        <v>121662007</v>
       </c>
       <c r="H15" t="n">
-        <v>-31598851</v>
+        <v>69764027</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -10,606 千)</t>
+          <t>📉 20d 巨變(減碼 -11,218 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-10931142</v>
+        <v>-60002451</v>
       </c>
       <c r="E16" t="n">
-        <v>-5176967</v>
+        <v>-2639783</v>
       </c>
       <c r="F16" t="n">
-        <v>-57423379</v>
+        <v>-40792414</v>
       </c>
       <c r="G16" t="n">
-        <v>-46817100</v>
+        <v>-29574678</v>
       </c>
       <c r="H16" t="n">
-        <v>-8946192</v>
+        <v>-2817285</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>鴻海</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 58,999 千)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-5310396</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-26077963</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-25812684</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-84811700</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-218940347</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>華邦電</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,35 +466,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📈 20d 巨變(加碼 75,106 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>1488980</v>
+        <v>-4629374</v>
       </c>
       <c r="E2" t="n">
-        <v>-5059249</v>
+        <v>-60002451</v>
       </c>
       <c r="F2" t="n">
-        <v>3928985</v>
+        <v>34313326</v>
       </c>
       <c r="G2" t="n">
-        <v>-719507</v>
+        <v>-40792414</v>
       </c>
       <c r="H2" t="n">
-        <v>-63614824</v>
+        <v>47040860</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
@@ -506,26 +506,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 14,757 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 17,136 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>6</v>
       </c>
       <c r="D3" t="n">
+        <v>50434520</v>
+      </c>
+      <c r="E3" t="n">
         <v>50423677</v>
       </c>
-      <c r="E3" t="n">
-        <v>46641870</v>
-      </c>
       <c r="F3" t="n">
+        <v>74759147</v>
+      </c>
+      <c r="G3" t="n">
         <v>57623007</v>
       </c>
-      <c r="G3" t="n">
-        <v>42865866</v>
-      </c>
       <c r="H3" t="n">
-        <v>-32527849</v>
+        <v>-25752678</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -541,26 +541,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 13,995 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 10,872 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
+        <v>29313824</v>
+      </c>
+      <c r="E4" t="n">
         <v>33414902</v>
       </c>
-      <c r="E4" t="n">
-        <v>31395127</v>
-      </c>
       <c r="F4" t="n">
+        <v>51531316</v>
+      </c>
+      <c r="G4" t="n">
         <v>40658860</v>
       </c>
-      <c r="G4" t="n">
-        <v>26663812</v>
-      </c>
       <c r="H4" t="n">
-        <v>-114490397</v>
+        <v>-111209421</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
+        <v>-1257845</v>
+      </c>
+      <c r="E5" t="n">
         <v>-3003076</v>
       </c>
-      <c r="E5" t="n">
-        <v>-3225420</v>
-      </c>
       <c r="F5" t="n">
+        <v>2138933</v>
+      </c>
+      <c r="G5" t="n">
         <v>437104</v>
       </c>
-      <c r="G5" t="n">
-        <v>396806</v>
-      </c>
       <c r="H5" t="n">
-        <v>-25354771</v>
+        <v>-24216788</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,406 +618,441 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>10905516</v>
+        <v>4129564</v>
       </c>
       <c r="E6" t="n">
-        <v>4291633</v>
+        <v>1488980</v>
       </c>
       <c r="F6" t="n">
-        <v>3442141</v>
+        <v>3999110</v>
       </c>
       <c r="G6" t="n">
-        <v>10402296</v>
+        <v>3928985</v>
       </c>
       <c r="H6" t="n">
-        <v>-85831007</v>
+        <v>-61698937</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>150838</v>
+        <v>7885151</v>
       </c>
       <c r="E7" t="n">
-        <v>-352123</v>
+        <v>10905516</v>
       </c>
       <c r="F7" t="n">
-        <v>-7706197</v>
+        <v>5483081</v>
       </c>
       <c r="G7" t="n">
-        <v>-9847705</v>
+        <v>3442141</v>
       </c>
       <c r="H7" t="n">
-        <v>-30307123</v>
+        <v>-87372218</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-17295226</v>
+        <v>3144196</v>
       </c>
       <c r="E8" t="n">
-        <v>-11060516</v>
+        <v>-112539</v>
       </c>
       <c r="F8" t="n">
-        <v>-1446054</v>
+        <v>-1889411</v>
       </c>
       <c r="G8" t="n">
-        <v>4106453</v>
+        <v>-1761458</v>
       </c>
       <c r="H8" t="n">
-        <v>12794153</v>
+        <v>-13075949</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>聯鈞</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>8801197</v>
+        <v>-11799934</v>
       </c>
       <c r="E9" t="n">
-        <v>20209361</v>
+        <v>-17295226</v>
       </c>
       <c r="F9" t="n">
-        <v>14076176</v>
+        <v>-438224</v>
       </c>
       <c r="G9" t="n">
-        <v>6903276</v>
+        <v>-1446054</v>
       </c>
       <c r="H9" t="n">
-        <v>-28471738</v>
+        <v>16978390</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-198063</v>
+        <v>7168748</v>
       </c>
       <c r="E10" t="n">
-        <v>-262038</v>
+        <v>8801197</v>
       </c>
       <c r="F10" t="n">
-        <v>564291</v>
+        <v>19674967</v>
       </c>
       <c r="G10" t="n">
-        <v>-114636</v>
+        <v>14076176</v>
       </c>
       <c r="H10" t="n">
-        <v>11543748</v>
+        <v>-26338452</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -11,357 千)</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-42126042</v>
+        <v>4684051</v>
       </c>
       <c r="E11" t="n">
-        <v>-42783017</v>
+        <v>-246956</v>
       </c>
       <c r="F11" t="n">
-        <v>-155114153</v>
+        <v>357971</v>
       </c>
       <c r="G11" t="n">
-        <v>-143757075</v>
+        <v>-2133588</v>
       </c>
       <c r="H11" t="n">
-        <v>-302204269</v>
+        <v>-7011693</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>宇瞻</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 54,446 千)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>113149863</v>
+        <v>-2857394</v>
       </c>
       <c r="E12" t="n">
-        <v>87495305</v>
+        <v>150838</v>
       </c>
       <c r="F12" t="n">
-        <v>410963112</v>
+        <v>-9081464</v>
       </c>
       <c r="G12" t="n">
-        <v>356517442</v>
+        <v>-7706197</v>
       </c>
       <c r="H12" t="n">
-        <v>364807699</v>
+        <v>-33092690</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>瑞昱</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 14,405 千)</t>
+          <t>📈 20d 巨變(加碼 26,034 千)</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>30724905</v>
+        <v>-18709337</v>
       </c>
       <c r="E13" t="n">
-        <v>29851847</v>
+        <v>-42126042</v>
       </c>
       <c r="F13" t="n">
-        <v>85835178</v>
+        <v>-129080528</v>
       </c>
       <c r="G13" t="n">
-        <v>71430388</v>
+        <v>-155114153</v>
       </c>
       <c r="H13" t="n">
-        <v>82377469</v>
+        <v>-288424170</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -29,423 千)</t>
+          <t>📈 20d 巨變(加碼 47,371 千)</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-28962854</v>
+        <v>136949595</v>
       </c>
       <c r="E14" t="n">
-        <v>-3151387</v>
+        <v>113149863</v>
       </c>
       <c r="F14" t="n">
-        <v>-43130027</v>
+        <v>458333814</v>
       </c>
       <c r="G14" t="n">
-        <v>-13707361</v>
+        <v>410963112</v>
       </c>
       <c r="H14" t="n">
-        <v>-299258948</v>
+        <v>404820245</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 12,843 千)</t>
+          <t>📈 20d 巨變(加碼 16,051 千)</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>41911273</v>
+        <v>26932200</v>
       </c>
       <c r="E15" t="n">
-        <v>120946904</v>
+        <v>30724905</v>
       </c>
       <c r="F15" t="n">
-        <v>134504527</v>
+        <v>101886462</v>
       </c>
       <c r="G15" t="n">
-        <v>121662007</v>
+        <v>85835178</v>
       </c>
       <c r="H15" t="n">
-        <v>69764027</v>
+        <v>87543288</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -11,218 千)</t>
+          <t>📉 20d 巨變(減碼 -8,692 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-60002451</v>
+        <v>-13076217</v>
       </c>
       <c r="E16" t="n">
-        <v>-2639783</v>
+        <v>-23939079</v>
       </c>
       <c r="F16" t="n">
-        <v>-40792414</v>
+        <v>-76149660</v>
       </c>
       <c r="G16" t="n">
-        <v>-29574678</v>
+        <v>-67457530</v>
       </c>
       <c r="H16" t="n">
-        <v>-2817285</v>
+        <v>-11022153</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 58,999 千)</t>
+          <t>📈 20d 巨變(加碼 26,648 千)</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
+        <v>27757547</v>
+      </c>
+      <c r="E17" t="n">
+        <v>41911273</v>
+      </c>
+      <c r="F17" t="n">
+        <v>161152099</v>
+      </c>
+      <c r="G17" t="n">
+        <v>134504527</v>
+      </c>
+      <c r="H17" t="n">
+        <v>88045391</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -48,012 千)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-14262392</v>
+      </c>
+      <c r="E18" t="n">
         <v>-5310396</v>
       </c>
-      <c r="E17" t="n">
-        <v>-26077963</v>
-      </c>
-      <c r="F17" t="n">
+      <c r="F18" t="n">
+        <v>-73824566</v>
+      </c>
+      <c r="G18" t="n">
         <v>-25812684</v>
       </c>
-      <c r="G17" t="n">
-        <v>-84811700</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-218940347</v>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="H18" t="n">
+        <v>-225562020</v>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>華邦電</t>
         </is>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,182 +466,182 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📈 20d 巨變(加碼 75,106 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 36,301 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-4629374</v>
+        <v>22342285</v>
       </c>
       <c r="E2" t="n">
-        <v>-60002451</v>
+        <v>-14262392</v>
       </c>
       <c r="F2" t="n">
-        <v>34313326</v>
+        <v>-37523903</v>
       </c>
       <c r="G2" t="n">
-        <v>-40792414</v>
+        <v>-73824566</v>
       </c>
       <c r="H2" t="n">
-        <v>47040860</v>
+        <v>-131461223</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 17,136 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 20,292 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>50434520</v>
+        <v>-262256</v>
       </c>
       <c r="E3" t="n">
-        <v>50423677</v>
+        <v>-13076217</v>
       </c>
       <c r="F3" t="n">
-        <v>74759147</v>
+        <v>-55857907</v>
       </c>
       <c r="G3" t="n">
-        <v>57623007</v>
+        <v>-76149660</v>
       </c>
       <c r="H3" t="n">
-        <v>-25752678</v>
+        <v>20060966</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 10,872 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 13,602 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>29313824</v>
+        <v>21212067</v>
       </c>
       <c r="E4" t="n">
-        <v>33414902</v>
+        <v>7168748</v>
       </c>
       <c r="F4" t="n">
-        <v>51531316</v>
+        <v>33276861</v>
       </c>
       <c r="G4" t="n">
-        <v>40658860</v>
+        <v>19674967</v>
       </c>
       <c r="H4" t="n">
-        <v>-111209421</v>
+        <v>-16638705</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 12,001 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>-1257845</v>
+        <v>38737102</v>
       </c>
       <c r="E5" t="n">
-        <v>-3003076</v>
+        <v>50434520</v>
       </c>
       <c r="F5" t="n">
-        <v>2138933</v>
+        <v>86760132</v>
       </c>
       <c r="G5" t="n">
-        <v>437104</v>
+        <v>74759147</v>
       </c>
       <c r="H5" t="n">
-        <v>-24216788</v>
+        <v>-38561303</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 9,853 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>4129564</v>
+        <v>27899755</v>
       </c>
       <c r="E6" t="n">
-        <v>1488980</v>
+        <v>29313824</v>
       </c>
       <c r="F6" t="n">
-        <v>3999110</v>
+        <v>61384256</v>
       </c>
       <c r="G6" t="n">
-        <v>3928985</v>
+        <v>51531316</v>
       </c>
       <c r="H6" t="n">
-        <v>-61698937</v>
+        <v>-108036978</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,408 +653,338 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>7885151</v>
+        <v>-186309</v>
       </c>
       <c r="E7" t="n">
-        <v>10905516</v>
+        <v>-1257845</v>
       </c>
       <c r="F7" t="n">
-        <v>5483081</v>
+        <v>2664774</v>
       </c>
       <c r="G7" t="n">
-        <v>3442141</v>
+        <v>2138933</v>
       </c>
       <c r="H7" t="n">
-        <v>-87372218</v>
+        <v>-21368161</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>3144196</v>
+        <v>5049951</v>
       </c>
       <c r="E8" t="n">
-        <v>-112539</v>
+        <v>4129564</v>
       </c>
       <c r="F8" t="n">
-        <v>-1889411</v>
+        <v>3064956</v>
       </c>
       <c r="G8" t="n">
-        <v>-1761458</v>
+        <v>3999110</v>
       </c>
       <c r="H8" t="n">
-        <v>-13075949</v>
+        <v>-61824958</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-11799934</v>
+        <v>6889006</v>
       </c>
       <c r="E9" t="n">
-        <v>-17295226</v>
+        <v>7885151</v>
       </c>
       <c r="F9" t="n">
-        <v>-438224</v>
+        <v>9340545</v>
       </c>
       <c r="G9" t="n">
-        <v>-1446054</v>
+        <v>5483081</v>
       </c>
       <c r="H9" t="n">
-        <v>16978390</v>
+        <v>-77925668</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>7168748</v>
+        <v>-9636224</v>
       </c>
       <c r="E10" t="n">
-        <v>8801197</v>
+        <v>-11799934</v>
       </c>
       <c r="F10" t="n">
-        <v>19674967</v>
+        <v>-2768811</v>
       </c>
       <c r="G10" t="n">
-        <v>14076176</v>
+        <v>-438224</v>
       </c>
       <c r="H10" t="n">
-        <v>-26338452</v>
+        <v>15162318</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>4684051</v>
+        <v>4377564</v>
       </c>
       <c r="E11" t="n">
-        <v>-246956</v>
+        <v>3144196</v>
       </c>
       <c r="F11" t="n">
-        <v>357971</v>
+        <v>-999859</v>
       </c>
       <c r="G11" t="n">
-        <v>-2133588</v>
+        <v>-1889411</v>
       </c>
       <c r="H11" t="n">
-        <v>-7011693</v>
+        <v>-12281104</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>聯鈞</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>🟢 5d 翻綠 / 📈 20d 巨變(加碼 9,550 千)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-2857394</v>
+        <v>4984324</v>
       </c>
       <c r="E12" t="n">
-        <v>150838</v>
+        <v>-4629374</v>
       </c>
       <c r="F12" t="n">
-        <v>-9081464</v>
+        <v>43863209</v>
       </c>
       <c r="G12" t="n">
-        <v>-7706197</v>
+        <v>34313326</v>
       </c>
       <c r="H12" t="n">
-        <v>-33092690</v>
+        <v>50652710</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 26,034 千)</t>
+          <t>📈 20d 巨變(加碼 18,519 千)</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-18709337</v>
+        <v>131514031</v>
       </c>
       <c r="E13" t="n">
-        <v>-42126042</v>
+        <v>136949595</v>
       </c>
       <c r="F13" t="n">
-        <v>-129080528</v>
+        <v>476852963</v>
       </c>
       <c r="G13" t="n">
-        <v>-155114153</v>
+        <v>458333814</v>
       </c>
       <c r="H13" t="n">
-        <v>-288424170</v>
+        <v>415559685</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 47,371 千)</t>
+          <t>📈 20d 巨變(加碼 10,207 千)</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>136949595</v>
+        <v>20108667</v>
       </c>
       <c r="E14" t="n">
-        <v>113149863</v>
+        <v>26932200</v>
       </c>
       <c r="F14" t="n">
-        <v>458333814</v>
+        <v>112093456</v>
       </c>
       <c r="G14" t="n">
-        <v>410963112</v>
+        <v>101886462</v>
       </c>
       <c r="H14" t="n">
-        <v>404820245</v>
+        <v>68694263</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 16,051 千)</t>
+          <t>📈 20d 巨變(加碼 23,790 千)</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>26932200</v>
+        <v>-9318024</v>
       </c>
       <c r="E15" t="n">
-        <v>30724905</v>
+        <v>-15375509</v>
       </c>
       <c r="F15" t="n">
-        <v>101886462</v>
+        <v>-42568767</v>
       </c>
       <c r="G15" t="n">
-        <v>85835178</v>
+        <v>-66359052</v>
       </c>
       <c r="H15" t="n">
-        <v>87543288</v>
+        <v>-941547</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -8,692 千)</t>
+          <t>📈 20d 巨變(加碼 20,255 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-13076217</v>
+        <v>38115721</v>
       </c>
       <c r="E16" t="n">
-        <v>-23939079</v>
+        <v>27757547</v>
       </c>
       <c r="F16" t="n">
-        <v>-76149660</v>
+        <v>181407583</v>
       </c>
       <c r="G16" t="n">
-        <v>-67457530</v>
+        <v>161152099</v>
       </c>
       <c r="H16" t="n">
-        <v>-11022153</v>
+        <v>120605434</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 26,648 千)</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="n">
-        <v>27757547</v>
-      </c>
-      <c r="E17" t="n">
-        <v>41911273</v>
-      </c>
-      <c r="F17" t="n">
-        <v>161152099</v>
-      </c>
-      <c r="G17" t="n">
-        <v>134504527</v>
-      </c>
-      <c r="H17" t="n">
-        <v>88045391</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
           <t>緯創</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -48,012 千)</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>-14262392</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-5310396</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-73824566</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-25812684</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-225562020</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>華邦電</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,140 +466,140 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 36,301 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 20,182 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>22342285</v>
+        <v>30111922</v>
       </c>
       <c r="E2" t="n">
-        <v>-14262392</v>
+        <v>-262256</v>
       </c>
       <c r="F2" t="n">
-        <v>-37523903</v>
+        <v>-35676240</v>
       </c>
       <c r="G2" t="n">
-        <v>-73824566</v>
+        <v>-55857907</v>
       </c>
       <c r="H2" t="n">
-        <v>-131461223</v>
+        <v>45957706</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 20,292 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>-262256</v>
+        <v>2144003</v>
       </c>
       <c r="E3" t="n">
-        <v>-13076217</v>
+        <v>-186309</v>
       </c>
       <c r="F3" t="n">
-        <v>-55857907</v>
+        <v>1972781</v>
       </c>
       <c r="G3" t="n">
-        <v>-76149660</v>
+        <v>2664774</v>
       </c>
       <c r="H3" t="n">
-        <v>20060966</v>
+        <v>-17830799</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 13,602 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>21212067</v>
+        <v>-854035</v>
       </c>
       <c r="E4" t="n">
-        <v>7168748</v>
+        <v>2884668</v>
       </c>
       <c r="F4" t="n">
-        <v>33276861</v>
+        <v>12111366</v>
       </c>
       <c r="G4" t="n">
-        <v>19674967</v>
+        <v>12884564</v>
       </c>
       <c r="H4" t="n">
-        <v>-16638705</v>
+        <v>16776391</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>金像電</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 12,001 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 16,189 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>38737102</v>
+        <v>27598947</v>
       </c>
       <c r="E5" t="n">
-        <v>50434520</v>
+        <v>21212067</v>
       </c>
       <c r="F5" t="n">
-        <v>86760132</v>
+        <v>49465929</v>
       </c>
       <c r="G5" t="n">
-        <v>74759147</v>
+        <v>33276861</v>
       </c>
       <c r="H5" t="n">
-        <v>-38561303</v>
+        <v>-301215</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
@@ -611,26 +611,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 9,853 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 8,135 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>6</v>
       </c>
       <c r="D6" t="n">
+        <v>23559106</v>
+      </c>
+      <c r="E6" t="n">
         <v>27899755</v>
       </c>
-      <c r="E6" t="n">
-        <v>29313824</v>
-      </c>
       <c r="F6" t="n">
+        <v>69519305</v>
+      </c>
+      <c r="G6" t="n">
         <v>61384256</v>
       </c>
-      <c r="G6" t="n">
-        <v>51531316</v>
-      </c>
       <c r="H6" t="n">
-        <v>-108036978</v>
+        <v>-108895607</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -641,35 +641,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 30,292 千)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>-186309</v>
+        <v>44991667</v>
       </c>
       <c r="E7" t="n">
-        <v>-1257845</v>
+        <v>22342285</v>
       </c>
       <c r="F7" t="n">
-        <v>2664774</v>
+        <v>-7231973</v>
       </c>
       <c r="G7" t="n">
-        <v>2138933</v>
+        <v>-37523903</v>
       </c>
       <c r="H7" t="n">
-        <v>-21368161</v>
+        <v>-139547958</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
+        <v>7378878</v>
+      </c>
+      <c r="E8" t="n">
         <v>5049951</v>
       </c>
-      <c r="E8" t="n">
-        <v>4129564</v>
-      </c>
       <c r="F8" t="n">
+        <v>3092270</v>
+      </c>
+      <c r="G8" t="n">
         <v>3064956</v>
       </c>
-      <c r="G8" t="n">
-        <v>3999110</v>
-      </c>
       <c r="H8" t="n">
-        <v>-61824958</v>
+        <v>-58640101</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -723,19 +723,19 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
+        <v>1850126</v>
+      </c>
+      <c r="E9" t="n">
         <v>6889006</v>
       </c>
-      <c r="E9" t="n">
-        <v>7885151</v>
-      </c>
       <c r="F9" t="n">
+        <v>2087818</v>
+      </c>
+      <c r="G9" t="n">
         <v>9340545</v>
       </c>
-      <c r="G9" t="n">
-        <v>5483081</v>
-      </c>
       <c r="H9" t="n">
-        <v>-77925668</v>
+        <v>-75822696</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -746,35 +746,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-9636224</v>
+        <v>26141952</v>
       </c>
       <c r="E10" t="n">
-        <v>-11799934</v>
+        <v>38737102</v>
       </c>
       <c r="F10" t="n">
-        <v>-2768811</v>
+        <v>89341541</v>
       </c>
       <c r="G10" t="n">
-        <v>-438224</v>
+        <v>86760132</v>
       </c>
       <c r="H10" t="n">
-        <v>15162318</v>
+        <v>-35398980</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
@@ -793,19 +793,19 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
+        <v>2319538</v>
+      </c>
+      <c r="E11" t="n">
         <v>4377564</v>
       </c>
-      <c r="E11" t="n">
-        <v>3144196</v>
-      </c>
       <c r="F11" t="n">
+        <v>-2003720</v>
+      </c>
+      <c r="G11" t="n">
         <v>-999859</v>
       </c>
-      <c r="G11" t="n">
-        <v>-1889411</v>
-      </c>
       <c r="H11" t="n">
-        <v>-12281104</v>
+        <v>-13727272</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -816,175 +816,280 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠 / 📈 20d 巨變(加碼 9,550 千)</t>
+          <t>🟢 5d 翻綠 / 📈 20d 巨變(加碼 20,948 千)</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>4984324</v>
+        <v>28471203</v>
       </c>
       <c r="E12" t="n">
-        <v>-4629374</v>
+        <v>-9636224</v>
       </c>
       <c r="F12" t="n">
-        <v>43863209</v>
+        <v>18178800</v>
       </c>
       <c r="G12" t="n">
-        <v>34313326</v>
+        <v>-2768811</v>
       </c>
       <c r="H12" t="n">
-        <v>50652710</v>
+        <v>44190621</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 18,519 千)</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>131514031</v>
+        <v>677537</v>
       </c>
       <c r="E13" t="n">
-        <v>136949595</v>
+        <v>-1923260</v>
       </c>
       <c r="F13" t="n">
-        <v>476852963</v>
+        <v>376693</v>
       </c>
       <c r="G13" t="n">
-        <v>458333814</v>
+        <v>-588452</v>
       </c>
       <c r="H13" t="n">
-        <v>415559685</v>
+        <v>40427</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>華星光</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 10,207 千)</t>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>20108667</v>
+        <v>1545319</v>
       </c>
       <c r="E14" t="n">
-        <v>26932200</v>
+        <v>-109527</v>
       </c>
       <c r="F14" t="n">
-        <v>112093456</v>
+        <v>-5518300</v>
       </c>
       <c r="G14" t="n">
-        <v>101886462</v>
+        <v>-6635362</v>
       </c>
       <c r="H14" t="n">
-        <v>68694263</v>
+        <v>-581848</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>全友</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 23,790 千)</t>
+          <t>📉 20d 巨變(減碼 -12,188 千)</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-9318024</v>
+        <v>-23534715</v>
       </c>
       <c r="E15" t="n">
-        <v>-15375509</v>
+        <v>-25764530</v>
       </c>
       <c r="F15" t="n">
-        <v>-42568767</v>
+        <v>-138449378</v>
       </c>
       <c r="G15" t="n">
-        <v>-66359052</v>
+        <v>-126260950</v>
       </c>
       <c r="H15" t="n">
-        <v>-941547</v>
+        <v>-272770401</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 20,255 千)</t>
+          <t>📈 20d 巨變(加碼 14,025 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
+        <v>108405340</v>
+      </c>
+      <c r="E16" t="n">
+        <v>131514031</v>
+      </c>
+      <c r="F16" t="n">
+        <v>490877831</v>
+      </c>
+      <c r="G16" t="n">
+        <v>476852963</v>
+      </c>
+      <c r="H16" t="n">
+        <v>434205339</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>長榮航</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -9,832 千)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-19057585</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-9318024</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-52400799</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-42568767</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-13255930</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 32,227 千)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>54729872</v>
+      </c>
+      <c r="E18" t="n">
         <v>38115721</v>
       </c>
-      <c r="E16" t="n">
-        <v>27757547</v>
-      </c>
-      <c r="F16" t="n">
+      <c r="F18" t="n">
+        <v>213634222</v>
+      </c>
+      <c r="G18" t="n">
         <v>181407583</v>
       </c>
-      <c r="G16" t="n">
-        <v>161152099</v>
-      </c>
-      <c r="H16" t="n">
-        <v>120605434</v>
-      </c>
-      <c r="I16" t="inlineStr">
+      <c r="H18" t="n">
+        <v>145895865</v>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>緯創</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 10,601 千)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>27201353</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4984324</v>
+      </c>
+      <c r="F19" t="n">
+        <v>54464068</v>
+      </c>
+      <c r="G19" t="n">
+        <v>43863209</v>
+      </c>
+      <c r="H19" t="n">
+        <v>65543079</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>鴻海</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,26 +471,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 20,182 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 10,561 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
+        <v>41793866</v>
+      </c>
+      <c r="E2" t="n">
         <v>30111922</v>
       </c>
-      <c r="E2" t="n">
-        <v>-262256</v>
-      </c>
       <c r="F2" t="n">
+        <v>-25115508</v>
+      </c>
+      <c r="G2" t="n">
         <v>-35676240</v>
       </c>
-      <c r="G2" t="n">
-        <v>-55857907</v>
-      </c>
       <c r="H2" t="n">
-        <v>45957706</v>
+        <v>54432161</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -501,280 +501,280 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 12,451 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>2144003</v>
+        <v>14297808</v>
       </c>
       <c r="E3" t="n">
-        <v>-186309</v>
+        <v>26141952</v>
       </c>
       <c r="F3" t="n">
-        <v>1972781</v>
+        <v>101792510</v>
       </c>
       <c r="G3" t="n">
-        <v>2664774</v>
+        <v>89341541</v>
       </c>
       <c r="H3" t="n">
-        <v>-17830799</v>
+        <v>-28916688</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 9,183 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>-854035</v>
+        <v>16211932</v>
       </c>
       <c r="E4" t="n">
-        <v>2884668</v>
+        <v>23559106</v>
       </c>
       <c r="F4" t="n">
-        <v>12111366</v>
+        <v>78702261</v>
       </c>
       <c r="G4" t="n">
-        <v>12884564</v>
+        <v>69519305</v>
       </c>
       <c r="H4" t="n">
-        <v>16776391</v>
+        <v>-103657199</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 16,189 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>27598947</v>
+        <v>4019376</v>
       </c>
       <c r="E5" t="n">
-        <v>21212067</v>
+        <v>2144003</v>
       </c>
       <c r="F5" t="n">
-        <v>49465929</v>
+        <v>4432401</v>
       </c>
       <c r="G5" t="n">
-        <v>33276861</v>
+        <v>1972781</v>
       </c>
       <c r="H5" t="n">
-        <v>-301215</v>
+        <v>-18098308</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 8,135 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>23559106</v>
+        <v>8547026</v>
       </c>
       <c r="E6" t="n">
-        <v>27899755</v>
+        <v>7378878</v>
       </c>
       <c r="F6" t="n">
-        <v>69519305</v>
+        <v>4312930</v>
       </c>
       <c r="G6" t="n">
-        <v>61384256</v>
+        <v>3092270</v>
       </c>
       <c r="H6" t="n">
-        <v>-108895607</v>
+        <v>-54812288</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 30,292 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>44991667</v>
+        <v>15000836</v>
       </c>
       <c r="E7" t="n">
-        <v>22342285</v>
+        <v>27598947</v>
       </c>
       <c r="F7" t="n">
-        <v>-7231973</v>
+        <v>49378870</v>
       </c>
       <c r="G7" t="n">
-        <v>-37523903</v>
+        <v>49465929</v>
       </c>
       <c r="H7" t="n">
-        <v>-139547958</v>
+        <v>-19156471</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>7378878</v>
+        <v>69684964</v>
       </c>
       <c r="E8" t="n">
-        <v>5049951</v>
+        <v>44991667</v>
       </c>
       <c r="F8" t="n">
-        <v>3092270</v>
+        <v>-4519770</v>
       </c>
       <c r="G8" t="n">
-        <v>3064956</v>
+        <v>-7231973</v>
       </c>
       <c r="H8" t="n">
-        <v>-58640101</v>
+        <v>-98988099</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1850126</v>
+        <v>-2359353</v>
       </c>
       <c r="E9" t="n">
-        <v>6889006</v>
+        <v>-854035</v>
       </c>
       <c r="F9" t="n">
-        <v>2087818</v>
+        <v>11631631</v>
       </c>
       <c r="G9" t="n">
-        <v>9340545</v>
+        <v>12111366</v>
       </c>
       <c r="H9" t="n">
-        <v>-75822696</v>
+        <v>17050325</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>金像電</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🔴 5d 翻紅 / 📉 20d 巨變(減碼 -15,482 千)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>26141952</v>
+        <v>-5707550</v>
       </c>
       <c r="E10" t="n">
-        <v>38737102</v>
+        <v>1850126</v>
       </c>
       <c r="F10" t="n">
-        <v>89341541</v>
+        <v>-13394221</v>
       </c>
       <c r="G10" t="n">
-        <v>86760132</v>
+        <v>2087818</v>
       </c>
       <c r="H10" t="n">
-        <v>-35398980</v>
+        <v>-81273338</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
@@ -793,19 +793,19 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
+        <v>1769794</v>
+      </c>
+      <c r="E11" t="n">
         <v>2319538</v>
       </c>
-      <c r="E11" t="n">
-        <v>4377564</v>
-      </c>
       <c r="F11" t="n">
+        <v>-2004547</v>
+      </c>
+      <c r="G11" t="n">
         <v>-2003720</v>
       </c>
-      <c r="G11" t="n">
-        <v>-999859</v>
-      </c>
       <c r="H11" t="n">
-        <v>-13727272</v>
+        <v>-13468593</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -816,70 +816,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠 / 📈 20d 巨變(加碼 20,948 千)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>28471203</v>
+        <v>-1960698</v>
       </c>
       <c r="E12" t="n">
-        <v>-9636224</v>
+        <v>907139</v>
       </c>
       <c r="F12" t="n">
-        <v>18178800</v>
+        <v>-1353369</v>
       </c>
       <c r="G12" t="n">
-        <v>-2768811</v>
+        <v>508917</v>
       </c>
       <c r="H12" t="n">
-        <v>44190621</v>
+        <v>2727161</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>高力</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>677537</v>
+        <v>-1253755</v>
       </c>
       <c r="E13" t="n">
-        <v>-1923260</v>
+        <v>970654</v>
       </c>
       <c r="F13" t="n">
-        <v>376693</v>
+        <v>2131851</v>
       </c>
       <c r="G13" t="n">
-        <v>-588452</v>
+        <v>3116399</v>
       </c>
       <c r="H13" t="n">
-        <v>40427</v>
+        <v>2126185</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>建榮</t>
         </is>
       </c>
     </row>
@@ -891,26 +891,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="n">
+        <v>-2249371</v>
+      </c>
+      <c r="E14" t="n">
         <v>1545319</v>
       </c>
-      <c r="E14" t="n">
-        <v>-109527</v>
-      </c>
       <c r="F14" t="n">
+        <v>-7728913</v>
+      </c>
+      <c r="G14" t="n">
         <v>-5518300</v>
       </c>
-      <c r="G14" t="n">
-        <v>-6635362</v>
-      </c>
       <c r="H14" t="n">
-        <v>-581848</v>
+        <v>-6206692</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -926,26 +926,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -12,188 千)</t>
+          <t>📈 20d 巨變(加碼 12,168 千)</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
+        <v>-72582</v>
+      </c>
+      <c r="E15" t="n">
         <v>-23534715</v>
       </c>
-      <c r="E15" t="n">
-        <v>-25764530</v>
-      </c>
       <c r="F15" t="n">
+        <v>-126281282</v>
+      </c>
+      <c r="G15" t="n">
         <v>-138449378</v>
       </c>
-      <c r="G15" t="n">
-        <v>-126260950</v>
-      </c>
       <c r="H15" t="n">
-        <v>-272770401</v>
+        <v>-261533501</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -961,26 +961,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 14,025 千)</t>
+          <t>📈 20d 巨變(加碼 9,026 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
+        <v>119499613</v>
+      </c>
+      <c r="E16" t="n">
         <v>108405340</v>
       </c>
-      <c r="E16" t="n">
-        <v>131514031</v>
-      </c>
       <c r="F16" t="n">
+        <v>499904271</v>
+      </c>
+      <c r="G16" t="n">
         <v>490877831</v>
       </c>
-      <c r="G16" t="n">
-        <v>476852963</v>
-      </c>
       <c r="H16" t="n">
-        <v>434205339</v>
+        <v>456520564</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,35 +991,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -9,832 千)</t>
+          <t>📈 20d 巨變(加碼 8,371 千)</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-19057585</v>
+        <v>8164230</v>
       </c>
       <c r="E17" t="n">
-        <v>-9318024</v>
+        <v>11870276</v>
       </c>
       <c r="F17" t="n">
-        <v>-52400799</v>
+        <v>120873873</v>
       </c>
       <c r="G17" t="n">
-        <v>-42568767</v>
+        <v>112502543</v>
       </c>
       <c r="H17" t="n">
-        <v>-13255930</v>
+        <v>72171567</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
@@ -1031,26 +1031,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 32,227 千)</t>
+          <t>📈 20d 巨變(加碼 44,363 千)</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
+        <v>86320245</v>
+      </c>
+      <c r="E18" t="n">
         <v>54729872</v>
       </c>
-      <c r="E18" t="n">
-        <v>38115721</v>
-      </c>
       <c r="F18" t="n">
+        <v>257997143</v>
+      </c>
+      <c r="G18" t="n">
         <v>213634222</v>
       </c>
-      <c r="G18" t="n">
-        <v>181407583</v>
-      </c>
       <c r="H18" t="n">
-        <v>145895865</v>
+        <v>153894040</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1061,33 +1061,68 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 10,601 千)</t>
+          <t>📈 20d 巨變(加碼 32,203 千)</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
+        <v>60262588</v>
+      </c>
+      <c r="E19" t="n">
+        <v>28471203</v>
+      </c>
+      <c r="F19" t="n">
+        <v>50382051</v>
+      </c>
+      <c r="G19" t="n">
+        <v>18178800</v>
+      </c>
+      <c r="H19" t="n">
+        <v>78511071</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 54,911 千)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>65494730</v>
+      </c>
+      <c r="E20" t="n">
         <v>27201353</v>
       </c>
-      <c r="E19" t="n">
-        <v>4984324</v>
-      </c>
-      <c r="F19" t="n">
+      <c r="F20" t="n">
+        <v>109375506</v>
+      </c>
+      <c r="G20" t="n">
         <v>54464068</v>
       </c>
-      <c r="G19" t="n">
-        <v>43863209</v>
-      </c>
-      <c r="H19" t="n">
-        <v>65543079</v>
-      </c>
-      <c r="I19" t="inlineStr">
+      <c r="H20" t="n">
+        <v>78477635</v>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>鴻海</t>
         </is>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,26 +471,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 10,561 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 11,927 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
+        <v>51644971</v>
+      </c>
+      <c r="E2" t="n">
         <v>41793866</v>
       </c>
-      <c r="E2" t="n">
-        <v>30111922</v>
-      </c>
       <c r="F2" t="n">
+        <v>-13188893</v>
+      </c>
+      <c r="G2" t="n">
         <v>-25115508</v>
       </c>
-      <c r="G2" t="n">
-        <v>-35676240</v>
-      </c>
       <c r="H2" t="n">
-        <v>54432161</v>
+        <v>64424481</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -501,112 +501,112 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 12,451 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 9,307 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>14297808</v>
+        <v>20208805</v>
       </c>
       <c r="E3" t="n">
-        <v>26141952</v>
+        <v>15000836</v>
       </c>
       <c r="F3" t="n">
-        <v>101792510</v>
+        <v>58685658</v>
       </c>
       <c r="G3" t="n">
-        <v>89341541</v>
+        <v>49378870</v>
       </c>
       <c r="H3" t="n">
-        <v>-28916688</v>
+        <v>-44108702</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 9,183 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 12,753 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>16211932</v>
+        <v>6128018</v>
       </c>
       <c r="E4" t="n">
-        <v>23559106</v>
+        <v>14297808</v>
       </c>
       <c r="F4" t="n">
-        <v>78702261</v>
+        <v>114545213</v>
       </c>
       <c r="G4" t="n">
-        <v>69519305</v>
+        <v>101792510</v>
       </c>
       <c r="H4" t="n">
-        <v>-103657199</v>
+        <v>-26021132</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📉 20d 巨變(減碼 -27,141 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>4019376</v>
+        <v>14607099</v>
       </c>
       <c r="E5" t="n">
-        <v>2144003</v>
+        <v>69684964</v>
       </c>
       <c r="F5" t="n">
-        <v>4432401</v>
+        <v>-31660278</v>
       </c>
       <c r="G5" t="n">
-        <v>1972781</v>
+        <v>-4519770</v>
       </c>
       <c r="H5" t="n">
-        <v>-18098308</v>
+        <v>-170070129</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,30 +618,30 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>8547026</v>
+        <v>3726178</v>
       </c>
       <c r="E6" t="n">
-        <v>7378878</v>
+        <v>4019376</v>
       </c>
       <c r="F6" t="n">
-        <v>4312930</v>
+        <v>4400332</v>
       </c>
       <c r="G6" t="n">
-        <v>3092270</v>
+        <v>4432401</v>
       </c>
       <c r="H6" t="n">
-        <v>-54812288</v>
+        <v>-20555226</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,476 +653,336 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>15000836</v>
+        <v>5376976</v>
       </c>
       <c r="E7" t="n">
-        <v>27598947</v>
+        <v>8547026</v>
       </c>
       <c r="F7" t="n">
-        <v>49378870</v>
+        <v>4912635</v>
       </c>
       <c r="G7" t="n">
-        <v>49465929</v>
+        <v>4312930</v>
       </c>
       <c r="H7" t="n">
-        <v>-19156471</v>
+        <v>-51629075</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>69684964</v>
+        <v>2502737</v>
       </c>
       <c r="E8" t="n">
-        <v>44991667</v>
+        <v>1769794</v>
       </c>
       <c r="F8" t="n">
-        <v>-4519770</v>
+        <v>405654</v>
       </c>
       <c r="G8" t="n">
-        <v>-7231973</v>
+        <v>-2004547</v>
       </c>
       <c r="H8" t="n">
-        <v>-98988099</v>
+        <v>-10302149</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>聯鈞</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-2359353</v>
+        <v>9655676</v>
       </c>
       <c r="E9" t="n">
-        <v>-854035</v>
+        <v>16211932</v>
       </c>
       <c r="F9" t="n">
-        <v>11631631</v>
+        <v>80770627</v>
       </c>
       <c r="G9" t="n">
-        <v>12111366</v>
+        <v>78702261</v>
       </c>
       <c r="H9" t="n">
-        <v>17050325</v>
+        <v>-102622764</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅 / 📉 20d 巨變(減碼 -15,482 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-5707550</v>
+        <v>59001</v>
       </c>
       <c r="E10" t="n">
-        <v>1850126</v>
+        <v>-1533703</v>
       </c>
       <c r="F10" t="n">
-        <v>-13394221</v>
+        <v>-8158176</v>
       </c>
       <c r="G10" t="n">
-        <v>2087818</v>
+        <v>-8233752</v>
       </c>
       <c r="H10" t="n">
-        <v>-81273338</v>
+        <v>-11385036</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1769794</v>
+        <v>-2529669</v>
       </c>
       <c r="E11" t="n">
-        <v>2319538</v>
+        <v>-2359353</v>
       </c>
       <c r="F11" t="n">
-        <v>-2004547</v>
+        <v>11196326</v>
       </c>
       <c r="G11" t="n">
-        <v>-2003720</v>
+        <v>11631631</v>
       </c>
       <c r="H11" t="n">
-        <v>-13468593</v>
+        <v>16814146</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>金像電</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-1960698</v>
+        <v>732671</v>
       </c>
       <c r="E12" t="n">
-        <v>907139</v>
+        <v>-2121076</v>
       </c>
       <c r="F12" t="n">
-        <v>-1353369</v>
+        <v>-5797769</v>
       </c>
       <c r="G12" t="n">
-        <v>508917</v>
+        <v>-5338396</v>
       </c>
       <c r="H12" t="n">
-        <v>2727161</v>
+        <v>2216798</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>致茂</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-1253755</v>
+        <v>155186</v>
       </c>
       <c r="E13" t="n">
-        <v>970654</v>
+        <v>260255</v>
       </c>
       <c r="F13" t="n">
-        <v>2131851</v>
+        <v>-4705299</v>
       </c>
       <c r="G13" t="n">
-        <v>3116399</v>
+        <v>-4846994</v>
       </c>
       <c r="H13" t="n">
-        <v>2126185</v>
+        <v>-10583640</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>亞力</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>📉 20d 巨變(減碼 -60,185 千)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2249371</v>
+        <v>90384984</v>
       </c>
       <c r="E14" t="n">
-        <v>1545319</v>
+        <v>119499613</v>
       </c>
       <c r="F14" t="n">
-        <v>-7728913</v>
+        <v>439719735</v>
       </c>
       <c r="G14" t="n">
-        <v>-5518300</v>
+        <v>499904271</v>
       </c>
       <c r="H14" t="n">
-        <v>-6206692</v>
+        <v>465457565</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 12,168 千)</t>
+          <t>📉 20d 巨變(減碼 -10,683 千)</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-72582</v>
+        <v>76196536</v>
       </c>
       <c r="E15" t="n">
-        <v>-23534715</v>
+        <v>86320245</v>
       </c>
       <c r="F15" t="n">
-        <v>-126281282</v>
+        <v>247313872</v>
       </c>
       <c r="G15" t="n">
-        <v>-138449378</v>
+        <v>257997143</v>
       </c>
       <c r="H15" t="n">
-        <v>-261533501</v>
+        <v>112180166</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 9,026 千)</t>
+          <t>📈 20d 巨變(加碼 22,435 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>119499613</v>
+        <v>120846109</v>
       </c>
       <c r="E16" t="n">
-        <v>108405340</v>
+        <v>65494730</v>
       </c>
       <c r="F16" t="n">
-        <v>499904271</v>
+        <v>131810596</v>
       </c>
       <c r="G16" t="n">
-        <v>490877831</v>
+        <v>109375506</v>
       </c>
       <c r="H16" t="n">
-        <v>456520564</v>
+        <v>81321065</v>
       </c>
       <c r="I16" t="inlineStr">
-        <is>
-          <t>長榮航</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>3045</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 8,371 千)</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="n">
-        <v>8164230</v>
-      </c>
-      <c r="E17" t="n">
-        <v>11870276</v>
-      </c>
-      <c r="F17" t="n">
-        <v>120873873</v>
-      </c>
-      <c r="G17" t="n">
-        <v>112502543</v>
-      </c>
-      <c r="H17" t="n">
-        <v>72171567</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>台灣大</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 44,363 千)</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>86320245</v>
-      </c>
-      <c r="E18" t="n">
-        <v>54729872</v>
-      </c>
-      <c r="F18" t="n">
-        <v>257997143</v>
-      </c>
-      <c r="G18" t="n">
-        <v>213634222</v>
-      </c>
-      <c r="H18" t="n">
-        <v>153894040</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2301</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 32,203 千)</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>60262588</v>
-      </c>
-      <c r="E19" t="n">
-        <v>28471203</v>
-      </c>
-      <c r="F19" t="n">
-        <v>50382051</v>
-      </c>
-      <c r="G19" t="n">
-        <v>18178800</v>
-      </c>
-      <c r="H19" t="n">
-        <v>78511071</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>光寶科</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2317</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 54,911 千)</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>65494730</v>
-      </c>
-      <c r="E20" t="n">
-        <v>27201353</v>
-      </c>
-      <c r="F20" t="n">
-        <v>109375506</v>
-      </c>
-      <c r="G20" t="n">
-        <v>54464068</v>
-      </c>
-      <c r="H20" t="n">
-        <v>78477635</v>
-      </c>
-      <c r="I20" t="inlineStr">
         <is>
           <t>鴻海</t>
         </is>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,182 +466,182 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 11,927 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -23,192 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>51644971</v>
+        <v>-1805053</v>
       </c>
       <c r="E2" t="n">
-        <v>41793866</v>
+        <v>1636359</v>
       </c>
       <c r="F2" t="n">
-        <v>-13188893</v>
+        <v>105156611</v>
       </c>
       <c r="G2" t="n">
-        <v>-25115508</v>
+        <v>128348387</v>
       </c>
       <c r="H2" t="n">
-        <v>64424481</v>
+        <v>82272976</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 9,307 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -13,282 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>20208805</v>
+        <v>56275822</v>
       </c>
       <c r="E3" t="n">
-        <v>15000836</v>
+        <v>51644971</v>
       </c>
       <c r="F3" t="n">
-        <v>58685658</v>
+        <v>-26471323</v>
       </c>
       <c r="G3" t="n">
-        <v>49378870</v>
+        <v>-13188893</v>
       </c>
       <c r="H3" t="n">
-        <v>-44108702</v>
+        <v>66572051</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 12,753 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>6128018</v>
+        <v>2443174</v>
       </c>
       <c r="E4" t="n">
-        <v>14297808</v>
+        <v>3726178</v>
       </c>
       <c r="F4" t="n">
-        <v>114545213</v>
+        <v>3776296</v>
       </c>
       <c r="G4" t="n">
-        <v>101792510</v>
+        <v>4400332</v>
       </c>
       <c r="H4" t="n">
-        <v>-26021132</v>
+        <v>-20700247</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📉 20d 巨變(減碼 -27,141 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>14607099</v>
+        <v>4351053</v>
       </c>
       <c r="E5" t="n">
-        <v>69684964</v>
+        <v>5376976</v>
       </c>
       <c r="F5" t="n">
-        <v>-31660278</v>
+        <v>4717425</v>
       </c>
       <c r="G5" t="n">
-        <v>-4519770</v>
+        <v>4912635</v>
       </c>
       <c r="H5" t="n">
-        <v>-170070129</v>
+        <v>-50739111</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>3726178</v>
+        <v>1625479</v>
       </c>
       <c r="E6" t="n">
-        <v>4019376</v>
+        <v>-1373383</v>
       </c>
       <c r="F6" t="n">
-        <v>4400332</v>
+        <v>-4749654</v>
       </c>
       <c r="G6" t="n">
-        <v>4432401</v>
+        <v>-4333145</v>
       </c>
       <c r="H6" t="n">
-        <v>-20555226</v>
+        <v>-36680225</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>瑞昱</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,30 +653,30 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>5376976</v>
+        <v>19554982</v>
       </c>
       <c r="E7" t="n">
-        <v>8547026</v>
+        <v>20208805</v>
       </c>
       <c r="F7" t="n">
-        <v>4912635</v>
+        <v>56417558</v>
       </c>
       <c r="G7" t="n">
-        <v>4312930</v>
+        <v>58685658</v>
       </c>
       <c r="H7" t="n">
-        <v>-51629075</v>
+        <v>-42629239</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,23 +688,23 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>2502737</v>
+        <v>760365</v>
       </c>
       <c r="E8" t="n">
-        <v>1769794</v>
+        <v>6128018</v>
       </c>
       <c r="F8" t="n">
-        <v>405654</v>
+        <v>108976760</v>
       </c>
       <c r="G8" t="n">
-        <v>-2004547</v>
+        <v>114545213</v>
       </c>
       <c r="H8" t="n">
-        <v>-10302149</v>
+        <v>-24613614</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
@@ -723,19 +723,19 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
+        <v>7319153</v>
+      </c>
+      <c r="E9" t="n">
         <v>9655676</v>
       </c>
-      <c r="E9" t="n">
-        <v>16211932</v>
-      </c>
       <c r="F9" t="n">
+        <v>76134845</v>
+      </c>
+      <c r="G9" t="n">
         <v>80770627</v>
       </c>
-      <c r="G9" t="n">
-        <v>78702261</v>
-      </c>
       <c r="H9" t="n">
-        <v>-102622764</v>
+        <v>-101678311</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -758,19 +758,19 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
+        <v>1470619</v>
+      </c>
+      <c r="E10" t="n">
         <v>59001</v>
       </c>
-      <c r="E10" t="n">
-        <v>-1533703</v>
-      </c>
       <c r="F10" t="n">
+        <v>-7397391</v>
+      </c>
+      <c r="G10" t="n">
         <v>-8158176</v>
       </c>
-      <c r="G10" t="n">
-        <v>-8233752</v>
-      </c>
       <c r="H10" t="n">
-        <v>-11385036</v>
+        <v>-11313388</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -793,19 +793,19 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
+        <v>-3360115</v>
+      </c>
+      <c r="E11" t="n">
         <v>-2529669</v>
       </c>
-      <c r="E11" t="n">
-        <v>-2359353</v>
-      </c>
       <c r="F11" t="n">
+        <v>8471703</v>
+      </c>
+      <c r="G11" t="n">
         <v>11196326</v>
       </c>
-      <c r="G11" t="n">
-        <v>11631631</v>
-      </c>
       <c r="H11" t="n">
-        <v>16814146</v>
+        <v>16016270</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -816,173 +816,243 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🔴 5d 翻紅 / 📉 20d 巨變(減碼 -36,532 千)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>732671</v>
+        <v>-22102683</v>
       </c>
       <c r="E12" t="n">
-        <v>-2121076</v>
+        <v>14607099</v>
       </c>
       <c r="F12" t="n">
-        <v>-5797769</v>
+        <v>-68192106</v>
       </c>
       <c r="G12" t="n">
-        <v>-5338396</v>
+        <v>-31660278</v>
       </c>
       <c r="H12" t="n">
-        <v>2216798</v>
+        <v>-213401584</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>155186</v>
+        <v>2822049</v>
       </c>
       <c r="E13" t="n">
-        <v>260255</v>
+        <v>732671</v>
       </c>
       <c r="F13" t="n">
-        <v>-4705299</v>
+        <v>-6435363</v>
       </c>
       <c r="G13" t="n">
-        <v>-4846994</v>
+        <v>-5797769</v>
       </c>
       <c r="H13" t="n">
-        <v>-10583640</v>
+        <v>2361498</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>致茂</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -60,185 千)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>90384984</v>
+        <v>-1588329</v>
       </c>
       <c r="E14" t="n">
-        <v>119499613</v>
+        <v>708473</v>
       </c>
       <c r="F14" t="n">
-        <v>439719735</v>
+        <v>5356</v>
       </c>
       <c r="G14" t="n">
-        <v>499904271</v>
+        <v>5035078</v>
       </c>
       <c r="H14" t="n">
-        <v>465457565</v>
+        <v>-3464765</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -10,683 千)</t>
+          <t>📈 20d 巨變(加碼 13,390 千)</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>76196536</v>
+        <v>-13265018</v>
       </c>
       <c r="E15" t="n">
-        <v>86320245</v>
+        <v>-126579</v>
       </c>
       <c r="F15" t="n">
-        <v>247313872</v>
+        <v>-112747361</v>
       </c>
       <c r="G15" t="n">
-        <v>257997143</v>
+        <v>-126137562</v>
       </c>
       <c r="H15" t="n">
-        <v>112180166</v>
+        <v>-260632965</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 22,435 千)</t>
+          <t>📉 20d 巨變(減碼 -11,990 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
+        <v>72372811</v>
+      </c>
+      <c r="E16" t="n">
+        <v>90384984</v>
+      </c>
+      <c r="F16" t="n">
+        <v>427729983</v>
+      </c>
+      <c r="G16" t="n">
+        <v>439719735</v>
+      </c>
+      <c r="H16" t="n">
+        <v>487457938</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>長榮航</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 22,572 千)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>75073382</v>
+      </c>
+      <c r="E17" t="n">
+        <v>76196536</v>
+      </c>
+      <c r="F17" t="n">
+        <v>269885673</v>
+      </c>
+      <c r="G17" t="n">
+        <v>247313872</v>
+      </c>
+      <c r="H17" t="n">
+        <v>129338376</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -11,071 千)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>65659835</v>
+      </c>
+      <c r="E18" t="n">
         <v>120846109</v>
       </c>
-      <c r="E16" t="n">
-        <v>65494730</v>
-      </c>
-      <c r="F16" t="n">
+      <c r="F18" t="n">
+        <v>120739342</v>
+      </c>
+      <c r="G18" t="n">
         <v>131810596</v>
       </c>
-      <c r="G16" t="n">
-        <v>109375506</v>
-      </c>
-      <c r="H16" t="n">
-        <v>81321065</v>
-      </c>
-      <c r="I16" t="inlineStr">
+      <c r="H18" t="n">
+        <v>75992936</v>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>鴻海</t>
         </is>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,112 +466,112 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -23,192 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>-1805053</v>
+        <v>-3660172</v>
       </c>
       <c r="E2" t="n">
-        <v>1636359</v>
+        <v>760365</v>
       </c>
       <c r="F2" t="n">
-        <v>105156611</v>
+        <v>106631237</v>
       </c>
       <c r="G2" t="n">
-        <v>128348387</v>
+        <v>108976760</v>
       </c>
       <c r="H2" t="n">
-        <v>82272976</v>
+        <v>-10455367</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -13,282 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>56275822</v>
+        <v>3453510</v>
       </c>
       <c r="E3" t="n">
-        <v>51644971</v>
+        <v>-1259091</v>
       </c>
       <c r="F3" t="n">
-        <v>-26471323</v>
+        <v>-24415957</v>
       </c>
       <c r="G3" t="n">
-        <v>-13188893</v>
+        <v>-25525302</v>
       </c>
       <c r="H3" t="n">
-        <v>66572051</v>
+        <v>-48083435</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -11,729 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>2443174</v>
+        <v>-3832561</v>
       </c>
       <c r="E4" t="n">
-        <v>3726178</v>
+        <v>-1805053</v>
       </c>
       <c r="F4" t="n">
-        <v>3776296</v>
+        <v>93427674</v>
       </c>
       <c r="G4" t="n">
-        <v>4400332</v>
+        <v>105156611</v>
       </c>
       <c r="H4" t="n">
-        <v>-20700247</v>
+        <v>98953244</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,100 +583,100 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>4351053</v>
+        <v>2255926</v>
       </c>
       <c r="E5" t="n">
-        <v>5376976</v>
+        <v>2443174</v>
       </c>
       <c r="F5" t="n">
-        <v>4717425</v>
+        <v>3864585</v>
       </c>
       <c r="G5" t="n">
-        <v>4912635</v>
+        <v>3776296</v>
       </c>
       <c r="H5" t="n">
-        <v>-50739111</v>
+        <v>-18766116</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1625479</v>
+        <v>4064690</v>
       </c>
       <c r="E6" t="n">
-        <v>-1373383</v>
+        <v>4351053</v>
       </c>
       <c r="F6" t="n">
-        <v>-4749654</v>
+        <v>3431998</v>
       </c>
       <c r="G6" t="n">
-        <v>-4333145</v>
+        <v>4717425</v>
       </c>
       <c r="H6" t="n">
-        <v>-36680225</v>
+        <v>-40780445</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>19554982</v>
+        <v>-87610</v>
       </c>
       <c r="E7" t="n">
-        <v>20208805</v>
+        <v>597489</v>
       </c>
       <c r="F7" t="n">
-        <v>56417558</v>
+        <v>7177572</v>
       </c>
       <c r="G7" t="n">
-        <v>58685658</v>
+        <v>5228940</v>
       </c>
       <c r="H7" t="n">
-        <v>-42629239</v>
+        <v>14444890</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,338 +688,338 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>760365</v>
+        <v>2763060</v>
       </c>
       <c r="E8" t="n">
-        <v>6128018</v>
+        <v>7319153</v>
       </c>
       <c r="F8" t="n">
-        <v>108976760</v>
+        <v>75675435</v>
       </c>
       <c r="G8" t="n">
-        <v>114545213</v>
+        <v>76134845</v>
       </c>
       <c r="H8" t="n">
-        <v>-24613614</v>
+        <v>-92191165</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>7319153</v>
+        <v>1715277</v>
       </c>
       <c r="E9" t="n">
-        <v>9655676</v>
+        <v>1470619</v>
       </c>
       <c r="F9" t="n">
-        <v>76134845</v>
+        <v>-5233338</v>
       </c>
       <c r="G9" t="n">
-        <v>80770627</v>
+        <v>-7397391</v>
       </c>
       <c r="H9" t="n">
-        <v>-101678311</v>
+        <v>-10115259</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1470619</v>
+        <v>-5551959</v>
       </c>
       <c r="E10" t="n">
-        <v>59001</v>
+        <v>-3360115</v>
       </c>
       <c r="F10" t="n">
-        <v>-7397391</v>
+        <v>4600438</v>
       </c>
       <c r="G10" t="n">
-        <v>-8158176</v>
+        <v>8471703</v>
       </c>
       <c r="H10" t="n">
-        <v>-11313388</v>
+        <v>14095033</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>金像電</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-3360115</v>
+        <v>1210368</v>
       </c>
       <c r="E11" t="n">
-        <v>-2529669</v>
+        <v>1625479</v>
       </c>
       <c r="F11" t="n">
-        <v>8471703</v>
+        <v>-1736795</v>
       </c>
       <c r="G11" t="n">
-        <v>11196326</v>
+        <v>-4749654</v>
       </c>
       <c r="H11" t="n">
-        <v>16016270</v>
+        <v>-36879777</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>瑞昱</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅 / 📉 20d 巨變(減碼 -36,532 千)</t>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-22102683</v>
+        <v>3543783</v>
       </c>
       <c r="E12" t="n">
-        <v>14607099</v>
+        <v>2822049</v>
       </c>
       <c r="F12" t="n">
-        <v>-68192106</v>
+        <v>-6720003</v>
       </c>
       <c r="G12" t="n">
-        <v>-31660278</v>
+        <v>-6435363</v>
       </c>
       <c r="H12" t="n">
-        <v>-213401584</v>
+        <v>1660958</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>致茂</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>2822049</v>
+        <v>1328699</v>
       </c>
       <c r="E13" t="n">
-        <v>732671</v>
+        <v>-1588329</v>
       </c>
       <c r="F13" t="n">
-        <v>-6435363</v>
+        <v>3411489</v>
       </c>
       <c r="G13" t="n">
-        <v>-5797769</v>
+        <v>5356</v>
       </c>
       <c r="H13" t="n">
-        <v>2361498</v>
+        <v>-562210</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>📉 20d 巨變(減碼 -58,376 千)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1588329</v>
+        <v>58403023</v>
       </c>
       <c r="E14" t="n">
-        <v>708473</v>
+        <v>72372811</v>
       </c>
       <c r="F14" t="n">
-        <v>5356</v>
+        <v>369354221</v>
       </c>
       <c r="G14" t="n">
-        <v>5035078</v>
+        <v>427729983</v>
       </c>
       <c r="H14" t="n">
-        <v>-3464765</v>
+        <v>528287725</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 13,390 千)</t>
+          <t>📈 20d 巨變(加碼 59,538 千)</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-13265018</v>
+        <v>73896644</v>
       </c>
       <c r="E15" t="n">
-        <v>-126579</v>
+        <v>56275822</v>
       </c>
       <c r="F15" t="n">
-        <v>-112747361</v>
+        <v>33067040</v>
       </c>
       <c r="G15" t="n">
-        <v>-126137562</v>
+        <v>-26471323</v>
       </c>
       <c r="H15" t="n">
-        <v>-260632965</v>
+        <v>91052626</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -11,990 千)</t>
+          <t>📈 20d 巨變(加碼 12,302 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>72372811</v>
+        <v>70763174</v>
       </c>
       <c r="E16" t="n">
-        <v>90384984</v>
+        <v>75073382</v>
       </c>
       <c r="F16" t="n">
-        <v>427729983</v>
+        <v>282188032</v>
       </c>
       <c r="G16" t="n">
-        <v>439719735</v>
+        <v>269885673</v>
       </c>
       <c r="H16" t="n">
-        <v>487457938</v>
+        <v>128735885</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 22,572 千)</t>
+          <t>📈 20d 巨變(加碼 33,796 千)</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>75073382</v>
+        <v>14178423</v>
       </c>
       <c r="E17" t="n">
-        <v>76196536</v>
+        <v>19554982</v>
       </c>
       <c r="F17" t="n">
-        <v>269885673</v>
+        <v>90213642</v>
       </c>
       <c r="G17" t="n">
-        <v>247313872</v>
+        <v>56417558</v>
       </c>
       <c r="H17" t="n">
-        <v>129338376</v>
+        <v>10794787</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
@@ -1031,30 +1031,65 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -11,071 千)</t>
+          <t>📈 20d 巨變(加碼 9,061 千)</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
+        <v>63405217</v>
+      </c>
+      <c r="E18" t="n">
         <v>65659835</v>
       </c>
-      <c r="E18" t="n">
-        <v>120846109</v>
-      </c>
       <c r="F18" t="n">
+        <v>129800285</v>
+      </c>
+      <c r="G18" t="n">
         <v>120739342</v>
       </c>
-      <c r="G18" t="n">
-        <v>131810596</v>
-      </c>
       <c r="H18" t="n">
-        <v>75992936</v>
+        <v>22542677</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>鴻海</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 32,705 千)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-29042645</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-22102683</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-35487257</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-68192106</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-313321960</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>華邦電</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -466,147 +466,147 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 15,914 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-3660172</v>
+        <v>12498779</v>
       </c>
       <c r="E2" t="n">
-        <v>760365</v>
+        <v>-3428975</v>
       </c>
       <c r="F2" t="n">
-        <v>106631237</v>
+        <v>-94669017</v>
       </c>
       <c r="G2" t="n">
-        <v>108976760</v>
+        <v>-110583463</v>
       </c>
       <c r="H2" t="n">
-        <v>-10455367</v>
+        <v>-262123586</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 41,840 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>3453510</v>
+        <v>4191206</v>
       </c>
       <c r="E3" t="n">
-        <v>-1259091</v>
+        <v>-29042645</v>
       </c>
       <c r="F3" t="n">
-        <v>-24415957</v>
+        <v>6352940</v>
       </c>
       <c r="G3" t="n">
-        <v>-25525302</v>
+        <v>-35487257</v>
       </c>
       <c r="H3" t="n">
-        <v>-48083435</v>
+        <v>-290223876</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -11,729 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>-3832561</v>
+        <v>-2437003</v>
       </c>
       <c r="E4" t="n">
-        <v>-1805053</v>
+        <v>-3660172</v>
       </c>
       <c r="F4" t="n">
-        <v>93427674</v>
+        <v>107269851</v>
       </c>
       <c r="G4" t="n">
-        <v>105156611</v>
+        <v>106631237</v>
       </c>
       <c r="H4" t="n">
-        <v>98953244</v>
+        <v>-6934332</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -9,310 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>2255926</v>
+        <v>-3181586</v>
       </c>
       <c r="E5" t="n">
-        <v>2443174</v>
+        <v>-3832561</v>
       </c>
       <c r="F5" t="n">
-        <v>3864585</v>
+        <v>84117724</v>
       </c>
       <c r="G5" t="n">
-        <v>3776296</v>
+        <v>93427674</v>
       </c>
       <c r="H5" t="n">
-        <v>-18766116</v>
+        <v>102987488</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,163 +618,163 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>4064690</v>
+        <v>1188437</v>
       </c>
       <c r="E6" t="n">
-        <v>4351053</v>
+        <v>2255926</v>
       </c>
       <c r="F6" t="n">
-        <v>3431998</v>
+        <v>4326672</v>
       </c>
       <c r="G6" t="n">
-        <v>4717425</v>
+        <v>3864585</v>
       </c>
       <c r="H6" t="n">
-        <v>-40780445</v>
+        <v>-13965287</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-87610</v>
+        <v>1755558</v>
       </c>
       <c r="E7" t="n">
-        <v>597489</v>
+        <v>4064690</v>
       </c>
       <c r="F7" t="n">
-        <v>7177572</v>
+        <v>2061572</v>
       </c>
       <c r="G7" t="n">
-        <v>5228940</v>
+        <v>3431998</v>
       </c>
       <c r="H7" t="n">
-        <v>14444890</v>
+        <v>-33224974</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>2763060</v>
+        <v>-941919</v>
       </c>
       <c r="E8" t="n">
-        <v>7319153</v>
+        <v>-87610</v>
       </c>
       <c r="F8" t="n">
-        <v>75675435</v>
+        <v>6112239</v>
       </c>
       <c r="G8" t="n">
-        <v>76134845</v>
+        <v>7177572</v>
       </c>
       <c r="H8" t="n">
-        <v>-92191165</v>
+        <v>13037499</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1715277</v>
+        <v>2660348</v>
       </c>
       <c r="E9" t="n">
-        <v>1470619</v>
+        <v>2763060</v>
       </c>
       <c r="F9" t="n">
-        <v>-5233338</v>
+        <v>74010933</v>
       </c>
       <c r="G9" t="n">
-        <v>-7397391</v>
+        <v>75675435</v>
       </c>
       <c r="H9" t="n">
-        <v>-10115259</v>
+        <v>-86697932</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>-5551959</v>
+        <v>-897125</v>
       </c>
       <c r="E10" t="n">
-        <v>-3360115</v>
+        <v>1227205</v>
       </c>
       <c r="F10" t="n">
-        <v>4600438</v>
+        <v>5927164</v>
       </c>
       <c r="G10" t="n">
-        <v>8471703</v>
+        <v>11915188</v>
       </c>
       <c r="H10" t="n">
-        <v>14095033</v>
+        <v>826547</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>立隆電</t>
         </is>
       </c>
     </row>
@@ -793,19 +793,19 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
+        <v>1168371</v>
+      </c>
+      <c r="E11" t="n">
         <v>1210368</v>
       </c>
-      <c r="E11" t="n">
-        <v>1625479</v>
-      </c>
       <c r="F11" t="n">
+        <v>-1217741</v>
+      </c>
+      <c r="G11" t="n">
         <v>-1736795</v>
       </c>
-      <c r="G11" t="n">
-        <v>-4749654</v>
-      </c>
       <c r="H11" t="n">
-        <v>-36879777</v>
+        <v>-37212329</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -816,280 +816,280 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>3543783</v>
+        <v>3153658</v>
       </c>
       <c r="E12" t="n">
-        <v>2822049</v>
+        <v>1715277</v>
       </c>
       <c r="F12" t="n">
-        <v>-6720003</v>
+        <v>-4620995</v>
       </c>
       <c r="G12" t="n">
-        <v>-6435363</v>
+        <v>-5233338</v>
       </c>
       <c r="H12" t="n">
-        <v>1660958</v>
+        <v>-12275804</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>1328699</v>
+        <v>-2300496</v>
       </c>
       <c r="E13" t="n">
-        <v>-1588329</v>
+        <v>-5551959</v>
       </c>
       <c r="F13" t="n">
-        <v>3411489</v>
+        <v>4491271</v>
       </c>
       <c r="G13" t="n">
-        <v>5356</v>
+        <v>4600438</v>
       </c>
       <c r="H13" t="n">
-        <v>-562210</v>
+        <v>15457916</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>金像電</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -58,376 千)</t>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>58403023</v>
+        <v>1693836</v>
       </c>
       <c r="E14" t="n">
-        <v>72372811</v>
+        <v>3543783</v>
       </c>
       <c r="F14" t="n">
-        <v>369354221</v>
+        <v>-6987519</v>
       </c>
       <c r="G14" t="n">
-        <v>427729983</v>
+        <v>-6720003</v>
       </c>
       <c r="H14" t="n">
-        <v>528287725</v>
+        <v>2025005</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>致茂</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 59,538 千)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>73896644</v>
+        <v>-4764236</v>
       </c>
       <c r="E15" t="n">
-        <v>56275822</v>
+        <v>3453510</v>
       </c>
       <c r="F15" t="n">
-        <v>33067040</v>
+        <v>-26641559</v>
       </c>
       <c r="G15" t="n">
-        <v>-26471323</v>
+        <v>-24415957</v>
       </c>
       <c r="H15" t="n">
-        <v>91052626</v>
+        <v>-56228525</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 12,302 千)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>70763174</v>
+        <v>-205134</v>
       </c>
       <c r="E16" t="n">
-        <v>75073382</v>
+        <v>2480704</v>
       </c>
       <c r="F16" t="n">
-        <v>282188032</v>
+        <v>-633034</v>
       </c>
       <c r="G16" t="n">
-        <v>269885673</v>
+        <v>2909045</v>
       </c>
       <c r="H16" t="n">
-        <v>128735885</v>
+        <v>896856</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>華星光</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 33,796 千)</t>
+          <t>📉 20d 巨變(減碼 -47,761 千)</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>14178423</v>
+        <v>44699944</v>
       </c>
       <c r="E17" t="n">
-        <v>19554982</v>
+        <v>58403023</v>
       </c>
       <c r="F17" t="n">
-        <v>90213642</v>
+        <v>321593054</v>
       </c>
       <c r="G17" t="n">
-        <v>56417558</v>
+        <v>369354221</v>
       </c>
       <c r="H17" t="n">
-        <v>10794787</v>
+        <v>561190142</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 9,061 千)</t>
+          <t>📈 20d 巨變(加碼 15,193 千)</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>63405217</v>
+        <v>64269472</v>
       </c>
       <c r="E18" t="n">
-        <v>65659835</v>
+        <v>73896644</v>
       </c>
       <c r="F18" t="n">
-        <v>129800285</v>
+        <v>48259831</v>
       </c>
       <c r="G18" t="n">
-        <v>120739342</v>
+        <v>33067040</v>
       </c>
       <c r="H18" t="n">
-        <v>22542677</v>
+        <v>100478534</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 32,705 千)</t>
+          <t>📉 20d 巨變(減碼 -12,395 千)</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-29042645</v>
+        <v>-26078598</v>
       </c>
       <c r="E19" t="n">
-        <v>-22102683</v>
+        <v>-24281330</v>
       </c>
       <c r="F19" t="n">
-        <v>-35487257</v>
+        <v>-37682076</v>
       </c>
       <c r="G19" t="n">
-        <v>-68192106</v>
+        <v>-25287318</v>
       </c>
       <c r="H19" t="n">
-        <v>-313321960</v>
+        <v>-91394244</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -471,26 +471,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 15,914 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
+        <v>2874444</v>
+      </c>
+      <c r="E2" t="n">
         <v>12498779</v>
       </c>
-      <c r="E2" t="n">
-        <v>-3428975</v>
-      </c>
       <c r="F2" t="n">
+        <v>-88614833</v>
+      </c>
+      <c r="G2" t="n">
         <v>-94669017</v>
       </c>
-      <c r="G2" t="n">
-        <v>-110583463</v>
-      </c>
       <c r="H2" t="n">
-        <v>-262123586</v>
+        <v>-252418068</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -501,112 +501,112 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 41,840 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>4191206</v>
+        <v>-2697219</v>
       </c>
       <c r="E3" t="n">
-        <v>-29042645</v>
+        <v>-3181586</v>
       </c>
       <c r="F3" t="n">
-        <v>6352940</v>
+        <v>82130726</v>
       </c>
       <c r="G3" t="n">
-        <v>-35487257</v>
+        <v>84117724</v>
       </c>
       <c r="H3" t="n">
-        <v>-290223876</v>
+        <v>104853360</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>-2437003</v>
+        <v>523372</v>
       </c>
       <c r="E4" t="n">
-        <v>-3660172</v>
+        <v>1755558</v>
       </c>
       <c r="F4" t="n">
-        <v>107269851</v>
+        <v>1283553</v>
       </c>
       <c r="G4" t="n">
-        <v>106631237</v>
+        <v>2061572</v>
       </c>
       <c r="H4" t="n">
-        <v>-6934332</v>
+        <v>-25731567</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -9,310 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>-3181586</v>
+        <v>-4766561</v>
       </c>
       <c r="E5" t="n">
-        <v>-3832561</v>
+        <v>-2437003</v>
       </c>
       <c r="F5" t="n">
-        <v>84117724</v>
+        <v>106412566</v>
       </c>
       <c r="G5" t="n">
-        <v>93427674</v>
+        <v>107269851</v>
       </c>
       <c r="H5" t="n">
-        <v>102987488</v>
+        <v>1294197</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,478 +618,478 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1188437</v>
+        <v>182500</v>
       </c>
       <c r="E6" t="n">
-        <v>2255926</v>
+        <v>2660348</v>
       </c>
       <c r="F6" t="n">
-        <v>4326672</v>
+        <v>72203461</v>
       </c>
       <c r="G6" t="n">
-        <v>3864585</v>
+        <v>74010933</v>
       </c>
       <c r="H6" t="n">
-        <v>-13965287</v>
+        <v>-84113649</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1755558</v>
+        <v>-5622234</v>
       </c>
       <c r="E7" t="n">
-        <v>4064690</v>
+        <v>-2300496</v>
       </c>
       <c r="F7" t="n">
-        <v>2061572</v>
+        <v>468754</v>
       </c>
       <c r="G7" t="n">
-        <v>3431998</v>
+        <v>4491271</v>
       </c>
       <c r="H7" t="n">
-        <v>-33224974</v>
+        <v>11597081</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>金像電</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>-941919</v>
+        <v>17477</v>
       </c>
       <c r="E8" t="n">
-        <v>-87610</v>
+        <v>1168371</v>
       </c>
       <c r="F8" t="n">
-        <v>6112239</v>
+        <v>-1259436</v>
       </c>
       <c r="G8" t="n">
-        <v>7177572</v>
+        <v>-1217741</v>
       </c>
       <c r="H8" t="n">
-        <v>13037499</v>
+        <v>-37434477</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>瑞昱</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>2660348</v>
+        <v>-2632383</v>
       </c>
       <c r="E9" t="n">
-        <v>2763060</v>
+        <v>-941919</v>
       </c>
       <c r="F9" t="n">
-        <v>74010933</v>
+        <v>4514692</v>
       </c>
       <c r="G9" t="n">
-        <v>75675435</v>
+        <v>6112239</v>
       </c>
       <c r="H9" t="n">
-        <v>-86697932</v>
+        <v>11697628</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-897125</v>
+        <v>1455284</v>
       </c>
       <c r="E10" t="n">
-        <v>1227205</v>
+        <v>3153658</v>
       </c>
       <c r="F10" t="n">
-        <v>5927164</v>
+        <v>-3161512</v>
       </c>
       <c r="G10" t="n">
-        <v>11915188</v>
+        <v>-4620995</v>
       </c>
       <c r="H10" t="n">
-        <v>826547</v>
+        <v>-11270844</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🔴 5d 翻紅 / 📉 20d 巨變(減碼 -45,647 千)</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>1168371</v>
+        <v>-35873745</v>
       </c>
       <c r="E11" t="n">
-        <v>1210368</v>
+        <v>4191206</v>
       </c>
       <c r="F11" t="n">
-        <v>-1217741</v>
+        <v>-39294461</v>
       </c>
       <c r="G11" t="n">
-        <v>-1736795</v>
+        <v>6352940</v>
       </c>
       <c r="H11" t="n">
-        <v>-37212329</v>
+        <v>-269191678</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>3153658</v>
+        <v>803879</v>
       </c>
       <c r="E12" t="n">
-        <v>1715277</v>
+        <v>1693836</v>
       </c>
       <c r="F12" t="n">
-        <v>-4620995</v>
+        <v>-7096887</v>
       </c>
       <c r="G12" t="n">
-        <v>-5233338</v>
+        <v>-6987519</v>
       </c>
       <c r="H12" t="n">
-        <v>-12275804</v>
+        <v>2113144</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>致茂</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-2300496</v>
+        <v>-409587</v>
       </c>
       <c r="E13" t="n">
-        <v>-5551959</v>
+        <v>-897125</v>
       </c>
       <c r="F13" t="n">
-        <v>4491271</v>
+        <v>7038822</v>
       </c>
       <c r="G13" t="n">
-        <v>4600438</v>
+        <v>5927164</v>
       </c>
       <c r="H13" t="n">
-        <v>15457916</v>
+        <v>1419937</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>立隆電</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>1693836</v>
+        <v>2015361</v>
       </c>
       <c r="E14" t="n">
-        <v>3543783</v>
+        <v>-205134</v>
       </c>
       <c r="F14" t="n">
-        <v>-6987519</v>
+        <v>1785572</v>
       </c>
       <c r="G14" t="n">
-        <v>-6720003</v>
+        <v>-633034</v>
       </c>
       <c r="H14" t="n">
-        <v>2025005</v>
+        <v>4016944</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>華星光</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>📉 20d 巨變(減碼 -25,712 千)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-4764236</v>
+        <v>-33903117</v>
       </c>
       <c r="E15" t="n">
-        <v>3453510</v>
+        <v>-8267161</v>
       </c>
       <c r="F15" t="n">
-        <v>-26641559</v>
+        <v>-34419812</v>
       </c>
       <c r="G15" t="n">
-        <v>-24415957</v>
+        <v>-8707611</v>
       </c>
       <c r="H15" t="n">
-        <v>-56228525</v>
+        <v>-33032782</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>寶雅</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>📉 20d 巨變(減碼 -24,945 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-205134</v>
+        <v>20039266</v>
       </c>
       <c r="E16" t="n">
-        <v>2480704</v>
+        <v>44699944</v>
       </c>
       <c r="F16" t="n">
-        <v>-633034</v>
+        <v>296647820</v>
       </c>
       <c r="G16" t="n">
-        <v>2909045</v>
+        <v>321593054</v>
       </c>
       <c r="H16" t="n">
-        <v>896856</v>
+        <v>575720013</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -47,761 千)</t>
+          <t>📉 20d 巨變(減碼 -19,572 千)</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>44699944</v>
+        <v>42292721</v>
       </c>
       <c r="E17" t="n">
-        <v>58403023</v>
+        <v>64269472</v>
       </c>
       <c r="F17" t="n">
-        <v>321593054</v>
+        <v>28688331</v>
       </c>
       <c r="G17" t="n">
-        <v>369354221</v>
+        <v>48259831</v>
       </c>
       <c r="H17" t="n">
-        <v>561190142</v>
+        <v>23590243</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 15,193 千)</t>
+          <t>📈 20d 巨變(加碼 25,548 千)</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>64269472</v>
+        <v>35558772</v>
       </c>
       <c r="E18" t="n">
-        <v>73896644</v>
+        <v>4790271</v>
       </c>
       <c r="F18" t="n">
-        <v>48259831</v>
+        <v>119645121</v>
       </c>
       <c r="G18" t="n">
-        <v>33067040</v>
+        <v>94097255</v>
       </c>
       <c r="H18" t="n">
-        <v>100478534</v>
+        <v>25811017</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -12,395 千)</t>
+          <t>📈 20d 巨變(加碼 22,490 千)</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-26078598</v>
+        <v>52527942</v>
       </c>
       <c r="E19" t="n">
-        <v>-24281330</v>
+        <v>60135123</v>
       </c>
       <c r="F19" t="n">
-        <v>-37682076</v>
+        <v>158189205</v>
       </c>
       <c r="G19" t="n">
-        <v>-25287318</v>
+        <v>135698980</v>
       </c>
       <c r="H19" t="n">
-        <v>-91394244</v>
+        <v>18291747</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,217 +466,217 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -40,062 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>2874444</v>
+        <v>-2578438</v>
       </c>
       <c r="E2" t="n">
-        <v>12498779</v>
+        <v>52527942</v>
       </c>
       <c r="F2" t="n">
-        <v>-88614833</v>
+        <v>118127649</v>
       </c>
       <c r="G2" t="n">
-        <v>-94669017</v>
+        <v>158189205</v>
       </c>
       <c r="H2" t="n">
-        <v>-252418068</v>
+        <v>-95410202</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -10,469 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>-2697219</v>
+        <v>-1708608</v>
       </c>
       <c r="E3" t="n">
-        <v>-3181586</v>
+        <v>182500</v>
       </c>
       <c r="F3" t="n">
-        <v>82130726</v>
+        <v>61734379</v>
       </c>
       <c r="G3" t="n">
-        <v>84117724</v>
+        <v>72203461</v>
       </c>
       <c r="H3" t="n">
-        <v>104853360</v>
+        <v>-80177094</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 8,187 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>523372</v>
+        <v>10858127</v>
       </c>
       <c r="E4" t="n">
-        <v>1755558</v>
+        <v>2874444</v>
       </c>
       <c r="F4" t="n">
-        <v>1283553</v>
+        <v>-80427866</v>
       </c>
       <c r="G4" t="n">
-        <v>2061572</v>
+        <v>-88614833</v>
       </c>
       <c r="H4" t="n">
-        <v>-25731567</v>
+        <v>-261730109</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -18,913 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>-4766561</v>
+        <v>-8178225</v>
       </c>
       <c r="E5" t="n">
-        <v>-2437003</v>
+        <v>-2697219</v>
       </c>
       <c r="F5" t="n">
-        <v>106412566</v>
+        <v>63217716</v>
       </c>
       <c r="G5" t="n">
-        <v>107269851</v>
+        <v>82130726</v>
       </c>
       <c r="H5" t="n">
-        <v>1294197</v>
+        <v>103981760</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -15,575 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>182500</v>
+        <v>-5992547</v>
       </c>
       <c r="E6" t="n">
-        <v>2660348</v>
+        <v>-4766561</v>
       </c>
       <c r="F6" t="n">
-        <v>72203461</v>
+        <v>90837725</v>
       </c>
       <c r="G6" t="n">
-        <v>74010933</v>
+        <v>106412566</v>
       </c>
       <c r="H6" t="n">
-        <v>-84113649</v>
+        <v>5806417</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-5622234</v>
+        <v>-719540</v>
       </c>
       <c r="E7" t="n">
-        <v>-2300496</v>
+        <v>523372</v>
       </c>
       <c r="F7" t="n">
-        <v>468754</v>
+        <v>772661</v>
       </c>
       <c r="G7" t="n">
-        <v>4491271</v>
+        <v>1283553</v>
       </c>
       <c r="H7" t="n">
-        <v>11597081</v>
+        <v>-20801746</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,408 +688,373 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>17477</v>
+        <v>-2935294</v>
       </c>
       <c r="E8" t="n">
-        <v>1168371</v>
+        <v>-2632383</v>
       </c>
       <c r="F8" t="n">
-        <v>-1259436</v>
+        <v>3904426</v>
       </c>
       <c r="G8" t="n">
-        <v>-1217741</v>
+        <v>4514692</v>
       </c>
       <c r="H8" t="n">
-        <v>-37434477</v>
+        <v>11310024</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-2632383</v>
+        <v>280865</v>
       </c>
       <c r="E9" t="n">
-        <v>-941919</v>
+        <v>803879</v>
       </c>
       <c r="F9" t="n">
-        <v>4514692</v>
+        <v>-5703919</v>
       </c>
       <c r="G9" t="n">
-        <v>6112239</v>
+        <v>-7096887</v>
       </c>
       <c r="H9" t="n">
-        <v>11697628</v>
+        <v>2453569</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>致茂</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>1455284</v>
+        <v>-3131833</v>
       </c>
       <c r="E10" t="n">
-        <v>3153658</v>
+        <v>-409587</v>
       </c>
       <c r="F10" t="n">
-        <v>-3161512</v>
+        <v>5123111</v>
       </c>
       <c r="G10" t="n">
-        <v>-4620995</v>
+        <v>7038822</v>
       </c>
       <c r="H10" t="n">
-        <v>-11270844</v>
+        <v>782538</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>立隆電</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅 / 📉 20d 巨變(減碼 -45,647 千)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-35873745</v>
+        <v>-240142</v>
       </c>
       <c r="E11" t="n">
-        <v>4191206</v>
+        <v>2015361</v>
       </c>
       <c r="F11" t="n">
-        <v>-39294461</v>
+        <v>-1355138</v>
       </c>
       <c r="G11" t="n">
-        <v>6352940</v>
+        <v>1785572</v>
       </c>
       <c r="H11" t="n">
-        <v>-269191678</v>
+        <v>2484157</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>華星光</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>803879</v>
+        <v>-2311789</v>
       </c>
       <c r="E12" t="n">
-        <v>1693836</v>
+        <v>1331206</v>
       </c>
       <c r="F12" t="n">
-        <v>-7096887</v>
+        <v>3399484</v>
       </c>
       <c r="G12" t="n">
-        <v>-6987519</v>
+        <v>4247843</v>
       </c>
       <c r="H12" t="n">
-        <v>2113144</v>
+        <v>-3943373</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>宇瞻</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-409587</v>
+        <v>219599</v>
       </c>
       <c r="E13" t="n">
-        <v>-897125</v>
+        <v>-1872108</v>
       </c>
       <c r="F13" t="n">
-        <v>7038822</v>
+        <v>-4629465</v>
       </c>
       <c r="G13" t="n">
-        <v>5927164</v>
+        <v>-6625705</v>
       </c>
       <c r="H13" t="n">
-        <v>1419937</v>
+        <v>-5477307</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>全友</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>📈 20d 巨變(加碼 9,142 千)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2015361</v>
+        <v>13546041</v>
       </c>
       <c r="E14" t="n">
-        <v>-205134</v>
+        <v>4219633</v>
       </c>
       <c r="F14" t="n">
-        <v>1785572</v>
+        <v>16757210</v>
       </c>
       <c r="G14" t="n">
-        <v>-633034</v>
+        <v>7615354</v>
       </c>
       <c r="H14" t="n">
-        <v>4016944</v>
+        <v>5966372</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -25,712 千)</t>
+          <t>📉 20d 巨變(減碼 -21,879 千)</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-33903117</v>
+        <v>4439570</v>
       </c>
       <c r="E15" t="n">
-        <v>-8267161</v>
+        <v>20039266</v>
       </c>
       <c r="F15" t="n">
-        <v>-34419812</v>
+        <v>274768619</v>
       </c>
       <c r="G15" t="n">
-        <v>-8707611</v>
+        <v>296647820</v>
       </c>
       <c r="H15" t="n">
-        <v>-33032782</v>
+        <v>582263605</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -24,945 千)</t>
+          <t>📈 20d 巨變(加碼 64,673 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>20039266</v>
+        <v>75849877</v>
       </c>
       <c r="E16" t="n">
-        <v>44699944</v>
+        <v>42292721</v>
       </c>
       <c r="F16" t="n">
-        <v>296647820</v>
+        <v>93361215</v>
       </c>
       <c r="G16" t="n">
-        <v>321593054</v>
+        <v>28688331</v>
       </c>
       <c r="H16" t="n">
-        <v>575720013</v>
+        <v>46847779</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -19,572 千)</t>
+          <t>📈 20d 巨變(加碼 10,336 千)</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>42292721</v>
+        <v>16628646</v>
       </c>
       <c r="E17" t="n">
-        <v>64269472</v>
+        <v>4600887</v>
       </c>
       <c r="F17" t="n">
-        <v>28688331</v>
+        <v>64147887</v>
       </c>
       <c r="G17" t="n">
-        <v>48259831</v>
+        <v>53812108</v>
       </c>
       <c r="H17" t="n">
-        <v>23590243</v>
+        <v>94600161</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 25,548 千)</t>
+          <t>📈 20d 巨變(加碼 19,938 千)</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>35558772</v>
+        <v>-4664898</v>
       </c>
       <c r="E18" t="n">
-        <v>4790271</v>
+        <v>-35873745</v>
       </c>
       <c r="F18" t="n">
-        <v>119645121</v>
+        <v>-19356337</v>
       </c>
       <c r="G18" t="n">
-        <v>94097255</v>
+        <v>-39294461</v>
       </c>
       <c r="H18" t="n">
-        <v>25811017</v>
+        <v>-310322940</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>英業達</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2317</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 22,490 千)</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>52527942</v>
-      </c>
-      <c r="E19" t="n">
-        <v>60135123</v>
-      </c>
-      <c r="F19" t="n">
-        <v>158189205</v>
-      </c>
-      <c r="G19" t="n">
-        <v>135698980</v>
-      </c>
-      <c r="H19" t="n">
-        <v>18291747</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>鴻海</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,385 +466,385 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -40,062 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -32,732 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-2578438</v>
+        <v>-33684480</v>
       </c>
       <c r="E2" t="n">
-        <v>52527942</v>
+        <v>4439570</v>
       </c>
       <c r="F2" t="n">
-        <v>118127649</v>
+        <v>242036513</v>
       </c>
       <c r="G2" t="n">
-        <v>158189205</v>
+        <v>274768619</v>
       </c>
       <c r="H2" t="n">
-        <v>-95410202</v>
+        <v>566139928</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -10,469 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 14,761 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>-1708608</v>
+        <v>5966729</v>
       </c>
       <c r="E3" t="n">
-        <v>182500</v>
+        <v>-105134</v>
       </c>
       <c r="F3" t="n">
-        <v>61734379</v>
+        <v>-32636433</v>
       </c>
       <c r="G3" t="n">
-        <v>72203461</v>
+        <v>-47397139</v>
       </c>
       <c r="H3" t="n">
-        <v>-80177094</v>
+        <v>-19078743</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 8,187 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 84,267 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>10858127</v>
+        <v>94557475</v>
       </c>
       <c r="E4" t="n">
-        <v>2874444</v>
+        <v>-4664898</v>
       </c>
       <c r="F4" t="n">
-        <v>-80427866</v>
+        <v>64910699</v>
       </c>
       <c r="G4" t="n">
-        <v>-88614833</v>
+        <v>-19356337</v>
       </c>
       <c r="H4" t="n">
-        <v>-261730109</v>
+        <v>-254432022</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -18,913 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>-8178225</v>
+        <v>3680162</v>
       </c>
       <c r="E5" t="n">
-        <v>-2697219</v>
+        <v>-9257132</v>
       </c>
       <c r="F5" t="n">
-        <v>63217716</v>
+        <v>-33453823</v>
       </c>
       <c r="G5" t="n">
-        <v>82130726</v>
+        <v>-35632420</v>
       </c>
       <c r="H5" t="n">
-        <v>103981760</v>
+        <v>-217193206</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -15,575 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>-5992547</v>
+        <v>5821586</v>
       </c>
       <c r="E6" t="n">
-        <v>-4766561</v>
+        <v>-2578438</v>
       </c>
       <c r="F6" t="n">
-        <v>90837725</v>
+        <v>125467779</v>
       </c>
       <c r="G6" t="n">
-        <v>106412566</v>
+        <v>118127649</v>
       </c>
       <c r="H6" t="n">
-        <v>5806417</v>
+        <v>-92338307</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>-719540</v>
+        <v>-1189934</v>
       </c>
       <c r="E7" t="n">
-        <v>523372</v>
+        <v>-1708608</v>
       </c>
       <c r="F7" t="n">
-        <v>772661</v>
+        <v>60460925</v>
       </c>
       <c r="G7" t="n">
-        <v>1283553</v>
+        <v>61734379</v>
       </c>
       <c r="H7" t="n">
-        <v>-20801746</v>
+        <v>-78713967</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 41,160 千)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>-2935294</v>
+        <v>7192120</v>
       </c>
       <c r="E8" t="n">
-        <v>-2632383</v>
+        <v>10858127</v>
       </c>
       <c r="F8" t="n">
-        <v>3904426</v>
+        <v>-39268249</v>
       </c>
       <c r="G8" t="n">
-        <v>4514692</v>
+        <v>-80427866</v>
       </c>
       <c r="H8" t="n">
-        <v>11310024</v>
+        <v>-264754456</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -16,680 千)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>280865</v>
+        <v>-11851258</v>
       </c>
       <c r="E9" t="n">
-        <v>803879</v>
+        <v>-8178225</v>
       </c>
       <c r="F9" t="n">
-        <v>-5703919</v>
+        <v>46537538</v>
       </c>
       <c r="G9" t="n">
-        <v>-7096887</v>
+        <v>63217716</v>
       </c>
       <c r="H9" t="n">
-        <v>2453569</v>
+        <v>102033134</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -21,301 千)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-3131833</v>
+        <v>-11662344</v>
       </c>
       <c r="E10" t="n">
-        <v>-409587</v>
+        <v>-5992547</v>
       </c>
       <c r="F10" t="n">
-        <v>5123111</v>
+        <v>69536570</v>
       </c>
       <c r="G10" t="n">
-        <v>7038822</v>
+        <v>90837725</v>
       </c>
       <c r="H10" t="n">
-        <v>782538</v>
+        <v>1544138</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-240142</v>
+        <v>-1993</v>
       </c>
       <c r="E11" t="n">
-        <v>2015361</v>
+        <v>1789304</v>
       </c>
       <c r="F11" t="n">
-        <v>-1355138</v>
+        <v>9076608</v>
       </c>
       <c r="G11" t="n">
-        <v>1785572</v>
+        <v>9240973</v>
       </c>
       <c r="H11" t="n">
-        <v>2484157</v>
+        <v>-1642828</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>鈊象</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-2311789</v>
+        <v>964024</v>
       </c>
       <c r="E12" t="n">
-        <v>1331206</v>
+        <v>-1793396</v>
       </c>
       <c r="F12" t="n">
-        <v>3399484</v>
+        <v>2693498</v>
       </c>
       <c r="G12" t="n">
-        <v>4247843</v>
+        <v>1374607</v>
       </c>
       <c r="H12" t="n">
-        <v>-3943373</v>
+        <v>-8361039</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
@@ -856,26 +856,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>2</v>
       </c>
       <c r="D13" t="n">
+        <v>868790</v>
+      </c>
+      <c r="E13" t="n">
         <v>219599</v>
       </c>
-      <c r="E13" t="n">
-        <v>-1872108</v>
-      </c>
       <c r="F13" t="n">
+        <v>-7883908</v>
+      </c>
+      <c r="G13" t="n">
         <v>-4629465</v>
       </c>
-      <c r="G13" t="n">
-        <v>-6625705</v>
-      </c>
       <c r="H13" t="n">
-        <v>-5477307</v>
+        <v>-7270438</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -886,175 +886,35 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 9,142 千)</t>
+          <t>📉 20d 巨變(減碼 -19,874 千)</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>13546041</v>
+        <v>-32073464</v>
       </c>
       <c r="E14" t="n">
-        <v>4219633</v>
+        <v>-19131259</v>
       </c>
       <c r="F14" t="n">
-        <v>16757210</v>
+        <v>-52713661</v>
       </c>
       <c r="G14" t="n">
-        <v>7615354</v>
+        <v>-32840065</v>
       </c>
       <c r="H14" t="n">
-        <v>5966372</v>
+        <v>-112448356</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>中興電</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -21,879 千)</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="n">
-        <v>4439570</v>
-      </c>
-      <c r="E15" t="n">
-        <v>20039266</v>
-      </c>
-      <c r="F15" t="n">
-        <v>274768619</v>
-      </c>
-      <c r="G15" t="n">
-        <v>296647820</v>
-      </c>
-      <c r="H15" t="n">
-        <v>582263605</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>長榮航</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 64,673 千)</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="n">
-        <v>75849877</v>
-      </c>
-      <c r="E16" t="n">
-        <v>42292721</v>
-      </c>
-      <c r="F16" t="n">
-        <v>93361215</v>
-      </c>
-      <c r="G16" t="n">
-        <v>28688331</v>
-      </c>
-      <c r="H16" t="n">
-        <v>46847779</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2301</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 10,336 千)</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="n">
-        <v>16628646</v>
-      </c>
-      <c r="E17" t="n">
-        <v>4600887</v>
-      </c>
-      <c r="F17" t="n">
-        <v>64147887</v>
-      </c>
-      <c r="G17" t="n">
-        <v>53812108</v>
-      </c>
-      <c r="H17" t="n">
-        <v>94600161</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>光寶科</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 19,938 千)</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>-4664898</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-35873745</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-19356337</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-39294461</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-310322940</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>華邦電</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,455 +466,630 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -32,732 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -9,097 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>-33684480</v>
+        <v>-11096464</v>
       </c>
       <c r="E2" t="n">
-        <v>4439570</v>
+        <v>5821586</v>
       </c>
       <c r="F2" t="n">
-        <v>242036513</v>
+        <v>116370404</v>
       </c>
       <c r="G2" t="n">
-        <v>274768619</v>
+        <v>125467779</v>
       </c>
       <c r="H2" t="n">
-        <v>566139928</v>
+        <v>-120302282</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 14,761 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -9,949 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>5966729</v>
+        <v>-10637226</v>
       </c>
       <c r="E3" t="n">
-        <v>-105134</v>
+        <v>-11662344</v>
       </c>
       <c r="F3" t="n">
-        <v>-32636433</v>
+        <v>59587282</v>
       </c>
       <c r="G3" t="n">
-        <v>-47397139</v>
+        <v>69536570</v>
       </c>
       <c r="H3" t="n">
-        <v>-19078743</v>
+        <v>-158375</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 84,267 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📈 20d 巨變(加碼 10,454 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>94557475</v>
+        <v>-9604663</v>
       </c>
       <c r="E4" t="n">
-        <v>-4664898</v>
+        <v>-33684480</v>
       </c>
       <c r="F4" t="n">
-        <v>64910699</v>
+        <v>252490615</v>
       </c>
       <c r="G4" t="n">
-        <v>-19356337</v>
+        <v>242036513</v>
       </c>
       <c r="H4" t="n">
-        <v>-254432022</v>
+        <v>652634058</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 13,655 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>3680162</v>
+        <v>15904438</v>
       </c>
       <c r="E5" t="n">
-        <v>-9257132</v>
+        <v>5966729</v>
       </c>
       <c r="F5" t="n">
-        <v>-33453823</v>
+        <v>-18981019</v>
       </c>
       <c r="G5" t="n">
-        <v>-35632420</v>
+        <v>-32636433</v>
       </c>
       <c r="H5" t="n">
-        <v>-217193206</v>
+        <v>-13025103</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -11,208 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>5821586</v>
+        <v>66926629</v>
       </c>
       <c r="E6" t="n">
-        <v>-2578438</v>
+        <v>94557475</v>
       </c>
       <c r="F6" t="n">
-        <v>125467779</v>
+        <v>53702719</v>
       </c>
       <c r="G6" t="n">
-        <v>118127649</v>
+        <v>64910699</v>
       </c>
       <c r="H6" t="n">
-        <v>-92338307</v>
+        <v>-269176108</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-1189934</v>
+        <v>11514683</v>
       </c>
       <c r="E7" t="n">
-        <v>-1708608</v>
+        <v>7192120</v>
       </c>
       <c r="F7" t="n">
-        <v>60460925</v>
+        <v>-33154462</v>
       </c>
       <c r="G7" t="n">
-        <v>61734379</v>
+        <v>-39268249</v>
       </c>
       <c r="H7" t="n">
-        <v>-78713967</v>
+        <v>-257392428</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 41,160 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>7192120</v>
+        <v>-167536</v>
       </c>
       <c r="E8" t="n">
-        <v>10858127</v>
+        <v>-11851258</v>
       </c>
       <c r="F8" t="n">
-        <v>-39268249</v>
+        <v>51417823</v>
       </c>
       <c r="G8" t="n">
-        <v>-80427866</v>
+        <v>46537538</v>
       </c>
       <c r="H8" t="n">
-        <v>-264754456</v>
+        <v>113033163</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -16,680 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-11851258</v>
+        <v>-2042866</v>
       </c>
       <c r="E9" t="n">
-        <v>-8178225</v>
+        <v>-2525259</v>
       </c>
       <c r="F9" t="n">
-        <v>46537538</v>
+        <v>87834</v>
       </c>
       <c r="G9" t="n">
-        <v>63217716</v>
+        <v>-158116</v>
       </c>
       <c r="H9" t="n">
-        <v>102033134</v>
+        <v>-13901791</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -21,301 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-11662344</v>
+        <v>3723601</v>
       </c>
       <c r="E10" t="n">
-        <v>-5992547</v>
+        <v>441317</v>
       </c>
       <c r="F10" t="n">
-        <v>69536570</v>
+        <v>10165787</v>
       </c>
       <c r="G10" t="n">
-        <v>90837725</v>
+        <v>11555161</v>
       </c>
       <c r="H10" t="n">
-        <v>1544138</v>
+        <v>-825143</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-1993</v>
+        <v>6878367</v>
       </c>
       <c r="E11" t="n">
-        <v>1789304</v>
+        <v>3680162</v>
       </c>
       <c r="F11" t="n">
-        <v>9076608</v>
+        <v>-33224403</v>
       </c>
       <c r="G11" t="n">
-        <v>9240973</v>
+        <v>-33453823</v>
       </c>
       <c r="H11" t="n">
-        <v>-1642828</v>
+        <v>-194472832</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>964024</v>
+        <v>485074</v>
       </c>
       <c r="E12" t="n">
-        <v>-1793396</v>
+        <v>-1189934</v>
       </c>
       <c r="F12" t="n">
-        <v>2693498</v>
+        <v>59995387</v>
       </c>
       <c r="G12" t="n">
-        <v>1374607</v>
+        <v>60460925</v>
       </c>
       <c r="H12" t="n">
-        <v>-8361039</v>
+        <v>-73905487</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>868790</v>
+        <v>-10636970</v>
       </c>
       <c r="E13" t="n">
-        <v>219599</v>
+        <v>-5999735</v>
       </c>
       <c r="F13" t="n">
-        <v>-7883908</v>
+        <v>-6961960</v>
       </c>
       <c r="G13" t="n">
-        <v>-4629465</v>
+        <v>-2025305</v>
       </c>
       <c r="H13" t="n">
-        <v>-7270438</v>
+        <v>3120821</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -19,874 千)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-535578</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-1993</v>
+      </c>
+      <c r="F14" t="n">
+        <v>8525086</v>
+      </c>
+      <c r="G14" t="n">
+        <v>9076608</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-2521412</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>鈊象</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3227</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-741275</v>
+      </c>
+      <c r="E15" t="n">
+        <v>398650</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5738706</v>
+      </c>
+      <c r="G15" t="n">
+        <v>6043030</v>
+      </c>
+      <c r="H15" t="n">
+        <v>8090632</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>原相</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>6285</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>🔴 5d 翻紅</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-2589126</v>
+      </c>
+      <c r="E16" t="n">
+        <v>964024</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2378137</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2693498</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-5516142</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>啟碁</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 18,880 千)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
         <v>1</v>
       </c>
-      <c r="D14" t="n">
-        <v>-32073464</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-19131259</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-52713661</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-32840065</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-112448356</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>國巨*</t>
+      <c r="D17" t="n">
+        <v>45129594</v>
+      </c>
+      <c r="E17" t="n">
+        <v>63676037</v>
+      </c>
+      <c r="F17" t="n">
+        <v>110876193</v>
+      </c>
+      <c r="G17" t="n">
+        <v>91996225</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3446719</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -13,864 千)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>15498547</v>
+      </c>
+      <c r="E18" t="n">
+        <v>27902209</v>
+      </c>
+      <c r="F18" t="n">
+        <v>271817266</v>
+      </c>
+      <c r="G18" t="n">
+        <v>285681599</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5411468</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -18,636 千)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>36014856</v>
+      </c>
+      <c r="E19" t="n">
+        <v>54502532</v>
+      </c>
+      <c r="F19" t="n">
+        <v>105232470</v>
+      </c>
+      <c r="G19" t="n">
+        <v>123868168</v>
+      </c>
+      <c r="H19" t="n">
+        <v>64210930</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>英業達</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,26 +471,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -9,097 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -30,495 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
+        <v>-17816873</v>
+      </c>
+      <c r="E2" t="n">
         <v>-11096464</v>
       </c>
-      <c r="E2" t="n">
-        <v>5821586</v>
-      </c>
       <c r="F2" t="n">
+        <v>85875217</v>
+      </c>
+      <c r="G2" t="n">
         <v>116370404</v>
       </c>
-      <c r="G2" t="n">
-        <v>125467779</v>
-      </c>
       <c r="H2" t="n">
-        <v>-120302282</v>
+        <v>-156181809</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -501,147 +501,147 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -9,949 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>-10637226</v>
+        <v>84382</v>
       </c>
       <c r="E3" t="n">
-        <v>-11662344</v>
+        <v>-4019258</v>
       </c>
       <c r="F3" t="n">
-        <v>59587282</v>
+        <v>-18950248</v>
       </c>
       <c r="G3" t="n">
-        <v>69536570</v>
+        <v>-19805373</v>
       </c>
       <c r="H3" t="n">
-        <v>-158375</v>
+        <v>-56310384</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📈 20d 巨變(加碼 10,454 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📉 20d 巨變(減碼 -8,221 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>-9604663</v>
+        <v>4771328</v>
       </c>
       <c r="E4" t="n">
-        <v>-33684480</v>
+        <v>11514683</v>
       </c>
       <c r="F4" t="n">
-        <v>252490615</v>
+        <v>-41375309</v>
       </c>
       <c r="G4" t="n">
-        <v>242036513</v>
+        <v>-33154462</v>
       </c>
       <c r="H4" t="n">
-        <v>652634058</v>
+        <v>-260533719</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 13,655 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -10,352 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>15904438</v>
+        <v>-10959719</v>
       </c>
       <c r="E5" t="n">
-        <v>5966729</v>
+        <v>-10637226</v>
       </c>
       <c r="F5" t="n">
-        <v>-18981019</v>
+        <v>49234796</v>
       </c>
       <c r="G5" t="n">
-        <v>-32636433</v>
+        <v>59587282</v>
       </c>
       <c r="H5" t="n">
-        <v>-13025103</v>
+        <v>2026978</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -11,208 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>66926629</v>
+        <v>15202927</v>
       </c>
       <c r="E6" t="n">
-        <v>94557475</v>
+        <v>15899893</v>
       </c>
       <c r="F6" t="n">
-        <v>53702719</v>
+        <v>16490648</v>
       </c>
       <c r="G6" t="n">
-        <v>64910699</v>
+        <v>18191881</v>
       </c>
       <c r="H6" t="n">
-        <v>-269176108</v>
+        <v>-623454</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,65 +653,65 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>11514683</v>
+        <v>16391894</v>
       </c>
       <c r="E7" t="n">
-        <v>7192120</v>
+        <v>15904438</v>
       </c>
       <c r="F7" t="n">
-        <v>-33154462</v>
+        <v>-17683702</v>
       </c>
       <c r="G7" t="n">
-        <v>-39268249</v>
+        <v>-18981019</v>
       </c>
       <c r="H7" t="n">
-        <v>-257392428</v>
+        <v>-20186292</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-167536</v>
+        <v>8608762</v>
       </c>
       <c r="E8" t="n">
-        <v>-11851258</v>
+        <v>6878367</v>
       </c>
       <c r="F8" t="n">
-        <v>51417823</v>
+        <v>-38872081</v>
       </c>
       <c r="G8" t="n">
-        <v>46537538</v>
+        <v>-33224403</v>
       </c>
       <c r="H8" t="n">
-        <v>113033163</v>
+        <v>-169983792</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,30 +723,30 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-2042866</v>
+        <v>4231108</v>
       </c>
       <c r="E9" t="n">
-        <v>-2525259</v>
+        <v>485074</v>
       </c>
       <c r="F9" t="n">
-        <v>87834</v>
+        <v>58259335</v>
       </c>
       <c r="G9" t="n">
-        <v>-158116</v>
+        <v>59995387</v>
       </c>
       <c r="H9" t="n">
-        <v>-13901791</v>
+        <v>-68244746</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,170 +758,170 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>3723601</v>
+        <v>29951991</v>
       </c>
       <c r="E10" t="n">
-        <v>441317</v>
+        <v>66926629</v>
       </c>
       <c r="F10" t="n">
-        <v>10165787</v>
+        <v>60628483</v>
       </c>
       <c r="G10" t="n">
-        <v>11555161</v>
+        <v>53702719</v>
       </c>
       <c r="H10" t="n">
-        <v>-825143</v>
+        <v>-218747935</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🟢 5d 翻綠 / 📉 20d 巨變(減碼 -9,648 千)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>6878367</v>
+        <v>3041316</v>
       </c>
       <c r="E11" t="n">
-        <v>3680162</v>
+        <v>-9604663</v>
       </c>
       <c r="F11" t="n">
-        <v>-33224403</v>
+        <v>242842156</v>
       </c>
       <c r="G11" t="n">
-        <v>-33453823</v>
+        <v>252490615</v>
       </c>
       <c r="H11" t="n">
-        <v>-194472832</v>
+        <v>701486092</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>485074</v>
+        <v>-11351228</v>
       </c>
       <c r="E12" t="n">
-        <v>-1189934</v>
+        <v>-10636970</v>
       </c>
       <c r="F12" t="n">
-        <v>59995387</v>
+        <v>-8804572</v>
       </c>
       <c r="G12" t="n">
-        <v>60460925</v>
+        <v>-6961960</v>
       </c>
       <c r="H12" t="n">
-        <v>-73905487</v>
+        <v>1310677</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-10636970</v>
+        <v>339090</v>
       </c>
       <c r="E13" t="n">
-        <v>-5999735</v>
+        <v>-799690</v>
       </c>
       <c r="F13" t="n">
-        <v>-6961960</v>
+        <v>-6693264</v>
       </c>
       <c r="G13" t="n">
-        <v>-2025305</v>
+        <v>-6937627</v>
       </c>
       <c r="H13" t="n">
-        <v>3120821</v>
+        <v>1588202</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>健鼎</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-535578</v>
+        <v>4719706</v>
       </c>
       <c r="E14" t="n">
-        <v>-1993</v>
+        <v>-167536</v>
       </c>
       <c r="F14" t="n">
-        <v>8525086</v>
+        <v>43711916</v>
       </c>
       <c r="G14" t="n">
-        <v>9076608</v>
+        <v>51417823</v>
       </c>
       <c r="H14" t="n">
-        <v>-2521412</v>
+        <v>114864395</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,161 +933,231 @@
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>-741275</v>
+        <v>-1496746</v>
       </c>
       <c r="E15" t="n">
-        <v>398650</v>
+        <v>-535578</v>
       </c>
       <c r="F15" t="n">
-        <v>5738706</v>
+        <v>8176320</v>
       </c>
       <c r="G15" t="n">
-        <v>6043030</v>
+        <v>8525086</v>
       </c>
       <c r="H15" t="n">
-        <v>8090632</v>
+        <v>-333518</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>鈊象</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>-2589126</v>
+        <v>1112469</v>
       </c>
       <c r="E16" t="n">
-        <v>964024</v>
+        <v>-1152586</v>
       </c>
       <c r="F16" t="n">
-        <v>2378137</v>
+        <v>-4448986</v>
       </c>
       <c r="G16" t="n">
-        <v>2693498</v>
+        <v>-4832973</v>
       </c>
       <c r="H16" t="n">
-        <v>-5516142</v>
+        <v>2709313</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>華星光</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 18,880 千)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>45129594</v>
+        <v>-1196705</v>
       </c>
       <c r="E17" t="n">
-        <v>63676037</v>
+        <v>-741275</v>
       </c>
       <c r="F17" t="n">
-        <v>110876193</v>
+        <v>5119276</v>
       </c>
       <c r="G17" t="n">
-        <v>91996225</v>
+        <v>5738706</v>
       </c>
       <c r="H17" t="n">
-        <v>3446719</v>
+        <v>8018141</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>原相</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -13,864 千)</t>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>15498547</v>
+        <v>208179</v>
       </c>
       <c r="E18" t="n">
-        <v>27902209</v>
+        <v>-133230</v>
       </c>
       <c r="F18" t="n">
-        <v>271817266</v>
+        <v>-8003157</v>
       </c>
       <c r="G18" t="n">
-        <v>285681599</v>
+        <v>-8267378</v>
       </c>
       <c r="H18" t="n">
-        <v>5411468</v>
+        <v>-8077898</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>全友</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -18,636 千)</t>
+          <t>📉 20d 巨變(減碼 -15,659 千)</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
+        <v>8358095</v>
+      </c>
+      <c r="E19" t="n">
+        <v>15498547</v>
+      </c>
+      <c r="F19" t="n">
+        <v>256158631</v>
+      </c>
+      <c r="G19" t="n">
+        <v>271817266</v>
+      </c>
+      <c r="H19" t="n">
+        <v>9291539</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 8,728 千)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>19285697</v>
+      </c>
+      <c r="E20" t="n">
+        <v>9394837</v>
+      </c>
+      <c r="F20" t="n">
+        <v>79103642</v>
+      </c>
+      <c r="G20" t="n">
+        <v>70375350</v>
+      </c>
+      <c r="H20" t="n">
+        <v>89349999</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -14,902 千)</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>33080418</v>
+      </c>
+      <c r="E21" t="n">
         <v>36014856</v>
       </c>
-      <c r="E19" t="n">
-        <v>54502532</v>
-      </c>
-      <c r="F19" t="n">
+      <c r="F21" t="n">
+        <v>90330108</v>
+      </c>
+      <c r="G21" t="n">
         <v>105232470</v>
       </c>
-      <c r="G19" t="n">
-        <v>123868168</v>
-      </c>
-      <c r="H19" t="n">
-        <v>64210930</v>
-      </c>
-      <c r="I19" t="inlineStr">
+      <c r="H21" t="n">
+        <v>53088396</v>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>英業達</t>
         </is>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,252 +466,252 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -30,495 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -27,257 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-17816873</v>
+        <v>-3513673</v>
       </c>
       <c r="E2" t="n">
-        <v>-11096464</v>
+        <v>8358095</v>
       </c>
       <c r="F2" t="n">
-        <v>85875217</v>
+        <v>228901190</v>
       </c>
       <c r="G2" t="n">
-        <v>116370404</v>
+        <v>256158631</v>
       </c>
       <c r="H2" t="n">
-        <v>-156181809</v>
+        <v>49343042</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -27,744 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>84382</v>
+        <v>-57251918</v>
       </c>
       <c r="E3" t="n">
-        <v>-4019258</v>
+        <v>-17816873</v>
       </c>
       <c r="F3" t="n">
-        <v>-18950248</v>
+        <v>58130971</v>
       </c>
       <c r="G3" t="n">
-        <v>-19805373</v>
+        <v>85875217</v>
       </c>
       <c r="H3" t="n">
-        <v>-56310384</v>
+        <v>-138068592</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📉 20d 巨變(減碼 -8,221 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>4771328</v>
+        <v>20120723</v>
       </c>
       <c r="E4" t="n">
-        <v>11514683</v>
+        <v>16391894</v>
       </c>
       <c r="F4" t="n">
-        <v>-41375309</v>
+        <v>-16479590</v>
       </c>
       <c r="G4" t="n">
-        <v>-33154462</v>
+        <v>-17683702</v>
       </c>
       <c r="H4" t="n">
-        <v>-260533719</v>
+        <v>-19396546</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -10,352 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>-10959719</v>
+        <v>11199710</v>
       </c>
       <c r="E5" t="n">
-        <v>-10637226</v>
+        <v>8608762</v>
       </c>
       <c r="F5" t="n">
-        <v>49234796</v>
+        <v>-33559502</v>
       </c>
       <c r="G5" t="n">
-        <v>59587282</v>
+        <v>-38872081</v>
       </c>
       <c r="H5" t="n">
-        <v>2026978</v>
+        <v>-134043225</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>15202927</v>
+        <v>-10839680</v>
       </c>
       <c r="E6" t="n">
-        <v>15899893</v>
+        <v>-10959719</v>
       </c>
       <c r="F6" t="n">
-        <v>16490648</v>
+        <v>45333437</v>
       </c>
       <c r="G6" t="n">
-        <v>18191881</v>
+        <v>49234796</v>
       </c>
       <c r="H6" t="n">
-        <v>-623454</v>
+        <v>1924975</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>16391894</v>
+        <v>-10737230</v>
       </c>
       <c r="E7" t="n">
-        <v>15904438</v>
+        <v>-11351228</v>
       </c>
       <c r="F7" t="n">
-        <v>-17683702</v>
+        <v>-10867086</v>
       </c>
       <c r="G7" t="n">
-        <v>-18981019</v>
+        <v>-8804572</v>
       </c>
       <c r="H7" t="n">
-        <v>-20186292</v>
+        <v>719102</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>8608762</v>
+        <v>6073721</v>
       </c>
       <c r="E8" t="n">
-        <v>6878367</v>
+        <v>4231108</v>
       </c>
       <c r="F8" t="n">
-        <v>-38872081</v>
+        <v>53863280</v>
       </c>
       <c r="G8" t="n">
-        <v>-33224403</v>
+        <v>58259335</v>
       </c>
       <c r="H8" t="n">
-        <v>-169983792</v>
+        <v>-66246857</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,441 +723,336 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>4231108</v>
+        <v>56012615</v>
       </c>
       <c r="E9" t="n">
-        <v>485074</v>
+        <v>29951991</v>
       </c>
       <c r="F9" t="n">
-        <v>58259335</v>
+        <v>63745871</v>
       </c>
       <c r="G9" t="n">
-        <v>59995387</v>
+        <v>60628483</v>
       </c>
       <c r="H9" t="n">
-        <v>-68244746</v>
+        <v>-213836808</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>29951991</v>
+        <v>-3456220</v>
       </c>
       <c r="E10" t="n">
-        <v>66926629</v>
+        <v>781764</v>
       </c>
       <c r="F10" t="n">
-        <v>60628483</v>
+        <v>5478212</v>
       </c>
       <c r="G10" t="n">
-        <v>53702719</v>
+        <v>6506159</v>
       </c>
       <c r="H10" t="n">
-        <v>-218747935</v>
+        <v>-1679868</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠 / 📉 20d 巨變(減碼 -9,648 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>3041316</v>
+        <v>200887</v>
       </c>
       <c r="E11" t="n">
-        <v>-9604663</v>
+        <v>-243604</v>
       </c>
       <c r="F11" t="n">
-        <v>242842156</v>
+        <v>-519770</v>
       </c>
       <c r="G11" t="n">
-        <v>252490615</v>
+        <v>-757943</v>
       </c>
       <c r="H11" t="n">
-        <v>701486092</v>
+        <v>-10137141</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>亞力</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-11351228</v>
+        <v>-5273518</v>
       </c>
       <c r="E12" t="n">
-        <v>-10636970</v>
+        <v>4771328</v>
       </c>
       <c r="F12" t="n">
-        <v>-8804572</v>
+        <v>-45254673</v>
       </c>
       <c r="G12" t="n">
-        <v>-6961960</v>
+        <v>-41375309</v>
       </c>
       <c r="H12" t="n">
-        <v>1310677</v>
+        <v>-256695610</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>339090</v>
+        <v>-636712</v>
       </c>
       <c r="E13" t="n">
-        <v>-799690</v>
+        <v>-1496746</v>
       </c>
       <c r="F13" t="n">
-        <v>-6693264</v>
+        <v>8722932</v>
       </c>
       <c r="G13" t="n">
-        <v>-6937627</v>
+        <v>8176320</v>
       </c>
       <c r="H13" t="n">
-        <v>1588202</v>
+        <v>1423392</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>鈊象</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>4719706</v>
+        <v>-1269112</v>
       </c>
       <c r="E14" t="n">
-        <v>-167536</v>
+        <v>1112469</v>
       </c>
       <c r="F14" t="n">
-        <v>43711916</v>
+        <v>-2515773</v>
       </c>
       <c r="G14" t="n">
-        <v>51417823</v>
+        <v>-4448986</v>
       </c>
       <c r="H14" t="n">
-        <v>114864395</v>
+        <v>2799943</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>華星光</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>📉 20d 巨變(減碼 -9,065 千)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1496746</v>
+        <v>6742514</v>
       </c>
       <c r="E15" t="n">
-        <v>-535578</v>
+        <v>3041316</v>
       </c>
       <c r="F15" t="n">
-        <v>8176320</v>
+        <v>233776698</v>
       </c>
       <c r="G15" t="n">
-        <v>8525086</v>
+        <v>242842156</v>
       </c>
       <c r="H15" t="n">
-        <v>-333518</v>
+        <v>722149194</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>📈 20d 巨變(加碼 14,375 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1112469</v>
+        <v>22767688</v>
       </c>
       <c r="E16" t="n">
-        <v>-1152586</v>
+        <v>4719706</v>
       </c>
       <c r="F16" t="n">
-        <v>-4448986</v>
+        <v>58086546</v>
       </c>
       <c r="G16" t="n">
-        <v>-4832973</v>
+        <v>43711916</v>
       </c>
       <c r="H16" t="n">
-        <v>2709313</v>
+        <v>130619246</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>📉 20d 巨變(減碼 -21,539 千)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1196705</v>
+        <v>33279267</v>
       </c>
       <c r="E17" t="n">
-        <v>-741275</v>
+        <v>32305140</v>
       </c>
       <c r="F17" t="n">
-        <v>5119276</v>
+        <v>94672080</v>
       </c>
       <c r="G17" t="n">
-        <v>5738706</v>
+        <v>116210783</v>
       </c>
       <c r="H17" t="n">
-        <v>8018141</v>
+        <v>18358226</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>📉 20d 巨變(減碼 -11,328 千)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>208179</v>
+        <v>8232950</v>
       </c>
       <c r="E18" t="n">
-        <v>-133230</v>
+        <v>33080418</v>
       </c>
       <c r="F18" t="n">
-        <v>-8003157</v>
+        <v>79001919</v>
       </c>
       <c r="G18" t="n">
-        <v>-8267378</v>
+        <v>90330108</v>
       </c>
       <c r="H18" t="n">
-        <v>-8077898</v>
+        <v>56375309</v>
       </c>
       <c r="I18" t="inlineStr">
-        <is>
-          <t>全友</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -15,659 千)</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>8358095</v>
-      </c>
-      <c r="E19" t="n">
-        <v>15498547</v>
-      </c>
-      <c r="F19" t="n">
-        <v>256158631</v>
-      </c>
-      <c r="G19" t="n">
-        <v>271817266</v>
-      </c>
-      <c r="H19" t="n">
-        <v>9291539</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2301</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 8,728 千)</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>19285697</v>
-      </c>
-      <c r="E20" t="n">
-        <v>9394837</v>
-      </c>
-      <c r="F20" t="n">
-        <v>79103642</v>
-      </c>
-      <c r="G20" t="n">
-        <v>70375350</v>
-      </c>
-      <c r="H20" t="n">
-        <v>89349999</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>光寶科</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2356</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -14,902 千)</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>33080418</v>
-      </c>
-      <c r="E21" t="n">
-        <v>36014856</v>
-      </c>
-      <c r="F21" t="n">
-        <v>90330108</v>
-      </c>
-      <c r="G21" t="n">
-        <v>105232470</v>
-      </c>
-      <c r="H21" t="n">
-        <v>53088396</v>
-      </c>
-      <c r="I21" t="inlineStr">
         <is>
           <t>英業達</t>
         </is>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,35 +466,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -27,257 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -12,105 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-3513673</v>
+        <v>-1634783</v>
       </c>
       <c r="E2" t="n">
-        <v>8358095</v>
+        <v>17642461</v>
       </c>
       <c r="F2" t="n">
-        <v>228901190</v>
+        <v>59340879</v>
       </c>
       <c r="G2" t="n">
-        <v>256158631</v>
+        <v>71445420</v>
       </c>
       <c r="H2" t="n">
-        <v>49343042</v>
+        <v>79095646</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
@@ -506,26 +506,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -27,744 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -27,996 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>8</v>
       </c>
       <c r="D3" t="n">
+        <v>-28130167</v>
+      </c>
+      <c r="E3" t="n">
         <v>-57251918</v>
       </c>
-      <c r="E3" t="n">
-        <v>-17816873</v>
-      </c>
       <c r="F3" t="n">
+        <v>30135053</v>
+      </c>
+      <c r="G3" t="n">
         <v>58130971</v>
       </c>
-      <c r="G3" t="n">
-        <v>85875217</v>
-      </c>
       <c r="H3" t="n">
-        <v>-138068592</v>
+        <v>-138991246</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -536,523 +536,488 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -84,323 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>20120723</v>
+        <v>-19146200</v>
       </c>
       <c r="E4" t="n">
-        <v>16391894</v>
+        <v>-3513673</v>
       </c>
       <c r="F4" t="n">
-        <v>-16479590</v>
+        <v>144577790</v>
       </c>
       <c r="G4" t="n">
-        <v>-17683702</v>
+        <v>228901190</v>
       </c>
       <c r="H4" t="n">
-        <v>-19396546</v>
+        <v>39956516</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>11199710</v>
+        <v>-111110</v>
       </c>
       <c r="E5" t="n">
-        <v>8608762</v>
+        <v>585397</v>
       </c>
       <c r="F5" t="n">
-        <v>-33559502</v>
+        <v>10329422</v>
       </c>
       <c r="G5" t="n">
-        <v>-38872081</v>
+        <v>10865923</v>
       </c>
       <c r="H5" t="n">
-        <v>-134043225</v>
+        <v>1900275</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>-10839680</v>
+        <v>16429775</v>
       </c>
       <c r="E6" t="n">
-        <v>-10959719</v>
+        <v>20120723</v>
       </c>
       <c r="F6" t="n">
-        <v>45333437</v>
+        <v>-14794426</v>
       </c>
       <c r="G6" t="n">
-        <v>49234796</v>
+        <v>-16479590</v>
       </c>
       <c r="H6" t="n">
-        <v>1924975</v>
+        <v>-17475442</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-10737230</v>
+        <v>14124261</v>
       </c>
       <c r="E7" t="n">
-        <v>-11351228</v>
+        <v>11199710</v>
       </c>
       <c r="F7" t="n">
-        <v>-10867086</v>
+        <v>-33610697</v>
       </c>
       <c r="G7" t="n">
-        <v>-8804572</v>
+        <v>-33559502</v>
       </c>
       <c r="H7" t="n">
-        <v>719102</v>
+        <v>-114182548</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>6073721</v>
+        <v>457701</v>
       </c>
       <c r="E8" t="n">
-        <v>4231108</v>
+        <v>-594703</v>
       </c>
       <c r="F8" t="n">
-        <v>53863280</v>
+        <v>-19610978</v>
       </c>
       <c r="G8" t="n">
-        <v>58259335</v>
+        <v>-19795810</v>
       </c>
       <c r="H8" t="n">
-        <v>-66246857</v>
+        <v>-44940528</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>56012615</v>
+        <v>-8607786</v>
       </c>
       <c r="E9" t="n">
-        <v>29951991</v>
+        <v>-10839680</v>
       </c>
       <c r="F9" t="n">
-        <v>63745871</v>
+        <v>41951362</v>
       </c>
       <c r="G9" t="n">
-        <v>60628483</v>
+        <v>45333437</v>
       </c>
       <c r="H9" t="n">
-        <v>-213836808</v>
+        <v>7340155</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-3456220</v>
+        <v>-10838873</v>
       </c>
       <c r="E10" t="n">
-        <v>781764</v>
+        <v>-10737230</v>
       </c>
       <c r="F10" t="n">
-        <v>5478212</v>
+        <v>-12268276</v>
       </c>
       <c r="G10" t="n">
-        <v>6506159</v>
+        <v>-10867086</v>
       </c>
       <c r="H10" t="n">
-        <v>-1679868</v>
+        <v>266108</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>200887</v>
+        <v>9864108</v>
       </c>
       <c r="E11" t="n">
-        <v>-243604</v>
+        <v>6073721</v>
       </c>
       <c r="F11" t="n">
-        <v>-519770</v>
+        <v>51226078</v>
       </c>
       <c r="G11" t="n">
-        <v>-757943</v>
+        <v>53863280</v>
       </c>
       <c r="H11" t="n">
-        <v>-10137141</v>
+        <v>-63199695</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-5273518</v>
+        <v>66697209</v>
       </c>
       <c r="E12" t="n">
-        <v>4771328</v>
+        <v>56012615</v>
       </c>
       <c r="F12" t="n">
-        <v>-45254673</v>
+        <v>71329014</v>
       </c>
       <c r="G12" t="n">
-        <v>-41375309</v>
+        <v>63745871</v>
       </c>
       <c r="H12" t="n">
-        <v>-256695610</v>
+        <v>-156979358</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-636712</v>
+        <v>1877870</v>
       </c>
       <c r="E13" t="n">
-        <v>-1496746</v>
+        <v>-234316</v>
       </c>
       <c r="F13" t="n">
-        <v>8722932</v>
+        <v>3565418</v>
       </c>
       <c r="G13" t="n">
-        <v>8176320</v>
+        <v>3220714</v>
       </c>
       <c r="H13" t="n">
-        <v>1423392</v>
+        <v>2187020</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>立隆電</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-1269112</v>
+        <v>-3466075</v>
       </c>
       <c r="E14" t="n">
-        <v>1112469</v>
+        <v>-3456220</v>
       </c>
       <c r="F14" t="n">
-        <v>-2515773</v>
+        <v>6424170</v>
       </c>
       <c r="G14" t="n">
-        <v>-4448986</v>
+        <v>5478212</v>
       </c>
       <c r="H14" t="n">
-        <v>2799943</v>
+        <v>1959263</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -9,065 千)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>6742514</v>
+        <v>-2014791</v>
       </c>
       <c r="E15" t="n">
-        <v>3041316</v>
+        <v>1145589</v>
       </c>
       <c r="F15" t="n">
-        <v>233776698</v>
+        <v>4244354</v>
       </c>
       <c r="G15" t="n">
-        <v>242842156</v>
+        <v>6245104</v>
       </c>
       <c r="H15" t="n">
-        <v>722149194</v>
+        <v>-357855</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>聯鈞</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 14,375 千)</t>
+          <t>📈 20d 巨變(加碼 25,700 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>22767688</v>
+        <v>16815958</v>
       </c>
       <c r="E16" t="n">
-        <v>4719706</v>
+        <v>33279267</v>
       </c>
       <c r="F16" t="n">
-        <v>58086546</v>
+        <v>120371727</v>
       </c>
       <c r="G16" t="n">
-        <v>43711916</v>
+        <v>94672080</v>
       </c>
       <c r="H16" t="n">
-        <v>130619246</v>
+        <v>55967148</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -21,539 千)</t>
+          <t>📉 20d 巨變(減碼 -8,637 千)</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>33279267</v>
+        <v>610071</v>
       </c>
       <c r="E17" t="n">
-        <v>32305140</v>
+        <v>8232950</v>
       </c>
       <c r="F17" t="n">
-        <v>94672080</v>
+        <v>70365049</v>
       </c>
       <c r="G17" t="n">
-        <v>116210783</v>
+        <v>79001919</v>
       </c>
       <c r="H17" t="n">
-        <v>18358226</v>
+        <v>46013468</v>
       </c>
       <c r="I17" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2356</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -11,328 千)</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>8232950</v>
-      </c>
-      <c r="E18" t="n">
-        <v>33080418</v>
-      </c>
-      <c r="F18" t="n">
-        <v>79001919</v>
-      </c>
-      <c r="G18" t="n">
-        <v>90330108</v>
-      </c>
-      <c r="H18" t="n">
-        <v>56375309</v>
-      </c>
-      <c r="I18" t="inlineStr">
         <is>
           <t>英業達</t>
         </is>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,357 +466,357 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -12,105 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 15,432 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-1634783</v>
+        <v>307776</v>
       </c>
       <c r="E2" t="n">
-        <v>17642461</v>
+        <v>-8511617</v>
       </c>
       <c r="F2" t="n">
-        <v>59340879</v>
+        <v>-24474459</v>
       </c>
       <c r="G2" t="n">
-        <v>71445420</v>
+        <v>-39906111</v>
       </c>
       <c r="H2" t="n">
-        <v>79095646</v>
+        <v>-232326851</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -27,996 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>-28130167</v>
+        <v>-10874805</v>
       </c>
       <c r="E3" t="n">
-        <v>-57251918</v>
+        <v>610071</v>
       </c>
       <c r="F3" t="n">
-        <v>30135053</v>
+        <v>70351457</v>
       </c>
       <c r="G3" t="n">
-        <v>58130971</v>
+        <v>70365049</v>
       </c>
       <c r="H3" t="n">
-        <v>-138991246</v>
+        <v>49765611</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -84,323 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>-19146200</v>
+        <v>-34730967</v>
       </c>
       <c r="E4" t="n">
-        <v>-3513673</v>
+        <v>-28130167</v>
       </c>
       <c r="F4" t="n">
-        <v>144577790</v>
+        <v>32121080</v>
       </c>
       <c r="G4" t="n">
-        <v>228901190</v>
+        <v>30135053</v>
       </c>
       <c r="H4" t="n">
-        <v>39956516</v>
+        <v>-142520151</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -42,028 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>-111110</v>
+        <v>-28183082</v>
       </c>
       <c r="E5" t="n">
-        <v>585397</v>
+        <v>-19146200</v>
       </c>
       <c r="F5" t="n">
-        <v>10329422</v>
+        <v>102550056</v>
       </c>
       <c r="G5" t="n">
-        <v>10865923</v>
+        <v>144577790</v>
       </c>
       <c r="H5" t="n">
-        <v>1900275</v>
+        <v>30363872</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 12,591 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>16429775</v>
+        <v>25727986</v>
       </c>
       <c r="E6" t="n">
-        <v>20120723</v>
+        <v>66697209</v>
       </c>
       <c r="F6" t="n">
-        <v>-14794426</v>
+        <v>83920386</v>
       </c>
       <c r="G6" t="n">
-        <v>-16479590</v>
+        <v>71329014</v>
       </c>
       <c r="H6" t="n">
-        <v>-17475442</v>
+        <v>-142057663</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>14124261</v>
+        <v>-269757</v>
       </c>
       <c r="E7" t="n">
-        <v>11199710</v>
+        <v>-111110</v>
       </c>
       <c r="F7" t="n">
-        <v>-33610697</v>
+        <v>10136939</v>
       </c>
       <c r="G7" t="n">
-        <v>-33559502</v>
+        <v>10329422</v>
       </c>
       <c r="H7" t="n">
-        <v>-114182548</v>
+        <v>1512151</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>457701</v>
+        <v>5766357</v>
       </c>
       <c r="E8" t="n">
-        <v>-594703</v>
+        <v>1925842</v>
       </c>
       <c r="F8" t="n">
-        <v>-19610978</v>
+        <v>11721715</v>
       </c>
       <c r="G8" t="n">
-        <v>-19795810</v>
+        <v>8072258</v>
       </c>
       <c r="H8" t="n">
-        <v>-44940528</v>
+        <v>-2207746</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-8607786</v>
+        <v>15827263</v>
       </c>
       <c r="E9" t="n">
-        <v>-10839680</v>
+        <v>16429775</v>
       </c>
       <c r="F9" t="n">
-        <v>41951362</v>
+        <v>-10723164</v>
       </c>
       <c r="G9" t="n">
-        <v>45333437</v>
+        <v>-14794426</v>
       </c>
       <c r="H9" t="n">
-        <v>7340155</v>
+        <v>-15059823</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-10838873</v>
+        <v>7196742</v>
       </c>
       <c r="E10" t="n">
-        <v>-10737230</v>
+        <v>14124261</v>
       </c>
       <c r="F10" t="n">
-        <v>-12268276</v>
+        <v>-32515415</v>
       </c>
       <c r="G10" t="n">
-        <v>-10867086</v>
+        <v>-33610697</v>
       </c>
       <c r="H10" t="n">
-        <v>266108</v>
+        <v>-114476046</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>9864108</v>
+        <v>-4990781</v>
       </c>
       <c r="E11" t="n">
-        <v>6073721</v>
+        <v>-8607786</v>
       </c>
       <c r="F11" t="n">
-        <v>51226078</v>
+        <v>34541760</v>
       </c>
       <c r="G11" t="n">
-        <v>53863280</v>
+        <v>41951362</v>
       </c>
       <c r="H11" t="n">
-        <v>-63199695</v>
+        <v>6694881</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,58 +828,58 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>66697209</v>
+        <v>9171411</v>
       </c>
       <c r="E12" t="n">
-        <v>56012615</v>
+        <v>9864108</v>
       </c>
       <c r="F12" t="n">
-        <v>71329014</v>
+        <v>44614454</v>
       </c>
       <c r="G12" t="n">
-        <v>63745871</v>
+        <v>51226078</v>
       </c>
       <c r="H12" t="n">
-        <v>-156979358</v>
+        <v>-62429265</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1877870</v>
+        <v>-2510945</v>
       </c>
       <c r="E13" t="n">
-        <v>-234316</v>
+        <v>-4582769</v>
       </c>
       <c r="F13" t="n">
-        <v>3565418</v>
+        <v>-11294781</v>
       </c>
       <c r="G13" t="n">
-        <v>3220714</v>
+        <v>-11351513</v>
       </c>
       <c r="H13" t="n">
-        <v>2187020</v>
+        <v>44046</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>金像電</t>
         </is>
       </c>
     </row>
@@ -891,26 +891,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🟢 5d 翻綠 / 📈 20d 巨變(加碼 11,642 千)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
+        <v>8328879</v>
+      </c>
+      <c r="E14" t="n">
         <v>-3466075</v>
       </c>
-      <c r="E14" t="n">
-        <v>-3456220</v>
-      </c>
       <c r="F14" t="n">
+        <v>18066170</v>
+      </c>
+      <c r="G14" t="n">
         <v>6424170</v>
       </c>
-      <c r="G14" t="n">
-        <v>5478212</v>
-      </c>
       <c r="H14" t="n">
-        <v>1959263</v>
+        <v>13710810</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -926,26 +926,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" t="n">
+        <v>-1769848</v>
+      </c>
+      <c r="E15" t="n">
         <v>-2014791</v>
       </c>
-      <c r="E15" t="n">
-        <v>1145589</v>
-      </c>
       <c r="F15" t="n">
+        <v>8067052</v>
+      </c>
+      <c r="G15" t="n">
         <v>4244354</v>
       </c>
-      <c r="G15" t="n">
-        <v>6245104</v>
-      </c>
       <c r="H15" t="n">
-        <v>-357855</v>
+        <v>43719</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -961,65 +961,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 25,700 千)</t>
+          <t>📈 20d 巨變(加碼 19,379 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
+        <v>32874992</v>
+      </c>
+      <c r="E16" t="n">
         <v>16815958</v>
       </c>
-      <c r="E16" t="n">
-        <v>33279267</v>
-      </c>
       <c r="F16" t="n">
+        <v>139750634</v>
+      </c>
+      <c r="G16" t="n">
         <v>120371727</v>
       </c>
-      <c r="G16" t="n">
-        <v>94672080</v>
-      </c>
       <c r="H16" t="n">
-        <v>55967148</v>
+        <v>61999912</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>南亞科</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2356</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -8,637 千)</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="n">
-        <v>610071</v>
-      </c>
-      <c r="E17" t="n">
-        <v>8232950</v>
-      </c>
-      <c r="F17" t="n">
-        <v>70365049</v>
-      </c>
-      <c r="G17" t="n">
-        <v>79001919</v>
-      </c>
-      <c r="H17" t="n">
-        <v>46013468</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>英業達</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,182 +466,182 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 15,432 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -8,068 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>307776</v>
+        <v>-33239706</v>
       </c>
       <c r="E2" t="n">
-        <v>-8511617</v>
+        <v>-34730967</v>
       </c>
       <c r="F2" t="n">
-        <v>-24474459</v>
+        <v>24053371</v>
       </c>
       <c r="G2" t="n">
-        <v>-39906111</v>
+        <v>32121080</v>
       </c>
       <c r="H2" t="n">
-        <v>-232326851</v>
+        <v>-134147330</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -15,117 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>-10874805</v>
+        <v>-5014913</v>
       </c>
       <c r="E3" t="n">
-        <v>610071</v>
+        <v>-4990781</v>
       </c>
       <c r="F3" t="n">
-        <v>70351457</v>
+        <v>19424791</v>
       </c>
       <c r="G3" t="n">
-        <v>70365049</v>
+        <v>34541760</v>
       </c>
       <c r="H3" t="n">
-        <v>49765611</v>
+        <v>10436223</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>-34730967</v>
+        <v>-1362386</v>
       </c>
       <c r="E4" t="n">
-        <v>-28130167</v>
+        <v>101863</v>
       </c>
       <c r="F4" t="n">
-        <v>32121080</v>
+        <v>16607124</v>
       </c>
       <c r="G4" t="n">
-        <v>30135053</v>
+        <v>16303063</v>
       </c>
       <c r="H4" t="n">
-        <v>-142520151</v>
+        <v>2362859</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -42,028 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>-28183082</v>
+        <v>-66839</v>
       </c>
       <c r="E5" t="n">
-        <v>-19146200</v>
+        <v>-269757</v>
       </c>
       <c r="F5" t="n">
-        <v>102550056</v>
+        <v>10324019</v>
       </c>
       <c r="G5" t="n">
-        <v>144577790</v>
+        <v>10136939</v>
       </c>
       <c r="H5" t="n">
-        <v>30363872</v>
+        <v>3521614</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 12,591 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>25727986</v>
+        <v>2850398</v>
       </c>
       <c r="E6" t="n">
-        <v>66697209</v>
+        <v>7196742</v>
       </c>
       <c r="F6" t="n">
-        <v>83920386</v>
+        <v>-28066289</v>
       </c>
       <c r="G6" t="n">
-        <v>71329014</v>
+        <v>-32515415</v>
       </c>
       <c r="H6" t="n">
-        <v>-142057663</v>
+        <v>-84769307</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,30 +653,30 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-269757</v>
+        <v>-29568545</v>
       </c>
       <c r="E7" t="n">
-        <v>-111110</v>
+        <v>-28183082</v>
       </c>
       <c r="F7" t="n">
-        <v>10136939</v>
+        <v>94808897</v>
       </c>
       <c r="G7" t="n">
-        <v>10329422</v>
+        <v>102550056</v>
       </c>
       <c r="H7" t="n">
-        <v>1512151</v>
+        <v>43746329</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,303 +688,408 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>5766357</v>
+        <v>8237800</v>
       </c>
       <c r="E8" t="n">
-        <v>1925842</v>
+        <v>9171411</v>
       </c>
       <c r="F8" t="n">
-        <v>11721715</v>
+        <v>39385689</v>
       </c>
       <c r="G8" t="n">
-        <v>8072258</v>
+        <v>44614454</v>
       </c>
       <c r="H8" t="n">
-        <v>-2207746</v>
+        <v>-63690696</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>15827263</v>
+        <v>30168750</v>
       </c>
       <c r="E9" t="n">
-        <v>16429775</v>
+        <v>25727986</v>
       </c>
       <c r="F9" t="n">
-        <v>-10723164</v>
+        <v>90395019</v>
       </c>
       <c r="G9" t="n">
-        <v>-14794426</v>
+        <v>83920386</v>
       </c>
       <c r="H9" t="n">
-        <v>-15059823</v>
+        <v>-128527733</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>7196742</v>
+        <v>-3110110</v>
       </c>
       <c r="E10" t="n">
-        <v>14124261</v>
+        <v>-2510945</v>
       </c>
       <c r="F10" t="n">
-        <v>-32515415</v>
+        <v>-11663362</v>
       </c>
       <c r="G10" t="n">
-        <v>-33610697</v>
+        <v>-11294781</v>
       </c>
       <c r="H10" t="n">
-        <v>-114476046</v>
+        <v>685798</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>金像電</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-4990781</v>
+        <v>-5754608</v>
       </c>
       <c r="E11" t="n">
-        <v>-8607786</v>
+        <v>307776</v>
       </c>
       <c r="F11" t="n">
-        <v>34541760</v>
+        <v>-23433430</v>
       </c>
       <c r="G11" t="n">
-        <v>41951362</v>
+        <v>-24474459</v>
       </c>
       <c r="H11" t="n">
-        <v>6694881</v>
+        <v>-198474535</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>9171411</v>
+        <v>6736878</v>
       </c>
       <c r="E12" t="n">
-        <v>9864108</v>
+        <v>15827263</v>
       </c>
       <c r="F12" t="n">
-        <v>44614454</v>
+        <v>-9554603</v>
       </c>
       <c r="G12" t="n">
-        <v>51226078</v>
+        <v>-10723164</v>
       </c>
       <c r="H12" t="n">
-        <v>-62429265</v>
+        <v>-4856253</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-2510945</v>
+        <v>-2894716</v>
       </c>
       <c r="E13" t="n">
-        <v>-4582769</v>
+        <v>-1769848</v>
       </c>
       <c r="F13" t="n">
-        <v>-11294781</v>
+        <v>7585145</v>
       </c>
       <c r="G13" t="n">
-        <v>-11351513</v>
+        <v>8067052</v>
       </c>
       <c r="H13" t="n">
-        <v>44046</v>
+        <v>-695372</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>聯鈞</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠 / 📈 20d 巨變(加碼 11,642 千)</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>8328879</v>
+        <v>2599149</v>
       </c>
       <c r="E14" t="n">
-        <v>-3466075</v>
+        <v>-449672</v>
       </c>
       <c r="F14" t="n">
-        <v>18066170</v>
+        <v>6584932</v>
       </c>
       <c r="G14" t="n">
-        <v>6424170</v>
+        <v>4241747</v>
       </c>
       <c r="H14" t="n">
-        <v>13710810</v>
+        <v>-276914</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>宇瞻</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>-1769848</v>
+        <v>2122254</v>
       </c>
       <c r="E15" t="n">
-        <v>-2014791</v>
+        <v>-10874805</v>
       </c>
       <c r="F15" t="n">
-        <v>8067052</v>
+        <v>73527600</v>
       </c>
       <c r="G15" t="n">
-        <v>4244354</v>
+        <v>70351457</v>
       </c>
       <c r="H15" t="n">
-        <v>43719</v>
+        <v>66439283</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 19,379 千)</t>
+          <t>📉 20d 巨變(減碼 -12,586 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
+        <v>38063099</v>
+      </c>
+      <c r="E16" t="n">
+        <v>55324024</v>
+      </c>
+      <c r="F16" t="n">
+        <v>218375490</v>
+      </c>
+      <c r="G16" t="n">
+        <v>230961950</v>
+      </c>
+      <c r="H16" t="n">
+        <v>756616311</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>長榮航</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3260</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 9,867 千)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>19230086</v>
+      </c>
+      <c r="E17" t="n">
+        <v>8328879</v>
+      </c>
+      <c r="F17" t="n">
+        <v>27933648</v>
+      </c>
+      <c r="G17" t="n">
+        <v>18066170</v>
+      </c>
+      <c r="H17" t="n">
+        <v>24706230</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>威剛</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -11,564 千)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>9422761</v>
+      </c>
+      <c r="E18" t="n">
         <v>32874992</v>
       </c>
-      <c r="E16" t="n">
-        <v>16815958</v>
-      </c>
-      <c r="F16" t="n">
+      <c r="F18" t="n">
+        <v>128186743</v>
+      </c>
+      <c r="G18" t="n">
         <v>139750634</v>
       </c>
-      <c r="G16" t="n">
-        <v>120371727</v>
-      </c>
-      <c r="H16" t="n">
-        <v>61999912</v>
-      </c>
-      <c r="I16" t="inlineStr">
+      <c r="H18" t="n">
+        <v>64283013</v>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>南亞科</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 11,455 千)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>9991366</v>
+      </c>
+      <c r="E19" t="n">
+        <v>92044</v>
+      </c>
+      <c r="F19" t="n">
+        <v>72452752</v>
+      </c>
+      <c r="G19" t="n">
+        <v>60997587</v>
+      </c>
+      <c r="H19" t="n">
+        <v>90226753</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>光寶科</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,182 +466,182 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -8,068 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📈 20d 巨變(加碼 8,706 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-33239706</v>
+        <v>-250513</v>
       </c>
       <c r="E2" t="n">
-        <v>-34730967</v>
+        <v>9991366</v>
       </c>
       <c r="F2" t="n">
-        <v>24053371</v>
+        <v>81158761</v>
       </c>
       <c r="G2" t="n">
-        <v>32121080</v>
+        <v>72452752</v>
       </c>
       <c r="H2" t="n">
-        <v>-134147330</v>
+        <v>91290694</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -15,117 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>-5014913</v>
+        <v>-40901380</v>
       </c>
       <c r="E3" t="n">
-        <v>-4990781</v>
+        <v>-33239706</v>
       </c>
       <c r="F3" t="n">
-        <v>19424791</v>
+        <v>28618223</v>
       </c>
       <c r="G3" t="n">
-        <v>34541760</v>
+        <v>24053371</v>
       </c>
       <c r="H3" t="n">
-        <v>10436223</v>
+        <v>-134016861</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -11,424 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>-1362386</v>
+        <v>-31639365</v>
       </c>
       <c r="E4" t="n">
-        <v>101863</v>
+        <v>-29568545</v>
       </c>
       <c r="F4" t="n">
-        <v>16607124</v>
+        <v>83384407</v>
       </c>
       <c r="G4" t="n">
-        <v>16303063</v>
+        <v>94808897</v>
       </c>
       <c r="H4" t="n">
-        <v>2362859</v>
+        <v>43289437</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -8,808 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>-66839</v>
+        <v>-2128871</v>
       </c>
       <c r="E5" t="n">
-        <v>-269757</v>
+        <v>-5014913</v>
       </c>
       <c r="F5" t="n">
-        <v>10324019</v>
+        <v>10616359</v>
       </c>
       <c r="G5" t="n">
-        <v>10136939</v>
+        <v>19424791</v>
       </c>
       <c r="H5" t="n">
-        <v>3521614</v>
+        <v>6221121</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 15,663 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>2850398</v>
+        <v>26923604</v>
       </c>
       <c r="E6" t="n">
-        <v>7196742</v>
+        <v>30168750</v>
       </c>
       <c r="F6" t="n">
-        <v>-28066289</v>
+        <v>106058468</v>
       </c>
       <c r="G6" t="n">
-        <v>-32515415</v>
+        <v>90395019</v>
       </c>
       <c r="H6" t="n">
-        <v>-84769307</v>
+        <v>-158620330</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,65 +653,65 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-29568545</v>
+        <v>-639181</v>
       </c>
       <c r="E7" t="n">
-        <v>-28183082</v>
+        <v>-1362386</v>
       </c>
       <c r="F7" t="n">
-        <v>94808897</v>
+        <v>17896186</v>
       </c>
       <c r="G7" t="n">
-        <v>102550056</v>
+        <v>16607124</v>
       </c>
       <c r="H7" t="n">
-        <v>43746329</v>
+        <v>2192050</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>8237800</v>
+        <v>3950336</v>
       </c>
       <c r="E8" t="n">
-        <v>9171411</v>
+        <v>2850398</v>
       </c>
       <c r="F8" t="n">
-        <v>39385689</v>
+        <v>-29165529</v>
       </c>
       <c r="G8" t="n">
-        <v>44614454</v>
+        <v>-28066289</v>
       </c>
       <c r="H8" t="n">
-        <v>-63690696</v>
+        <v>-74179223</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,23 +723,23 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>30168750</v>
+        <v>8662230</v>
       </c>
       <c r="E9" t="n">
-        <v>25727986</v>
+        <v>8237800</v>
       </c>
       <c r="F9" t="n">
-        <v>90395019</v>
+        <v>39112792</v>
       </c>
       <c r="G9" t="n">
-        <v>83920386</v>
+        <v>39385689</v>
       </c>
       <c r="H9" t="n">
-        <v>-128527733</v>
+        <v>-60623198</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
@@ -758,19 +758,19 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
+        <v>-1656864</v>
+      </c>
+      <c r="E10" t="n">
         <v>-3110110</v>
       </c>
-      <c r="E10" t="n">
-        <v>-2510945</v>
-      </c>
       <c r="F10" t="n">
+        <v>-13683534</v>
+      </c>
+      <c r="G10" t="n">
         <v>-11663362</v>
       </c>
-      <c r="G10" t="n">
-        <v>-11294781</v>
-      </c>
       <c r="H10" t="n">
-        <v>685798</v>
+        <v>541823</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -781,315 +781,245 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-5754608</v>
+        <v>14453</v>
       </c>
       <c r="E11" t="n">
-        <v>307776</v>
+        <v>-916597</v>
       </c>
       <c r="F11" t="n">
-        <v>-23433430</v>
+        <v>-2677073</v>
       </c>
       <c r="G11" t="n">
-        <v>-24474459</v>
+        <v>-3677350</v>
       </c>
       <c r="H11" t="n">
-        <v>-198474535</v>
+        <v>-18466826</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>瑞昱</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>6736878</v>
+        <v>-864991</v>
       </c>
       <c r="E12" t="n">
-        <v>15827263</v>
+        <v>-66839</v>
       </c>
       <c r="F12" t="n">
-        <v>-9554603</v>
+        <v>9956853</v>
       </c>
       <c r="G12" t="n">
-        <v>-10723164</v>
+        <v>10324019</v>
       </c>
       <c r="H12" t="n">
-        <v>-4856253</v>
+        <v>5054426</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-2894716</v>
+        <v>6716285</v>
       </c>
       <c r="E13" t="n">
-        <v>-1769848</v>
+        <v>6736878</v>
       </c>
       <c r="F13" t="n">
-        <v>7585145</v>
+        <v>-5790450</v>
       </c>
       <c r="G13" t="n">
-        <v>8067052</v>
+        <v>-9554603</v>
       </c>
       <c r="H13" t="n">
-        <v>-695372</v>
+        <v>729403</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>2599149</v>
+        <v>-2836884</v>
       </c>
       <c r="E14" t="n">
-        <v>-449672</v>
+        <v>-2894716</v>
       </c>
       <c r="F14" t="n">
-        <v>6584932</v>
+        <v>8257824</v>
       </c>
       <c r="G14" t="n">
-        <v>4241747</v>
+        <v>7585145</v>
       </c>
       <c r="H14" t="n">
-        <v>-276914</v>
+        <v>2804290</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>聯鈞</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>2122254</v>
+        <v>-468098</v>
       </c>
       <c r="E15" t="n">
-        <v>-10874805</v>
+        <v>-1081356</v>
       </c>
       <c r="F15" t="n">
-        <v>73527600</v>
+        <v>5529477</v>
       </c>
       <c r="G15" t="n">
-        <v>70351457</v>
+        <v>3059118</v>
       </c>
       <c r="H15" t="n">
-        <v>66439283</v>
+        <v>-1877099</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -12,586 千)</t>
+          <t>📈 20d 巨變(加碼 13,508 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>38063099</v>
+        <v>-3660617</v>
       </c>
       <c r="E16" t="n">
-        <v>55324024</v>
+        <v>-5754608</v>
       </c>
       <c r="F16" t="n">
-        <v>218375490</v>
+        <v>-9925225</v>
       </c>
       <c r="G16" t="n">
-        <v>230961950</v>
+        <v>-23433430</v>
       </c>
       <c r="H16" t="n">
-        <v>756616311</v>
+        <v>-184082800</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 9,867 千)</t>
+          <t>📉 20d 巨變(減碼 -34,980 千)</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>19230086</v>
+        <v>27248419</v>
       </c>
       <c r="E17" t="n">
-        <v>8328879</v>
+        <v>38063099</v>
       </c>
       <c r="F17" t="n">
-        <v>27933648</v>
+        <v>183395019</v>
       </c>
       <c r="G17" t="n">
-        <v>18066170</v>
+        <v>218375490</v>
       </c>
       <c r="H17" t="n">
-        <v>24706230</v>
+        <v>752988187</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>威剛</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -11,564 千)</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>9422761</v>
-      </c>
-      <c r="E18" t="n">
-        <v>32874992</v>
-      </c>
-      <c r="F18" t="n">
-        <v>128186743</v>
-      </c>
-      <c r="G18" t="n">
-        <v>139750634</v>
-      </c>
-      <c r="H18" t="n">
-        <v>64283013</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2301</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 11,455 千)</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>9991366</v>
-      </c>
-      <c r="E19" t="n">
-        <v>92044</v>
-      </c>
-      <c r="F19" t="n">
-        <v>72452752</v>
-      </c>
-      <c r="G19" t="n">
-        <v>60997587</v>
-      </c>
-      <c r="H19" t="n">
-        <v>90226753</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>光寶科</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,35 +466,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📈 20d 巨變(加碼 8,706 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 16,415 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-250513</v>
+        <v>8961658</v>
       </c>
       <c r="E2" t="n">
-        <v>9991366</v>
+        <v>-3660617</v>
       </c>
       <c r="F2" t="n">
-        <v>81158761</v>
+        <v>6490002</v>
       </c>
       <c r="G2" t="n">
-        <v>72452752</v>
+        <v>-9925225</v>
       </c>
       <c r="H2" t="n">
-        <v>91290694</v>
+        <v>-173974184</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
@@ -513,19 +513,19 @@
         <v>7</v>
       </c>
       <c r="D3" t="n">
+        <v>-32908004</v>
+      </c>
+      <c r="E3" t="n">
         <v>-40901380</v>
       </c>
-      <c r="E3" t="n">
-        <v>-33239706</v>
-      </c>
       <c r="F3" t="n">
+        <v>27862750</v>
+      </c>
+      <c r="G3" t="n">
         <v>28618223</v>
       </c>
-      <c r="G3" t="n">
-        <v>24053371</v>
-      </c>
       <c r="H3" t="n">
-        <v>-134016861</v>
+        <v>-127504230</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -536,287 +536,287 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -11,424 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -10,265 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>-31639365</v>
+        <v>6379191</v>
       </c>
       <c r="E4" t="n">
-        <v>-29568545</v>
+        <v>8662230</v>
       </c>
       <c r="F4" t="n">
-        <v>83384407</v>
+        <v>28847344</v>
       </c>
       <c r="G4" t="n">
-        <v>94808897</v>
+        <v>39112792</v>
       </c>
       <c r="H4" t="n">
-        <v>43289437</v>
+        <v>-63407339</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -8,808 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 29,566 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>-2128871</v>
+        <v>45801048</v>
       </c>
       <c r="E5" t="n">
-        <v>-5014913</v>
+        <v>26923604</v>
       </c>
       <c r="F5" t="n">
-        <v>10616359</v>
+        <v>135624882</v>
       </c>
       <c r="G5" t="n">
-        <v>19424791</v>
+        <v>106058468</v>
       </c>
       <c r="H5" t="n">
-        <v>6221121</v>
+        <v>-150982974</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 15,663 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>26923604</v>
+        <v>-196442</v>
       </c>
       <c r="E6" t="n">
-        <v>30168750</v>
+        <v>-639181</v>
       </c>
       <c r="F6" t="n">
-        <v>106058468</v>
+        <v>18912355</v>
       </c>
       <c r="G6" t="n">
-        <v>90395019</v>
+        <v>17896186</v>
       </c>
       <c r="H6" t="n">
-        <v>-158620330</v>
+        <v>2963271</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-639181</v>
+        <v>3489292</v>
       </c>
       <c r="E7" t="n">
-        <v>-1362386</v>
+        <v>3950336</v>
       </c>
       <c r="F7" t="n">
-        <v>17896186</v>
+        <v>-26918823</v>
       </c>
       <c r="G7" t="n">
-        <v>16607124</v>
+        <v>-29165529</v>
       </c>
       <c r="H7" t="n">
-        <v>2192050</v>
+        <v>-58539829</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>3950336</v>
+        <v>-1216972</v>
       </c>
       <c r="E8" t="n">
-        <v>2850398</v>
+        <v>-250513</v>
       </c>
       <c r="F8" t="n">
-        <v>-29165529</v>
+        <v>81288964</v>
       </c>
       <c r="G8" t="n">
-        <v>-28066289</v>
+        <v>81158761</v>
       </c>
       <c r="H8" t="n">
-        <v>-74179223</v>
+        <v>89285383</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>8662230</v>
+        <v>-25178665</v>
       </c>
       <c r="E9" t="n">
-        <v>8237800</v>
+        <v>-31639365</v>
       </c>
       <c r="F9" t="n">
-        <v>39112792</v>
+        <v>82775621</v>
       </c>
       <c r="G9" t="n">
-        <v>39385689</v>
+        <v>83384407</v>
       </c>
       <c r="H9" t="n">
-        <v>-60623198</v>
+        <v>50330193</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-1656864</v>
+        <v>277832</v>
       </c>
       <c r="E10" t="n">
-        <v>-3110110</v>
+        <v>-448112</v>
       </c>
       <c r="F10" t="n">
-        <v>-13683534</v>
+        <v>-17687688</v>
       </c>
       <c r="G10" t="n">
-        <v>-11663362</v>
+        <v>-17797331</v>
       </c>
       <c r="H10" t="n">
-        <v>541823</v>
+        <v>-48882854</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>14453</v>
+        <v>-462363</v>
       </c>
       <c r="E11" t="n">
-        <v>-916597</v>
+        <v>-1656864</v>
       </c>
       <c r="F11" t="n">
-        <v>-2677073</v>
+        <v>-15166722</v>
       </c>
       <c r="G11" t="n">
-        <v>-3677350</v>
+        <v>-13683534</v>
       </c>
       <c r="H11" t="n">
-        <v>-18466826</v>
+        <v>572441</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>金像電</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,23 +828,23 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-864991</v>
+        <v>-617395</v>
       </c>
       <c r="E12" t="n">
-        <v>-66839</v>
+        <v>50149</v>
       </c>
       <c r="F12" t="n">
-        <v>9956853</v>
+        <v>7180272</v>
       </c>
       <c r="G12" t="n">
-        <v>10324019</v>
+        <v>7726286</v>
       </c>
       <c r="H12" t="n">
-        <v>5054426</v>
+        <v>6227213</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>奇鋐</t>
         </is>
       </c>
     </row>
@@ -863,19 +863,19 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
+        <v>5332671</v>
+      </c>
+      <c r="E13" t="n">
         <v>6716285</v>
       </c>
-      <c r="E13" t="n">
-        <v>6736878</v>
-      </c>
       <c r="F13" t="n">
+        <v>-215777</v>
+      </c>
+      <c r="G13" t="n">
         <v>-5790450</v>
       </c>
-      <c r="G13" t="n">
-        <v>-9554603</v>
-      </c>
       <c r="H13" t="n">
-        <v>729403</v>
+        <v>3680130</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,30 +898,30 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-2836884</v>
+        <v>-191197</v>
       </c>
       <c r="E14" t="n">
-        <v>-2894716</v>
+        <v>1381905</v>
       </c>
       <c r="F14" t="n">
-        <v>8257824</v>
+        <v>6488136</v>
       </c>
       <c r="G14" t="n">
-        <v>7585145</v>
+        <v>8513657</v>
       </c>
       <c r="H14" t="n">
-        <v>2804290</v>
+        <v>5465206</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>鈊象</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,93 +933,58 @@
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>-468098</v>
+        <v>-478772</v>
       </c>
       <c r="E15" t="n">
-        <v>-1081356</v>
+        <v>-2836884</v>
       </c>
       <c r="F15" t="n">
-        <v>5529477</v>
+        <v>8117808</v>
       </c>
       <c r="G15" t="n">
-        <v>3059118</v>
+        <v>8257824</v>
       </c>
       <c r="H15" t="n">
-        <v>-1877099</v>
+        <v>3367108</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>聯鈞</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 13,508 千)</t>
+          <t>📉 20d 巨變(減碼 -14,916 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-3660617</v>
+        <v>-2991690</v>
       </c>
       <c r="E16" t="n">
-        <v>-5754608</v>
+        <v>-2128871</v>
       </c>
       <c r="F16" t="n">
-        <v>-9925225</v>
+        <v>-4300123</v>
       </c>
       <c r="G16" t="n">
-        <v>-23433430</v>
+        <v>10616359</v>
       </c>
       <c r="H16" t="n">
-        <v>-184082800</v>
+        <v>-1614537</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>台積電</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -34,980 千)</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="n">
-        <v>27248419</v>
-      </c>
-      <c r="E17" t="n">
-        <v>38063099</v>
-      </c>
-      <c r="F17" t="n">
-        <v>183395019</v>
-      </c>
-      <c r="G17" t="n">
-        <v>218375490</v>
-      </c>
-      <c r="H17" t="n">
-        <v>752988187</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>長榮航</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,350 +466,350 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 16,415 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 51,857 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>8961658</v>
+        <v>-10417764</v>
       </c>
       <c r="E2" t="n">
-        <v>-3660617</v>
+        <v>-32908004</v>
       </c>
       <c r="F2" t="n">
-        <v>6490002</v>
+        <v>79719740</v>
       </c>
       <c r="G2" t="n">
-        <v>-9925225</v>
+        <v>27862750</v>
       </c>
       <c r="H2" t="n">
-        <v>-173974184</v>
+        <v>-111207351</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>-32908004</v>
+        <v>170783</v>
       </c>
       <c r="E3" t="n">
-        <v>-40901380</v>
+        <v>-3849938</v>
       </c>
       <c r="F3" t="n">
-        <v>27862750</v>
+        <v>-70653500</v>
       </c>
       <c r="G3" t="n">
-        <v>28618223</v>
+        <v>-63466638</v>
       </c>
       <c r="H3" t="n">
-        <v>-127504230</v>
+        <v>-73673015</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -10,265 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>6379191</v>
+        <v>291688</v>
       </c>
       <c r="E4" t="n">
-        <v>8662230</v>
+        <v>-462363</v>
       </c>
       <c r="F4" t="n">
-        <v>28847344</v>
+        <v>-15254843</v>
       </c>
       <c r="G4" t="n">
-        <v>39112792</v>
+        <v>-15166722</v>
       </c>
       <c r="H4" t="n">
-        <v>-63407339</v>
+        <v>1940195</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>金像電</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 29,566 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 8,458 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>45801048</v>
+        <v>12728121</v>
       </c>
       <c r="E5" t="n">
-        <v>26923604</v>
+        <v>8961658</v>
       </c>
       <c r="F5" t="n">
-        <v>135624882</v>
+        <v>14948052</v>
       </c>
       <c r="G5" t="n">
-        <v>106058468</v>
+        <v>6490002</v>
       </c>
       <c r="H5" t="n">
-        <v>-150982974</v>
+        <v>-173401013</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 30,811 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>-196442</v>
+        <v>8540407</v>
       </c>
       <c r="E6" t="n">
-        <v>-639181</v>
+        <v>3489292</v>
       </c>
       <c r="F6" t="n">
-        <v>18912355</v>
+        <v>3892564</v>
       </c>
       <c r="G6" t="n">
-        <v>17896186</v>
+        <v>-26918823</v>
       </c>
       <c r="H6" t="n">
-        <v>2963271</v>
+        <v>-51877221</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>3489292</v>
+        <v>-26559447</v>
       </c>
       <c r="E7" t="n">
-        <v>3950336</v>
+        <v>-25178665</v>
       </c>
       <c r="F7" t="n">
-        <v>-26918823</v>
+        <v>76107070</v>
       </c>
       <c r="G7" t="n">
-        <v>-29165529</v>
+        <v>82775621</v>
       </c>
       <c r="H7" t="n">
-        <v>-58539829</v>
+        <v>49414666</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-1216972</v>
+        <v>285061</v>
       </c>
       <c r="E8" t="n">
-        <v>-250513</v>
+        <v>277832</v>
       </c>
       <c r="F8" t="n">
-        <v>81288964</v>
+        <v>-15768962</v>
       </c>
       <c r="G8" t="n">
-        <v>81158761</v>
+        <v>-17687688</v>
       </c>
       <c r="H8" t="n">
-        <v>89285383</v>
+        <v>-47656581</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-25178665</v>
+        <v>52796521</v>
       </c>
       <c r="E9" t="n">
-        <v>-31639365</v>
+        <v>45801048</v>
       </c>
       <c r="F9" t="n">
-        <v>82775621</v>
+        <v>129435931</v>
       </c>
       <c r="G9" t="n">
-        <v>83384407</v>
+        <v>135624882</v>
       </c>
       <c r="H9" t="n">
-        <v>50330193</v>
+        <v>-154425435</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>277832</v>
+        <v>5730836</v>
       </c>
       <c r="E10" t="n">
-        <v>-448112</v>
+        <v>6379191</v>
       </c>
       <c r="F10" t="n">
-        <v>-17687688</v>
+        <v>23542012</v>
       </c>
       <c r="G10" t="n">
-        <v>-17797331</v>
+        <v>28847344</v>
       </c>
       <c r="H10" t="n">
-        <v>-48882854</v>
+        <v>-65569151</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-462363</v>
+        <v>1419211</v>
       </c>
       <c r="E11" t="n">
-        <v>-1656864</v>
+        <v>-469098</v>
       </c>
       <c r="F11" t="n">
-        <v>-15166722</v>
+        <v>-2374943</v>
       </c>
       <c r="G11" t="n">
-        <v>-13683534</v>
+        <v>-2668027</v>
       </c>
       <c r="H11" t="n">
-        <v>572441</v>
+        <v>-14857878</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>瑞昱</t>
         </is>
       </c>
     </row>
@@ -828,19 +828,19 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
+        <v>-600364</v>
+      </c>
+      <c r="E12" t="n">
         <v>-617395</v>
       </c>
-      <c r="E12" t="n">
-        <v>50149</v>
-      </c>
       <c r="F12" t="n">
+        <v>7008663</v>
+      </c>
+      <c r="G12" t="n">
         <v>7180272</v>
       </c>
-      <c r="G12" t="n">
-        <v>7726286</v>
-      </c>
       <c r="H12" t="n">
-        <v>6227213</v>
+        <v>5922917</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -851,35 +851,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>5332671</v>
+        <v>3253393</v>
       </c>
       <c r="E13" t="n">
-        <v>6716285</v>
+        <v>-196442</v>
       </c>
       <c r="F13" t="n">
-        <v>-215777</v>
+        <v>22215575</v>
       </c>
       <c r="G13" t="n">
-        <v>-5790450</v>
+        <v>18912355</v>
       </c>
       <c r="H13" t="n">
-        <v>3680130</v>
+        <v>4637068</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
@@ -898,19 +898,19 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
+        <v>-571420</v>
+      </c>
+      <c r="E14" t="n">
         <v>-191197</v>
       </c>
-      <c r="E14" t="n">
-        <v>1381905</v>
-      </c>
       <c r="F14" t="n">
+        <v>5979775</v>
+      </c>
+      <c r="G14" t="n">
         <v>6488136</v>
       </c>
-      <c r="G14" t="n">
-        <v>8513657</v>
-      </c>
       <c r="H14" t="n">
-        <v>5465206</v>
+        <v>6794579</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -926,26 +926,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" t="n">
+        <v>2202273</v>
+      </c>
+      <c r="E15" t="n">
         <v>-478772</v>
       </c>
-      <c r="E15" t="n">
-        <v>-2836884</v>
-      </c>
       <c r="F15" t="n">
+        <v>6559166</v>
+      </c>
+      <c r="G15" t="n">
         <v>8117808</v>
       </c>
-      <c r="G15" t="n">
-        <v>8257824</v>
-      </c>
       <c r="H15" t="n">
-        <v>3367108</v>
+        <v>4370540</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -956,35 +956,105 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -14,916 千)</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3293024</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-1216972</v>
+      </c>
+      <c r="F16" t="n">
+        <v>79929129</v>
+      </c>
+      <c r="G16" t="n">
+        <v>81288964</v>
+      </c>
+      <c r="H16" t="n">
+        <v>82282202</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -33,918 千)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
         <v>1</v>
       </c>
-      <c r="D16" t="n">
-        <v>-2991690</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-2128871</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-4300123</v>
-      </c>
-      <c r="G16" t="n">
-        <v>10616359</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-1614537</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>中華電</t>
+      <c r="D17" t="n">
+        <v>22226241</v>
+      </c>
+      <c r="E17" t="n">
+        <v>33054054</v>
+      </c>
+      <c r="F17" t="n">
+        <v>145417600</v>
+      </c>
+      <c r="G17" t="n">
+        <v>179335447</v>
+      </c>
+      <c r="H17" t="n">
+        <v>715120488</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>長榮航</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 30,801 千)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>27402353</v>
+      </c>
+      <c r="E18" t="n">
+        <v>23546436</v>
+      </c>
+      <c r="F18" t="n">
+        <v>171713159</v>
+      </c>
+      <c r="G18" t="n">
+        <v>140912290</v>
+      </c>
+      <c r="H18" t="n">
+        <v>75584615</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>南亞科</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,252 +466,252 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 51,857 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -59,421 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-10417764</v>
+        <v>-864947</v>
       </c>
       <c r="E2" t="n">
-        <v>-32908004</v>
+        <v>22226241</v>
       </c>
       <c r="F2" t="n">
-        <v>79719740</v>
+        <v>85996512</v>
       </c>
       <c r="G2" t="n">
-        <v>27862750</v>
+        <v>145417600</v>
       </c>
       <c r="H2" t="n">
-        <v>-111207351</v>
+        <v>570819168</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -62,657 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>170783</v>
+        <v>-2006335</v>
       </c>
       <c r="E3" t="n">
-        <v>-3849938</v>
+        <v>-10417764</v>
       </c>
       <c r="F3" t="n">
-        <v>-70653500</v>
+        <v>17062712</v>
       </c>
       <c r="G3" t="n">
-        <v>-63466638</v>
+        <v>79719740</v>
       </c>
       <c r="H3" t="n">
-        <v>-73673015</v>
+        <v>-124917972</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>291688</v>
+        <v>-9945482</v>
       </c>
       <c r="E4" t="n">
-        <v>-462363</v>
+        <v>13200496</v>
       </c>
       <c r="F4" t="n">
-        <v>-15254843</v>
+        <v>16660176</v>
       </c>
       <c r="G4" t="n">
-        <v>-15166722</v>
+        <v>16512348</v>
       </c>
       <c r="H4" t="n">
-        <v>1940195</v>
+        <v>14241753</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 8,458 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>12728121</v>
+        <v>-6155811</v>
       </c>
       <c r="E5" t="n">
-        <v>8961658</v>
+        <v>3293024</v>
       </c>
       <c r="F5" t="n">
-        <v>14948052</v>
+        <v>75933165</v>
       </c>
       <c r="G5" t="n">
-        <v>6490002</v>
+        <v>79929129</v>
       </c>
       <c r="H5" t="n">
-        <v>-173401013</v>
+        <v>99711239</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 30,811 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -45,170 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>8540407</v>
+        <v>-25756605</v>
       </c>
       <c r="E6" t="n">
-        <v>3489292</v>
+        <v>-26559447</v>
       </c>
       <c r="F6" t="n">
-        <v>3892564</v>
+        <v>30936571</v>
       </c>
       <c r="G6" t="n">
-        <v>-26918823</v>
+        <v>76107070</v>
       </c>
       <c r="H6" t="n">
-        <v>-51877221</v>
+        <v>63563957</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -36,966 千)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>-26559447</v>
+        <v>24417494</v>
       </c>
       <c r="E7" t="n">
-        <v>-25178665</v>
+        <v>52796521</v>
       </c>
       <c r="F7" t="n">
-        <v>76107070</v>
+        <v>92470228</v>
       </c>
       <c r="G7" t="n">
-        <v>82775621</v>
+        <v>129435931</v>
       </c>
       <c r="H7" t="n">
-        <v>49414666</v>
+        <v>-214366916</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>285061</v>
+        <v>7031215</v>
       </c>
       <c r="E8" t="n">
-        <v>277832</v>
+        <v>12728121</v>
       </c>
       <c r="F8" t="n">
-        <v>-15768962</v>
+        <v>9362315</v>
       </c>
       <c r="G8" t="n">
-        <v>-17687688</v>
+        <v>14948052</v>
       </c>
       <c r="H8" t="n">
-        <v>-47656581</v>
+        <v>-177311633</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,23 +723,23 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>52796521</v>
+        <v>9645933</v>
       </c>
       <c r="E9" t="n">
-        <v>45801048</v>
+        <v>8540407</v>
       </c>
       <c r="F9" t="n">
-        <v>129435931</v>
+        <v>7956754</v>
       </c>
       <c r="G9" t="n">
-        <v>135624882</v>
+        <v>3892564</v>
       </c>
       <c r="H9" t="n">
-        <v>-154425435</v>
+        <v>-46326754</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
@@ -758,19 +758,19 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
+        <v>4409190</v>
+      </c>
+      <c r="E10" t="n">
         <v>5730836</v>
       </c>
-      <c r="E10" t="n">
-        <v>6379191</v>
-      </c>
       <c r="F10" t="n">
+        <v>15895124</v>
+      </c>
+      <c r="G10" t="n">
         <v>23542012</v>
       </c>
-      <c r="G10" t="n">
-        <v>28847344</v>
-      </c>
       <c r="H10" t="n">
-        <v>-65569151</v>
+        <v>-76587556</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -781,280 +781,490 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1419211</v>
+        <v>-684600</v>
       </c>
       <c r="E11" t="n">
-        <v>-469098</v>
+        <v>291688</v>
       </c>
       <c r="F11" t="n">
-        <v>-2374943</v>
+        <v>-15232630</v>
       </c>
       <c r="G11" t="n">
-        <v>-2668027</v>
+        <v>-15254843</v>
       </c>
       <c r="H11" t="n">
-        <v>-14857878</v>
+        <v>847187</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>金像電</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 📈 20d 巨變(加碼 10,883 千)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-600364</v>
+        <v>882568</v>
       </c>
       <c r="E12" t="n">
-        <v>-617395</v>
+        <v>-969939</v>
       </c>
       <c r="F12" t="n">
-        <v>7008663</v>
+        <v>-3427060</v>
       </c>
       <c r="G12" t="n">
-        <v>7180272</v>
+        <v>-14309978</v>
       </c>
       <c r="H12" t="n">
-        <v>5922917</v>
+        <v>-47283016</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>3253393</v>
+        <v>984477</v>
       </c>
       <c r="E13" t="n">
-        <v>-196442</v>
+        <v>-1742204</v>
       </c>
       <c r="F13" t="n">
-        <v>22215575</v>
+        <v>-5314199</v>
       </c>
       <c r="G13" t="n">
-        <v>18912355</v>
+        <v>-7489579</v>
       </c>
       <c r="H13" t="n">
-        <v>4637068</v>
+        <v>-7424790</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>健鼎</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🔴 5d 翻紅 / 📉 20d 巨變(減碼 -17,818 千)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-571420</v>
+        <v>-15021775</v>
       </c>
       <c r="E14" t="n">
-        <v>-191197</v>
+        <v>170783</v>
       </c>
       <c r="F14" t="n">
-        <v>5979775</v>
+        <v>-88471176</v>
       </c>
       <c r="G14" t="n">
-        <v>6488136</v>
+        <v>-70653500</v>
       </c>
       <c r="H14" t="n">
-        <v>6794579</v>
+        <v>-91900017</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>🔴 5d 翻紅 / 📉 20d 巨變(減碼 -11,310 千)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>2202273</v>
+        <v>-6415981</v>
       </c>
       <c r="E15" t="n">
-        <v>-478772</v>
+        <v>6069438</v>
       </c>
       <c r="F15" t="n">
-        <v>6559166</v>
+        <v>-6652560</v>
       </c>
       <c r="G15" t="n">
-        <v>8117808</v>
+        <v>4657330</v>
       </c>
       <c r="H15" t="n">
-        <v>4370540</v>
+        <v>-10930381</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>3293024</v>
+        <v>103147</v>
       </c>
       <c r="E16" t="n">
-        <v>-1216972</v>
+        <v>1419211</v>
       </c>
       <c r="F16" t="n">
-        <v>79929129</v>
+        <v>-309589</v>
       </c>
       <c r="G16" t="n">
-        <v>81288964</v>
+        <v>-2374943</v>
       </c>
       <c r="H16" t="n">
-        <v>82282202</v>
+        <v>-17386835</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>瑞昱</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -33,918 千)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>22226241</v>
+        <v>-456855</v>
       </c>
       <c r="E17" t="n">
-        <v>33054054</v>
+        <v>-600364</v>
       </c>
       <c r="F17" t="n">
-        <v>145417600</v>
+        <v>6902444</v>
       </c>
       <c r="G17" t="n">
-        <v>179335447</v>
+        <v>7008663</v>
       </c>
       <c r="H17" t="n">
-        <v>715120488</v>
+        <v>5812840</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>奇鋐</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 30,801 千)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-1464412</v>
+      </c>
+      <c r="E18" t="n">
+        <v>647506</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-1411390</v>
+      </c>
+      <c r="G18" t="n">
+        <v>733752</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-2085177</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>亞力</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3293</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>🟢 5d 翻綠</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1805085</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-571420</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6164608</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5979775</v>
+      </c>
+      <c r="H19" t="n">
+        <v>8988451</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>鈊象</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>6446</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>🔴 5d 翻紅</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-1413808</v>
+      </c>
+      <c r="E20" t="n">
+        <v>835760</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-444359</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1005384</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-1884081</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>藥華藥</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>8271</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>🔴 5d 翻紅</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-369850</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2211824</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3402999</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4792482</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-207361</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>宇瞻</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 9,381 千)</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
         <v>1</v>
       </c>
-      <c r="D18" t="n">
-        <v>27402353</v>
-      </c>
-      <c r="E18" t="n">
-        <v>23546436</v>
-      </c>
-      <c r="F18" t="n">
-        <v>171713159</v>
-      </c>
-      <c r="G18" t="n">
-        <v>140912290</v>
-      </c>
-      <c r="H18" t="n">
-        <v>75584615</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>南亞科</t>
+      <c r="D22" t="n">
+        <v>16782923</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5523015</v>
+      </c>
+      <c r="F22" t="n">
+        <v>25505471</v>
+      </c>
+      <c r="G22" t="n">
+        <v>16124731</v>
+      </c>
+      <c r="H22" t="n">
+        <v>23696223</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>建準</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -13,020 千)</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1691833</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5463245</v>
+      </c>
+      <c r="F23" t="n">
+        <v>54007366</v>
+      </c>
+      <c r="G23" t="n">
+        <v>67027097</v>
+      </c>
+      <c r="H23" t="n">
+        <v>62211893</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>英業達</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2412</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -13,164 千)</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-5949419</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-3625025</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-25261730</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-12097340</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-5097387</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>中華電</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,140 +466,140 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -59,421 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -60,870 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>-864947</v>
+        <v>-29466174</v>
       </c>
       <c r="E2" t="n">
-        <v>22226241</v>
+        <v>24417494</v>
       </c>
       <c r="F2" t="n">
-        <v>85996512</v>
+        <v>31600627</v>
       </c>
       <c r="G2" t="n">
-        <v>145417600</v>
+        <v>92470228</v>
       </c>
       <c r="H2" t="n">
-        <v>570819168</v>
+        <v>-250761664</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -62,657 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 20,453 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>-2006335</v>
+        <v>533347</v>
       </c>
       <c r="E3" t="n">
-        <v>-10417764</v>
+        <v>-6415981</v>
       </c>
       <c r="F3" t="n">
-        <v>17062712</v>
+        <v>13800482</v>
       </c>
       <c r="G3" t="n">
-        <v>79719740</v>
+        <v>-6652560</v>
       </c>
       <c r="H3" t="n">
-        <v>-124917972</v>
+        <v>-17002057</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 11,344 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>-9945482</v>
+        <v>26989367</v>
       </c>
       <c r="E4" t="n">
-        <v>13200496</v>
+        <v>-2006335</v>
       </c>
       <c r="F4" t="n">
-        <v>16660176</v>
+        <v>28406237</v>
       </c>
       <c r="G4" t="n">
-        <v>16512348</v>
+        <v>17062712</v>
       </c>
       <c r="H4" t="n">
-        <v>14241753</v>
+        <v>-85969650</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 18,160 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>-6155811</v>
+        <v>13913205</v>
       </c>
       <c r="E5" t="n">
-        <v>3293024</v>
+        <v>7031215</v>
       </c>
       <c r="F5" t="n">
-        <v>75933165</v>
+        <v>27522695</v>
       </c>
       <c r="G5" t="n">
-        <v>79929129</v>
+        <v>9362315</v>
       </c>
       <c r="H5" t="n">
-        <v>99711239</v>
+        <v>-179096665</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
@@ -611,26 +611,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -45,170 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -17,164 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>6</v>
       </c>
       <c r="D6" t="n">
+        <v>-14881568</v>
+      </c>
+      <c r="E6" t="n">
         <v>-25756605</v>
       </c>
-      <c r="E6" t="n">
-        <v>-26559447</v>
-      </c>
       <c r="F6" t="n">
+        <v>13772967</v>
+      </c>
+      <c r="G6" t="n">
         <v>30936571</v>
       </c>
-      <c r="G6" t="n">
-        <v>76107070</v>
-      </c>
       <c r="H6" t="n">
-        <v>63563957</v>
+        <v>89896941</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -641,112 +641,112 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -36,966 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -31,911 千)</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>24417494</v>
+        <v>-8665886</v>
       </c>
       <c r="E7" t="n">
-        <v>52796521</v>
+        <v>-6155811</v>
       </c>
       <c r="F7" t="n">
-        <v>92470228</v>
+        <v>44021672</v>
       </c>
       <c r="G7" t="n">
-        <v>129435931</v>
+        <v>75933165</v>
       </c>
       <c r="H7" t="n">
-        <v>-214366916</v>
+        <v>91566667</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>7031215</v>
+        <v>2259280</v>
       </c>
       <c r="E8" t="n">
-        <v>12728121</v>
+        <v>882568</v>
       </c>
       <c r="F8" t="n">
-        <v>9362315</v>
+        <v>-7514312</v>
       </c>
       <c r="G8" t="n">
-        <v>14948052</v>
+        <v>-3427060</v>
       </c>
       <c r="H8" t="n">
-        <v>-177311633</v>
+        <v>-47992423</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>9645933</v>
+        <v>-5321402</v>
       </c>
       <c r="E9" t="n">
-        <v>8540407</v>
+        <v>-9945482</v>
       </c>
       <c r="F9" t="n">
-        <v>7956754</v>
+        <v>14630877</v>
       </c>
       <c r="G9" t="n">
-        <v>3892564</v>
+        <v>16660176</v>
       </c>
       <c r="H9" t="n">
-        <v>-46326754</v>
+        <v>11493487</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,240 +758,240 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>4409190</v>
+        <v>9875584</v>
       </c>
       <c r="E10" t="n">
-        <v>5730836</v>
+        <v>9645933</v>
       </c>
       <c r="F10" t="n">
-        <v>15895124</v>
+        <v>12124334</v>
       </c>
       <c r="G10" t="n">
-        <v>23542012</v>
+        <v>7956754</v>
       </c>
       <c r="H10" t="n">
-        <v>-76587556</v>
+        <v>-46984388</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-684600</v>
+        <v>160380</v>
       </c>
       <c r="E11" t="n">
-        <v>291688</v>
+        <v>-125958</v>
       </c>
       <c r="F11" t="n">
-        <v>-15232630</v>
+        <v>-12921538</v>
       </c>
       <c r="G11" t="n">
-        <v>-15254843</v>
+        <v>-14399876</v>
       </c>
       <c r="H11" t="n">
-        <v>847187</v>
+        <v>-49496116</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 📈 20d 巨變(加碼 10,883 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>882568</v>
+        <v>1002466</v>
       </c>
       <c r="E12" t="n">
-        <v>-969939</v>
+        <v>4409190</v>
       </c>
       <c r="F12" t="n">
-        <v>-3427060</v>
+        <v>16556152</v>
       </c>
       <c r="G12" t="n">
-        <v>-14309978</v>
+        <v>15895124</v>
       </c>
       <c r="H12" t="n">
-        <v>-47283016</v>
+        <v>-51503691</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>984477</v>
+        <v>1128550</v>
       </c>
       <c r="E13" t="n">
-        <v>-1742204</v>
+        <v>1883191</v>
       </c>
       <c r="F13" t="n">
-        <v>-5314199</v>
+        <v>10208309</v>
       </c>
       <c r="G13" t="n">
-        <v>-7489579</v>
+        <v>9946693</v>
       </c>
       <c r="H13" t="n">
-        <v>-7424790</v>
+        <v>-2187691</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅 / 📉 20d 巨變(減碼 -17,818 千)</t>
+          <t>🟢 5d 翻綠 / 📉 20d 巨變(減碼 -8,906 千)</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-15021775</v>
+        <v>2101180</v>
       </c>
       <c r="E14" t="n">
-        <v>170783</v>
+        <v>-864947</v>
       </c>
       <c r="F14" t="n">
-        <v>-88471176</v>
+        <v>77090859</v>
       </c>
       <c r="G14" t="n">
-        <v>-70653500</v>
+        <v>85996512</v>
       </c>
       <c r="H14" t="n">
-        <v>-91900017</v>
+        <v>562639446</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅 / 📉 20d 巨變(減碼 -11,310 千)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>-6415981</v>
+        <v>-721596</v>
       </c>
       <c r="E15" t="n">
-        <v>6069438</v>
+        <v>-456855</v>
       </c>
       <c r="F15" t="n">
-        <v>-6652560</v>
+        <v>6219586</v>
       </c>
       <c r="G15" t="n">
-        <v>4657330</v>
+        <v>6902444</v>
       </c>
       <c r="H15" t="n">
-        <v>-10930381</v>
+        <v>5368460</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>奇鋐</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>103147</v>
+        <v>934489</v>
       </c>
       <c r="E16" t="n">
-        <v>1419211</v>
+        <v>984477</v>
       </c>
       <c r="F16" t="n">
-        <v>-309589</v>
+        <v>-5484734</v>
       </c>
       <c r="G16" t="n">
-        <v>-2374943</v>
+        <v>-5314199</v>
       </c>
       <c r="H16" t="n">
-        <v>-17386835</v>
+        <v>-8413565</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>健鼎</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1003,268 +1003,93 @@
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>-456855</v>
+        <v>-631611</v>
       </c>
       <c r="E17" t="n">
-        <v>-600364</v>
+        <v>602133</v>
       </c>
       <c r="F17" t="n">
-        <v>6902444</v>
+        <v>6371900</v>
       </c>
       <c r="G17" t="n">
-        <v>7008663</v>
+        <v>8543243</v>
       </c>
       <c r="H17" t="n">
-        <v>5812840</v>
+        <v>9636074</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>📈 20d 巨變(加碼 16,016 千)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1464412</v>
+        <v>-6450067</v>
       </c>
       <c r="E18" t="n">
-        <v>647506</v>
+        <v>-15021775</v>
       </c>
       <c r="F18" t="n">
-        <v>-1411390</v>
+        <v>-72454938</v>
       </c>
       <c r="G18" t="n">
-        <v>733752</v>
+        <v>-88471176</v>
       </c>
       <c r="H18" t="n">
-        <v>-2085177</v>
+        <v>-75371386</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>📉 20d 巨變(減碼 -63,541 千)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1805085</v>
+        <v>1424587</v>
       </c>
       <c r="E19" t="n">
-        <v>-571420</v>
+        <v>39733111</v>
       </c>
       <c r="F19" t="n">
-        <v>6164608</v>
+        <v>104640659</v>
       </c>
       <c r="G19" t="n">
-        <v>5979775</v>
+        <v>168182110</v>
       </c>
       <c r="H19" t="n">
-        <v>8988451</v>
+        <v>4439717</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>鈊象</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>6446</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>🔴 5d 翻紅</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" t="n">
-        <v>-1413808</v>
-      </c>
-      <c r="E20" t="n">
-        <v>835760</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-444359</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1005384</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-1884081</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>藥華藥</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>8271</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>🔴 5d 翻紅</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" t="n">
-        <v>-369850</v>
-      </c>
-      <c r="E21" t="n">
-        <v>2211824</v>
-      </c>
-      <c r="F21" t="n">
-        <v>3402999</v>
-      </c>
-      <c r="G21" t="n">
-        <v>4792482</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-207361</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>宇瞻</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2421</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 9,381 千)</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="n">
-        <v>16782923</v>
-      </c>
-      <c r="E22" t="n">
-        <v>5523015</v>
-      </c>
-      <c r="F22" t="n">
-        <v>25505471</v>
-      </c>
-      <c r="G22" t="n">
-        <v>16124731</v>
-      </c>
-      <c r="H22" t="n">
-        <v>23696223</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>建準</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2356</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -13,020 千)</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1691833</v>
-      </c>
-      <c r="E23" t="n">
-        <v>5463245</v>
-      </c>
-      <c r="F23" t="n">
-        <v>54007366</v>
-      </c>
-      <c r="G23" t="n">
-        <v>67027097</v>
-      </c>
-      <c r="H23" t="n">
-        <v>62211893</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>英業達</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2412</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -13,164 千)</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="n">
-        <v>-5949419</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-3625025</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-25261730</v>
-      </c>
-      <c r="G24" t="n">
-        <v>-12097340</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-5097387</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>中華電</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,357 +466,357 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -60,870 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>-29466174</v>
+        <v>-2748208</v>
       </c>
       <c r="E2" t="n">
-        <v>24417494</v>
+        <v>533347</v>
       </c>
       <c r="F2" t="n">
-        <v>31600627</v>
+        <v>13791697</v>
       </c>
       <c r="G2" t="n">
-        <v>92470228</v>
+        <v>13800482</v>
       </c>
       <c r="H2" t="n">
-        <v>-250761664</v>
+        <v>-19343695</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 20,453 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>533347</v>
+        <v>2548397</v>
       </c>
       <c r="E3" t="n">
-        <v>-6415981</v>
+        <v>-4658754</v>
       </c>
       <c r="F3" t="n">
-        <v>13800482</v>
+        <v>-16049534</v>
       </c>
       <c r="G3" t="n">
-        <v>-6652560</v>
+        <v>-20184347</v>
       </c>
       <c r="H3" t="n">
-        <v>-17002057</v>
+        <v>4099578</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 11,344 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -24,238 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>26989367</v>
+        <v>-3278110</v>
       </c>
       <c r="E4" t="n">
-        <v>-2006335</v>
+        <v>13913205</v>
       </c>
       <c r="F4" t="n">
-        <v>28406237</v>
+        <v>3284474</v>
       </c>
       <c r="G4" t="n">
-        <v>17062712</v>
+        <v>27522695</v>
       </c>
       <c r="H4" t="n">
-        <v>-85969650</v>
+        <v>-191083648</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 18,160 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -25,674 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>13913205</v>
+        <v>-8418533</v>
       </c>
       <c r="E5" t="n">
-        <v>7031215</v>
+        <v>2101180</v>
       </c>
       <c r="F5" t="n">
-        <v>27522695</v>
+        <v>51417301</v>
       </c>
       <c r="G5" t="n">
-        <v>9362315</v>
+        <v>77090859</v>
       </c>
       <c r="H5" t="n">
-        <v>-179096665</v>
+        <v>560817999</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -17,164 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>-14881568</v>
+        <v>-904774</v>
       </c>
       <c r="E6" t="n">
-        <v>-25756605</v>
+        <v>1424587</v>
       </c>
       <c r="F6" t="n">
-        <v>13772967</v>
+        <v>98213650</v>
       </c>
       <c r="G6" t="n">
-        <v>30936571</v>
+        <v>104640659</v>
       </c>
       <c r="H6" t="n">
-        <v>89896941</v>
+        <v>5268142</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -31,911 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>-8665886</v>
+        <v>-28809211</v>
       </c>
       <c r="E7" t="n">
-        <v>-6155811</v>
+        <v>-29466174</v>
       </c>
       <c r="F7" t="n">
-        <v>44021672</v>
+        <v>37130707</v>
       </c>
       <c r="G7" t="n">
-        <v>75933165</v>
+        <v>31600627</v>
       </c>
       <c r="H7" t="n">
-        <v>91566667</v>
+        <v>-235868150</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -28,547 千)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>2259280</v>
+        <v>-11229529</v>
       </c>
       <c r="E8" t="n">
-        <v>882568</v>
+        <v>-14881568</v>
       </c>
       <c r="F8" t="n">
-        <v>-7514312</v>
+        <v>-14774153</v>
       </c>
       <c r="G8" t="n">
-        <v>-3427060</v>
+        <v>13772967</v>
       </c>
       <c r="H8" t="n">
-        <v>-47992423</v>
+        <v>96962847</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -26,685 千)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>-5321402</v>
+        <v>-3689740</v>
       </c>
       <c r="E9" t="n">
-        <v>-9945482</v>
+        <v>-8665886</v>
       </c>
       <c r="F9" t="n">
-        <v>14630877</v>
+        <v>17336636</v>
       </c>
       <c r="G9" t="n">
-        <v>16660176</v>
+        <v>44021672</v>
       </c>
       <c r="H9" t="n">
-        <v>11493487</v>
+        <v>94639625</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📉 20d 巨變(減碼 -45,397 千)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>9875584</v>
+        <v>20641180</v>
       </c>
       <c r="E10" t="n">
-        <v>9645933</v>
+        <v>26989367</v>
       </c>
       <c r="F10" t="n">
-        <v>12124334</v>
+        <v>-16990800</v>
       </c>
       <c r="G10" t="n">
-        <v>7956754</v>
+        <v>28406237</v>
       </c>
       <c r="H10" t="n">
-        <v>-46984388</v>
+        <v>-94388845</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>160380</v>
+        <v>-2113559</v>
       </c>
       <c r="E11" t="n">
-        <v>-125958</v>
+        <v>-5321402</v>
       </c>
       <c r="F11" t="n">
-        <v>-12921538</v>
+        <v>14914770</v>
       </c>
       <c r="G11" t="n">
-        <v>-14399876</v>
+        <v>14630877</v>
       </c>
       <c r="H11" t="n">
-        <v>-49496116</v>
+        <v>12294479</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,30 +828,30 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1002466</v>
+        <v>6822672</v>
       </c>
       <c r="E12" t="n">
-        <v>4409190</v>
+        <v>9875584</v>
       </c>
       <c r="F12" t="n">
-        <v>16556152</v>
+        <v>15193198</v>
       </c>
       <c r="G12" t="n">
-        <v>15895124</v>
+        <v>12124334</v>
       </c>
       <c r="H12" t="n">
-        <v>-51503691</v>
+        <v>-47271155</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,93 +863,93 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1128550</v>
+        <v>5304056</v>
       </c>
       <c r="E13" t="n">
-        <v>1883191</v>
+        <v>1002466</v>
       </c>
       <c r="F13" t="n">
-        <v>10208309</v>
+        <v>17939468</v>
       </c>
       <c r="G13" t="n">
-        <v>9946693</v>
+        <v>16556152</v>
       </c>
       <c r="H13" t="n">
-        <v>-2187691</v>
+        <v>-48436802</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠 / 📉 20d 巨變(減碼 -8,906 千)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>2101180</v>
+        <v>-1325059</v>
       </c>
       <c r="E14" t="n">
-        <v>-864947</v>
+        <v>1128550</v>
       </c>
       <c r="F14" t="n">
-        <v>77090859</v>
+        <v>7139647</v>
       </c>
       <c r="G14" t="n">
-        <v>85996512</v>
+        <v>10208309</v>
       </c>
       <c r="H14" t="n">
-        <v>562639446</v>
+        <v>-3409450</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>-721596</v>
+        <v>-5376300</v>
       </c>
       <c r="E15" t="n">
-        <v>-456855</v>
+        <v>2259280</v>
       </c>
       <c r="F15" t="n">
-        <v>6219586</v>
+        <v>-14661855</v>
       </c>
       <c r="G15" t="n">
-        <v>6902444</v>
+        <v>-7514312</v>
       </c>
       <c r="H15" t="n">
-        <v>5368460</v>
+        <v>-55022148</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
@@ -968,19 +968,19 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
+        <v>937139</v>
+      </c>
+      <c r="E16" t="n">
         <v>934489</v>
       </c>
-      <c r="E16" t="n">
-        <v>984477</v>
-      </c>
       <c r="F16" t="n">
+        <v>-5022493</v>
+      </c>
+      <c r="G16" t="n">
         <v>-5484734</v>
       </c>
-      <c r="G16" t="n">
-        <v>-5314199</v>
-      </c>
       <c r="H16" t="n">
-        <v>-8413565</v>
+        <v>-8487281</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,105 +991,175 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>-631611</v>
+        <v>-1484897</v>
       </c>
       <c r="E17" t="n">
-        <v>602133</v>
+        <v>670024</v>
       </c>
       <c r="F17" t="n">
-        <v>6371900</v>
+        <v>-1768470</v>
       </c>
       <c r="G17" t="n">
-        <v>8543243</v>
+        <v>-2772709</v>
       </c>
       <c r="H17" t="n">
-        <v>9636074</v>
+        <v>-811914</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>建榮</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 16,016 千)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>-6450067</v>
+        <v>-480705</v>
       </c>
       <c r="E18" t="n">
-        <v>-15021775</v>
+        <v>-631611</v>
       </c>
       <c r="F18" t="n">
-        <v>-72454938</v>
+        <v>5300661</v>
       </c>
       <c r="G18" t="n">
-        <v>-88471176</v>
+        <v>6371900</v>
       </c>
       <c r="H18" t="n">
-        <v>-75371386</v>
+        <v>9844216</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -63,541 千)</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>508087</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-2278749</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-2025750</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-2226762</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-56965</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>華星光</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -8,522 千)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
         <v>1</v>
       </c>
-      <c r="D19" t="n">
-        <v>1424587</v>
-      </c>
-      <c r="E19" t="n">
-        <v>39733111</v>
-      </c>
-      <c r="F19" t="n">
-        <v>104640659</v>
-      </c>
-      <c r="G19" t="n">
-        <v>168182110</v>
-      </c>
-      <c r="H19" t="n">
-        <v>4439717</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>南亞科</t>
+      <c r="D20" t="n">
+        <v>-23218155</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-6450067</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-80977243</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-72454938</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-92089705</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 8,179 千)</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1109971</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4718161</v>
+      </c>
+      <c r="F21" t="n">
+        <v>54657539</v>
+      </c>
+      <c r="G21" t="n">
+        <v>46478704</v>
+      </c>
+      <c r="H21" t="n">
+        <v>70664402</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>英業達</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,175 +466,175 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -43,583 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-2748208</v>
+        <v>-65437670</v>
       </c>
       <c r="E2" t="n">
-        <v>533347</v>
+        <v>-904774</v>
       </c>
       <c r="F2" t="n">
-        <v>13791697</v>
+        <v>54630518</v>
       </c>
       <c r="G2" t="n">
-        <v>13800482</v>
+        <v>98213650</v>
       </c>
       <c r="H2" t="n">
-        <v>-19343695</v>
+        <v>-29131224</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>2548397</v>
+        <v>-8739460</v>
       </c>
       <c r="E3" t="n">
-        <v>-4658754</v>
+        <v>-3278110</v>
       </c>
       <c r="F3" t="n">
-        <v>-16049534</v>
+        <v>6335171</v>
       </c>
       <c r="G3" t="n">
-        <v>-20184347</v>
+        <v>3284474</v>
       </c>
       <c r="H3" t="n">
-        <v>4099578</v>
+        <v>-192044403</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -24,238 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>-3278110</v>
+        <v>-1853678</v>
       </c>
       <c r="E4" t="n">
-        <v>13913205</v>
+        <v>1697792</v>
       </c>
       <c r="F4" t="n">
-        <v>3284474</v>
+        <v>16635719</v>
       </c>
       <c r="G4" t="n">
-        <v>27522695</v>
+        <v>16590771</v>
       </c>
       <c r="H4" t="n">
-        <v>-191083648</v>
+        <v>4461740</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -25,674 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>-8418533</v>
+        <v>-1067663</v>
       </c>
       <c r="E5" t="n">
-        <v>2101180</v>
+        <v>-2748208</v>
       </c>
       <c r="F5" t="n">
-        <v>51417301</v>
+        <v>21326416</v>
       </c>
       <c r="G5" t="n">
-        <v>77090859</v>
+        <v>13791697</v>
       </c>
       <c r="H5" t="n">
-        <v>560817999</v>
+        <v>-15855789</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>-904774</v>
+        <v>8149339</v>
       </c>
       <c r="E6" t="n">
-        <v>1424587</v>
+        <v>2548397</v>
       </c>
       <c r="F6" t="n">
-        <v>98213650</v>
+        <v>-10076019</v>
       </c>
       <c r="G6" t="n">
-        <v>104640659</v>
+        <v>-16049534</v>
       </c>
       <c r="H6" t="n">
-        <v>5268142</v>
+        <v>9333071</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
@@ -653,19 +653,19 @@
         <v>7</v>
       </c>
       <c r="D7" t="n">
+        <v>-85678322</v>
+      </c>
+      <c r="E7" t="n">
         <v>-28809211</v>
       </c>
-      <c r="E7" t="n">
-        <v>-29466174</v>
-      </c>
       <c r="F7" t="n">
+        <v>29150510</v>
+      </c>
+      <c r="G7" t="n">
         <v>37130707</v>
       </c>
-      <c r="G7" t="n">
-        <v>31600627</v>
-      </c>
       <c r="H7" t="n">
-        <v>-235868150</v>
+        <v>-262605372</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -681,26 +681,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -28,547 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 12,906 千)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>6</v>
       </c>
       <c r="D8" t="n">
+        <v>-1779114</v>
+      </c>
+      <c r="E8" t="n">
         <v>-11229529</v>
       </c>
-      <c r="E8" t="n">
-        <v>-14881568</v>
-      </c>
       <c r="F8" t="n">
+        <v>-1868580</v>
+      </c>
+      <c r="G8" t="n">
         <v>-14774153</v>
       </c>
-      <c r="G8" t="n">
-        <v>13772967</v>
-      </c>
       <c r="H8" t="n">
-        <v>96962847</v>
+        <v>99725741</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -711,77 +711,77 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -26,685 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📉 20d 巨變(減碼 -24,066 千)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>-3689740</v>
+        <v>69509</v>
       </c>
       <c r="E9" t="n">
-        <v>-8665886</v>
+        <v>20641180</v>
       </c>
       <c r="F9" t="n">
-        <v>17336636</v>
+        <v>-41056860</v>
       </c>
       <c r="G9" t="n">
-        <v>44021672</v>
+        <v>-16990800</v>
       </c>
       <c r="H9" t="n">
-        <v>94639625</v>
+        <v>-96711543</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📉 20d 巨變(減碼 -45,397 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>20641180</v>
+        <v>7097125</v>
       </c>
       <c r="E10" t="n">
-        <v>26989367</v>
+        <v>6822672</v>
       </c>
       <c r="F10" t="n">
-        <v>-16990800</v>
+        <v>20504661</v>
       </c>
       <c r="G10" t="n">
-        <v>28406237</v>
+        <v>15193198</v>
       </c>
       <c r="H10" t="n">
-        <v>-94388845</v>
+        <v>-43496353</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,30 +793,30 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-2113559</v>
+        <v>-7640902</v>
       </c>
       <c r="E11" t="n">
-        <v>-5321402</v>
+        <v>-3689740</v>
       </c>
       <c r="F11" t="n">
-        <v>14914770</v>
+        <v>10645985</v>
       </c>
       <c r="G11" t="n">
-        <v>14630877</v>
+        <v>17336636</v>
       </c>
       <c r="H11" t="n">
-        <v>12294479</v>
+        <v>87448859</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,170 +828,170 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>6822672</v>
+        <v>6122167</v>
       </c>
       <c r="E12" t="n">
-        <v>9875584</v>
+        <v>5304056</v>
       </c>
       <c r="F12" t="n">
-        <v>15193198</v>
+        <v>20008503</v>
       </c>
       <c r="G12" t="n">
-        <v>12124334</v>
+        <v>17939468</v>
       </c>
       <c r="H12" t="n">
-        <v>-47271155</v>
+        <v>-46460011</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>5304056</v>
+        <v>2048745</v>
       </c>
       <c r="E13" t="n">
-        <v>1002466</v>
+        <v>-33106</v>
       </c>
       <c r="F13" t="n">
-        <v>17939468</v>
+        <v>-5316853</v>
       </c>
       <c r="G13" t="n">
-        <v>16556152</v>
+        <v>-8375172</v>
       </c>
       <c r="H13" t="n">
-        <v>-48436802</v>
+        <v>-8008812</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>台燿</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-1325059</v>
+        <v>-453317</v>
       </c>
       <c r="E14" t="n">
-        <v>1128550</v>
+        <v>-480705</v>
       </c>
       <c r="F14" t="n">
-        <v>7139647</v>
+        <v>4846602</v>
       </c>
       <c r="G14" t="n">
-        <v>10208309</v>
+        <v>5300661</v>
       </c>
       <c r="H14" t="n">
-        <v>-3409450</v>
+        <v>10029633</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -9,733 千)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>-5376300</v>
+        <v>-6360078</v>
       </c>
       <c r="E15" t="n">
-        <v>2259280</v>
+        <v>-2113559</v>
       </c>
       <c r="F15" t="n">
-        <v>-14661855</v>
+        <v>5181487</v>
       </c>
       <c r="G15" t="n">
-        <v>-7514312</v>
+        <v>14914770</v>
       </c>
       <c r="H15" t="n">
-        <v>-55022148</v>
+        <v>7763638</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>937139</v>
+        <v>3862731</v>
       </c>
       <c r="E16" t="n">
-        <v>934489</v>
+        <v>-8418533</v>
       </c>
       <c r="F16" t="n">
-        <v>-5022493</v>
+        <v>58895347</v>
       </c>
       <c r="G16" t="n">
-        <v>-5484734</v>
+        <v>51417301</v>
       </c>
       <c r="H16" t="n">
-        <v>-8487281</v>
+        <v>569969934</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1003,163 +1003,58 @@
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>-1484897</v>
+        <v>-1216961</v>
       </c>
       <c r="E17" t="n">
-        <v>670024</v>
+        <v>1101624</v>
       </c>
       <c r="F17" t="n">
-        <v>-1768470</v>
+        <v>-2742139</v>
       </c>
       <c r="G17" t="n">
-        <v>-2772709</v>
+        <v>1082924</v>
       </c>
       <c r="H17" t="n">
-        <v>-811914</v>
+        <v>-897369</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>宇瞻</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>📈 20d 巨變(加碼 9,757 千)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-480705</v>
+        <v>17188724</v>
       </c>
       <c r="E18" t="n">
-        <v>-631611</v>
+        <v>10732516</v>
       </c>
       <c r="F18" t="n">
-        <v>5300661</v>
+        <v>71240830</v>
       </c>
       <c r="G18" t="n">
-        <v>6371900</v>
+        <v>61484085</v>
       </c>
       <c r="H18" t="n">
-        <v>9844216</v>
+        <v>141357830</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>統一超</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>4979</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>🟢 5d 翻綠</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" t="n">
-        <v>508087</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-2278749</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-2025750</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-2226762</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-56965</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>華星光</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -8,522 千)</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>-23218155</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-6450067</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-80977243</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-72454938</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-92089705</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2356</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 8,179 千)</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1109971</v>
-      </c>
-      <c r="E21" t="n">
-        <v>4718161</v>
-      </c>
-      <c r="F21" t="n">
-        <v>54657539</v>
-      </c>
-      <c r="G21" t="n">
-        <v>46478704</v>
-      </c>
-      <c r="H21" t="n">
-        <v>70664402</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>英業達</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,35 +466,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -43,583 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 48,686 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-65437670</v>
+        <v>-49192245</v>
       </c>
       <c r="E2" t="n">
-        <v>-904774</v>
+        <v>-85678322</v>
       </c>
       <c r="F2" t="n">
-        <v>54630518</v>
+        <v>77836684</v>
       </c>
       <c r="G2" t="n">
-        <v>98213650</v>
+        <v>29150510</v>
       </c>
       <c r="H2" t="n">
-        <v>-29131224</v>
+        <v>-257250653</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
@@ -513,19 +513,19 @@
         <v>7</v>
       </c>
       <c r="D3" t="n">
+        <v>-9886030</v>
+      </c>
+      <c r="E3" t="n">
         <v>-8739460</v>
       </c>
-      <c r="E3" t="n">
-        <v>-3278110</v>
-      </c>
       <c r="F3" t="n">
+        <v>7578596</v>
+      </c>
+      <c r="G3" t="n">
         <v>6335171</v>
       </c>
-      <c r="G3" t="n">
-        <v>3284474</v>
-      </c>
       <c r="H3" t="n">
-        <v>-192044403</v>
+        <v>-190159318</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -536,35 +536,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>-1853678</v>
+        <v>-64235104</v>
       </c>
       <c r="E4" t="n">
-        <v>1697792</v>
+        <v>-65437670</v>
       </c>
       <c r="F4" t="n">
-        <v>16635719</v>
+        <v>52912891</v>
       </c>
       <c r="G4" t="n">
-        <v>16590771</v>
+        <v>54630518</v>
       </c>
       <c r="H4" t="n">
-        <v>4461740</v>
+        <v>-28701281</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
@@ -583,19 +583,19 @@
         <v>7</v>
       </c>
       <c r="D5" t="n">
+        <v>-4081932</v>
+      </c>
+      <c r="E5" t="n">
         <v>-1067663</v>
       </c>
-      <c r="E5" t="n">
-        <v>-2748208</v>
-      </c>
       <c r="F5" t="n">
+        <v>20798715</v>
+      </c>
+      <c r="G5" t="n">
         <v>21326416</v>
       </c>
-      <c r="G5" t="n">
-        <v>13791697</v>
-      </c>
       <c r="H5" t="n">
-        <v>-15855789</v>
+        <v>-19437222</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -618,19 +618,19 @@
         <v>7</v>
       </c>
       <c r="D6" t="n">
+        <v>13678650</v>
+      </c>
+      <c r="E6" t="n">
         <v>8149339</v>
       </c>
-      <c r="E6" t="n">
-        <v>2548397</v>
-      </c>
       <c r="F6" t="n">
+        <v>-9899299</v>
+      </c>
+      <c r="G6" t="n">
         <v>-10076019</v>
       </c>
-      <c r="G6" t="n">
-        <v>-16049534</v>
-      </c>
       <c r="H6" t="n">
-        <v>9333071</v>
+        <v>10917309</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -641,175 +641,175 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 19,140 千)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>-85678322</v>
+        <v>20603243</v>
       </c>
       <c r="E7" t="n">
-        <v>-28809211</v>
+        <v>7097125</v>
       </c>
       <c r="F7" t="n">
-        <v>29150510</v>
+        <v>39644718</v>
       </c>
       <c r="G7" t="n">
-        <v>37130707</v>
+        <v>20504661</v>
       </c>
       <c r="H7" t="n">
-        <v>-262605372</v>
+        <v>-30659569</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 12,906 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 31,736 千)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>-1779114</v>
+        <v>25284953</v>
       </c>
       <c r="E8" t="n">
-        <v>-11229529</v>
+        <v>69509</v>
       </c>
       <c r="F8" t="n">
-        <v>-1868580</v>
+        <v>-9320940</v>
       </c>
       <c r="G8" t="n">
-        <v>-14774153</v>
+        <v>-41056860</v>
       </c>
       <c r="H8" t="n">
-        <v>99725741</v>
+        <v>-70303752</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📉 20d 巨變(減碼 -24,066 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>69509</v>
+        <v>-878553</v>
       </c>
       <c r="E9" t="n">
-        <v>20641180</v>
+        <v>-1853678</v>
       </c>
       <c r="F9" t="n">
-        <v>-41056860</v>
+        <v>17187347</v>
       </c>
       <c r="G9" t="n">
-        <v>-16990800</v>
+        <v>16635719</v>
       </c>
       <c r="H9" t="n">
-        <v>-96711543</v>
+        <v>4868347</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>7097125</v>
+        <v>-6988082</v>
       </c>
       <c r="E10" t="n">
-        <v>6822672</v>
+        <v>-7640902</v>
       </c>
       <c r="F10" t="n">
-        <v>20504661</v>
+        <v>13292089</v>
       </c>
       <c r="G10" t="n">
-        <v>15193198</v>
+        <v>10645985</v>
       </c>
       <c r="H10" t="n">
-        <v>-43496353</v>
+        <v>92223712</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-7640902</v>
+        <v>618043</v>
       </c>
       <c r="E11" t="n">
-        <v>-3689740</v>
+        <v>-772926</v>
       </c>
       <c r="F11" t="n">
-        <v>10645985</v>
+        <v>-6751613</v>
       </c>
       <c r="G11" t="n">
-        <v>17336636</v>
+        <v>-10457625</v>
       </c>
       <c r="H11" t="n">
-        <v>87448859</v>
+        <v>-48908351</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
@@ -828,19 +828,19 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
+        <v>7415840</v>
+      </c>
+      <c r="E12" t="n">
         <v>6122167</v>
       </c>
-      <c r="E12" t="n">
-        <v>5304056</v>
-      </c>
       <c r="F12" t="n">
+        <v>19981799</v>
+      </c>
+      <c r="G12" t="n">
         <v>20008503</v>
       </c>
-      <c r="G12" t="n">
-        <v>17939468</v>
-      </c>
       <c r="H12" t="n">
-        <v>-46460011</v>
+        <v>-45542262</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -851,112 +851,112 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>2048745</v>
+        <v>1961682</v>
       </c>
       <c r="E13" t="n">
-        <v>-33106</v>
+        <v>-988277</v>
       </c>
       <c r="F13" t="n">
-        <v>-5316853</v>
+        <v>-976510</v>
       </c>
       <c r="G13" t="n">
-        <v>-8375172</v>
+        <v>-2055389</v>
       </c>
       <c r="H13" t="n">
-        <v>-8008812</v>
+        <v>7042128</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>立隆電</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-453317</v>
+        <v>-6345101</v>
       </c>
       <c r="E14" t="n">
-        <v>-480705</v>
+        <v>-6360078</v>
       </c>
       <c r="F14" t="n">
-        <v>4846602</v>
+        <v>2249803</v>
       </c>
       <c r="G14" t="n">
-        <v>5300661</v>
+        <v>5181487</v>
       </c>
       <c r="H14" t="n">
-        <v>10029633</v>
+        <v>6154374</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -9,733 千)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>-6360078</v>
+        <v>-1406903</v>
       </c>
       <c r="E15" t="n">
-        <v>-2113559</v>
+        <v>1409762</v>
       </c>
       <c r="F15" t="n">
-        <v>5181487</v>
+        <v>3946569</v>
       </c>
       <c r="G15" t="n">
-        <v>14914770</v>
+        <v>5466191</v>
       </c>
       <c r="H15" t="n">
-        <v>7763638</v>
+        <v>2895515</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>聯鈞</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,93 +968,163 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>3862731</v>
+        <v>30392052</v>
       </c>
       <c r="E16" t="n">
-        <v>-8418533</v>
+        <v>-1779114</v>
       </c>
       <c r="F16" t="n">
-        <v>58895347</v>
+        <v>4898515</v>
       </c>
       <c r="G16" t="n">
-        <v>51417301</v>
+        <v>-1868580</v>
       </c>
       <c r="H16" t="n">
-        <v>569969934</v>
+        <v>123651046</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>-1216961</v>
+        <v>-467774</v>
       </c>
       <c r="E17" t="n">
-        <v>1101624</v>
+        <v>94060</v>
       </c>
       <c r="F17" t="n">
-        <v>-2742139</v>
+        <v>9767995</v>
       </c>
       <c r="G17" t="n">
-        <v>1082924</v>
+        <v>9305139</v>
       </c>
       <c r="H17" t="n">
-        <v>-897369</v>
+        <v>-1702555</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 9,757 千)</t>
+          <t>📉 20d 巨變(減碼 -24,467 千)</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>17188724</v>
+        <v>7796542</v>
       </c>
       <c r="E18" t="n">
-        <v>10732516</v>
+        <v>3862731</v>
       </c>
       <c r="F18" t="n">
-        <v>71240830</v>
+        <v>34428107</v>
       </c>
       <c r="G18" t="n">
-        <v>61484085</v>
+        <v>58895347</v>
       </c>
       <c r="H18" t="n">
-        <v>141357830</v>
+        <v>567503067</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>長榮航</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 27,873 千)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-6277951</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-27019403</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-53378840</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-81251717</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-78204906</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 11,965 千)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>23543954</v>
+      </c>
+      <c r="E20" t="n">
+        <v>6662495</v>
+      </c>
+      <c r="F20" t="n">
+        <v>65445506</v>
+      </c>
+      <c r="G20" t="n">
+        <v>53480787</v>
+      </c>
+      <c r="H20" t="n">
+        <v>84684579</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>英業達</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,497 +466,497 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 48,686 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 16,016 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-49192245</v>
+        <v>10803524</v>
       </c>
       <c r="E2" t="n">
-        <v>-85678322</v>
+        <v>-9886030</v>
       </c>
       <c r="F2" t="n">
-        <v>77836684</v>
+        <v>23594814</v>
       </c>
       <c r="G2" t="n">
-        <v>29150510</v>
+        <v>7578596</v>
       </c>
       <c r="H2" t="n">
-        <v>-257250653</v>
+        <v>-147208630</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 18,639 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>-9886030</v>
+        <v>23212601</v>
       </c>
       <c r="E3" t="n">
-        <v>-8739460</v>
+        <v>-4081932</v>
       </c>
       <c r="F3" t="n">
-        <v>7578596</v>
+        <v>39437936</v>
       </c>
       <c r="G3" t="n">
-        <v>6335171</v>
+        <v>20798715</v>
       </c>
       <c r="H3" t="n">
-        <v>-190159318</v>
+        <v>-29877776</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -20,300 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>-64235104</v>
+        <v>24424681</v>
       </c>
       <c r="E4" t="n">
-        <v>-65437670</v>
+        <v>30392052</v>
       </c>
       <c r="F4" t="n">
-        <v>52912891</v>
+        <v>-15401922</v>
       </c>
       <c r="G4" t="n">
-        <v>54630518</v>
+        <v>4898515</v>
       </c>
       <c r="H4" t="n">
-        <v>-28701281</v>
+        <v>165226975</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 28,342 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>-4081932</v>
+        <v>-15333916</v>
       </c>
       <c r="E5" t="n">
-        <v>-1067663</v>
+        <v>-49192245</v>
       </c>
       <c r="F5" t="n">
-        <v>20798715</v>
+        <v>106178957</v>
       </c>
       <c r="G5" t="n">
-        <v>21326416</v>
+        <v>77836684</v>
       </c>
       <c r="H5" t="n">
-        <v>-19437222</v>
+        <v>-29887464</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>13678650</v>
+        <v>-2073851</v>
       </c>
       <c r="E6" t="n">
-        <v>8149339</v>
+        <v>9585729</v>
       </c>
       <c r="F6" t="n">
-        <v>-9899299</v>
+        <v>15520514</v>
       </c>
       <c r="G6" t="n">
-        <v>-10076019</v>
+        <v>17362538</v>
       </c>
       <c r="H6" t="n">
-        <v>10917309</v>
+        <v>21591340</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 19,140 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>20603243</v>
+        <v>13638357</v>
       </c>
       <c r="E7" t="n">
-        <v>7097125</v>
+        <v>-6277951</v>
       </c>
       <c r="F7" t="n">
-        <v>39644718</v>
+        <v>-50551489</v>
       </c>
       <c r="G7" t="n">
-        <v>20504661</v>
+        <v>-53378840</v>
       </c>
       <c r="H7" t="n">
-        <v>-30659569</v>
+        <v>-67195790</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📈 20d 巨變(加碼 31,736 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>25284953</v>
+        <v>15173527</v>
       </c>
       <c r="E8" t="n">
-        <v>69509</v>
+        <v>13678650</v>
       </c>
       <c r="F8" t="n">
-        <v>-9320940</v>
+        <v>-6428031</v>
       </c>
       <c r="G8" t="n">
-        <v>-41056860</v>
+        <v>-9899299</v>
       </c>
       <c r="H8" t="n">
-        <v>-70303752</v>
+        <v>20394430</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>-878553</v>
+        <v>3058663</v>
       </c>
       <c r="E9" t="n">
-        <v>-1853678</v>
+        <v>-467774</v>
       </c>
       <c r="F9" t="n">
-        <v>17187347</v>
+        <v>11290079</v>
       </c>
       <c r="G9" t="n">
-        <v>16635719</v>
+        <v>9767995</v>
       </c>
       <c r="H9" t="n">
-        <v>4868347</v>
+        <v>-1174617</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -16,817 千)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-6988082</v>
+        <v>-58189126</v>
       </c>
       <c r="E10" t="n">
-        <v>-7640902</v>
+        <v>-64235104</v>
       </c>
       <c r="F10" t="n">
-        <v>13292089</v>
+        <v>36096340</v>
       </c>
       <c r="G10" t="n">
-        <v>10645985</v>
+        <v>52912891</v>
       </c>
       <c r="H10" t="n">
-        <v>92223712</v>
+        <v>19163732</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -12,295 千)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>618043</v>
+        <v>-12233190</v>
       </c>
       <c r="E11" t="n">
-        <v>-772926</v>
+        <v>-6988082</v>
       </c>
       <c r="F11" t="n">
-        <v>-6751613</v>
+        <v>997202</v>
       </c>
       <c r="G11" t="n">
-        <v>-10457625</v>
+        <v>13292089</v>
       </c>
       <c r="H11" t="n">
-        <v>-48908351</v>
+        <v>68277888</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📉 20d 巨變(減碼 -10,491 千)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>7415840</v>
+        <v>26530236</v>
       </c>
       <c r="E12" t="n">
-        <v>6122167</v>
+        <v>25284953</v>
       </c>
       <c r="F12" t="n">
-        <v>19981799</v>
+        <v>-19812269</v>
       </c>
       <c r="G12" t="n">
-        <v>20008503</v>
+        <v>-9320940</v>
       </c>
       <c r="H12" t="n">
-        <v>-45542262</v>
+        <v>-13663572</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1961682</v>
+        <v>-4306454</v>
       </c>
       <c r="E13" t="n">
-        <v>-988277</v>
+        <v>-6345101</v>
       </c>
       <c r="F13" t="n">
-        <v>-976510</v>
+        <v>8701751</v>
       </c>
       <c r="G13" t="n">
-        <v>-2055389</v>
+        <v>2249803</v>
       </c>
       <c r="H13" t="n">
-        <v>7042128</v>
+        <v>13668584</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>-6345101</v>
+        <v>17316014</v>
       </c>
       <c r="E14" t="n">
-        <v>-6360078</v>
+        <v>20603243</v>
       </c>
       <c r="F14" t="n">
-        <v>2249803</v>
+        <v>36690712</v>
       </c>
       <c r="G14" t="n">
-        <v>5181487</v>
+        <v>39644718</v>
       </c>
       <c r="H14" t="n">
-        <v>6154374</v>
+        <v>-25480053</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>-1406903</v>
+        <v>-873188</v>
       </c>
       <c r="E15" t="n">
-        <v>1409762</v>
+        <v>-250045</v>
       </c>
       <c r="F15" t="n">
-        <v>3946569</v>
+        <v>3605365</v>
       </c>
       <c r="G15" t="n">
-        <v>5466191</v>
+        <v>3841741</v>
       </c>
       <c r="H15" t="n">
-        <v>2895515</v>
+        <v>11174340</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,161 +968,91 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>30392052</v>
+        <v>1492182</v>
       </c>
       <c r="E16" t="n">
-        <v>-1779114</v>
+        <v>-878553</v>
       </c>
       <c r="F16" t="n">
-        <v>4898515</v>
+        <v>17636037</v>
       </c>
       <c r="G16" t="n">
-        <v>-1868580</v>
+        <v>17187347</v>
       </c>
       <c r="H16" t="n">
-        <v>123651046</v>
+        <v>16152565</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>-467774</v>
+        <v>-53994</v>
       </c>
       <c r="E17" t="n">
-        <v>94060</v>
+        <v>2306424</v>
       </c>
       <c r="F17" t="n">
-        <v>9767995</v>
+        <v>-4341033</v>
       </c>
       <c r="G17" t="n">
-        <v>9305139</v>
+        <v>-1599060</v>
       </c>
       <c r="H17" t="n">
-        <v>-1702555</v>
+        <v>-1202536</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>華星光</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -24,467 千)</t>
+          <t>📉 20d 巨變(減碼 -18,448 千)</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>7796542</v>
+        <v>7168392</v>
       </c>
       <c r="E18" t="n">
-        <v>3862731</v>
+        <v>23543954</v>
       </c>
       <c r="F18" t="n">
-        <v>34428107</v>
+        <v>46997335</v>
       </c>
       <c r="G18" t="n">
-        <v>58895347</v>
+        <v>65445506</v>
       </c>
       <c r="H18" t="n">
-        <v>567503067</v>
+        <v>77155716</v>
       </c>
       <c r="I18" t="inlineStr">
-        <is>
-          <t>長榮航</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 27,873 千)</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>-6277951</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-27019403</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-53378840</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-81251717</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-78204906</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2356</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 11,965 千)</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>23543954</v>
-      </c>
-      <c r="E20" t="n">
-        <v>6662495</v>
-      </c>
-      <c r="F20" t="n">
-        <v>65445506</v>
-      </c>
-      <c r="G20" t="n">
-        <v>53480787</v>
-      </c>
-      <c r="H20" t="n">
-        <v>84684579</v>
-      </c>
-      <c r="I20" t="inlineStr">
         <is>
           <t>英業達</t>
         </is>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,140 +466,140 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 16,016 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -45,685 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>10803524</v>
+        <v>-22924140</v>
       </c>
       <c r="E2" t="n">
-        <v>-9886030</v>
+        <v>24424681</v>
       </c>
       <c r="F2" t="n">
-        <v>23594814</v>
+        <v>-61086978</v>
       </c>
       <c r="G2" t="n">
-        <v>7578596</v>
+        <v>-15401922</v>
       </c>
       <c r="H2" t="n">
-        <v>-147208630</v>
+        <v>132847626</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠 / 📈 20d 巨變(加碼 18,639 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -17,642 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>23212601</v>
+        <v>-12333032</v>
       </c>
       <c r="E3" t="n">
-        <v>-4081932</v>
+        <v>7168392</v>
       </c>
       <c r="F3" t="n">
-        <v>39437936</v>
+        <v>29355401</v>
       </c>
       <c r="G3" t="n">
-        <v>20798715</v>
+        <v>46997335</v>
       </c>
       <c r="H3" t="n">
-        <v>-29877776</v>
+        <v>56242334</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -20,300 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -12,145 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>24424681</v>
+        <v>2111230</v>
       </c>
       <c r="E4" t="n">
-        <v>30392052</v>
+        <v>17316014</v>
       </c>
       <c r="F4" t="n">
-        <v>-15401922</v>
+        <v>24545912</v>
       </c>
       <c r="G4" t="n">
-        <v>4898515</v>
+        <v>36690712</v>
       </c>
       <c r="H4" t="n">
-        <v>165226975</v>
+        <v>-33475837</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 28,342 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>-15333916</v>
+        <v>10569397</v>
       </c>
       <c r="E5" t="n">
-        <v>-49192245</v>
+        <v>10803524</v>
       </c>
       <c r="F5" t="n">
-        <v>106178957</v>
+        <v>25593313</v>
       </c>
       <c r="G5" t="n">
-        <v>77836684</v>
+        <v>23594814</v>
       </c>
       <c r="H5" t="n">
-        <v>-29887464</v>
+        <v>-135608222</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
@@ -611,26 +611,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
+        <v>-2697636</v>
+      </c>
+      <c r="E6" t="n">
         <v>-2073851</v>
       </c>
-      <c r="E6" t="n">
-        <v>9585729</v>
-      </c>
       <c r="F6" t="n">
+        <v>15602652</v>
+      </c>
+      <c r="G6" t="n">
         <v>15520514</v>
       </c>
-      <c r="G6" t="n">
-        <v>17362538</v>
-      </c>
       <c r="H6" t="n">
-        <v>21591340</v>
+        <v>22554216</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -641,322 +641,322 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>13638357</v>
+        <v>-1398832</v>
       </c>
       <c r="E7" t="n">
-        <v>-6277951</v>
+        <v>-4306454</v>
       </c>
       <c r="F7" t="n">
-        <v>-50551489</v>
+        <v>10541909</v>
       </c>
       <c r="G7" t="n">
-        <v>-53378840</v>
+        <v>8701751</v>
       </c>
       <c r="H7" t="n">
-        <v>-67195790</v>
+        <v>14607033</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>15173527</v>
+        <v>2445455</v>
       </c>
       <c r="E8" t="n">
-        <v>13678650</v>
+        <v>13638357</v>
       </c>
       <c r="F8" t="n">
-        <v>-6428031</v>
+        <v>-43930885</v>
       </c>
       <c r="G8" t="n">
-        <v>-9899299</v>
+        <v>-50551489</v>
       </c>
       <c r="H8" t="n">
-        <v>20394430</v>
+        <v>-65656015</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>3058663</v>
+        <v>18065281</v>
       </c>
       <c r="E9" t="n">
-        <v>-467774</v>
+        <v>23212601</v>
       </c>
       <c r="F9" t="n">
-        <v>11290079</v>
+        <v>41706807</v>
       </c>
       <c r="G9" t="n">
-        <v>9767995</v>
+        <v>39437936</v>
       </c>
       <c r="H9" t="n">
-        <v>-1174617</v>
+        <v>-27968418</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -16,817 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-58189126</v>
+        <v>-11999662</v>
       </c>
       <c r="E10" t="n">
-        <v>-64235104</v>
+        <v>-12233190</v>
       </c>
       <c r="F10" t="n">
-        <v>36096340</v>
+        <v>-1630364</v>
       </c>
       <c r="G10" t="n">
-        <v>52912891</v>
+        <v>997202</v>
       </c>
       <c r="H10" t="n">
-        <v>19163732</v>
+        <v>66635104</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -12,295 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-12233190</v>
+        <v>3669069</v>
       </c>
       <c r="E11" t="n">
-        <v>-6988082</v>
+        <v>3058663</v>
       </c>
       <c r="F11" t="n">
-        <v>997202</v>
+        <v>10723720</v>
       </c>
       <c r="G11" t="n">
-        <v>13292089</v>
+        <v>11290079</v>
       </c>
       <c r="H11" t="n">
-        <v>68277888</v>
+        <v>-2266234</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 📉 20d 巨變(減碼 -10,491 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>26530236</v>
+        <v>-153358</v>
       </c>
       <c r="E12" t="n">
-        <v>25284953</v>
+        <v>-873188</v>
       </c>
       <c r="F12" t="n">
-        <v>-19812269</v>
+        <v>4462984</v>
       </c>
       <c r="G12" t="n">
-        <v>-9320940</v>
+        <v>3605365</v>
       </c>
       <c r="H12" t="n">
-        <v>-13663572</v>
+        <v>10152836</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🟢 5d 翻綠 / 📈 20d 巨變(加碼 19,107 千)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-4306454</v>
+        <v>14831777</v>
       </c>
       <c r="E13" t="n">
-        <v>-6345101</v>
+        <v>-58189126</v>
       </c>
       <c r="F13" t="n">
-        <v>8701751</v>
+        <v>55202964</v>
       </c>
       <c r="G13" t="n">
-        <v>2249803</v>
+        <v>36096340</v>
       </c>
       <c r="H13" t="n">
-        <v>13668584</v>
+        <v>63688926</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🔴 5d 翻紅 / 📉 20d 巨變(減碼 -12,150 千)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>17316014</v>
+        <v>-233468</v>
       </c>
       <c r="E14" t="n">
-        <v>20603243</v>
+        <v>26530236</v>
       </c>
       <c r="F14" t="n">
-        <v>36690712</v>
+        <v>-31962354</v>
       </c>
       <c r="G14" t="n">
-        <v>39644718</v>
+        <v>-19812269</v>
       </c>
       <c r="H14" t="n">
-        <v>-25480053</v>
+        <v>-24321377</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🟢 5d 翻綠 / 📈 20d 巨變(加碼 54,725 千)</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>-873188</v>
+        <v>133494762</v>
       </c>
       <c r="E15" t="n">
-        <v>-250045</v>
+        <v>-15333916</v>
       </c>
       <c r="F15" t="n">
-        <v>3605365</v>
+        <v>160904183</v>
       </c>
       <c r="G15" t="n">
-        <v>3841741</v>
+        <v>106178957</v>
       </c>
       <c r="H15" t="n">
-        <v>11174340</v>
+        <v>79629106</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,93 +968,23 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>1492182</v>
+        <v>555135</v>
       </c>
       <c r="E16" t="n">
-        <v>-878553</v>
+        <v>-2877133</v>
       </c>
       <c r="F16" t="n">
-        <v>17636037</v>
+        <v>2813258</v>
       </c>
       <c r="G16" t="n">
-        <v>17187347</v>
+        <v>2855638</v>
       </c>
       <c r="H16" t="n">
-        <v>16152565</v>
+        <v>5088672</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>中興電</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>4979</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>🔴 5d 翻紅</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" t="n">
-        <v>-53994</v>
-      </c>
-      <c r="E17" t="n">
-        <v>2306424</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-4341033</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-1599060</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-1202536</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>華星光</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2356</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -18,448 千)</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>7168392</v>
-      </c>
-      <c r="E18" t="n">
-        <v>23543954</v>
-      </c>
-      <c r="F18" t="n">
-        <v>46997335</v>
-      </c>
-      <c r="G18" t="n">
-        <v>65445506</v>
-      </c>
-      <c r="H18" t="n">
-        <v>77155716</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>英業達</t>
+          <t>聯鈞</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,70 +466,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -45,685 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 🟢 5d 翻綠 / 📉 20d 巨變(減碼 -26,237 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>-22924140</v>
+        <v>11319063</v>
       </c>
       <c r="E2" t="n">
-        <v>24424681</v>
+        <v>-233468</v>
       </c>
       <c r="F2" t="n">
-        <v>-61086978</v>
+        <v>-58199679</v>
       </c>
       <c r="G2" t="n">
-        <v>-15401922</v>
+        <v>-31962354</v>
       </c>
       <c r="H2" t="n">
-        <v>132847626</v>
+        <v>9139720</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📉 20d 巨變(減碼 -17,642 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 10,212 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>-12333032</v>
+        <v>29213823</v>
       </c>
       <c r="E3" t="n">
-        <v>7168392</v>
+        <v>18065281</v>
       </c>
       <c r="F3" t="n">
-        <v>29355401</v>
+        <v>51919009</v>
       </c>
       <c r="G3" t="n">
-        <v>46997335</v>
+        <v>41706807</v>
       </c>
       <c r="H3" t="n">
-        <v>56242334</v>
+        <v>-25644104</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
@@ -541,26 +541,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -12,145 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 12,463 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
+        <v>15496741</v>
+      </c>
+      <c r="E4" t="n">
         <v>2111230</v>
       </c>
-      <c r="E4" t="n">
-        <v>17316014</v>
-      </c>
       <c r="F4" t="n">
+        <v>37008415</v>
+      </c>
+      <c r="G4" t="n">
         <v>24545912</v>
       </c>
-      <c r="G4" t="n">
-        <v>36690712</v>
-      </c>
       <c r="H4" t="n">
-        <v>-33475837</v>
+        <v>-19161104</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -571,420 +571,490 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -19,017 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>10569397</v>
+        <v>-8760496</v>
       </c>
       <c r="E5" t="n">
-        <v>10803524</v>
+        <v>-12333032</v>
       </c>
       <c r="F5" t="n">
-        <v>25593313</v>
+        <v>10338271</v>
       </c>
       <c r="G5" t="n">
-        <v>23594814</v>
+        <v>29355401</v>
       </c>
       <c r="H5" t="n">
-        <v>-135608222</v>
+        <v>67832952</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>-2697636</v>
+        <v>19997518</v>
       </c>
       <c r="E6" t="n">
-        <v>-2073851</v>
+        <v>10569397</v>
       </c>
       <c r="F6" t="n">
-        <v>15602652</v>
+        <v>20407548</v>
       </c>
       <c r="G6" t="n">
-        <v>15520514</v>
+        <v>25593313</v>
       </c>
       <c r="H6" t="n">
-        <v>22554216</v>
+        <v>-123885929</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-1398832</v>
+        <v>3860807</v>
       </c>
       <c r="E7" t="n">
-        <v>-4306454</v>
+        <v>-4066941</v>
       </c>
       <c r="F7" t="n">
-        <v>10541909</v>
+        <v>-4752440</v>
       </c>
       <c r="G7" t="n">
-        <v>8701751</v>
+        <v>-6817017</v>
       </c>
       <c r="H7" t="n">
-        <v>14607033</v>
+        <v>-41666779</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>2445455</v>
+        <v>-2226169</v>
       </c>
       <c r="E8" t="n">
-        <v>13638357</v>
+        <v>-2697636</v>
       </c>
       <c r="F8" t="n">
-        <v>-43930885</v>
+        <v>15095122</v>
       </c>
       <c r="G8" t="n">
-        <v>-50551489</v>
+        <v>15602652</v>
       </c>
       <c r="H8" t="n">
-        <v>-65656015</v>
+        <v>23961124</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>18065281</v>
+        <v>-2523012</v>
       </c>
       <c r="E9" t="n">
-        <v>23212601</v>
+        <v>-1398832</v>
       </c>
       <c r="F9" t="n">
-        <v>41706807</v>
+        <v>6439924</v>
       </c>
       <c r="G9" t="n">
-        <v>39437936</v>
+        <v>10541909</v>
       </c>
       <c r="H9" t="n">
-        <v>-27968418</v>
+        <v>14780598</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-11999662</v>
+        <v>15777966</v>
       </c>
       <c r="E10" t="n">
-        <v>-12233190</v>
+        <v>2445455</v>
       </c>
       <c r="F10" t="n">
-        <v>-1630364</v>
+        <v>-36939548</v>
       </c>
       <c r="G10" t="n">
-        <v>997202</v>
+        <v>-43930885</v>
       </c>
       <c r="H10" t="n">
-        <v>66635104</v>
+        <v>-61823973</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>3669069</v>
+        <v>-23602047</v>
       </c>
       <c r="E11" t="n">
-        <v>3058663</v>
+        <v>-22924140</v>
       </c>
       <c r="F11" t="n">
-        <v>10723720</v>
+        <v>-63523914</v>
       </c>
       <c r="G11" t="n">
-        <v>11290079</v>
+        <v>-61086978</v>
       </c>
       <c r="H11" t="n">
-        <v>-2266234</v>
+        <v>161603479</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-153358</v>
+        <v>-13416646</v>
       </c>
       <c r="E12" t="n">
-        <v>-873188</v>
+        <v>-11999662</v>
       </c>
       <c r="F12" t="n">
-        <v>4462984</v>
+        <v>-680897</v>
       </c>
       <c r="G12" t="n">
-        <v>3605365</v>
+        <v>-1630364</v>
       </c>
       <c r="H12" t="n">
-        <v>10152836</v>
+        <v>77027181</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠 / 📈 20d 巨變(加碼 19,107 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>14831777</v>
+        <v>695718</v>
       </c>
       <c r="E13" t="n">
-        <v>-58189126</v>
+        <v>-749452</v>
       </c>
       <c r="F13" t="n">
-        <v>55202964</v>
+        <v>-4728977</v>
       </c>
       <c r="G13" t="n">
-        <v>36096340</v>
+        <v>-5533302</v>
       </c>
       <c r="H13" t="n">
-        <v>63688926</v>
+        <v>-24543782</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>亞翔</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅 / 📉 20d 巨變(減碼 -12,150 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-233468</v>
+        <v>-199897</v>
       </c>
       <c r="E14" t="n">
-        <v>26530236</v>
+        <v>-153358</v>
       </c>
       <c r="F14" t="n">
-        <v>-31962354</v>
+        <v>4577392</v>
       </c>
       <c r="G14" t="n">
-        <v>-19812269</v>
+        <v>4462984</v>
       </c>
       <c r="H14" t="n">
-        <v>-24321377</v>
+        <v>11912198</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠 / 📈 20d 巨變(加碼 54,725 千)</t>
+          <t>🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>133494762</v>
+        <v>-1581460</v>
       </c>
       <c r="E15" t="n">
-        <v>-15333916</v>
+        <v>774261</v>
       </c>
       <c r="F15" t="n">
-        <v>160904183</v>
+        <v>-5622571</v>
       </c>
       <c r="G15" t="n">
-        <v>106178957</v>
+        <v>-1247367</v>
       </c>
       <c r="H15" t="n">
-        <v>79629106</v>
+        <v>-3544663</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>華星光</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>📈 20d 巨變(加碼 27,050 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>555135</v>
+        <v>-2484187</v>
       </c>
       <c r="E16" t="n">
-        <v>-2877133</v>
+        <v>-3510015</v>
       </c>
       <c r="F16" t="n">
-        <v>2813258</v>
+        <v>-32071263</v>
       </c>
       <c r="G16" t="n">
-        <v>2855638</v>
+        <v>-59121168</v>
       </c>
       <c r="H16" t="n">
-        <v>5088672</v>
+        <v>-66948024</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>寶雅*</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 10,322 千)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>9603953</v>
+      </c>
+      <c r="E17" t="n">
+        <v>14831777</v>
+      </c>
+      <c r="F17" t="n">
+        <v>65524882</v>
+      </c>
+      <c r="G17" t="n">
+        <v>55202964</v>
+      </c>
+      <c r="H17" t="n">
+        <v>59809028</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -27,289 千)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>60610861</v>
+      </c>
+      <c r="E18" t="n">
+        <v>133494762</v>
+      </c>
+      <c r="F18" t="n">
+        <v>133615313</v>
+      </c>
+      <c r="G18" t="n">
+        <v>160904183</v>
+      </c>
+      <c r="H18" t="n">
+        <v>40084409</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>華邦電</t>
         </is>
       </c>
     </row>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,252 +466,252 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 🟢 5d 翻綠 / 📉 20d 巨變(減碼 -26,237 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📈 20d 巨變(加碼 10,468 千)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>11319063</v>
+        <v>-2309475</v>
       </c>
       <c r="E2" t="n">
-        <v>-233468</v>
+        <v>10300087</v>
       </c>
       <c r="F2" t="n">
-        <v>-58199679</v>
+        <v>52146302</v>
       </c>
       <c r="G2" t="n">
-        <v>-31962354</v>
+        <v>41678122</v>
       </c>
       <c r="H2" t="n">
-        <v>9139720</v>
+        <v>518092701</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 10,212 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 29,968 千)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>29213823</v>
+        <v>10246775</v>
       </c>
       <c r="E3" t="n">
-        <v>18065281</v>
+        <v>11319063</v>
       </c>
       <c r="F3" t="n">
-        <v>51919009</v>
+        <v>-28231647</v>
       </c>
       <c r="G3" t="n">
-        <v>41706807</v>
+        <v>-58199679</v>
       </c>
       <c r="H3" t="n">
-        <v>-25644104</v>
+        <v>5744734</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📈 20d 巨變(加碼 12,463 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>15496741</v>
+        <v>1167329</v>
       </c>
       <c r="E4" t="n">
-        <v>2111230</v>
+        <v>-2484187</v>
       </c>
       <c r="F4" t="n">
-        <v>37008415</v>
+        <v>-27012390</v>
       </c>
       <c r="G4" t="n">
-        <v>24545912</v>
+        <v>-32071263</v>
       </c>
       <c r="H4" t="n">
-        <v>-19161104</v>
+        <v>-68017964</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>寶雅*</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 📉 20d 巨變(減碼 -19,017 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -44,080 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>-8760496</v>
+        <v>-60119017</v>
       </c>
       <c r="E5" t="n">
-        <v>-12333032</v>
+        <v>-23602047</v>
       </c>
       <c r="F5" t="n">
-        <v>10338271</v>
+        <v>-107603778</v>
       </c>
       <c r="G5" t="n">
-        <v>29355401</v>
+        <v>-63523914</v>
       </c>
       <c r="H5" t="n">
-        <v>67832952</v>
+        <v>127849403</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -12,239 千)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>19997518</v>
+        <v>-6937120</v>
       </c>
       <c r="E6" t="n">
-        <v>10569397</v>
+        <v>-13416646</v>
       </c>
       <c r="F6" t="n">
-        <v>20407548</v>
+        <v>-12919781</v>
       </c>
       <c r="G6" t="n">
-        <v>25593313</v>
+        <v>-680897</v>
       </c>
       <c r="H6" t="n">
-        <v>-123885929</v>
+        <v>76315941</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -14,040 千)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>3860807</v>
+        <v>-16437846</v>
       </c>
       <c r="E7" t="n">
-        <v>-4066941</v>
+        <v>-8760496</v>
       </c>
       <c r="F7" t="n">
-        <v>-4752440</v>
+        <v>-3702035</v>
       </c>
       <c r="G7" t="n">
-        <v>-6817017</v>
+        <v>10338271</v>
       </c>
       <c r="H7" t="n">
-        <v>-41666779</v>
+        <v>60731597</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-2226169</v>
+        <v>19013989</v>
       </c>
       <c r="E8" t="n">
-        <v>-2697636</v>
+        <v>19997518</v>
       </c>
       <c r="F8" t="n">
-        <v>15095122</v>
+        <v>14491033</v>
       </c>
       <c r="G8" t="n">
-        <v>15602652</v>
+        <v>20407548</v>
       </c>
       <c r="H8" t="n">
-        <v>23961124</v>
+        <v>-125830213</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,336 +723,441 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-2523012</v>
+        <v>-2328594</v>
       </c>
       <c r="E9" t="n">
-        <v>-1398832</v>
+        <v>-2226169</v>
       </c>
       <c r="F9" t="n">
-        <v>6439924</v>
+        <v>14518305</v>
       </c>
       <c r="G9" t="n">
-        <v>10541909</v>
+        <v>15095122</v>
       </c>
       <c r="H9" t="n">
-        <v>14780598</v>
+        <v>23734395</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>15777966</v>
+        <v>-176658</v>
       </c>
       <c r="E10" t="n">
-        <v>2445455</v>
+        <v>-199897</v>
       </c>
       <c r="F10" t="n">
-        <v>-36939548</v>
+        <v>5389484</v>
       </c>
       <c r="G10" t="n">
-        <v>-43930885</v>
+        <v>4577392</v>
       </c>
       <c r="H10" t="n">
-        <v>-61823973</v>
+        <v>12120854</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-23602047</v>
+        <v>18470978</v>
       </c>
       <c r="E11" t="n">
-        <v>-22924140</v>
+        <v>15777966</v>
       </c>
       <c r="F11" t="n">
-        <v>-63523914</v>
+        <v>-43649480</v>
       </c>
       <c r="G11" t="n">
-        <v>-61086978</v>
+        <v>-36939548</v>
       </c>
       <c r="H11" t="n">
-        <v>161603479</v>
+        <v>-63771994</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-13416646</v>
+        <v>30496334</v>
       </c>
       <c r="E12" t="n">
-        <v>-11999662</v>
+        <v>29213823</v>
       </c>
       <c r="F12" t="n">
-        <v>-680897</v>
+        <v>51927884</v>
       </c>
       <c r="G12" t="n">
-        <v>-1630364</v>
+        <v>51919009</v>
       </c>
       <c r="H12" t="n">
-        <v>77027181</v>
+        <v>-20873687</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>695718</v>
+        <v>10214227</v>
       </c>
       <c r="E13" t="n">
-        <v>-749452</v>
+        <v>15496741</v>
       </c>
       <c r="F13" t="n">
-        <v>-4728977</v>
+        <v>39976020</v>
       </c>
       <c r="G13" t="n">
-        <v>-5533302</v>
+        <v>37008415</v>
       </c>
       <c r="H13" t="n">
-        <v>-24543782</v>
+        <v>-20668816</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>-199897</v>
+        <v>959066</v>
       </c>
       <c r="E14" t="n">
-        <v>-153358</v>
+        <v>-1098737</v>
       </c>
       <c r="F14" t="n">
-        <v>4577392</v>
+        <v>-3144835</v>
       </c>
       <c r="G14" t="n">
-        <v>4462984</v>
+        <v>-3882056</v>
       </c>
       <c r="H14" t="n">
-        <v>11912198</v>
+        <v>-16456714</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>瑞昱</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>-1581460</v>
+        <v>678009</v>
       </c>
       <c r="E15" t="n">
-        <v>774261</v>
+        <v>695718</v>
       </c>
       <c r="F15" t="n">
-        <v>-5622571</v>
+        <v>-4012448</v>
       </c>
       <c r="G15" t="n">
-        <v>-1247367</v>
+        <v>-4728977</v>
       </c>
       <c r="H15" t="n">
-        <v>-3544663</v>
+        <v>-24434353</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>亞翔</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 27,050 千)</t>
+          <t>🔴 5d 翻紅 / 📉 20d 巨變(減碼 -10,108 千)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>-2484187</v>
+        <v>-6955457</v>
       </c>
       <c r="E16" t="n">
-        <v>-3510015</v>
+        <v>3860807</v>
       </c>
       <c r="F16" t="n">
-        <v>-32071263</v>
+        <v>-14860437</v>
       </c>
       <c r="G16" t="n">
-        <v>-59121168</v>
+        <v>-4752440</v>
       </c>
       <c r="H16" t="n">
-        <v>-66948024</v>
+        <v>-50374691</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 10,322 千)</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>9603953</v>
+        <v>12359</v>
       </c>
       <c r="E17" t="n">
-        <v>14831777</v>
+        <v>-2523012</v>
       </c>
       <c r="F17" t="n">
-        <v>65524882</v>
+        <v>3386702</v>
       </c>
       <c r="G17" t="n">
-        <v>55202964</v>
+        <v>6439924</v>
       </c>
       <c r="H17" t="n">
-        <v>59809028</v>
+        <v>12785128</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -27,289 千)</t>
+          <t>📉 20d 巨變(減碼 -8,878 千)</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
+        <v>2915041</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2511917</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6004719</v>
+      </c>
+      <c r="G18" t="n">
+        <v>14883055</v>
+      </c>
+      <c r="H18" t="n">
+        <v>21718415</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>中興電</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3045</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 8,066 千)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>10305477</v>
+      </c>
+      <c r="E19" t="n">
+        <v>17477662</v>
+      </c>
+      <c r="F19" t="n">
+        <v>89724532</v>
+      </c>
+      <c r="G19" t="n">
+        <v>81658966</v>
+      </c>
+      <c r="H19" t="n">
+        <v>146309120</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>台灣大</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -45,251 千)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>41493231</v>
+      </c>
+      <c r="E20" t="n">
+        <v>9603953</v>
+      </c>
+      <c r="F20" t="n">
+        <v>20273872</v>
+      </c>
+      <c r="G20" t="n">
+        <v>65524882</v>
+      </c>
+      <c r="H20" t="n">
+        <v>57298940</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -18,040 千)</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>81759531</v>
+      </c>
+      <c r="E21" t="n">
         <v>60610861</v>
       </c>
-      <c r="E18" t="n">
-        <v>133494762</v>
-      </c>
-      <c r="F18" t="n">
+      <c r="F21" t="n">
+        <v>115574939</v>
+      </c>
+      <c r="G21" t="n">
         <v>133615313</v>
       </c>
-      <c r="G18" t="n">
-        <v>160904183</v>
-      </c>
-      <c r="H18" t="n">
-        <v>40084409</v>
-      </c>
-      <c r="I18" t="inlineStr">
+      <c r="H21" t="n">
+        <v>34495857</v>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>華邦電</t>
         </is>

--- a/data/台股_翻轉警報.xlsx
+++ b/data/台股_翻轉警報.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,35 +466,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🔴 5d 翻紅 / 📈 20d 巨變(加碼 10,468 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣) / 🚨 20d↔60d 背離(由賣轉買) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>-2309475</v>
+        <v>-1956622</v>
       </c>
       <c r="E2" t="n">
-        <v>10300087</v>
+        <v>10214227</v>
       </c>
       <c r="F2" t="n">
-        <v>52146302</v>
+        <v>34007934</v>
       </c>
       <c r="G2" t="n">
-        <v>41678122</v>
+        <v>39976020</v>
       </c>
       <c r="H2" t="n">
-        <v>518092701</v>
+        <v>-20002881</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
@@ -506,26 +506,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🚨 20d↔60d 背離(由買轉賣) / 📈 20d 巨變(加碼 29,968 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 🔴 5d 翻紅</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
+        <v>-19911926</v>
+      </c>
+      <c r="E3" t="n">
         <v>10246775</v>
       </c>
-      <c r="E3" t="n">
-        <v>11319063</v>
-      </c>
       <c r="F3" t="n">
+        <v>-35054452</v>
+      </c>
+      <c r="G3" t="n">
         <v>-28231647</v>
       </c>
-      <c r="G3" t="n">
-        <v>-58199679</v>
-      </c>
       <c r="H3" t="n">
-        <v>5744734</v>
+        <v>1993824</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -536,392 +536,392 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買) / 🟢 5d 翻綠</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買) / 📉 20d 巨變(減碼 -11,070 千)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1167329</v>
+        <v>26025516</v>
       </c>
       <c r="E4" t="n">
-        <v>-2484187</v>
+        <v>30496334</v>
       </c>
       <c r="F4" t="n">
-        <v>-27012390</v>
+        <v>40857502</v>
       </c>
       <c r="G4" t="n">
-        <v>-32071263</v>
+        <v>51927884</v>
       </c>
       <c r="H4" t="n">
-        <v>-68017964</v>
+        <v>-28925938</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -44,080 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -14,829 千)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>-60119017</v>
+        <v>-29474185</v>
       </c>
       <c r="E5" t="n">
-        <v>-23602047</v>
+        <v>-16437846</v>
       </c>
       <c r="F5" t="n">
-        <v>-107603778</v>
+        <v>-18531211</v>
       </c>
       <c r="G5" t="n">
-        <v>-63523914</v>
+        <v>-3702035</v>
       </c>
       <c r="H5" t="n">
-        <v>127849403</v>
+        <v>61139440</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -12,239 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>-6937120</v>
+        <v>8877774</v>
       </c>
       <c r="E6" t="n">
-        <v>-13416646</v>
+        <v>19013989</v>
       </c>
       <c r="F6" t="n">
-        <v>-12919781</v>
+        <v>9264250</v>
       </c>
       <c r="G6" t="n">
-        <v>-680897</v>
+        <v>14491033</v>
       </c>
       <c r="H6" t="n">
-        <v>76315941</v>
+        <v>-134081343</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣) / 📉 20d 巨變(減碼 -14,040 千)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-16437846</v>
+        <v>-1858027</v>
       </c>
       <c r="E7" t="n">
-        <v>-8760496</v>
+        <v>-2328594</v>
       </c>
       <c r="F7" t="n">
-        <v>-3702035</v>
+        <v>14987241</v>
       </c>
       <c r="G7" t="n">
-        <v>10338271</v>
+        <v>14518305</v>
       </c>
       <c r="H7" t="n">
-        <v>60731597</v>
+        <v>23973854</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>19013989</v>
+        <v>2289845</v>
       </c>
       <c r="E8" t="n">
-        <v>19997518</v>
+        <v>1167329</v>
       </c>
       <c r="F8" t="n">
-        <v>14491033</v>
+        <v>-19450013</v>
       </c>
       <c r="G8" t="n">
-        <v>20407548</v>
+        <v>-27012390</v>
       </c>
       <c r="H8" t="n">
-        <v>-125830213</v>
+        <v>-66225179</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>寶雅*</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-2328594</v>
+        <v>-80785282</v>
       </c>
       <c r="E9" t="n">
-        <v>-2226169</v>
+        <v>-60119017</v>
       </c>
       <c r="F9" t="n">
-        <v>14518305</v>
+        <v>-103788976</v>
       </c>
       <c r="G9" t="n">
-        <v>15095122</v>
+        <v>-107603778</v>
       </c>
       <c r="H9" t="n">
-        <v>23734395</v>
+        <v>131108443</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由買轉賣)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由買轉賣)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-176658</v>
+        <v>-12413589</v>
       </c>
       <c r="E10" t="n">
-        <v>-199897</v>
+        <v>-6937120</v>
       </c>
       <c r="F10" t="n">
-        <v>5389484</v>
+        <v>-12240223</v>
       </c>
       <c r="G10" t="n">
-        <v>4577392</v>
+        <v>-12919781</v>
       </c>
       <c r="H10" t="n">
-        <v>12120854</v>
+        <v>75614325</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 5d↔20d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>18470978</v>
+        <v>-96513</v>
       </c>
       <c r="E11" t="n">
-        <v>15777966</v>
+        <v>1252892</v>
       </c>
       <c r="F11" t="n">
-        <v>-43649480</v>
+        <v>1352310</v>
       </c>
       <c r="G11" t="n">
-        <v>-36939548</v>
+        <v>3164534</v>
       </c>
       <c r="H11" t="n">
-        <v>-63771994</v>
+        <v>10457964</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>零壹</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🟢 5d 翻綠 / 📈 20d 巨變(加碼 24,163 千)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>30496334</v>
+        <v>8196467</v>
       </c>
       <c r="E12" t="n">
-        <v>29213823</v>
+        <v>-2309475</v>
       </c>
       <c r="F12" t="n">
-        <v>51927884</v>
+        <v>76309054</v>
       </c>
       <c r="G12" t="n">
-        <v>51919009</v>
+        <v>52146302</v>
       </c>
       <c r="H12" t="n">
-        <v>-20873687</v>
+        <v>526131776</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🚨 20d↔60d 背離(由賣轉買)</t>
+          <t>🚨 三期方向不一致(5d↔20d↔60d)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>10214227</v>
+        <v>-316461</v>
       </c>
       <c r="E13" t="n">
-        <v>15496741</v>
+        <v>12359</v>
       </c>
       <c r="F13" t="n">
-        <v>39976020</v>
+        <v>1492025</v>
       </c>
       <c r="G13" t="n">
-        <v>37008415</v>
+        <v>3386702</v>
       </c>
       <c r="H13" t="n">
-        <v>-20668816</v>
+        <v>10847044</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🚨 三期方向不一致(5d↔20d↔60d) / 🟢 5d 翻綠</t>
+          <t>🔴 5d 翻紅 / 📈 20d 巨變(加碼 16,703 千)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>959066</v>
+        <v>-5641323</v>
       </c>
       <c r="E14" t="n">
-        <v>-1098737</v>
+        <v>18470978</v>
       </c>
       <c r="F14" t="n">
-        <v>-3144835</v>
+        <v>-26946699</v>
       </c>
       <c r="G14" t="n">
-        <v>-3882056</v>
+        <v>-43649480</v>
       </c>
       <c r="H14" t="n">
-        <v>-16456714</v>
+        <v>-69358463</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,231 +933,126 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>678009</v>
+        <v>1754411</v>
       </c>
       <c r="E15" t="n">
-        <v>695718</v>
+        <v>959066</v>
       </c>
       <c r="F15" t="n">
-        <v>-4012448</v>
+        <v>-2159820</v>
       </c>
       <c r="G15" t="n">
-        <v>-4728977</v>
+        <v>-3144835</v>
       </c>
       <c r="H15" t="n">
-        <v>-24434353</v>
+        <v>-15843684</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>瑞昱</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🔴 5d 翻紅 / 📉 20d 巨變(減碼 -10,108 千)</t>
+          <t>🟢 5d 翻綠</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>-6955457</v>
+        <v>1661861</v>
       </c>
       <c r="E16" t="n">
-        <v>3860807</v>
+        <v>-399669</v>
       </c>
       <c r="F16" t="n">
-        <v>-14860437</v>
+        <v>-542475</v>
       </c>
       <c r="G16" t="n">
-        <v>-4752440</v>
+        <v>-3245178</v>
       </c>
       <c r="H16" t="n">
-        <v>-50374691</v>
+        <v>-9498920</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>全友</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>🟢 5d 翻綠</t>
+          <t>📈 20d 巨變(加碼 14,199 千)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>12359</v>
+        <v>25199166</v>
       </c>
       <c r="E17" t="n">
-        <v>-2523012</v>
+        <v>16846399</v>
       </c>
       <c r="F17" t="n">
-        <v>3386702</v>
+        <v>26962211</v>
       </c>
       <c r="G17" t="n">
-        <v>6439924</v>
+        <v>12762927</v>
       </c>
       <c r="H17" t="n">
-        <v>12785128</v>
+        <v>52599333</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -8,878 千)</t>
+          <t>📉 20d 巨變(減碼 -87,069 千)</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2915041</v>
+        <v>45227120</v>
       </c>
       <c r="E18" t="n">
-        <v>2511917</v>
+        <v>81759531</v>
       </c>
       <c r="F18" t="n">
-        <v>6004719</v>
+        <v>28506329</v>
       </c>
       <c r="G18" t="n">
-        <v>14883055</v>
+        <v>115574939</v>
       </c>
       <c r="H18" t="n">
-        <v>21718415</v>
+        <v>3318165</v>
       </c>
       <c r="I18" t="inlineStr">
-        <is>
-          <t>中興電</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>3045</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 8,066 千)</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>10305477</v>
-      </c>
-      <c r="E19" t="n">
-        <v>17477662</v>
-      </c>
-      <c r="F19" t="n">
-        <v>89724532</v>
-      </c>
-      <c r="G19" t="n">
-        <v>81658966</v>
-      </c>
-      <c r="H19" t="n">
-        <v>146309120</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>台灣大</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -45,251 千)</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>41493231</v>
-      </c>
-      <c r="E20" t="n">
-        <v>9603953</v>
-      </c>
-      <c r="F20" t="n">
-        <v>20273872</v>
-      </c>
-      <c r="G20" t="n">
-        <v>65524882</v>
-      </c>
-      <c r="H20" t="n">
-        <v>57298940</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -18,040 千)</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>81759531</v>
-      </c>
-      <c r="E21" t="n">
-        <v>60610861</v>
-      </c>
-      <c r="F21" t="n">
-        <v>115574939</v>
-      </c>
-      <c r="G21" t="n">
-        <v>133615313</v>
-      </c>
-      <c r="H21" t="n">
-        <v>34495857</v>
-      </c>
-      <c r="I21" t="inlineStr">
         <is>
           <t>華邦電</t>
         </is>
